--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -682,10 +682,10 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>BOOT/IDLE حفظ</t>
+          <t>BOOT حفظ (تغییر نکند)</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>IDLE/BATTERY</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>INPUT</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>INPUT</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -2406,6 +2406,84 @@
       <c r="R24" s="9" t="inlineStr"/>
       <c r="S24" s="9" t="inlineStr"/>
       <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>CO-021</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Fault با snapshot نامعتبر</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>fault≠0 با snapshot.valid=false (v=20700), بررسی اولویت invalid</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>FAULT_ADC</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>PB11 حفظ</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>BOOT حفظ</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>در invalid، fault نباید FAULT شود</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr"/>
+      <c r="P25" s="9" t="inlineStr"/>
+      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="R25" s="9" t="inlineStr"/>
+      <c r="S25" s="9" t="inlineStr"/>
+      <c r="T25" s="9" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>پس از 2500ms هنوز SAFE High? Actually PB11 Low؛ پس از 3000ms PB11 High (وصل) و state=INPUT. PASS: reconnect پس از 3000ms. FAIL: reconnect زود یا عدم reconnect.</t>
+          <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>PASS: 3000ms → INPUT High. FAIL: early or no reconnect.</t>
+          <t>PASS: قبل 3000 SAFE Low، بعد 3000 INPUT High. FAIL: early or no reconnect.</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr"/>
@@ -2504,10 +2504,6 @@
       <c r="O26" s="20" t="inlineStr"/>
       <c r="P26" s="20" t="inlineStr"/>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <autoFilter ref="A4:P26"/>
   <mergeCells count="3">
@@ -3339,7 +3335,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
+          <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$P$26</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,8 +117,29 @@
     <font>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -160,8 +182,13 @@
         <bgColor rgb="00E9EDF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -227,11 +254,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -314,6 +355,18 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3950,4 +4003,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول تغییر مسیر (Changeover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Changeover_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -778,7 +778,7 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>این فایل برای اعتبارسنجی منطق Changeover تهیه شده است: بررسی snapshot.valid، fault_mask، input_present، v_bat24_mv، فلگ UI و تایمر 3000ms.</t>
+          <t>این فایل برای اعتبارسنجی منطق Changeover تهیه شده است: بررسی snapshot.valid، fault_mask، input_present، v_bat24_mv، قفل داخلی باتری کم و تایمر 3000ms.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present و فلگ UI را ست کن؛ fault_mask را از Fault اعمال کن.</t>
+          <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present و قفل داخلی باتری کم را ست کن؛ fault_mask را از Fault اعمال کن.</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -862,7 +862,7 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present و قفل داخلی باتری کم را ست کن؛ fault_mask را از Fault اعمال کن.</t>
+          <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present را ست کن؛ قفل داخلی باتری کم فقط با ولتاژ زیر ۲۱۰۰۰ میلی‌ولت بسته می‌شود (مستقیم ست نمی‌شود)؛ fault_mask را از Fault اعمال کن.</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1029,6 +1029,28 @@
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1069,7 +1091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2556,6 +2578,76 @@
       </c>
       <c r="O26" s="20" t="inlineStr"/>
       <c r="P26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CO-023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_control</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MODULE_MEASUREMENT=0 یا GetSnapshot=false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>برد را با measurement خاموش بیلد کن یا ADC را نگه دار تا valid=false بماند؛ state را در 3s مشاهده کن</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>هیچ فیلد snapshot حاوی زباله پشته نباشد؛ Changeover باید فقط روی valid گیت بزند و PB11 امن بماند؛ task_control مانند task_comm/task_ui/task_protection هر 9 فیلد را صفر کند</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>امن</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>بدون تصمیم بر اساس زباله؛ PB11 حفظ</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:P26"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1091,7 +1091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2635,17 +2635,73 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CO-024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>وصل مجدد 30s پایداری ورودی</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>برد در SAFE پس از قطع، v_bat=24V</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ورودی را وصل و 30s نگه دار سپس 3s ولتاژ 21200</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>input=true v=24000</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>33s</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>بعد 30s پایداری + 3s ولتاژ، PB11 High-&gt;Low و INPUT</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>thermal+30s</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>fault=0x3F (همه) با valid=true اعمال کن</t>
+          <t>fault برابر 63 (همهٔ بیت‌های خطا با هم) و valid=true اعمال کن</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -2697,8 +2697,6 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>thermal+30s</t>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1238,7 +1238,10 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>snapshot.valid=false با v_bat=24000 input=false fault=0 را اعمال و 500ms صبر کن</t>
+          <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد؛ PB11 باید High و امن باشد.
+گام ۲: یک snapshot نامعتبر اعمال کن: valid=false ولی v_bat=24000، input=false و fault=0.
+گام ۳: 500 میلی‌ثانیه صبر کن و وضعیت (state) و پایهٔ PB11 را بخوان.
+گام ۴: وضعیت قبلی (BOOT یا هر وضعیت قبلی) و PB11 باید بدون هیچ تغییری حفظ شده باشند؛ رفتن به FAULT یا IDLE یا تغییر PB11 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -1300,7 +1303,11 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>2s شرط قطع (v=20900+flag true) → 1s valid=false → 2s قطع دوباره را اعمال کن</t>
+          <t>گام ۱: برد در وضعیت BATTERY باشد.
+گام ۲: دو ثانیه شرط قطع را اعمال کن: snapshot معتبر با v=20900 و flag=true.
+گام ۳: بعد یک ثانیه snapshot نامعتبر بده (valid=false).
+گام ۴: دوباره دو ثانیه شرط قطع را اعمال کن و PB11 را زیر نظر بگیر.
+گام ۵: PB11 نباید قطع شود؛ آن یک ثانیهٔ نامعتبر تایمر 3 ثانیه‌ای را از نو شروع می‌کند، پس در هیچ‌کدام از دو بازهٔ 2 ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -1362,7 +1369,10 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>valid=false با fault=FAULT_ADC را اعمال کن</t>
+          <t>گام ۱: برد در وضعیت BATTERY باشد.
+گام ۲: snapshot نامعتبر با fault=FAULT_ADC (مقدار 1) و v=25000 اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت نباید FAULT شود و PB11 نباید تغییر کند؛ fault همراه snapshot نامعتبر شمرده نمی‌شود و تایمر قطع هم reset می‌شود.</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -1424,7 +1434,10 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>valid=true v=24000 input true با fault=FAULT_ADC را اعمال کن</t>
+          <t>گام ۱: برد در وضعیت INPUT یا BATTERY باشد.
+گام ۲: snapshot معتبر با v=24000، input=true و fault=FAULT_ADC (مقدار 1) اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت باید FAULT شود ولی PB11 دقیقاً همان قبلی بماند (از High به Low نرود) و تایمر قطع reset شود.</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -1486,7 +1499,10 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>fault برابر 63 (همهٔ بیت‌های خطا با هم) و valid=true اعمال کن</t>
+          <t>گام ۱: برد از قبل در وضعیت FAULT باشد.
+گام ۲: snapshot معتبر با fault برابر 63 (همهٔ بیت‌های خطا با هم) اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن و هر سه پایهٔ PB11 و PB5 و PB7 را چک کن.
+گام ۴: وضعیت باید FAULT بماند و هیچ‌کدام از سه پایه نباید تغییر کرده باشند.</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -1548,7 +1564,10 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>valid=true v=24000 input=false (Vin≤20V) fault0</t>
+          <t>گام ۱: برد در BOOT با snapshot معتبر باشد.
+گام ۲: snapshot معتبر با v=24000، input=false (یعنی Vin حداکثر 20 ولت) و fault=0 اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت باید BATTERY شود و PB11 باید High و امن (متصل) باشد؛ رفتن به INPUT یا SAFE یا FAULT یعنی رد تست.</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
@@ -1610,7 +1629,10 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>valid=true v=24000 input=true (Vin≥21V) fault0</t>
+          <t>گام ۱: برد در BOOT یا BATTERY باشد.
+گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -1672,7 +1694,10 @@
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>valid=true v=20900 (&lt;21000) flag true, input false را 3500ms نگه دار</t>
+          <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
+گام ۲: snapshot معتبر با v=20900 (کمتر از 21000)، flag=true و input=false اعمال کن.
+گام ۳: این شرط را 3500 میلی‌ثانیه پیوسته نگه دار و ساعت بگیر.
+گام ۴: در 2500 میلی‌ثانیه اول باید هنوز BATTERY/INPUT و PB11 وصل باشد؛ فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت SAFE شود. قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -1734,7 +1759,10 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>valid=true v=20700 (&lt;20800) flag false input false را 3500ms نگه دار</t>
+          <t>گام ۱: برد در BATTERY و flag=false باشد.
+گام ۲: snapshot معتبر با v=20700 (کمتر از 20800)، flag=false و input=false اعمال کن.
+گام ۳: 3500 میلی‌ثانیه پیوسته نگه دار.
+گام ۴: بعد از 3000 میلی‌ثانیه باید SAFE با PB11 قطع شود؛ این قطع به flag ربطی ندارد و با flag=false هم باید اتفاق بیفتد.</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -1796,7 +1824,10 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>valid=true v=21000 (دقیق مرز &lt;21000) با flag true و input=true (Vin=24V) را 3500ms (≥3000) پایدار نگه دار</t>
+          <t>گام ۱: برد در BATTERY باشد.
+گام ۲: snapshot معتبر با v دقیقاً 21000 (مرز)، flag=true و input=true (Vin=24 ولت) اعمال کن.
+گام ۳: 3500 میلی‌ثانیه پایدار نگه دار.
+گام ۴: هیچ قطعی نباید رخ دهد (شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی»)؛ وضعیت باید INPUT شده باشد (چون ورودی حاضر است) و PB11 High و امن بماند.</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
@@ -1858,7 +1889,10 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>valid=true v=20800 flag false 3500ms</t>
+          <t>گام ۱: برد در BATTERY باشد.
+گام ۲: snapshot معتبر با v دقیقاً 20800 و flag=false اعمال کن.
+گام ۳: 3500 میلی‌ثانیه نگه دار.
+گام ۴: هیچ قطعی نباید رخ دهد؛ قطع فقط برای «کمتر از 20800» است و روی خودِ مرز 20800 نباید اتفاق بیفتد.</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -1920,7 +1954,10 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>valid=true v=20900 (&lt;21000) flag true با input=true (Vin=24V) را فقط 2500ms (&lt;3000) نگه دار سپس v=24000 کن</t>
+          <t>گام ۱: برد در BATTERY باشد.
+گام ۲: snapshot معتبر با v=20900، flag=true و input=true (Vin=24 ولت) بده.
+گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000) و بعد ولتاژ را به 24000 برگردان.
+گام ۴: تا 2500 میلی‌ثانیه باید هنوز INPUT و PB11 وصل باشد؛ SAFE شدن زودتر از 3000 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -1982,7 +2019,10 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>از SAFE (پس از CO-008)، input=true و v=21300 (≥21200) را 3500ms نگه دار</t>
+          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
+گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
+گام ۳: 3500 میلی‌ثانیه نگه دار و PB11 را زیر نظر بگیر.
+گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -2044,7 +2084,10 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>input true v=21200 (دقیق) 3500ms</t>
+          <t>گام ۱: برد در SAFE باشد.
+گام ۲: input=true و v دقیقاً 21200 اعمال کن (روی خودِ مرز).
+گام ۳: 3500 میلی‌ثانیه نگه دار.
+گام ۴: بعد از 3000 میلی‌ثانیه باید INPUT و PB11 وصل شده باشد؛ شرط وصل «دست‌کم 21200» است، پس روی مرز هم باید وصل شود.</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -2106,7 +2149,10 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>input true v=21300 فقط 2500ms نگه دار</t>
+          <t>گام ۱: برد در SAFE باشد.
+گام ۲: input=true و v=21300 اعمال کن.
+گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000).
+گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -2168,7 +2214,9 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>پس از reconnect موفق، state را بخوان</t>
+          <t>گام ۱: تست CO-013 را انجام بده تا وصل مجدد موفق اتفاق بیفتد.
+گام ۲: بلافاصله (در حد 100 میلی‌ثانیه بعد) وضعیت را بخوان.
+گام ۳: وضعیت باید INPUT باشد؛ IDLE برای snapshot معتبر هرگز نباید دیده شود.</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -2230,7 +2278,9 @@
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>valid=true input true → INPUT High، سپس valid=false 500ms → PB11 چک</t>
+          <t>گام ۱: برد را با snapshot معتبر و input=true به INPUT ببر و PB11 را چک کن که وصل (High) است.
+گام ۲: حالا valid=false کن و 500 میلی‌ثانیه صبر کن.
+گام ۳: PB11 را دوباره بخوان: باید بدون تغییر همان High مانده باشد.</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -2292,7 +2342,10 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>valid=true با fault!=0 → FAULT → PB11 چک</t>
+          <t>گام ۱: برد در INPUT باشد.
+گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
+گام ۳: 500 میلی‌ثانیه صبر کن و PB11 را بخوان.
+گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -2354,7 +2407,9 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>در تمام تست‌های CO-001 تا CO-015، PB5 (BAT_SWITCH) و PB7 (RELAY) را با اسکوپ/لاگ BSP چک کن</t>
+          <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015 که انجام می‌دهی، علاوه بر PB11 دو پایهٔ PB5 (BAT_SWITCH) و PB7 (RELAY) را هم با اسیلوسکوپ یا لاگ BSP زیر نظر بگیر.
+گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
+گام ۳: PB5 باید همیشه High امن (active-low) و PB7 همیشه Low بماند؛ هر تغییر (toggle) روی این دو یعنی رد تست.</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -2416,7 +2471,10 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>کد را بازرسی کن: فقط func__BspGpio_Write(BSP_GPIO_PROTECT_BATTERY) مجاز باشد؛ اسکوپ PB11 را چک کن</t>
+          <t>گام ۱: کد changeover.c را بازبینی کن: تنها جایی که اجازهٔ نوشتن روی خروجی دارد باید func__BspGpio_Write با BSP_GPIO_PROTECT_BATTERY (همان PB11) باشد.
+گام ۲: دنبال هر ارجاع مستقیم به board_pins یا HAL یا PB5/PB7 در این مسیر بگرد؛ نباید هیچ‌کدام باشد.
+گام ۳: با اسیلوسکوپ PB11 را در چند تست قبلی چک کن که فقط همان تغییر می‌کند.
+گام ۴: اگر PB5 یا PB7 در هیچ تستی تغییر نکرد، قبول است.</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -2478,7 +2536,10 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>تغییر فرکانس تیک را شبیه‌سازی یا کد را چک کن: فقط func__Rtos_MillisecondsToTicks و osKernelGetTickCount استفاده شود، tick=1ms فرض نشود</t>
+          <t>گام ۱: کد را بازبینی کن: همهٔ تبدیل‌های میلی‌ثانیه به تیک باید فقط از func__Rtos_MillisecondsToTicks و زمان فعلی از osKernelGetTickCount گرفته شود.
+گام ۲: دنبال هر جا که «تیک برابر 1 میلی‌ثانیه» فرض شده باشد بگرد؛ نباید هیچ جا باشد.
+گام ۳: در صورت امکان فرکانس تیک را در شبیه‌سازی تغییر بده و تست 3000 میلی‌ثانیه‌ای قطع را تکرار کن.
+گام ۴: رفتار باید با هر فرکانس تیک درست بماند؛ وابستگی به فرض 1 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -2540,7 +2601,10 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>tick freq=0 شبیه‌سازی (MillisecondsToTicks==0) → valid=true v=20700 flag true 3500ms</t>
+          <t>گام ۱: برد در BATTERY و شرط قطع برقرار باشد.
+گام ۲: در شبیه‌سازی کاری کن فرکانس تیک صفر شود، طوری که func__Rtos_MillisecondsToTicks مقدار 0 برگرداند.
+گام ۳: snapshot معتبر با v=20700 و flag=true را 3500 میلی‌ثانیه نگه دار.
+گام ۴: هیچ قطع یا وصل فوری نباید اتفاق بیفتد؛ وضعیت و PB11 باید حفظ شوند و فقط تایمر reset شود. قطع فوری یعنی رد تست.</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -2602,7 +2666,10 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>برد را با measurement خاموش بیلد کن یا ADC را نگه دار تا valid=false بماند؛ state را در 3s مشاهده کن</t>
+          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن (یا ADC را نگه دار تا valid=false بماند).
+گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
+گام ۳: هیچ فیلد snapshot نباید زبالهٔ پشته داشته باشد: task_control مثل task_comm و task_ui و task_protection هر 9 فیلد را از قبل صفر می‌کند.
+گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند؛ هیچ تصمیمی بر اساس زباله قبول نیست.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2669,7 +2736,10 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ورودی را وصل و 30s نگه دار سپس 3s ولتاژ 21200</t>
+          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
+گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
+گام ۳: بعد از آن 3 ثانیه ولتاژ را روی 21200 نگه دار (در مجموع 33 ثانیه).
+گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -2754,7 +2754,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>بعد 30s پایداری + 3s ولتاژ، PB11 High-&gt;Low و INPUT</t>
+          <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -16,17 +16,19 @@
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$P$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,8 +140,121 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00C00000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00808080"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="7"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +300,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -272,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -366,6 +496,128 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,6 +982,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -755,162 +1008,177 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Changeover — منطق قطع/وصل باتری</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>ChangeOver | PB11 (BSP_GPIO_PROTECT_BATTERY) | آستانه‌ها: 21000/20800/21200 و فیلتر 3000ms | نسخه 2.1 — فقط PB11، زمان rtos_time</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="9" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>این فایل برای اعتبارسنجی منطق Changeover تهیه شده است: بررسی snapshot.valid، fault_mask، input_present، v_bat24_mv، قفل داخلی باتری کم و تایمر 3000ms.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار mV و ms و state/PB11 قابل اندازه‌گیری تعریف شده است.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است. فقط یک Workbook برای Changeover باقی بماند.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>دامنه: فقط Changeover؛ Measurement برای snapshot، Fault برای fault_mask و UI برای فلگ</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>منطق (snapshot-first): اگر snapshot==NULL یا valid==false → هیچ تصمیمی، state حفظ، PB11 حفظ، تایمر reset، fault هم state را تغییر نمی‌دهد، زمان نامعتبر شمرده نشود.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>فقط وقتی snapshot معتبر و fault!=0 → state=FAULT بدون تغییر هیچ pin (PB11/PB5/PB7).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>قطع با گیت: v_bat&lt;21000 و flag true به‌مدت پیوسته 3000ms → قطع (PB11 Low) → SAFE. قطع مستقل: v_bat&lt;20800 مستقل از فلگ 3000ms → SAFE.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>وصل مجدد: input_present==true و v_bat≥21200 به‌مدت پیوسته 3000ms → وصل (PB11 High) → INPUT (هرگز IDLE).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>زمان فقط با func__Rtos_MillisecondsToTicks و osKernelGetTickCount؛ فرض tick=1ms ممنوع؛ durationTicks==0 → هیچ قطع/وصل فوری.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>روش اجرای تست</t>
         </is>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>۱) برد را با منبع آزمایشگاهی و رعایت ایمنی تغذیه کن؛ PB11 را با DMM/اسکوپ نسبت به GND اندازه بگیر (فعال Low). PB5/PB7 را هم هم‌زمان اسکوپ کن و مطمئن شو تغییری ندارند.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>۲) firmware موردنظر را پروگرام کن؛ commit و شناسه برد را در «تأیید نهایی» ثبت کن.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present را ست کن؛ قفل داخلی باتری کم فقط با ولتاژ زیر ۲۱۰۰۰ میلی‌ولت بسته می‌شود (مستقیم ست نمی‌شود)؛ fault_mask را از Fault اعمال کن.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>۴) برای تست 3000ms: شرط را حداقل 3500ms پایدار نگه دار و سپس PB11 و state را بخوان؛ برای تست &lt;3000ms: پس از 2500ms بخوان و مطمئن شو هنوز تغییر نکرده.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>۵) برای snapshot نامعتبر: valid=false یا NULL تزریق کن و ببین state و PB11 حفظ می‌ماند (باید «state فعلی حفظ شود» نه IDLE ثابت).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>۶) نتیجه واقعی را بنویس و در صورت رد، در «ثبت ایراد» ردیف بساز.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>تاریخچه نسخه</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
@@ -929,22 +1197,22 @@
       <c r="P21" s="9" t="n"/>
     </row>
     <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="42" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
         <is>
           <t>تکمیل ۲۲ تست مطابق لیست درخواستی، ستون‌های ۱۶گانه، PASS/FAIL per test، زمان rtos_time و duration0 guard</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
@@ -963,22 +1231,22 @@
       <c r="P22" s="9" t="n"/>
     </row>
     <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="42" t="inlineStr">
         <is>
           <t>snapshot-first با MillisecondsToTicks، نگاشت BATTERY/INPUT/SAFE/FAULT بدون IDLE</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>a4a5bf2</t>
         </is>
@@ -997,22 +1265,22 @@
       <c r="P23" s="9" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="42" t="inlineStr">
         <is>
           <t>پیاده‌سازی با 21 سناریو</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>d0adc6f</t>
         </is>
@@ -1031,22 +1299,22 @@
       <c r="P24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
@@ -1088,155 +1356,158 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Changeover (قطع/وصل باتری با 3000ms)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ورودی‌ها بر حسب mV؛ زمان‌ها بر حسب ms. PB11 فقط از BSP_GPIO_PROTECT_BATTERY (فعال Low) — PB5/PB7 ممنوع. ورودی‌ها: valid، v_bat، input_present، flag، fault.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>snapshot نامعتبر → «state فعلی حفظ شود» (نه IDLE ثابت). CO-010/012 باید INPUT باشد. معیار قبولی هر ردیف توضیح می‌دهد PASS چیست و FAIL چیست.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="37" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="37" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="37" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="37" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="37" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="Q4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>CO-001</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر / حفظ</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>Init → BOOT, PB11 High-safe</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد؛ PB11 باید High و امن باشد.
 گام ۲: یک snapshot نامعتبر اعمال کن: valid=false ولی v_bat=24000، input=false و fault=0.
@@ -1244,64 +1515,68 @@
 گام ۴: وضعیت قبلی (BOOT یا هر وضعیت قبلی) و PB11 باید بدون هیچ تغییری حفظ شده باشند؛ رفتن به FAULT یا IDLE یا تغییر PB11 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>valid=false, v=24000, input=false, flag false, fault0</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="50" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
         <is>
           <t>state حفظ شود: «state فعلی حفظ شود» (BOOT/BATTERY/INPUT/SAFE قبلی) و PB11 حفظ (High-safe). PASS: state و PB11 بدون تغییر. FAIL: هر تغییر به FAULT یا IDLE یا تغییر PB11.</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="48" t="inlineStr">
         <is>
           <t>PASS: state فعلی حفظ. FAIL: تغییر خودبه‌خود.</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr"/>
+      <c r="K5" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr"/>
-      <c r="M5" s="18" t="inlineStr"/>
-      <c r="N5" s="18" t="inlineStr">
+      <c r="L5" s="53" t="inlineStr"/>
+      <c r="M5" s="48" t="inlineStr"/>
+      <c r="N5" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="18" t="inlineStr"/>
-      <c r="P5" s="18" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="O5" s="50" t="inlineStr"/>
+      <c r="P5" s="50" t="inlineStr"/>
+      <c r="Q5" s="54">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="67.5" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>CO-002</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر / تایمر reset</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>BATTERY با شرط قطع نیمه‌کاره</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
 گام ۲: دو ثانیه شرط قطع را اعمال کن: snapshot معتبر با v=20900 و flag=true.
@@ -1310,64 +1585,68 @@
 گام ۵: PB11 نباید قطع شود؛ آن یک ثانیهٔ نامعتبر تایمر 3 ثانیه‌ای را از نو شروع می‌کند، پس در هیچ‌کدام از دو بازهٔ 2 ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="57" t="inlineStr">
         <is>
           <t>valid true 2s → false 1s → true 2s, v20900 flag true</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="57" t="inlineStr">
         <is>
           <t>2+1+2s</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="55" t="inlineStr">
         <is>
           <t>PB11 نباید پس از 2s اول قطع شود؛ پس از 1s invalid، تایمر reset و 2s بعدی هم هنوز قطع نشود (نیاز به 3s پیوسته). PASS: invalid تایمر را reset. FAIL: قطع زود در 2s.</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>PASS: reset پس از invalid. FAIL: قطع زود.</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="J6" s="55" t="inlineStr"/>
+      <c r="K6" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="L6" s="58" t="inlineStr"/>
+      <c r="M6" s="55" t="inlineStr"/>
+      <c r="N6" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="O6" s="57" t="inlineStr"/>
+      <c r="P6" s="57" t="inlineStr"/>
+      <c r="Q6" s="59">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>CO-003</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر + Fault</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
 گام ۲: snapshot نامعتبر با fault=FAULT_ADC (مقدار 1) و v=25000 اعمال کن.
@@ -1375,64 +1654,68 @@
 گام ۴: وضعیت نباید FAULT شود و PB11 نباید تغییر کند؛ fault همراه snapshot نامعتبر شمرده نمی‌شود و تایمر قطع هم reset می‌شود.</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>valid=false, fault=1 (ADC), v25000</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="50" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="48" t="inlineStr">
         <is>
           <t>state حفظ شود (نه FAULT)، PB11 حفظ، تایمر reset. PASS: fault همراه invalid نباید FAULT شود. FAIL: FAULT شدن.</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" s="48" t="inlineStr">
         <is>
           <t>PASS: حفظ state قبلی. FAIL: FAULT.</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="J7" s="51" t="inlineStr"/>
+      <c r="K7" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr"/>
-      <c r="M7" s="18" t="inlineStr"/>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="L7" s="53" t="inlineStr"/>
+      <c r="M7" s="48" t="inlineStr"/>
+      <c r="N7" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="18" t="inlineStr"/>
-      <c r="P7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="O7" s="50" t="inlineStr"/>
+      <c r="P7" s="50" t="inlineStr"/>
+      <c r="Q7" s="54">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>CO-004</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>Fault با snapshot معتبر</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>INPUT/BATTERY</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت INPUT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true و fault=FAULT_ADC (مقدار 1) اعمال کن.
@@ -1440,64 +1723,68 @@
 گام ۴: وضعیت باید FAULT شود ولی PB11 دقیقاً همان قبلی بماند (از High به Low نرود) و تایمر قطع reset شود.</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="57" t="inlineStr">
         <is>
           <t>valid=true, v24000, input true, fault 1</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="57" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="55" t="inlineStr">
         <is>
           <t>state=FAULT، PB11 حفظ (بدون تغییر High→Low)، تایمر reset. PASS: FAULT بدون تغییر PB11. FAIL: تغییر PB11 یا ماندن در INPUT.</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="55" t="inlineStr">
         <is>
           <t>PASS: FAULT و PB11 حفظ. FAIL: تغییر PB11.</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="J8" s="55" t="inlineStr"/>
+      <c r="K8" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="20" t="inlineStr"/>
-      <c r="M8" s="20" t="inlineStr"/>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="L8" s="58" t="inlineStr"/>
+      <c r="M8" s="55" t="inlineStr"/>
+      <c r="N8" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O8" s="20" t="inlineStr"/>
-      <c r="P8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="O8" s="57" t="inlineStr"/>
+      <c r="P8" s="57" t="inlineStr"/>
+      <c r="Q8" s="59">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>CO-005</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>Fault چند بیتی</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>FAULT قبلی</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد از قبل در وضعیت FAULT باشد.
 گام ۲: snapshot معتبر با fault برابر 63 (همهٔ بیت‌های خطا با هم) اعمال کن.
@@ -1505,64 +1792,68 @@
 گام ۴: وضعیت باید FAULT بماند و هیچ‌کدام از سه پایه نباید تغییر کرده باشند.</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>valid true, fault ALL</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="50" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>state=FAULT، هیچ pin (PB11/PB5/PB7) تغییر نکند. PASS: همه fault‌ها → FAULT بدون pin. FAIL: هر تغییر pin.</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="48" t="inlineStr">
         <is>
           <t>PASS: همه fault → FAULT no pin. FAIL: pin change.</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr"/>
+      <c r="K9" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr"/>
-      <c r="M9" s="18" t="inlineStr"/>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="L9" s="53" t="inlineStr"/>
+      <c r="M9" s="48" t="inlineStr"/>
+      <c r="N9" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr"/>
-      <c r="P9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="O9" s="50" t="inlineStr"/>
+      <c r="P9" s="50" t="inlineStr"/>
+      <c r="Q9" s="54">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>CO-006</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>ورودی قطع → BATTERY</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>BOOT با snapshot معتبر</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در BOOT با snapshot معتبر باشد.
 گام ۲: snapshot معتبر با v=24000، input=false (یعنی Vin حداکثر 20 ولت) و fault=0 اعمال کن.
@@ -1570,64 +1861,68 @@
 گام ۴: وضعیت باید BATTERY شود و PB11 باید High و امن (متصل) باشد؛ رفتن به INPUT یا SAFE یا FAULT یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="57" t="inlineStr">
         <is>
           <t>valid true, v24000, input false</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="55" t="inlineStr">
         <is>
           <t>state=BATTERY, PB11 High-safe (متصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="55" t="inlineStr">
         <is>
           <t>PASS: BATTERY. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="J10" s="55" t="inlineStr"/>
+      <c r="K10" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="L10" s="58" t="inlineStr"/>
+      <c r="M10" s="55" t="inlineStr"/>
+      <c r="N10" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="O10" s="57" t="inlineStr"/>
+      <c r="P10" s="57" t="inlineStr"/>
+      <c r="Q10" s="59">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>CO-007</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>ورودی حاضر → INPUT</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>BOOT/BATTERY</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در BOOT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
@@ -1635,64 +1930,68 @@
 گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>valid true, v24000, input true</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="50" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="48" t="inlineStr">
         <is>
           <t>state=INPUT, PB11 High-safe. PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="48" t="inlineStr">
         <is>
           <t>PASS: INPUT. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="J11" s="51" t="inlineStr"/>
+      <c r="K11" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr"/>
-      <c r="M11" s="18" t="inlineStr"/>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="L11" s="53" t="inlineStr"/>
+      <c r="M11" s="48" t="inlineStr"/>
+      <c r="N11" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr"/>
-      <c r="P11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="O11" s="50" t="inlineStr"/>
+      <c r="P11" s="50" t="inlineStr"/>
+      <c r="Q11" s="54">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>CO-008</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>قطع با گیت / 21000 + flag</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="55" t="inlineStr">
         <is>
           <t>BATTERY/INPUT, PB11 High</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
 گام ۲: snapshot معتبر با v=20900 (کمتر از 21000)، flag=true و input=false اعمال کن.
@@ -1700,64 +1999,68 @@
 گام ۴: در 2500 میلی‌ثانیه اول باید هنوز BATTERY/INPUT و PB11 وصل باشد؛ فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت SAFE شود. قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="57" t="inlineStr">
         <is>
           <t>v20900 (&lt;21000) flag true</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="57" t="inlineStr">
         <is>
           <t>3500ms (≥3000)</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="55" t="inlineStr">
         <is>
           <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 High؛ پس از 3000ms PB11 Low (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="55" t="inlineStr">
         <is>
           <t>PASS: 2500 still no cut, 3000 SAFE. FAIL: early or no cut.</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="L12" s="58" t="inlineStr"/>
+      <c r="M12" s="55" t="inlineStr"/>
+      <c r="N12" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="O12" s="57" t="inlineStr"/>
+      <c r="P12" s="57" t="inlineStr"/>
+      <c r="Q12" s="59">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>CO-009</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>قطع مستقل / 20800</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>BATTERY, flag false</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY و flag=false باشد.
 گام ۲: snapshot معتبر با v=20700 (کمتر از 20800)، flag=false و input=false اعمال کن.
@@ -1765,64 +2068,68 @@
 گام ۴: بعد از 3000 میلی‌ثانیه باید SAFE با PB11 قطع شود؛ این قطع به flag ربطی ندارد و با flag=false هم باید اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>v20700 (&lt;20800) flag false</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="50" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="48" t="inlineStr">
         <is>
           <t>پس از 3000ms SAFE با PB11 Low مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="48" t="inlineStr">
         <is>
           <t>PASS: independent cut. FAIL: no cut due flag.</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="J13" s="51" t="inlineStr"/>
+      <c r="K13" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr"/>
-      <c r="M13" s="18" t="inlineStr"/>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="L13" s="53" t="inlineStr"/>
+      <c r="M13" s="48" t="inlineStr"/>
+      <c r="N13" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O13" s="18" t="inlineStr"/>
-      <c r="P13" s="18" t="inlineStr"/>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="O13" s="50" t="inlineStr"/>
+      <c r="P13" s="50" t="inlineStr"/>
+      <c r="Q13" s="54">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>CO-010</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>مرز دقیق 21000 نباید cut</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v دقیقاً 21000 (مرز)، flag=true و input=true (Vin=24 ولت) اعمال کن.
@@ -1830,64 +2137,68 @@
 گام ۴: هیچ قطعی نباید رخ دهد (شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی»)؛ وضعیت باید INPUT شده باشد (چون ورودی حاضر است) و PB11 High و امن بماند.</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="57" t="inlineStr">
         <is>
           <t>valid=true, v=21000 (دقیق) flag=true, input=true (Vin≥21V)</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="57" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="55" t="inlineStr">
         <is>
           <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 High-safe بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="I14" s="55" t="inlineStr">
         <is>
           <t>PASS: با v=21000 و input true، state=INPUT و PB11 High. FAIL: هر cut یا BATTERY.</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="J14" s="55" t="inlineStr"/>
+      <c r="K14" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="20" t="inlineStr"/>
-      <c r="M14" s="20" t="inlineStr"/>
-      <c r="N14" s="20" t="inlineStr">
+      <c r="L14" s="58" t="inlineStr"/>
+      <c r="M14" s="55" t="inlineStr"/>
+      <c r="N14" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="O14" s="57" t="inlineStr"/>
+      <c r="P14" s="57" t="inlineStr"/>
+      <c r="Q14" s="59">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>CO-011</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>مرز دقیق 20800 نباید cut</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v دقیقاً 20800 و flag=false اعمال کن.
@@ -1895,64 +2206,68 @@
 گام ۴: هیچ قطعی نباید رخ دهد؛ قطع فقط برای «کمتر از 20800» است و روی خودِ مرز 20800 نباید اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>v=20800 flag false</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="48" t="inlineStr">
         <is>
           <t>هیچ قطع نشود. PASS: need &lt;20800. FAIL: cut at exact.</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="48" t="inlineStr">
         <is>
           <t>PASS: 20800 no independent cut. FAIL: cut.</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="J15" s="51" t="inlineStr"/>
+      <c r="K15" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr"/>
-      <c r="M15" s="18" t="inlineStr"/>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="L15" s="53" t="inlineStr"/>
+      <c r="M15" s="48" t="inlineStr"/>
+      <c r="N15" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr"/>
-      <c r="P15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="O15" s="50" t="inlineStr"/>
+      <c r="P15" s="50" t="inlineStr"/>
+      <c r="Q15" s="54">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>CO-012</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>قطع &lt;3000ms نباید</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="55" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v=20900، flag=true و input=true (Vin=24 ولت) بده.
@@ -1960,64 +2275,68 @@
 گام ۴: تا 2500 میلی‌ثانیه باید هنوز INPUT و PB11 وصل باشد؛ SAFE شدن زودتر از 3000 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="57" t="inlineStr">
         <is>
           <t>valid=true, v=20900 (&lt;21000) flag=true, input=true, فقط 2500ms (&lt;3000)</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="57" t="inlineStr">
         <is>
           <t>2500ms</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="55" t="inlineStr">
         <is>
           <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 High. PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="55" t="inlineStr">
         <is>
           <t>PASS: 2500ms still INPUT (no cut). FAIL: early SAFE یا BATTERY.</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="J16" s="55" t="inlineStr"/>
+      <c r="K16" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="20" t="inlineStr"/>
-      <c r="M16" s="20" t="inlineStr"/>
-      <c r="N16" s="20" t="inlineStr">
+      <c r="L16" s="58" t="inlineStr"/>
+      <c r="M16" s="55" t="inlineStr"/>
+      <c r="N16" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-    </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="O16" s="57" t="inlineStr"/>
+      <c r="P16" s="57" t="inlineStr"/>
+      <c r="Q16" s="59">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>CO-013</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="48" t="inlineStr">
         <is>
           <t>وصل مجدد / 21200 + input</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>SAFE, PB11 Low</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
 گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
@@ -2025,64 +2344,68 @@
 گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>SAFE, input true, v21300</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="50" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="48" t="inlineStr">
         <is>
           <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="48" t="inlineStr">
         <is>
           <t>PASS: قبل 3000 SAFE Low، بعد 3000 INPUT High. FAIL: early or no reconnect.</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="J17" s="51" t="inlineStr"/>
+      <c r="K17" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="18" t="inlineStr"/>
-      <c r="M17" s="18" t="inlineStr"/>
-      <c r="N17" s="18" t="inlineStr">
+      <c r="L17" s="53" t="inlineStr"/>
+      <c r="M17" s="48" t="inlineStr"/>
+      <c r="N17" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O17" s="18" t="inlineStr"/>
-      <c r="P17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="O17" s="50" t="inlineStr"/>
+      <c r="P17" s="50" t="inlineStr"/>
+      <c r="Q17" s="54">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>CO-014</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>مرز دقیق 21200 باید reconnect</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="55" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در SAFE باشد.
 گام ۲: input=true و v دقیقاً 21200 اعمال کن (روی خودِ مرز).
@@ -2090,64 +2413,68 @@
 گام ۴: بعد از 3000 میلی‌ثانیه باید INPUT و PB11 وصل شده باشد؛ شرط وصل «دست‌کم 21200» است، پس روی مرز هم باید وصل شود.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="57" t="inlineStr">
         <is>
           <t>v=21200 input true</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="57" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="55" t="inlineStr">
         <is>
           <t>پس از 3000ms INPUT و PB11 High. PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="55" t="inlineStr">
         <is>
           <t>PASS: 21200 reconnects (need ≥). FAIL: no.</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="J18" s="55" t="inlineStr"/>
+      <c r="K18" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr"/>
-      <c r="M18" s="20" t="inlineStr"/>
-      <c r="N18" s="20" t="inlineStr">
+      <c r="L18" s="58" t="inlineStr"/>
+      <c r="M18" s="55" t="inlineStr"/>
+      <c r="N18" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O18" s="20" t="inlineStr"/>
-      <c r="P18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="O18" s="57" t="inlineStr"/>
+      <c r="P18" s="57" t="inlineStr"/>
+      <c r="Q18" s="59">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>CO-015</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="48" t="inlineStr">
         <is>
           <t>reconnect &lt;3000 نباید</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در SAFE باشد.
 گام ۲: input=true و v=21300 اعمال کن.
@@ -2155,192 +2482,204 @@
 گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>v21300 input true</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="50" t="inlineStr">
         <is>
           <t>2500ms</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="48" t="inlineStr">
         <is>
           <t>هنوز SAFE و PB11 Low. PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" s="48" t="inlineStr">
         <is>
           <t>PASS: 2500 still SAFE. FAIL: INPUT early.</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="J19" s="51" t="inlineStr"/>
+      <c r="K19" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L19" s="18" t="inlineStr"/>
-      <c r="M19" s="18" t="inlineStr"/>
-      <c r="N19" s="18" t="inlineStr">
+      <c r="L19" s="53" t="inlineStr"/>
+      <c r="M19" s="48" t="inlineStr"/>
+      <c r="N19" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O19" s="18" t="inlineStr"/>
-      <c r="P19" s="18" t="inlineStr"/>
-    </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="O19" s="50" t="inlineStr"/>
+      <c r="P19" s="50" t="inlineStr"/>
+      <c r="Q19" s="54">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="40.5" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>CO-016</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>پس از reconnect state INPUT</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>پس از CO-013</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>گام ۱: تست CO-013 را انجام بده تا وصل مجدد موفق اتفاق بیفتد.
 گام ۲: بلافاصله (در حد 100 میلی‌ثانیه بعد) وضعیت را بخوان.
 گام ۳: وضعیت باید INPUT باشد؛ IDLE برای snapshot معتبر هرگز نباید دیده شود.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="57" t="inlineStr">
         <is>
           <t>post-reconnect</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="57" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="55" t="inlineStr">
         <is>
           <t>state=INPUT باشد، نه IDLE (IDLE برای معتبر ممنوع). PASS: INPUT. FAIL: IDLE.</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="55" t="inlineStr">
         <is>
           <t>PASS: INPUT not IDLE. FAIL: IDLE.</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="J20" s="55" t="inlineStr"/>
+      <c r="K20" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr"/>
-      <c r="M20" s="20" t="inlineStr"/>
-      <c r="N20" s="20" t="inlineStr">
+      <c r="L20" s="58" t="inlineStr"/>
+      <c r="M20" s="55" t="inlineStr"/>
+      <c r="N20" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O20" s="20" t="inlineStr"/>
-      <c r="P20" s="20" t="inlineStr"/>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="O20" s="57" t="inlineStr"/>
+      <c r="P20" s="57" t="inlineStr"/>
+      <c r="Q20" s="59">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="40.5" customHeight="1">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>CO-017</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="48" t="inlineStr">
         <is>
           <t>PB11 در invalid حفظ</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>INPUT با PB11 High</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد را با snapshot معتبر و input=true به INPUT ببر و PB11 را چک کن که وصل (High) است.
 گام ۲: حالا valid=false کن و 500 میلی‌ثانیه صبر کن.
 گام ۳: PB11 را دوباره بخوان: باید بدون تغییر همان High مانده باشد.</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>valid true→false</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="50" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="48" t="inlineStr">
         <is>
           <t>PB11 Low-High بدون تغییر بماند (High). PASS: حفظ. FAIL: تغییر.</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="48" t="inlineStr">
         <is>
           <t>PASS: PB11 preserved in invalid. FAIL: change.</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="J21" s="51" t="inlineStr"/>
+      <c r="K21" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L21" s="18" t="inlineStr"/>
-      <c r="M21" s="18" t="inlineStr"/>
-      <c r="N21" s="18" t="inlineStr">
+      <c r="L21" s="53" t="inlineStr"/>
+      <c r="M21" s="48" t="inlineStr"/>
+      <c r="N21" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O21" s="18" t="inlineStr"/>
-      <c r="P21" s="18" t="inlineStr"/>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="O21" s="50" t="inlineStr"/>
+      <c r="P21" s="50" t="inlineStr"/>
+      <c r="Q21" s="54">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>CO-018</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>PB11 در fault حفظ</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="55" t="inlineStr">
         <is>
           <t>INPUT</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در INPUT باشد.
 گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
@@ -2348,128 +2687,136 @@
 گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="57" t="inlineStr">
         <is>
           <t>valid true fault1</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="57" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H22" s="55" t="inlineStr">
         <is>
           <t>PB11 حفظ (High). PASS. FAIL: Low شدن.</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="55" t="inlineStr">
         <is>
           <t>PASS: PB11 preserved in fault. FAIL: change.</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr"/>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="J22" s="55" t="inlineStr"/>
+      <c r="K22" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr"/>
-      <c r="M22" s="20" t="inlineStr"/>
-      <c r="N22" s="20" t="inlineStr">
+      <c r="L22" s="58" t="inlineStr"/>
+      <c r="M22" s="55" t="inlineStr"/>
+      <c r="N22" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O22" s="20" t="inlineStr"/>
-      <c r="P22" s="20" t="inlineStr"/>
-    </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="O22" s="57" t="inlineStr"/>
+      <c r="P22" s="57" t="inlineStr"/>
+      <c r="Q22" s="59">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="40.5" customHeight="1">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>CO-019</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="48" t="inlineStr">
         <is>
           <t>PB5 و PB7 هیچ‌گاه تغییر نکنند</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>هر حالت</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="60" t="inlineStr">
         <is>
           <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015 که انجام می‌دهی، علاوه بر PB11 دو پایهٔ PB5 (BAT_SWITCH) و PB7 (RELAY) را هم با اسیلوسکوپ یا لاگ BSP زیر نظر بگیر.
 گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
 گام ۳: PB5 باید همیشه High امن (active-low) و PB7 همیشه Low بماند؛ هر تغییر (toggle) روی این دو یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>تمام حالات</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="50" t="inlineStr">
         <is>
           <t>هر تست</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="48" t="inlineStr">
         <is>
           <t>PB5 و PB7 ثابت بمانند (PB5 High-safe active-low، PB7 Low). PASS: بدون تغییر. FAIL: هر toggle.</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="48" t="inlineStr">
         <is>
           <t>PASS: PB5/PB7 never change. FAIL: any toggle.</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr"/>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="J23" s="51" t="inlineStr"/>
+      <c r="K23" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L23" s="18" t="inlineStr"/>
-      <c r="M23" s="18" t="inlineStr"/>
-      <c r="N23" s="18" t="inlineStr">
+      <c r="L23" s="53" t="inlineStr"/>
+      <c r="M23" s="48" t="inlineStr"/>
+      <c r="N23" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O23" s="18" t="inlineStr"/>
-      <c r="P23" s="18" t="inlineStr"/>
-    </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="O23" s="50" t="inlineStr"/>
+      <c r="P23" s="50" t="inlineStr"/>
+      <c r="Q23" s="54">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>CO-020</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>فقط PROTECT_BATTERY مجاز</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>کد review + تست</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="61" t="inlineStr">
         <is>
           <t>گام ۱: کد changeover.c را بازبینی کن: تنها جایی که اجازهٔ نوشتن روی خروجی دارد باید func__BspGpio_Write با BSP_GPIO_PROTECT_BATTERY (همان PB11) باشد.
 گام ۲: دنبال هر ارجاع مستقیم به board_pins یا HAL یا PB5/PB7 در این مسیر بگرد؛ نباید هیچ‌کدام باشد.
@@ -2477,64 +2824,68 @@
 گام ۴: اگر PB5 یا PB7 در هیچ تستی تغییر نکرد، قبول است.</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="57" t="inlineStr">
         <is>
           <t>کد + PB11</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H24" s="55" t="inlineStr">
         <is>
           <t>هیچ کد board_pins/HAL/PB5/PB7 نباشد، فقط PB11 تغییر کند. PASS: فقط PB11. FAIL: PB5/7.</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I24" s="55" t="inlineStr">
         <is>
           <t>PASS: only PB11. FAIL: PB5/7 usage.</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="J24" s="55" t="inlineStr"/>
+      <c r="K24" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr"/>
-      <c r="M24" s="20" t="inlineStr"/>
-      <c r="N24" s="20" t="inlineStr">
+      <c r="L24" s="58" t="inlineStr"/>
+      <c r="M24" s="55" t="inlineStr"/>
+      <c r="N24" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O24" s="20" t="inlineStr"/>
-      <c r="P24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="O24" s="57" t="inlineStr"/>
+      <c r="P24" s="57" t="inlineStr"/>
+      <c r="Q24" s="59">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>CO-021</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="48" t="inlineStr">
         <is>
           <t>زمان از rtos_time</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>هر زمان</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>گام ۱: کد را بازبینی کن: همهٔ تبدیل‌های میلی‌ثانیه به تیک باید فقط از func__Rtos_MillisecondsToTicks و زمان فعلی از osKernelGetTickCount گرفته شود.
 گام ۲: دنبال هر جا که «تیک برابر 1 میلی‌ثانیه» فرض شده باشد بگرد؛ نباید هیچ جا باشد.
@@ -2542,64 +2893,68 @@
 گام ۴: رفتار باید با هر فرکانس تیک درست بماند؛ وابستگی به فرض 1 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>کد review</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="H25" s="48" t="inlineStr">
         <is>
           <t>زمان با rtos_time قابل‌حمل باشد، 3000ms با هر فرکانس تیک درست کار کند. PASS: portable. FAIL: فرض 1ms.</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="48" t="inlineStr">
         <is>
           <t>PASS: portable via rtos_time. FAIL: hardcoded 1ms.</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr"/>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="J25" s="51" t="inlineStr"/>
+      <c r="K25" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L25" s="18" t="inlineStr"/>
-      <c r="M25" s="18" t="inlineStr"/>
-      <c r="N25" s="18" t="inlineStr">
+      <c r="L25" s="53" t="inlineStr"/>
+      <c r="M25" s="48" t="inlineStr"/>
+      <c r="N25" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O25" s="18" t="inlineStr"/>
-      <c r="P25" s="18" t="inlineStr"/>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="O25" s="50" t="inlineStr"/>
+      <c r="P25" s="50" t="inlineStr"/>
+      <c r="Q25" s="54">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>CO-022</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
         <is>
           <t>durationTicks صفر → no immediate cut</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="55" t="inlineStr">
         <is>
           <t>BATTERY با شرط قطع</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E26" s="55" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY و شرط قطع برقرار باشد.
 گام ۲: در شبیه‌سازی کاری کن فرکانس تیک صفر شود، طوری که func__Rtos_MillisecondsToTicks مقدار 0 برگرداند.
@@ -2607,64 +2962,68 @@
 گام ۴: هیچ قطع یا وصل فوری نباید اتفاق بیفتد؛ وضعیت و PB11 باید حفظ شوند و فقط تایمر reset شود. قطع فوری یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F26" s="57" t="inlineStr">
         <is>
           <t>valid true v20700 durTicks0</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="57" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H26" s="55" t="inlineStr">
         <is>
           <t>هیچ قطع/وصل فوری انجام نشود، state و PB11 حفظ، تایمر reset. PASS: guard بدون تصمیم. FAIL: قطع فوری.</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="I26" s="55" t="inlineStr">
         <is>
           <t>PASS: guard preserves. FAIL: immediate cut.</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr"/>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="J26" s="55" t="inlineStr"/>
+      <c r="K26" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L26" s="20" t="inlineStr"/>
-      <c r="M26" s="20" t="inlineStr"/>
-      <c r="N26" s="20" t="inlineStr">
+      <c r="L26" s="58" t="inlineStr"/>
+      <c r="M26" s="55" t="inlineStr"/>
+      <c r="N26" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O26" s="20" t="inlineStr"/>
-      <c r="P26" s="20" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="O26" s="57" t="inlineStr"/>
+      <c r="P26" s="57" t="inlineStr"/>
+      <c r="Q26" s="59">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="inlineStr">
         <is>
           <t>CO-023</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="48" t="inlineStr">
         <is>
           <t>snapshot zeroing task_control</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>MODULE_MEASUREMENT=0 یا GetSnapshot=false</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن (یا ADC را نگه دار تا valid=false بماند).
 گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
@@ -2672,69 +3031,73 @@
 گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند؛ هیچ تصمیمی بر اساس زباله قبول نیست.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="50" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="50" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="48" t="inlineStr">
         <is>
           <t>هیچ فیلد snapshot حاوی زباله پشته نباشد؛ Changeover باید فقط روی valid گیت بزند و PB11 امن بماند؛ task_control مانند task_comm/task_ui/task_protection هر 9 فیلد را صفر کند</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="48" t="inlineStr">
         <is>
           <t>امن</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="48" t="inlineStr">
         <is>
           <t>بدون تصمیم بر اساس زباله؛ PB11 حفظ</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="48" t="n"/>
+      <c r="L27" s="62" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="M27" s="48" t="n"/>
+      <c r="N27" s="48" t="n"/>
+      <c r="O27" s="50" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="P27" s="50" t="n"/>
+      <c r="Q27" s="54" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>CO-024</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t>وصل مجدد 30s پایداری ورودی</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="55" t="inlineStr">
         <is>
           <t>برد در SAFE پس از قطع، v_bat=24V</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="61" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
 گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
@@ -2742,44 +3105,306 @@
 گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="57" t="inlineStr">
         <is>
           <t>input=true v=24000</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="57" t="inlineStr">
         <is>
           <t>33s</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="55" t="inlineStr">
         <is>
           <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="55" t="inlineStr">
         <is>
           <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="J28" s="55" t="n"/>
+      <c r="K28" s="55" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="L28" s="58" t="n"/>
+      <c r="M28" s="55" t="n"/>
+      <c r="N28" s="55" t="inlineStr">
         <is>
           <t>thermal+30s</t>
         </is>
       </c>
+      <c r="O28" s="57" t="n"/>
+      <c r="P28" s="57" t="n"/>
+      <c r="Q28" s="59">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="63">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="63">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="63">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="63">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="63">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="63">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="63">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="63">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="63">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="63">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="63">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="63">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="63">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="63">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="63">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="63">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="63">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="63">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="63">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="63">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="63">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="63">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="63">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="63">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="63">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="63">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="63">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="63">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="63">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Q62" s="63">
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="Q63" s="63">
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="Q64" s="63">
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="Q65" s="63">
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="Q66" s="63">
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="Q67" s="63">
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="Q68" s="63">
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P26"/>
+  <autoFilter ref="A4:Q28"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="L5:L108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId6"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -2789,6 +3414,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2803,431 +3429,436 @@
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوهای Changeover</t>
         </is>
       </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="9" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>این صفحه مرجع انتظار است؛ نتیجه واقعی فقط در «برنامه تست» ثبت شود. مقادیر از کد واقعی استخراج شده؛ مقدار حدسی وجود ندارد.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>شرط / مقدار (از کد)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>توضیح تکمیلی</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>valid==false یا NULL</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>state حفظ، PB11 حفظ، تایمر reset</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="66" t="inlineStr">
         <is>
           <t>changeover.c:valid check</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="65" t="inlineStr">
         <is>
           <t>زمان نامعتبر شمرده نشود</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="66" t="inlineStr">
         <is>
           <t>CO-001,002,017</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Fault</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>fault_mask !=0</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>state=FAULT، هیچ pin تغییر نکند</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>FAULT_NONE</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="65" t="inlineStr">
         <is>
           <t>بالاترین اولویت پس از valid</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="66" t="inlineStr">
         <is>
           <t>CO-004,005,018</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>قطع با آلارم</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>v&lt;21000 و فلگ true</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>پس از 3000ms PB11 Low (قطع) → SAFE</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="65" t="inlineStr">
         <is>
           <t>CHANGEOVER_BAT_LOW_ALARM_CUT_MV=21000</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="65" t="inlineStr">
         <is>
           <t>پیوسته</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="66" t="inlineStr">
         <is>
           <t>CO-008,010,012</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>قطع مستقل</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>v&lt;20800 (بدون فلگ)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>پس از 3000ms PB11 Low</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>CHANGEOVER_BAT_CRITICAL_CUT_MV=20800</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>مستقل</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>CO-009,011</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>فیلتر زمان</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>هر شرط &lt;3000ms</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>عدم قطع/وصل</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="65" t="inlineStr">
         <is>
           <t>CHANGEOVER_DURATION_MS=3000</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="65" t="inlineStr">
         <is>
           <t>از rtos_time</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="66" t="inlineStr">
         <is>
           <t>CO-012,015</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>وصل مجدد</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>input==true و v≥21200</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>پس از 3000ms PB11 High → INPUT</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>CHANGEOVER_BAT_RECONNECT_MV=21200</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>هر دو پیوسته</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="66" t="inlineStr">
         <is>
           <t>CO-013,014,016</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>پس از reconnect</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>state=INPUT</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>نه IDLE</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="66" t="inlineStr">
         <is>
           <t>app_types.h</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="65" t="inlineStr">
         <is>
           <t>IDLE ممنوع برای valid</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>CO-016</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>PB11 حفظ</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>invalid/fault</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="65" t="inlineStr">
         <is>
           <t>snapshot-first</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="66" t="inlineStr">
         <is>
           <t>CO-017,018</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t>PB5/PB7</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>هیچ‌گاه</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="66" t="inlineStr">
         <is>
           <t>bsp_gpio.h:Forbidden</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="65" t="inlineStr">
         <is>
           <t>فقط PROTECT_BATTERY</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>CO-019,020</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t>زمان</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>ticks→ms via rtos_time</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="65" t="inlineStr">
         <is>
           <t>بدون فرض 1ms</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr">
         <is>
           <t>func__Rtos_MillisecondsToTicks</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="65" t="inlineStr">
         <is>
           <t>قابل‌حمل</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="66" t="inlineStr">
         <is>
           <t>CO-021</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="65" t="inlineStr">
         <is>
           <t>duration0</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>Ticks==0</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="65" t="inlineStr">
         <is>
           <t>بدون تصمیم، حفظ state/PB11</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>changeover.c guard</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="65" t="inlineStr">
         <is>
           <t>frequency 0</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="66" t="inlineStr">
         <is>
           <t>CO-022</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="65" t="inlineStr">
         <is>
           <t>منبع داده</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>فقط 5 ورودی مجاز</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="65" t="inlineStr">
         <is>
           <t>عدم استفاده از v_in/v_bat12 و ...</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="66" t="inlineStr">
         <is>
           <t>app_types.h</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="65" t="inlineStr">
         <is>
           <t>محدودیت</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="66" t="inlineStr">
         <is>
           <t>CO-020</t>
         </is>
@@ -3238,6 +3869,25 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId17"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -3247,6 +3897,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3269,81 +3920,93 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
       </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="9" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="41" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="41" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="41" t="inlineStr">
         <is>
           <t>مدرک / مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="41" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="41" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="41" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="41" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -3513,6 +4176,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3528,43 +4192,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — Changeover — PB11</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بستن ایرادهای باز امضا شود. بدون تکمیل این صفحه، اعتبارسنجی ناقص است.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Changeover — PB11</t>
         </is>
@@ -3573,22 +4237,22 @@
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>2026-09-16 (2.1 — فیلتر 3000ms)</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="70" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>2.1 — فیلتر 3000ms</t>
         </is>
@@ -3597,17 +4261,17 @@
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
@@ -3617,13 +4281,13 @@
       <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr"/>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="70" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
@@ -3633,18 +4297,18 @@
       <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr"/>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="70" t="inlineStr">
         <is>
           <t>ابزار اندازه‌گیری</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسیلوسکوپ + تایمر RTOS</t>
         </is>
@@ -3653,12 +4317,12 @@
       <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
@@ -3669,12 +4333,12 @@
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="70" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
@@ -3685,12 +4349,12 @@
       <c r="F10" s="11" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
         <is>
           <t>آستانه‌ها</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>21000/20800/21200</t>
         </is>
@@ -3701,12 +4365,12 @@
       <c r="F11" s="11" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>فیلتر</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>3000ms</t>
         </is>
@@ -3717,12 +4381,12 @@
       <c r="F12" s="11" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>مجاز pin</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>فقط BSP_GPIO_PROTECT_BATTERY</t>
         </is>
@@ -3733,12 +4397,12 @@
       <c r="F13" s="11" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>ممنوع</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>PB5/PB7/HAL/board_pins</t>
         </is>
@@ -3749,29 +4413,29 @@
       <c r="F14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>فرمول پیشنهادی</t>
         </is>
@@ -3780,16 +4444,16 @@
       <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>تعداد کل تست‌ها</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="71">
         <f>COUNTA('برنامه تست'!A5:A200)</f>
         <v/>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>کل ردیف‌های برنامه تست</t>
         </is>
@@ -3799,21 +4463,21 @@
       <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>تعداد قبول (PASS)</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"قبول")</f>
         <v/>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = قبول</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
@@ -3822,21 +4486,21 @@
       <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>تعداد رد (FAIL)</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"رد")</f>
         <v/>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = رد</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
@@ -3845,21 +4509,21 @@
       <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>تعداد در انتظار</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = در انتظار</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
@@ -3868,16 +4532,16 @@
       <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>تعداد مسدود</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"مسدود")</f>
         <v/>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = مسدود</t>
         </is>
@@ -3887,16 +4551,16 @@
       <c r="F21" s="9" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="71">
         <f>IF(B17=0,"",TEXT(B18/B17,"0%"))</f>
         <v/>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
         <is>
           <t>PASS / TOTAL</t>
         </is>
@@ -3906,34 +4570,34 @@
       <c r="F22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>امضاها</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>نقش</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>نام و نام خانوادگی</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="41" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="41" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
@@ -3941,7 +4605,7 @@
       <c r="F24" s="9" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
@@ -3953,7 +4617,7 @@
       <c r="F25" s="9" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>بازبین فنی</t>
         </is>
@@ -3965,7 +4629,7 @@
       <c r="F26" s="9" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>تأیید نهایی</t>
         </is>
@@ -3977,7 +4641,7 @@
       <c r="F27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="69" t="inlineStr">
         <is>
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
@@ -4018,6 +4682,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4028,189 +4693,198 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>BoardTest</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>InputOk</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Charging</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>BatteryRun</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>هیسترزیس</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Snapshot</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Buzzer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>Changeover</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>نتیجه ایراد</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>باز</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>در حال بررسی</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="72" t="inlineStr">
         <is>
           <t>بسته</t>
         </is>
@@ -4224,7 +4898,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4236,55 +4910,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول تغییر مسیر (Changeover)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>Changeover_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -4297,6 +4972,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$64</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -253,6 +256,13 @@
       <sz val="7"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -402,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -619,6 +629,13 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1360,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2798,12 +2815,12 @@
     <row r="24" ht="54" customHeight="1">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>CO-020</t>
+          <t>CO-024</t>
         </is>
       </c>
       <c r="B24" s="55" t="inlineStr">
         <is>
-          <t>فقط PROTECT_BATTERY مجاز</t>
+          <t>وصل مجدد 30s پایداری ورودی</t>
         </is>
       </c>
       <c r="C24" s="56" t="inlineStr">
@@ -2813,291 +2830,10 @@
       </c>
       <c r="D24" s="55" t="inlineStr">
         <is>
-          <t>کد review + تست</t>
+          <t>برد در SAFE پس از قطع، v_bat=24V</t>
         </is>
       </c>
       <c r="E24" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: کد changeover.c را بازبینی کن: تنها جایی که اجازهٔ نوشتن روی خروجی دارد باید func__BspGpio_Write با BSP_GPIO_PROTECT_BATTERY (همان PB11) باشد.
-گام ۲: دنبال هر ارجاع مستقیم به board_pins یا HAL یا PB5/PB7 در این مسیر بگرد؛ نباید هیچ‌کدام باشد.
-گام ۳: با اسیلوسکوپ PB11 را در چند تست قبلی چک کن که فقط همان تغییر می‌کند.
-گام ۴: اگر PB5 یا PB7 در هیچ تستی تغییر نکرد، قبول است.</t>
-        </is>
-      </c>
-      <c r="F24" s="57" t="inlineStr">
-        <is>
-          <t>کد + PB11</t>
-        </is>
-      </c>
-      <c r="G24" s="57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="55" t="inlineStr">
-        <is>
-          <t>هیچ کد board_pins/HAL/PB5/PB7 نباشد، فقط PB11 تغییر کند. PASS: فقط PB11. FAIL: PB5/7.</t>
-        </is>
-      </c>
-      <c r="I24" s="55" t="inlineStr">
-        <is>
-          <t>PASS: only PB11. FAIL: PB5/7 usage.</t>
-        </is>
-      </c>
-      <c r="J24" s="55" t="inlineStr"/>
-      <c r="K24" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L24" s="58" t="inlineStr"/>
-      <c r="M24" s="55" t="inlineStr"/>
-      <c r="N24" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O24" s="57" t="inlineStr"/>
-      <c r="P24" s="57" t="inlineStr"/>
-      <c r="Q24" s="59">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="47" t="inlineStr">
-        <is>
-          <t>CO-021</t>
-        </is>
-      </c>
-      <c r="B25" s="48" t="inlineStr">
-        <is>
-          <t>زمان از rtos_time</t>
-        </is>
-      </c>
-      <c r="C25" s="50" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D25" s="48" t="inlineStr">
-        <is>
-          <t>هر زمان</t>
-        </is>
-      </c>
-      <c r="E25" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: کد را بازبینی کن: همهٔ تبدیل‌های میلی‌ثانیه به تیک باید فقط از func__Rtos_MillisecondsToTicks و زمان فعلی از osKernelGetTickCount گرفته شود.
-گام ۲: دنبال هر جا که «تیک برابر 1 میلی‌ثانیه» فرض شده باشد بگرد؛ نباید هیچ جا باشد.
-گام ۳: در صورت امکان فرکانس تیک را در شبیه‌سازی تغییر بده و تست 3000 میلی‌ثانیه‌ای قطع را تکرار کن.
-گام ۴: رفتار باید با هر فرکانس تیک درست بماند؛ وابستگی به فرض 1 میلی‌ثانیه یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F25" s="50" t="inlineStr">
-        <is>
-          <t>کد review</t>
-        </is>
-      </c>
-      <c r="G25" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="48" t="inlineStr">
-        <is>
-          <t>زمان با rtos_time قابل‌حمل باشد، 3000ms با هر فرکانس تیک درست کار کند. PASS: portable. FAIL: فرض 1ms.</t>
-        </is>
-      </c>
-      <c r="I25" s="48" t="inlineStr">
-        <is>
-          <t>PASS: portable via rtos_time. FAIL: hardcoded 1ms.</t>
-        </is>
-      </c>
-      <c r="J25" s="51" t="inlineStr"/>
-      <c r="K25" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L25" s="53" t="inlineStr"/>
-      <c r="M25" s="48" t="inlineStr"/>
-      <c r="N25" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O25" s="50" t="inlineStr"/>
-      <c r="P25" s="50" t="inlineStr"/>
-      <c r="Q25" s="54">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="47" t="inlineStr">
-        <is>
-          <t>CO-022</t>
-        </is>
-      </c>
-      <c r="B26" s="55" t="inlineStr">
-        <is>
-          <t>durationTicks صفر → no immediate cut</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D26" s="55" t="inlineStr">
-        <is>
-          <t>BATTERY با شرط قطع</t>
-        </is>
-      </c>
-      <c r="E26" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BATTERY و شرط قطع برقرار باشد.
-گام ۲: در شبیه‌سازی کاری کن فرکانس تیک صفر شود، طوری که func__Rtos_MillisecondsToTicks مقدار 0 برگرداند.
-گام ۳: snapshot معتبر با v=20700 و flag=true را 3500 میلی‌ثانیه نگه دار.
-گام ۴: هیچ قطع یا وصل فوری نباید اتفاق بیفتد؛ وضعیت و PB11 باید حفظ شوند و فقط تایمر reset شود. قطع فوری یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F26" s="57" t="inlineStr">
-        <is>
-          <t>valid true v20700 durTicks0</t>
-        </is>
-      </c>
-      <c r="G26" s="57" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H26" s="55" t="inlineStr">
-        <is>
-          <t>هیچ قطع/وصل فوری انجام نشود، state و PB11 حفظ، تایمر reset. PASS: guard بدون تصمیم. FAIL: قطع فوری.</t>
-        </is>
-      </c>
-      <c r="I26" s="55" t="inlineStr">
-        <is>
-          <t>PASS: guard preserves. FAIL: immediate cut.</t>
-        </is>
-      </c>
-      <c r="J26" s="55" t="inlineStr"/>
-      <c r="K26" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L26" s="58" t="inlineStr"/>
-      <c r="M26" s="55" t="inlineStr"/>
-      <c r="N26" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O26" s="57" t="inlineStr"/>
-      <c r="P26" s="57" t="inlineStr"/>
-      <c r="Q26" s="59">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="47" t="inlineStr">
-        <is>
-          <t>CO-023</t>
-        </is>
-      </c>
-      <c r="B27" s="48" t="inlineStr">
-        <is>
-          <t>snapshot zeroing task_control</t>
-        </is>
-      </c>
-      <c r="C27" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D27" s="48" t="inlineStr">
-        <is>
-          <t>MODULE_MEASUREMENT=0 یا GetSnapshot=false</t>
-        </is>
-      </c>
-      <c r="E27" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن (یا ADC را نگه دار تا valid=false بماند).
-گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
-گام ۳: هیچ فیلد snapshot نباید زبالهٔ پشته داشته باشد: task_control مثل task_comm و task_ui و task_protection هر 9 فیلد را از قبل صفر می‌کند.
-گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند؛ هیچ تصمیمی بر اساس زباله قبول نیست.</t>
-        </is>
-      </c>
-      <c r="F27" s="50" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G27" s="50" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H27" s="48" t="inlineStr">
-        <is>
-          <t>هیچ فیلد snapshot حاوی زباله پشته نباشد؛ Changeover باید فقط روی valid گیت بزند و PB11 امن بماند؛ task_control مانند task_comm/task_ui/task_protection هر 9 فیلد را صفر کند</t>
-        </is>
-      </c>
-      <c r="I27" s="48" t="inlineStr">
-        <is>
-          <t>امن</t>
-        </is>
-      </c>
-      <c r="J27" s="48" t="inlineStr">
-        <is>
-          <t>بدون تصمیم بر اساس زباله؛ PB11 حفظ</t>
-        </is>
-      </c>
-      <c r="K27" s="48" t="n"/>
-      <c r="L27" s="62" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M27" s="48" t="n"/>
-      <c r="N27" s="48" t="n"/>
-      <c r="O27" s="50" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P27" s="50" t="n"/>
-      <c r="Q27" s="54" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="47" t="inlineStr">
-        <is>
-          <t>CO-024</t>
-        </is>
-      </c>
-      <c r="B28" s="55" t="inlineStr">
-        <is>
-          <t>وصل مجدد 30s پایداری ورودی</t>
-        </is>
-      </c>
-      <c r="C28" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D28" s="55" t="inlineStr">
-        <is>
-          <t>برد در SAFE پس از قطع، v_bat=24V</t>
-        </is>
-      </c>
-      <c r="E28" s="61" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
 گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
@@ -3105,288 +2841,293 @@
 گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
         </is>
       </c>
-      <c r="F28" s="57" t="inlineStr">
+      <c r="F24" s="57" t="inlineStr">
         <is>
           <t>input=true v=24000</t>
         </is>
       </c>
-      <c r="G28" s="57" t="inlineStr">
+      <c r="G24" s="57" t="inlineStr">
         <is>
           <t>33s</t>
         </is>
       </c>
-      <c r="H28" s="55" t="inlineStr">
+      <c r="H24" s="55" t="inlineStr">
         <is>
           <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
         </is>
       </c>
-      <c r="I28" s="55" t="inlineStr">
+      <c r="I24" s="55" t="inlineStr">
         <is>
           <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
         </is>
       </c>
-      <c r="J28" s="55" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="J24" s="55" t="n"/>
+      <c r="K24" s="55" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="L28" s="58" t="n"/>
-      <c r="M28" s="55" t="n"/>
-      <c r="N28" s="55" t="inlineStr">
+      <c r="L24" s="58" t="n"/>
+      <c r="M24" s="55" t="n"/>
+      <c r="N24" s="55" t="inlineStr">
         <is>
           <t>thermal+30s</t>
         </is>
       </c>
-      <c r="O28" s="57" t="n"/>
-      <c r="P28" s="57" t="n"/>
-      <c r="Q28" s="59">
+      <c r="O24" s="57" t="n"/>
+      <c r="P24" s="57" t="n"/>
+      <c r="Q24" s="59">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="Q25" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="Q26" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="Q27" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>#'برنامه تست'!A12</t>
+        </is>
+      </c>
+      <c r="Q28" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="63">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="63">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="63">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="63">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="63">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="63">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="63">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="63">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="63">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="63">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="63">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="63">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="63">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="63">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="63">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="63">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="63">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="63">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="63">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="63">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="63">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="63">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="63">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="63">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="63">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="63">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="63">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="63">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="63">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="63">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="63">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="63">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="63">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="63">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="Q63" s="63">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="Q64" s="63">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="Q65" s="63">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="Q66" s="63">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="Q67" s="63">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="Q68" s="63">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q28"/>
+  <autoFilter ref="A4:Q64"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
@@ -3398,12 +3139,11 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId6"/>
+    <hyperlink ref="E17" location="'برنامه تست'!A12"/>
+    <hyperlink ref="D20" location="'برنامه تست'!A17"/>
+    <hyperlink ref="E20" location="'برنامه تست'!A17"/>
+    <hyperlink ref="E23" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E24" location="'برنامه تست'!A12"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3412,6 +3152,546 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="78" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>شناسه تست</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>ورودی‌ها</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="L4" s="37" t="inlineStr">
+        <is>
+          <t>شرح ایراد</t>
+        </is>
+      </c>
+      <c r="M4" s="37" t="inlineStr">
+        <is>
+          <t>مدرک تست</t>
+        </is>
+      </c>
+      <c r="N4" s="37" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>CO-020</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>فقط PROTECT_BATTERY مجاز</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>کد review + تست</t>
+        </is>
+      </c>
+      <c r="E5" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: کد changeover.c را بازبینی کن: تنها جایی که اجازهٔ نوشتن روی خروجی دارد باید func__BspGpio_Write با BSP_GPIO_PROTECT_BATTERY (همان PB11) باشد.
+گام ۲: دنبال هر ارجاع مستقیم به board_pins یا HAL یا PB5/PB7 در این مسیر بگرد؛ نباید هیچ‌کدام باشد.
+گام ۳: با اسیلوسکوپ PB11 را در چند تست قبلی چک کن که فقط همان تغییر می‌کند.
+گام ۴: اگر PB5 یا PB7 در هیچ تستی تغییر نکرد، قبول است.</t>
+        </is>
+      </c>
+      <c r="F5" s="57" t="inlineStr">
+        <is>
+          <t>کد + PB11</t>
+        </is>
+      </c>
+      <c r="G5" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>هیچ کد board_pins/HAL/PB5/PB7 نباشد، فقط PB11 تغییر کند. PASS: فقط PB11. FAIL: PB5/7.</t>
+        </is>
+      </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>PASS: only PB11. FAIL: PB5/7 usage.</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="58" t="n"/>
+      <c r="M5" s="55" t="n"/>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O5" s="57" t="n"/>
+      <c r="P5" s="57" t="n"/>
+      <c r="Q5" s="59">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>CO-021</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>زمان از rtos_time</t>
+        </is>
+      </c>
+      <c r="C6" s="50" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>هر زمان</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: کد را بازبینی کن: همهٔ تبدیل‌های میلی‌ثانیه به تیک باید فقط از func__Rtos_MillisecondsToTicks و زمان فعلی از osKernelGetTickCount گرفته شود.
+گام ۲: دنبال هر جا که «تیک برابر 1 میلی‌ثانیه» فرض شده باشد بگرد؛ نباید هیچ جا باشد.
+گام ۳: در صورت امکان فرکانس تیک را در شبیه‌سازی تغییر بده و تست 3000 میلی‌ثانیه‌ای قطع را تکرار کن.
+گام ۴: رفتار باید با هر فرکانس تیک درست بماند؛ وابستگی به فرض 1 میلی‌ثانیه یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
+        <is>
+          <t>کد review</t>
+        </is>
+      </c>
+      <c r="G6" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="48" t="inlineStr">
+        <is>
+          <t>زمان با rtos_time قابل‌حمل باشد، 3000ms با هر فرکانس تیک درست کار کند. PASS: portable. FAIL: فرض 1ms.</t>
+        </is>
+      </c>
+      <c r="I6" s="48" t="inlineStr">
+        <is>
+          <t>PASS: portable via rtos_time. FAIL: hardcoded 1ms.</t>
+        </is>
+      </c>
+      <c r="J6" s="51" t="n"/>
+      <c r="K6" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L6" s="53" t="n"/>
+      <c r="M6" s="48" t="n"/>
+      <c r="N6" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O6" s="50" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="54">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>CO-022</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>durationTicks صفر → no immediate cut</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>BATTERY با شرط قطع</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BATTERY و شرط قطع برقرار باشد.
+گام ۲: در شبیه‌سازی کاری کن فرکانس تیک صفر شود، طوری که func__Rtos_MillisecondsToTicks مقدار 0 برگرداند.
+گام ۳: snapshot معتبر با v=20700 و flag=true را 3500 میلی‌ثانیه نگه دار.
+گام ۴: هیچ قطع یا وصل فوری نباید اتفاق بیفتد؛ وضعیت و PB11 باید حفظ شوند و فقط تایمر reset شود. قطع فوری یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F7" s="57" t="inlineStr">
+        <is>
+          <t>valid true v20700 durTicks0</t>
+        </is>
+      </c>
+      <c r="G7" s="57" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>هیچ قطع/وصل فوری انجام نشود، state و PB11 حفظ، تایمر reset. PASS: guard بدون تصمیم. FAIL: قطع فوری.</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>PASS: guard preserves. FAIL: immediate cut.</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="n"/>
+      <c r="K7" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L7" s="58" t="n"/>
+      <c r="M7" s="55" t="n"/>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O7" s="57" t="n"/>
+      <c r="P7" s="57" t="n"/>
+      <c r="Q7" s="59">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>CO-023</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_control</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>MODULE_MEASUREMENT=0 یا GetSnapshot=false</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن (یا ADC را نگه دار تا valid=false بماند).
+گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
+گام ۳: هیچ فیلد snapshot نباید زبالهٔ پشته داشته باشد: task_control مثل task_comm و task_ui و task_protection هر 9 فیلد را از قبل صفر می‌کند.
+گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند؛ هیچ تصمیمی بر اساس زباله قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F8" s="50" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G8" s="50" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
+        <is>
+          <t>هیچ فیلد snapshot حاوی زباله پشته نباشد؛ Changeover باید فقط روی valid گیت بزند و PB11 امن بماند؛ task_control مانند task_comm/task_ui/task_protection هر 9 فیلد را صفر کند</t>
+        </is>
+      </c>
+      <c r="I8" s="48" t="inlineStr">
+        <is>
+          <t>امن</t>
+        </is>
+      </c>
+      <c r="J8" s="48" t="inlineStr">
+        <is>
+          <t>بدون تصمیم بر اساس زباله؛ PB11 حفظ</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n"/>
+      <c r="L8" s="62" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M8" s="48" t="n"/>
+      <c r="N8" s="48" t="n"/>
+      <c r="O8" s="50" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="63">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="63">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="63">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="63">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="63">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="63">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="63">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="63">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="63">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="63">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="63">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="63">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="63">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="63">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="63">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="63">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="63">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="63">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q8"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3871,22 +4151,22 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId17"/>
+    <hyperlink ref="F4" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F5" location="'برنامه تست'!A8"/>
+    <hyperlink ref="F6" location="'برنامه تست'!A12"/>
+    <hyperlink ref="F7" location="'برنامه تست'!A13"/>
+    <hyperlink ref="F8" location="'برنامه تست'!A16"/>
+    <hyperlink ref="F9" location="'برنامه تست'!A17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId2"/>
+    <hyperlink ref="F10" location="'برنامه تست'!A20"/>
+    <hyperlink ref="F11" location="'برنامه تست'!A21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId3"/>
+    <hyperlink ref="F12" location="'برنامه تست'!A23"/>
+    <hyperlink ref="F13" location="'تست‌های برنامه‌نویسی'!A6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId4"/>
+    <hyperlink ref="F14" location="'تست‌های برنامه‌نویسی'!A7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId5"/>
+    <hyperlink ref="F15" location="'تست‌های برنامه‌نویسی'!A5"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3894,7 +4174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4173,7 +4453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -4679,7 +4959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -4895,7 +5175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="فهرست‌ها" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -264,7 +267,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -325,6 +328,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -412,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -636,6 +644,9 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1377,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1504,1646 +1515,544 @@
       <c r="Q4" s="37" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
-        <is>
-          <t>CO-001</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>Snapshot نامعتبر / حفظ</t>
-        </is>
-      </c>
-      <c r="C5" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D5" s="48" t="inlineStr">
-        <is>
-          <t>Init → BOOT, PB11 High-safe</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد؛ PB11 باید High و امن باشد.
-گام ۲: یک snapshot نامعتبر اعمال کن: valid=false ولی v_bat=24000، input=false و fault=0.
-گام ۳: 500 میلی‌ثانیه صبر کن و وضعیت (state) و پایهٔ PB11 را بخوان.
-گام ۴: وضعیت قبلی (BOOT یا هر وضعیت قبلی) و PB11 باید بدون هیچ تغییری حفظ شده باشند؛ رفتن به FAULT یا IDLE یا تغییر PB11 یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F5" s="50" t="inlineStr">
-        <is>
-          <t>valid=false, v=24000, input=false, flag false, fault0</t>
-        </is>
-      </c>
-      <c r="G5" s="50" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H5" s="48" t="inlineStr">
-        <is>
-          <t>state حفظ شود: «state فعلی حفظ شود» (BOOT/BATTERY/INPUT/SAFE قبلی) و PB11 حفظ (High-safe). PASS: state و PB11 بدون تغییر. FAIL: هر تغییر به FAULT یا IDLE یا تغییر PB11.</t>
-        </is>
-      </c>
-      <c r="I5" s="48" t="inlineStr">
-        <is>
-          <t>PASS: state فعلی حفظ. FAIL: تغییر خودبه‌خود.</t>
-        </is>
-      </c>
-      <c r="J5" s="51" t="inlineStr"/>
-      <c r="K5" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L5" s="53" t="inlineStr"/>
-      <c r="M5" s="48" t="inlineStr"/>
-      <c r="N5" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O5" s="50" t="inlineStr"/>
-      <c r="P5" s="50" t="inlineStr"/>
-      <c r="Q5" s="54">
-        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+      <c r="Q5" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
-        <is>
-          <t>CO-002</t>
-        </is>
-      </c>
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>Snapshot نامعتبر / تایمر reset</t>
-        </is>
-      </c>
-      <c r="C6" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D6" s="55" t="inlineStr">
-        <is>
-          <t>BATTERY با شرط قطع نیمه‌کاره</t>
-        </is>
-      </c>
-      <c r="E6" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در وضعیت BATTERY باشد.
-گام ۲: دو ثانیه شرط قطع را اعمال کن: snapshot معتبر با v=20900 و flag=true.
-گام ۳: بعد یک ثانیه snapshot نامعتبر بده (valid=false).
-گام ۴: دوباره دو ثانیه شرط قطع را اعمال کن و PB11 را زیر نظر بگیر.
-گام ۵: PB11 نباید قطع شود؛ آن یک ثانیهٔ نامعتبر تایمر 3 ثانیه‌ای را از نو شروع می‌کند، پس در هیچ‌کدام از دو بازهٔ 2 ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F6" s="57" t="inlineStr">
-        <is>
-          <t>valid true 2s → false 1s → true 2s, v20900 flag true</t>
-        </is>
-      </c>
-      <c r="G6" s="57" t="inlineStr">
-        <is>
-          <t>2+1+2s</t>
-        </is>
-      </c>
-      <c r="H6" s="55" t="inlineStr">
-        <is>
-          <t>PB11 نباید پس از 2s اول قطع شود؛ پس از 1s invalid، تایمر reset و 2s بعدی هم هنوز قطع نشود (نیاز به 3s پیوسته). PASS: invalid تایمر را reset. FAIL: قطع زود در 2s.</t>
-        </is>
-      </c>
-      <c r="I6" s="55" t="inlineStr">
-        <is>
-          <t>PASS: reset پس از invalid. FAIL: قطع زود.</t>
-        </is>
-      </c>
-      <c r="J6" s="55" t="inlineStr"/>
-      <c r="K6" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L6" s="58" t="inlineStr"/>
-      <c r="M6" s="55" t="inlineStr"/>
-      <c r="N6" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O6" s="57" t="inlineStr"/>
-      <c r="P6" s="57" t="inlineStr"/>
-      <c r="Q6" s="59">
-        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+      <c r="Q6" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>CO-003</t>
-        </is>
-      </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>Snapshot نامعتبر + Fault</t>
-        </is>
-      </c>
-      <c r="C7" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="48" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="E7" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در وضعیت BATTERY باشد.
-گام ۲: snapshot نامعتبر با fault=FAULT_ADC (مقدار 1) و v=25000 اعمال کن.
-گام ۳: 500 میلی‌ثانیه صبر کن.
-گام ۴: وضعیت نباید FAULT شود و PB11 نباید تغییر کند؛ fault همراه snapshot نامعتبر شمرده نمی‌شود و تایمر قطع هم reset می‌شود.</t>
-        </is>
-      </c>
-      <c r="F7" s="50" t="inlineStr">
-        <is>
-          <t>valid=false, fault=1 (ADC), v25000</t>
-        </is>
-      </c>
-      <c r="G7" s="50" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H7" s="48" t="inlineStr">
-        <is>
-          <t>state حفظ شود (نه FAULT)، PB11 حفظ، تایمر reset. PASS: fault همراه invalid نباید FAULT شود. FAIL: FAULT شدن.</t>
-        </is>
-      </c>
-      <c r="I7" s="48" t="inlineStr">
-        <is>
-          <t>PASS: حفظ state قبلی. FAIL: FAULT.</t>
-        </is>
-      </c>
-      <c r="J7" s="51" t="inlineStr"/>
-      <c r="K7" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L7" s="53" t="inlineStr"/>
-      <c r="M7" s="48" t="inlineStr"/>
-      <c r="N7" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O7" s="50" t="inlineStr"/>
-      <c r="P7" s="50" t="inlineStr"/>
-      <c r="Q7" s="54">
-        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+      <c r="Q7" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
-        <is>
-          <t>CO-004</t>
-        </is>
-      </c>
-      <c r="B8" s="55" t="inlineStr">
-        <is>
-          <t>Fault با snapshot معتبر</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="55" t="inlineStr">
-        <is>
-          <t>INPUT/BATTERY</t>
-        </is>
-      </c>
-      <c r="E8" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در وضعیت INPUT یا BATTERY باشد.
-گام ۲: snapshot معتبر با v=24000، input=true و fault=FAULT_ADC (مقدار 1) اعمال کن.
-گام ۳: 500 میلی‌ثانیه صبر کن.
-گام ۴: وضعیت باید FAULT شود ولی PB11 دقیقاً همان قبلی بماند (از High به Low نرود) و تایمر قطع reset شود.</t>
-        </is>
-      </c>
-      <c r="F8" s="57" t="inlineStr">
-        <is>
-          <t>valid=true, v24000, input true, fault 1</t>
-        </is>
-      </c>
-      <c r="G8" s="57" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H8" s="55" t="inlineStr">
-        <is>
-          <t>state=FAULT، PB11 حفظ (بدون تغییر High→Low)، تایمر reset. PASS: FAULT بدون تغییر PB11. FAIL: تغییر PB11 یا ماندن در INPUT.</t>
-        </is>
-      </c>
-      <c r="I8" s="55" t="inlineStr">
-        <is>
-          <t>PASS: FAULT و PB11 حفظ. FAIL: تغییر PB11.</t>
-        </is>
-      </c>
-      <c r="J8" s="55" t="inlineStr"/>
-      <c r="K8" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L8" s="58" t="inlineStr"/>
-      <c r="M8" s="55" t="inlineStr"/>
-      <c r="N8" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O8" s="57" t="inlineStr"/>
-      <c r="P8" s="57" t="inlineStr"/>
-      <c r="Q8" s="59">
-        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>#'برنامه تست'!A12</t>
+        </is>
+      </c>
+      <c r="Q8" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>CO-005</t>
-        </is>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>Fault چند بیتی</t>
-        </is>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>FAULT قبلی</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد از قبل در وضعیت FAULT باشد.
-گام ۲: snapshot معتبر با fault برابر 63 (همهٔ بیت‌های خطا با هم) اعمال کن.
-گام ۳: 500 میلی‌ثانیه صبر کن و هر سه پایهٔ PB11 و PB5 و PB7 را چک کن.
-گام ۴: وضعیت باید FAULT بماند و هیچ‌کدام از سه پایه نباید تغییر کرده باشند.</t>
-        </is>
-      </c>
-      <c r="F9" s="50" t="inlineStr">
-        <is>
-          <t>valid true, fault ALL</t>
-        </is>
-      </c>
-      <c r="G9" s="50" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H9" s="48" t="inlineStr">
-        <is>
-          <t>state=FAULT، هیچ pin (PB11/PB5/PB7) تغییر نکند. PASS: همه fault‌ها → FAULT بدون pin. FAIL: هر تغییر pin.</t>
-        </is>
-      </c>
-      <c r="I9" s="48" t="inlineStr">
-        <is>
-          <t>PASS: همه fault → FAULT no pin. FAIL: pin change.</t>
-        </is>
-      </c>
-      <c r="J9" s="51" t="inlineStr"/>
-      <c r="K9" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L9" s="53" t="inlineStr"/>
-      <c r="M9" s="48" t="inlineStr"/>
-      <c r="N9" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O9" s="50" t="inlineStr"/>
-      <c r="P9" s="50" t="inlineStr"/>
-      <c r="Q9" s="54">
-        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+      <c r="Q9" s="63">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>CO-006</t>
-        </is>
-      </c>
-      <c r="B10" s="55" t="inlineStr">
-        <is>
-          <t>ورودی قطع → BATTERY</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="55" t="inlineStr">
-        <is>
-          <t>BOOT با snapshot معتبر</t>
-        </is>
-      </c>
-      <c r="E10" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BOOT با snapshot معتبر باشد.
-گام ۲: snapshot معتبر با v=24000، input=false (یعنی Vin حداکثر 20 ولت) و fault=0 اعمال کن.
-گام ۳: 500 میلی‌ثانیه صبر کن.
-گام ۴: وضعیت باید BATTERY شود و PB11 باید High و امن (متصل) باشد؛ رفتن به INPUT یا SAFE یا FAULT یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F10" s="57" t="inlineStr">
-        <is>
-          <t>valid true, v24000, input false</t>
-        </is>
-      </c>
-      <c r="G10" s="57" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H10" s="55" t="inlineStr">
-        <is>
-          <t>state=BATTERY, PB11 High-safe (متصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
-        </is>
-      </c>
-      <c r="I10" s="55" t="inlineStr">
-        <is>
-          <t>PASS: BATTERY. FAIL: otherwise.</t>
-        </is>
-      </c>
-      <c r="J10" s="55" t="inlineStr"/>
-      <c r="K10" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L10" s="58" t="inlineStr"/>
-      <c r="M10" s="55" t="inlineStr"/>
-      <c r="N10" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O10" s="57" t="inlineStr"/>
-      <c r="P10" s="57" t="inlineStr"/>
-      <c r="Q10" s="59">
-        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+      <c r="Q10" s="63">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>CO-007</t>
-        </is>
-      </c>
-      <c r="B11" s="48" t="inlineStr">
-        <is>
-          <t>ورودی حاضر → INPUT</t>
-        </is>
-      </c>
-      <c r="C11" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>BOOT/BATTERY</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BOOT یا BATTERY باشد.
-گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
-گام ۳: 500 میلی‌ثانیه صبر کن.
-گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
-        </is>
-      </c>
-      <c r="F11" s="50" t="inlineStr">
-        <is>
-          <t>valid true, v24000, input true</t>
-        </is>
-      </c>
-      <c r="G11" s="50" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H11" s="48" t="inlineStr">
-        <is>
-          <t>state=INPUT, PB11 High-safe. PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
-        </is>
-      </c>
-      <c r="I11" s="48" t="inlineStr">
-        <is>
-          <t>PASS: INPUT. FAIL: otherwise.</t>
-        </is>
-      </c>
-      <c r="J11" s="51" t="inlineStr"/>
-      <c r="K11" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L11" s="53" t="inlineStr"/>
-      <c r="M11" s="48" t="inlineStr"/>
-      <c r="N11" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O11" s="50" t="inlineStr"/>
-      <c r="P11" s="50" t="inlineStr"/>
-      <c r="Q11" s="54">
-        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+      <c r="Q11" s="63">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t>CO-008</t>
-        </is>
-      </c>
-      <c r="B12" s="55" t="inlineStr">
-        <is>
-          <t>قطع با گیت / 21000 + flag</t>
-        </is>
-      </c>
-      <c r="C12" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D12" s="55" t="inlineStr">
-        <is>
-          <t>BATTERY/INPUT, PB11 High</t>
-        </is>
-      </c>
-      <c r="E12" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
-گام ۲: snapshot معتبر با v=20900 (کمتر از 21000)، flag=true و input=false اعمال کن.
-گام ۳: این شرط را 3500 میلی‌ثانیه پیوسته نگه دار و ساعت بگیر.
-گام ۴: در 2500 میلی‌ثانیه اول باید هنوز BATTERY/INPUT و PB11 وصل باشد؛ فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت SAFE شود. قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F12" s="57" t="inlineStr">
-        <is>
-          <t>v20900 (&lt;21000) flag true</t>
-        </is>
-      </c>
-      <c r="G12" s="57" t="inlineStr">
-        <is>
-          <t>3500ms (≥3000)</t>
-        </is>
-      </c>
-      <c r="H12" s="55" t="inlineStr">
-        <is>
-          <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 High؛ پس از 3000ms PB11 Low (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
-        </is>
-      </c>
-      <c r="I12" s="55" t="inlineStr">
-        <is>
-          <t>PASS: 2500 still no cut, 3000 SAFE. FAIL: early or no cut.</t>
-        </is>
-      </c>
-      <c r="J12" s="55" t="inlineStr"/>
-      <c r="K12" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L12" s="58" t="inlineStr"/>
-      <c r="M12" s="55" t="inlineStr"/>
-      <c r="N12" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O12" s="57" t="inlineStr"/>
-      <c r="P12" s="57" t="inlineStr"/>
-      <c r="Q12" s="59">
-        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+      <c r="Q12" s="63">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>CO-009</t>
-        </is>
-      </c>
-      <c r="B13" s="48" t="inlineStr">
-        <is>
-          <t>قطع مستقل / 20800</t>
-        </is>
-      </c>
-      <c r="C13" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>BATTERY, flag false</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BATTERY و flag=false باشد.
-گام ۲: snapshot معتبر با v=20700 (کمتر از 20800)، flag=false و input=false اعمال کن.
-گام ۳: 3500 میلی‌ثانیه پیوسته نگه دار.
-گام ۴: بعد از 3000 میلی‌ثانیه باید SAFE با PB11 قطع شود؛ این قطع به flag ربطی ندارد و با flag=false هم باید اتفاق بیفتد.</t>
-        </is>
-      </c>
-      <c r="F13" s="50" t="inlineStr">
-        <is>
-          <t>v20700 (&lt;20800) flag false</t>
-        </is>
-      </c>
-      <c r="G13" s="50" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>پس از 3000ms SAFE با PB11 Low مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
-        </is>
-      </c>
-      <c r="I13" s="48" t="inlineStr">
-        <is>
-          <t>PASS: independent cut. FAIL: no cut due flag.</t>
-        </is>
-      </c>
-      <c r="J13" s="51" t="inlineStr"/>
-      <c r="K13" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L13" s="53" t="inlineStr"/>
-      <c r="M13" s="48" t="inlineStr"/>
-      <c r="N13" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O13" s="50" t="inlineStr"/>
-      <c r="P13" s="50" t="inlineStr"/>
-      <c r="Q13" s="54">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+      <c r="Q13" s="63">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>CO-010</t>
-        </is>
-      </c>
-      <c r="B14" s="55" t="inlineStr">
-        <is>
-          <t>مرز دقیق 21000 نباید cut</t>
-        </is>
-      </c>
-      <c r="C14" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="55" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="E14" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BATTERY باشد.
-گام ۲: snapshot معتبر با v دقیقاً 21000 (مرز)، flag=true و input=true (Vin=24 ولت) اعمال کن.
-گام ۳: 3500 میلی‌ثانیه پایدار نگه دار.
-گام ۴: هیچ قطعی نباید رخ دهد (شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی»)؛ وضعیت باید INPUT شده باشد (چون ورودی حاضر است) و PB11 High و امن بماند.</t>
-        </is>
-      </c>
-      <c r="F14" s="57" t="inlineStr">
-        <is>
-          <t>valid=true, v=21000 (دقیق) flag=true, input=true (Vin≥21V)</t>
-        </is>
-      </c>
-      <c r="G14" s="57" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H14" s="55" t="inlineStr">
-        <is>
-          <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 High-safe بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
-        </is>
-      </c>
-      <c r="I14" s="55" t="inlineStr">
-        <is>
-          <t>PASS: با v=21000 و input true، state=INPUT و PB11 High. FAIL: هر cut یا BATTERY.</t>
-        </is>
-      </c>
-      <c r="J14" s="55" t="inlineStr"/>
-      <c r="K14" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L14" s="58" t="inlineStr"/>
-      <c r="M14" s="55" t="inlineStr"/>
-      <c r="N14" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O14" s="57" t="inlineStr"/>
-      <c r="P14" s="57" t="inlineStr"/>
-      <c r="Q14" s="59">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+      <c r="Q14" s="63">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t>CO-011</t>
-        </is>
-      </c>
-      <c r="B15" s="48" t="inlineStr">
-        <is>
-          <t>مرز دقیق 20800 نباید cut</t>
-        </is>
-      </c>
-      <c r="C15" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BATTERY باشد.
-گام ۲: snapshot معتبر با v دقیقاً 20800 و flag=false اعمال کن.
-گام ۳: 3500 میلی‌ثانیه نگه دار.
-گام ۴: هیچ قطعی نباید رخ دهد؛ قطع فقط برای «کمتر از 20800» است و روی خودِ مرز 20800 نباید اتفاق بیفتد.</t>
-        </is>
-      </c>
-      <c r="F15" s="50" t="inlineStr">
-        <is>
-          <t>v=20800 flag false</t>
-        </is>
-      </c>
-      <c r="G15" s="50" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>هیچ قطع نشود. PASS: need &lt;20800. FAIL: cut at exact.</t>
-        </is>
-      </c>
-      <c r="I15" s="48" t="inlineStr">
-        <is>
-          <t>PASS: 20800 no independent cut. FAIL: cut.</t>
-        </is>
-      </c>
-      <c r="J15" s="51" t="inlineStr"/>
-      <c r="K15" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L15" s="53" t="inlineStr"/>
-      <c r="M15" s="48" t="inlineStr"/>
-      <c r="N15" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O15" s="50" t="inlineStr"/>
-      <c r="P15" s="50" t="inlineStr"/>
-      <c r="Q15" s="54">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+      <c r="Q15" s="63">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>CO-012</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="inlineStr">
-        <is>
-          <t>قطع &lt;3000ms نباید</t>
-        </is>
-      </c>
-      <c r="C16" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="55" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="E16" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در BATTERY باشد.
-گام ۲: snapshot معتبر با v=20900، flag=true و input=true (Vin=24 ولت) بده.
-گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000) و بعد ولتاژ را به 24000 برگردان.
-گام ۴: تا 2500 میلی‌ثانیه باید هنوز INPUT و PB11 وصل باشد؛ SAFE شدن زودتر از 3000 میلی‌ثانیه یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F16" s="57" t="inlineStr">
-        <is>
-          <t>valid=true, v=20900 (&lt;21000) flag=true, input=true, فقط 2500ms (&lt;3000)</t>
-        </is>
-      </c>
-      <c r="G16" s="57" t="inlineStr">
-        <is>
-          <t>2500ms</t>
-        </is>
-      </c>
-      <c r="H16" s="55" t="inlineStr">
-        <is>
-          <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 High. PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
-        </is>
-      </c>
-      <c r="I16" s="55" t="inlineStr">
-        <is>
-          <t>PASS: 2500ms still INPUT (no cut). FAIL: early SAFE یا BATTERY.</t>
-        </is>
-      </c>
-      <c r="J16" s="55" t="inlineStr"/>
-      <c r="K16" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L16" s="58" t="inlineStr"/>
-      <c r="M16" s="55" t="inlineStr"/>
-      <c r="N16" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O16" s="57" t="inlineStr"/>
-      <c r="P16" s="57" t="inlineStr"/>
-      <c r="Q16" s="59">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+      <c r="Q16" s="63">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>CO-013</t>
-        </is>
-      </c>
-      <c r="B17" s="48" t="inlineStr">
-        <is>
-          <t>وصل مجدد / 21200 + input</t>
-        </is>
-      </c>
-      <c r="C17" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="48" t="inlineStr">
-        <is>
-          <t>SAFE, PB11 Low</t>
-        </is>
-      </c>
-      <c r="E17" s="60" t="inlineStr">
-        <is>
-          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
-گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
-گام ۳: 3500 میلی‌ثانیه نگه دار و PB11 را زیر نظر بگیر.
-گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F17" s="50" t="inlineStr">
-        <is>
-          <t>SAFE, input true, v21300</t>
-        </is>
-      </c>
-      <c r="G17" s="50" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
-        </is>
-      </c>
-      <c r="I17" s="48" t="inlineStr">
-        <is>
-          <t>PASS: قبل 3000 SAFE Low، بعد 3000 INPUT High. FAIL: early or no reconnect.</t>
-        </is>
-      </c>
-      <c r="J17" s="51" t="inlineStr"/>
-      <c r="K17" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L17" s="53" t="inlineStr"/>
-      <c r="M17" s="48" t="inlineStr"/>
-      <c r="N17" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O17" s="50" t="inlineStr"/>
-      <c r="P17" s="50" t="inlineStr"/>
-      <c r="Q17" s="54">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+      <c r="Q17" s="63">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="47" t="inlineStr">
-        <is>
-          <t>CO-014</t>
-        </is>
-      </c>
-      <c r="B18" s="55" t="inlineStr">
-        <is>
-          <t>مرز دقیق 21200 باید reconnect</t>
-        </is>
-      </c>
-      <c r="C18" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D18" s="55" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="E18" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در SAFE باشد.
-گام ۲: input=true و v دقیقاً 21200 اعمال کن (روی خودِ مرز).
-گام ۳: 3500 میلی‌ثانیه نگه دار.
-گام ۴: بعد از 3000 میلی‌ثانیه باید INPUT و PB11 وصل شده باشد؛ شرط وصل «دست‌کم 21200» است، پس روی مرز هم باید وصل شود.</t>
-        </is>
-      </c>
-      <c r="F18" s="57" t="inlineStr">
-        <is>
-          <t>v=21200 input true</t>
-        </is>
-      </c>
-      <c r="G18" s="57" t="inlineStr">
-        <is>
-          <t>3500ms</t>
-        </is>
-      </c>
-      <c r="H18" s="55" t="inlineStr">
-        <is>
-          <t>پس از 3000ms INPUT و PB11 High. PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
-        </is>
-      </c>
-      <c r="I18" s="55" t="inlineStr">
-        <is>
-          <t>PASS: 21200 reconnects (need ≥). FAIL: no.</t>
-        </is>
-      </c>
-      <c r="J18" s="55" t="inlineStr"/>
-      <c r="K18" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L18" s="58" t="inlineStr"/>
-      <c r="M18" s="55" t="inlineStr"/>
-      <c r="N18" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O18" s="57" t="inlineStr"/>
-      <c r="P18" s="57" t="inlineStr"/>
-      <c r="Q18" s="59">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+      <c r="Q18" s="63">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>CO-015</t>
-        </is>
-      </c>
-      <c r="B19" s="48" t="inlineStr">
-        <is>
-          <t>reconnect &lt;3000 نباید</t>
-        </is>
-      </c>
-      <c r="C19" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D19" s="48" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="E19" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در SAFE باشد.
-گام ۲: input=true و v=21300 اعمال کن.
-گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000).
-گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F19" s="50" t="inlineStr">
-        <is>
-          <t>v21300 input true</t>
-        </is>
-      </c>
-      <c r="G19" s="50" t="inlineStr">
-        <is>
-          <t>2500ms</t>
-        </is>
-      </c>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>هنوز SAFE و PB11 Low. PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
-        </is>
-      </c>
-      <c r="I19" s="48" t="inlineStr">
-        <is>
-          <t>PASS: 2500 still SAFE. FAIL: INPUT early.</t>
-        </is>
-      </c>
-      <c r="J19" s="51" t="inlineStr"/>
-      <c r="K19" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L19" s="53" t="inlineStr"/>
-      <c r="M19" s="48" t="inlineStr"/>
-      <c r="N19" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O19" s="50" t="inlineStr"/>
-      <c r="P19" s="50" t="inlineStr"/>
-      <c r="Q19" s="54">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+      <c r="Q19" s="63">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="40.5" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>CO-016</t>
-        </is>
-      </c>
-      <c r="B20" s="55" t="inlineStr">
-        <is>
-          <t>پس از reconnect state INPUT</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>پس از CO-013</t>
-        </is>
-      </c>
-      <c r="E20" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: تست CO-013 را انجام بده تا وصل مجدد موفق اتفاق بیفتد.
-گام ۲: بلافاصله (در حد 100 میلی‌ثانیه بعد) وضعیت را بخوان.
-گام ۳: وضعیت باید INPUT باشد؛ IDLE برای snapshot معتبر هرگز نباید دیده شود.</t>
-        </is>
-      </c>
-      <c r="F20" s="57" t="inlineStr">
-        <is>
-          <t>post-reconnect</t>
-        </is>
-      </c>
-      <c r="G20" s="57" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H20" s="55" t="inlineStr">
-        <is>
-          <t>state=INPUT باشد، نه IDLE (IDLE برای معتبر ممنوع). PASS: INPUT. FAIL: IDLE.</t>
-        </is>
-      </c>
-      <c r="I20" s="55" t="inlineStr">
-        <is>
-          <t>PASS: INPUT not IDLE. FAIL: IDLE.</t>
-        </is>
-      </c>
-      <c r="J20" s="55" t="inlineStr"/>
-      <c r="K20" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L20" s="58" t="inlineStr"/>
-      <c r="M20" s="55" t="inlineStr"/>
-      <c r="N20" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O20" s="57" t="inlineStr"/>
-      <c r="P20" s="57" t="inlineStr"/>
-      <c r="Q20" s="59">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+      <c r="Q20" s="63">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="40.5" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>CO-017</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>PB11 در invalid حفظ</t>
-        </is>
-      </c>
-      <c r="C21" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D21" s="48" t="inlineStr">
-        <is>
-          <t>INPUT با PB11 High</t>
-        </is>
-      </c>
-      <c r="E21" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را با snapshot معتبر و input=true به INPUT ببر و PB11 را چک کن که وصل (High) است.
-گام ۲: حالا valid=false کن و 500 میلی‌ثانیه صبر کن.
-گام ۳: PB11 را دوباره بخوان: باید بدون تغییر همان High مانده باشد.</t>
-        </is>
-      </c>
-      <c r="F21" s="50" t="inlineStr">
-        <is>
-          <t>valid true→false</t>
-        </is>
-      </c>
-      <c r="G21" s="50" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>PB11 Low-High بدون تغییر بماند (High). PASS: حفظ. FAIL: تغییر.</t>
-        </is>
-      </c>
-      <c r="I21" s="48" t="inlineStr">
-        <is>
-          <t>PASS: PB11 preserved in invalid. FAIL: change.</t>
-        </is>
-      </c>
-      <c r="J21" s="51" t="inlineStr"/>
-      <c r="K21" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L21" s="53" t="inlineStr"/>
-      <c r="M21" s="48" t="inlineStr"/>
-      <c r="N21" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O21" s="50" t="inlineStr"/>
-      <c r="P21" s="50" t="inlineStr"/>
-      <c r="Q21" s="54">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+      <c r="Q21" s="63">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t>CO-018</t>
-        </is>
-      </c>
-      <c r="B22" s="55" t="inlineStr">
-        <is>
-          <t>PB11 در fault حفظ</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D22" s="55" t="inlineStr">
-        <is>
-          <t>INPUT</t>
-        </is>
-      </c>
-      <c r="E22" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: برد در INPUT باشد.
-گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
-گام ۳: 500 میلی‌ثانیه صبر کن و PB11 را بخوان.
-گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F22" s="57" t="inlineStr">
-        <is>
-          <t>valid true fault1</t>
-        </is>
-      </c>
-      <c r="G22" s="57" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H22" s="55" t="inlineStr">
-        <is>
-          <t>PB11 حفظ (High). PASS. FAIL: Low شدن.</t>
-        </is>
-      </c>
-      <c r="I22" s="55" t="inlineStr">
-        <is>
-          <t>PASS: PB11 preserved in fault. FAIL: change.</t>
-        </is>
-      </c>
-      <c r="J22" s="55" t="inlineStr"/>
-      <c r="K22" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L22" s="58" t="inlineStr"/>
-      <c r="M22" s="55" t="inlineStr"/>
-      <c r="N22" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O22" s="57" t="inlineStr"/>
-      <c r="P22" s="57" t="inlineStr"/>
-      <c r="Q22" s="59">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+      <c r="Q22" s="63">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>CO-019</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>PB5 و PB7 هیچ‌گاه تغییر نکنند</t>
-        </is>
-      </c>
-      <c r="C23" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D23" s="48" t="inlineStr">
-        <is>
-          <t>هر حالت</t>
-        </is>
-      </c>
-      <c r="E23" s="60" t="inlineStr">
-        <is>
-          <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015 که انجام می‌دهی، علاوه بر PB11 دو پایهٔ PB5 (BAT_SWITCH) و PB7 (RELAY) را هم با اسیلوسکوپ یا لاگ BSP زیر نظر بگیر.
-گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
-گام ۳: PB5 باید همیشه High امن (active-low) و PB7 همیشه Low بماند؛ هر تغییر (toggle) روی این دو یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F23" s="50" t="inlineStr">
-        <is>
-          <t>تمام حالات</t>
-        </is>
-      </c>
-      <c r="G23" s="50" t="inlineStr">
-        <is>
-          <t>هر تست</t>
-        </is>
-      </c>
-      <c r="H23" s="48" t="inlineStr">
-        <is>
-          <t>PB5 و PB7 ثابت بمانند (PB5 High-safe active-low، PB7 Low). PASS: بدون تغییر. FAIL: هر toggle.</t>
-        </is>
-      </c>
-      <c r="I23" s="48" t="inlineStr">
-        <is>
-          <t>PASS: PB5/PB7 never change. FAIL: any toggle.</t>
-        </is>
-      </c>
-      <c r="J23" s="51" t="inlineStr"/>
-      <c r="K23" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L23" s="53" t="inlineStr"/>
-      <c r="M23" s="48" t="inlineStr"/>
-      <c r="N23" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O23" s="50" t="inlineStr"/>
-      <c r="P23" s="50" t="inlineStr"/>
-      <c r="Q23" s="54">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+      <c r="Q23" s="63">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="47" t="inlineStr">
-        <is>
-          <t>CO-024</t>
-        </is>
-      </c>
-      <c r="B24" s="55" t="inlineStr">
-        <is>
-          <t>وصل مجدد 30s پایداری ورودی</t>
-        </is>
-      </c>
-      <c r="C24" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D24" s="55" t="inlineStr">
-        <is>
-          <t>برد در SAFE پس از قطع، v_bat=24V</t>
-        </is>
-      </c>
-      <c r="E24" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
-گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
-گام ۳: بعد از آن 3 ثانیه ولتاژ را روی 21200 نگه دار (در مجموع 33 ثانیه).
-گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F24" s="57" t="inlineStr">
-        <is>
-          <t>input=true v=24000</t>
-        </is>
-      </c>
-      <c r="G24" s="57" t="inlineStr">
-        <is>
-          <t>33s</t>
-        </is>
-      </c>
-      <c r="H24" s="55" t="inlineStr">
-        <is>
-          <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
-        </is>
-      </c>
-      <c r="I24" s="55" t="inlineStr">
-        <is>
-          <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
-        </is>
-      </c>
-      <c r="J24" s="55" t="n"/>
-      <c r="K24" s="55" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="L24" s="58" t="n"/>
-      <c r="M24" s="55" t="n"/>
-      <c r="N24" s="55" t="inlineStr">
-        <is>
-          <t>thermal+30s</t>
-        </is>
-      </c>
-      <c r="O24" s="57" t="n"/>
-      <c r="P24" s="57" t="n"/>
-      <c r="Q24" s="59">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+      <c r="Q24" s="63">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
       <c r="Q25" s="63">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="Q26" s="63">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="Q27" s="63">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>#'برنامه تست'!A12</t>
-        </is>
-      </c>
       <c r="Q28" s="63">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="63">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="63">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="63">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="63">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="63">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="63">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="63">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="63">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="63">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="63">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="63">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="63">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="63">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="63">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="63">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="63">
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="47" t="inlineStr">
+        <is>
+          <t>CO-025</t>
+        </is>
+      </c>
+      <c r="B45" s="48" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C45" s="50" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D45" s="48" t="inlineStr">
+        <is>
+          <t>دستگاه روشن، باتری وصل و یک بار (مثلاً لامپ) روی خروجی</t>
+        </is>
+      </c>
+      <c r="E45" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه را فقط با باتری روشن کن و مطمئن شو بار روشن است.
+گام ۲: ولتاژ باتری را با منبع آزمایشگاهی آرام پایین بیاور تا زیر 21 ولت برسد.
+گام ۳: چند ثانیه صبر کن و بار را نگاه کن.
+گام ۴: بار باید خاموش شود (خروجی قطع شود)؛ تا وقتی باتری بالای 21 ولت است بار نباید قطع شود.</t>
+        </is>
+      </c>
+      <c r="F45" s="48" t="inlineStr">
+        <is>
+          <t>باتری از 24 ولت تا زیر 21 ولت</t>
+        </is>
+      </c>
+      <c r="G45" s="50" t="inlineStr">
+        <is>
+          <t>چند ثانیه</t>
+        </is>
+      </c>
+      <c r="H45" s="48" t="inlineStr">
+        <is>
+          <t>با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود</t>
+        </is>
+      </c>
+      <c r="I45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="48" t="inlineStr">
+        <is>
+          <t>بار قطع شود؛ قطع زودهنگام وقتی باتری هنوز بالای حد است = رد</t>
+        </is>
+      </c>
+      <c r="K45" s="48" t="inlineStr"/>
+      <c r="L45" s="80" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M45" s="48" t="n"/>
+      <c r="N45" s="48" t="n"/>
+      <c r="O45" s="50" t="n"/>
+      <c r="P45" s="50" t="n"/>
+      <c r="Q45" s="54">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="47" t="inlineStr">
+        <is>
+          <t>CO-026</t>
+        </is>
+      </c>
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C46" s="57" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D46" s="61" t="inlineStr">
+        <is>
+          <t>پایان CO-025 (خروجی قطع است)</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: از پایان CO-025 شروع کن که خروجی قطع و بار خاموش است.
+گام ۲: برق شهر (ورودی) را وصل کن و ولتاژ باتری را به بالای 21.2 ولت برگردان (با شارژ یا منبع).
+گام ۳: چند ثانیه صبر کن.
+گام ۴: بار باید دوباره روشن شود؛ اگر ولتاژ باتری هنوز پایین است نباید وصل شود.</t>
+        </is>
+      </c>
+      <c r="F46" s="55" t="inlineStr">
+        <is>
+          <t>ورودی حاضر + باتری بالای 21.2 ولت</t>
+        </is>
+      </c>
+      <c r="G46" s="57" t="inlineStr">
+        <is>
+          <t>چند ثانیه</t>
+        </is>
+      </c>
+      <c r="H46" s="55" t="inlineStr">
+        <is>
+          <t>خروجی وصل و بار روشن می‌شود</t>
+        </is>
+      </c>
+      <c r="I46" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="55" t="inlineStr">
+        <is>
+          <t>بار دوباره روشن شود؛ وصل شدن با باتری پایین = رد</t>
+        </is>
+      </c>
+      <c r="K46" s="55" t="inlineStr"/>
+      <c r="L46" s="80" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="57" t="n"/>
+      <c r="P46" s="57" t="n"/>
+      <c r="Q46" s="59">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="47" t="inlineStr">
+        <is>
+          <t>CO-027</t>
+        </is>
+      </c>
+      <c r="B47" s="48" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C47" s="50" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D47" s="48" t="inlineStr">
+        <is>
+          <t>دستگاه با برق شهر و باتری وصل، بار روشن</t>
+        </is>
+      </c>
+      <c r="E47" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه را با برق شهر و باتری روشن کن و بار را روشن ببین.
+گام ۲: برق شهر را بکش؛ دستگاه نباید خاموش شود و بار باید بی‌وقفه روشن بماند (کار روی باتری).
+گام ۳: برق شهر را برگردان؛ دستگاه باید به حالت عادی برگردد و شارژ از سر گرفته شود.
+گام ۴: در هیچ‌کدام از این دو جابه‌جایی نباید دستگاه در وضعیت خطا گیر کند.</t>
+        </is>
+      </c>
+      <c r="F47" s="48" t="inlineStr">
+        <is>
+          <t>قطع و وصل برق شهر</t>
+        </is>
+      </c>
+      <c r="G47" s="50" t="inlineStr">
+        <is>
+          <t>چند ثانیه</t>
+        </is>
+      </c>
+      <c r="H47" s="48" t="inlineStr">
+        <is>
+          <t>ادامهٔ بی‌وقفهٔ کار بار و برگشت عادی</t>
+        </is>
+      </c>
+      <c r="I47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="48" t="inlineStr">
+        <is>
+          <t>بار هرگز خاموش نشود و دستگاه بعد از برگشت شهر عادی کار کند</t>
+        </is>
+      </c>
+      <c r="K47" s="48" t="inlineStr"/>
+      <c r="L47" s="80" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M47" s="48" t="n"/>
+      <c r="N47" s="48" t="n"/>
+      <c r="O47" s="50" t="n"/>
+      <c r="P47" s="50" t="n"/>
+      <c r="Q47" s="54">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="54" customHeight="1">
+      <c r="A48" s="47" t="inlineStr">
+        <is>
+          <t>CO-028</t>
+        </is>
+      </c>
+      <c r="B48" s="55" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C48" s="57" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D48" s="55" t="inlineStr">
+        <is>
+          <t>دستگاه در حال کار عادی با بار روشن</t>
+        </is>
+      </c>
+      <c r="E48" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه در حال کار عادی باشد و بار روشن.
+گام ۲: یک خطای شارژر بساز (حین شارژ سیم باتری را قطع کن تا آلارم قطع باتری بیاید).
+گام ۳: چراغ و بوق خطا را ببین و هم‌زمان بار را نگاه کن.
+گام ۴: بار نباید قطع‌ووصل یا چشمک بزند؛ خروجی باید همان وضعیت قبل از خطا را نگه دارد.</t>
+        </is>
+      </c>
+      <c r="F48" s="55" t="inlineStr">
+        <is>
+          <t>خطای قطع باتری حین شارژ</t>
+        </is>
+      </c>
+      <c r="G48" s="57" t="inlineStr">
+        <is>
+          <t>چند ثانیه</t>
+        </is>
+      </c>
+      <c r="H48" s="55" t="inlineStr">
+        <is>
+          <t>آلارم خطا می‌آید ولی خروجی تکان نمی‌خورد</t>
+        </is>
+      </c>
+      <c r="I48" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="55" t="inlineStr">
+        <is>
+          <t>بار بدون هیچ تکانی روشن بماند</t>
+        </is>
+      </c>
+      <c r="K48" s="55" t="inlineStr"/>
+      <c r="L48" s="80" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="57" t="n"/>
+      <c r="P48" s="57" t="n"/>
+      <c r="Q48" s="59">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="Q45" s="63">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="Q46" s="63">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="Q47" s="63">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="Q48" s="63">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="Q49" s="63">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="Q50" s="63">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="Q51" s="63">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="Q52" s="63">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="Q53" s="63">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="Q54" s="63">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="Q55" s="63">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="Q56" s="63">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="Q57" s="63">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="Q58" s="63">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="Q59" s="63">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="Q60" s="63">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="Q61" s="63">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="Q62" s="63">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="Q63" s="63">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="Q64" s="63">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:Q64"/>
+  <autoFilter ref="A4:Q48"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="L5:L108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="L45 L46 L47 L48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E17" location="'برنامه تست'!A12"/>
-    <hyperlink ref="D20" location="'برنامه تست'!A17"/>
-    <hyperlink ref="E20" location="'برنامه تست'!A17"/>
-    <hyperlink ref="E23" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E24" location="'برنامه تست'!A12"/>
+    <hyperlink ref="D46" location="'برنامه تست'!A45"/>
+    <hyperlink ref="E46" location="'برنامه تست'!A45"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3152,6 +2061,1650 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>شناسه تست</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>ورودی‌ها</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="L4" s="37" t="inlineStr">
+        <is>
+          <t>شرح ایراد</t>
+        </is>
+      </c>
+      <c r="M4" s="37" t="inlineStr">
+        <is>
+          <t>مدرک تست</t>
+        </is>
+      </c>
+      <c r="N4" s="37" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>CO-001</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Snapshot نامعتبر / حفظ</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>Init → BOOT, PB11 High-safe</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد؛ PB11 باید High و امن باشد.
+گام ۲: یک snapshot نامعتبر اعمال کن: valid=false ولی v_bat=24000، input=false و fault=0.
+گام ۳: 500 میلی‌ثانیه صبر کن و وضعیت (state) و پایهٔ PB11 را بخوان.
+گام ۴: وضعیت قبلی (BOOT یا هر وضعیت قبلی) و PB11 باید بدون هیچ تغییری حفظ شده باشند؛ رفتن به FAULT یا IDLE یا تغییر PB11 یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
+        <is>
+          <t>valid=false, v=24000, input=false, flag false, fault0</t>
+        </is>
+      </c>
+      <c r="G5" s="50" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H5" s="48" t="inlineStr">
+        <is>
+          <t>state حفظ شود: «state فعلی حفظ شود» (BOOT/BATTERY/INPUT/SAFE قبلی) و PB11 حفظ (High-safe). PASS: state و PB11 بدون تغییر. FAIL: هر تغییر به FAULT یا IDLE یا تغییر PB11.</t>
+        </is>
+      </c>
+      <c r="I5" s="48" t="inlineStr">
+        <is>
+          <t>PASS: state فعلی حفظ. FAIL: تغییر خودبه‌خود.</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="n"/>
+      <c r="K5" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="53" t="n"/>
+      <c r="M5" s="48" t="n"/>
+      <c r="N5" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O5" s="50" t="n"/>
+      <c r="P5" s="50" t="n"/>
+      <c r="Q5" s="54">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="67.5" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>CO-002</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>Snapshot نامعتبر / تایمر reset</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>BATTERY با شرط قطع نیمه‌کاره</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در وضعیت BATTERY باشد.
+گام ۲: دو ثانیه شرط قطع را اعمال کن: snapshot معتبر با v=20900 و flag=true.
+گام ۳: بعد یک ثانیه snapshot نامعتبر بده (valid=false).
+گام ۴: دوباره دو ثانیه شرط قطع را اعمال کن و PB11 را زیر نظر بگیر.
+گام ۵: PB11 نباید قطع شود؛ آن یک ثانیهٔ نامعتبر تایمر 3 ثانیه‌ای را از نو شروع می‌کند، پس در هیچ‌کدام از دو بازهٔ 2 ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F6" s="57" t="inlineStr">
+        <is>
+          <t>valid true 2s → false 1s → true 2s, v20900 flag true</t>
+        </is>
+      </c>
+      <c r="G6" s="57" t="inlineStr">
+        <is>
+          <t>2+1+2s</t>
+        </is>
+      </c>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>PB11 نباید پس از 2s اول قطع شود؛ پس از 1s invalid، تایمر reset و 2s بعدی هم هنوز قطع نشود (نیاز به 3s پیوسته). PASS: invalid تایمر را reset. FAIL: قطع زود در 2s.</t>
+        </is>
+      </c>
+      <c r="I6" s="55" t="inlineStr">
+        <is>
+          <t>PASS: reset پس از invalid. FAIL: قطع زود.</t>
+        </is>
+      </c>
+      <c r="J6" s="55" t="n"/>
+      <c r="K6" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L6" s="58" t="n"/>
+      <c r="M6" s="55" t="n"/>
+      <c r="N6" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O6" s="57" t="n"/>
+      <c r="P6" s="57" t="n"/>
+      <c r="Q6" s="59">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>CO-003</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>Snapshot نامعتبر + Fault</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در وضعیت BATTERY باشد.
+گام ۲: snapshot نامعتبر با fault=FAULT_ADC (مقدار 1) و v=25000 اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت نباید FAULT شود و PB11 نباید تغییر کند؛ fault همراه snapshot نامعتبر شمرده نمی‌شود و تایمر قطع هم reset می‌شود.</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
+        <is>
+          <t>valid=false, fault=1 (ADC), v25000</t>
+        </is>
+      </c>
+      <c r="G7" s="50" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="inlineStr">
+        <is>
+          <t>state حفظ شود (نه FAULT)، PB11 حفظ، تایمر reset. PASS: fault همراه invalid نباید FAULT شود. FAIL: FAULT شدن.</t>
+        </is>
+      </c>
+      <c r="I7" s="48" t="inlineStr">
+        <is>
+          <t>PASS: حفظ state قبلی. FAIL: FAULT.</t>
+        </is>
+      </c>
+      <c r="J7" s="51" t="n"/>
+      <c r="K7" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L7" s="53" t="n"/>
+      <c r="M7" s="48" t="n"/>
+      <c r="N7" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O7" s="50" t="n"/>
+      <c r="P7" s="50" t="n"/>
+      <c r="Q7" s="54">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>CO-004</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>Fault با snapshot معتبر</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>INPUT/BATTERY</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در وضعیت INPUT یا BATTERY باشد.
+گام ۲: snapshot معتبر با v=24000، input=true و fault=FAULT_ADC (مقدار 1) اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت باید FAULT شود ولی PB11 دقیقاً همان قبلی بماند (از High به Low نرود) و تایمر قطع reset شود.</t>
+        </is>
+      </c>
+      <c r="F8" s="57" t="inlineStr">
+        <is>
+          <t>valid=true, v24000, input true, fault 1</t>
+        </is>
+      </c>
+      <c r="G8" s="57" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H8" s="55" t="inlineStr">
+        <is>
+          <t>state=FAULT، PB11 حفظ (بدون تغییر High→Low)، تایمر reset. PASS: FAULT بدون تغییر PB11. FAIL: تغییر PB11 یا ماندن در INPUT.</t>
+        </is>
+      </c>
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>PASS: FAULT و PB11 حفظ. FAIL: تغییر PB11.</t>
+        </is>
+      </c>
+      <c r="J8" s="55" t="n"/>
+      <c r="K8" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L8" s="58" t="n"/>
+      <c r="M8" s="55" t="n"/>
+      <c r="N8" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O8" s="57" t="n"/>
+      <c r="P8" s="57" t="n"/>
+      <c r="Q8" s="59">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>CO-005</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Fault چند بیتی</t>
+        </is>
+      </c>
+      <c r="C9" s="50" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>FAULT قبلی</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد از قبل در وضعیت FAULT باشد.
+گام ۲: snapshot معتبر با fault برابر 63 (همهٔ بیت‌های خطا با هم) اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن و هر سه پایهٔ PB11 و PB5 و PB7 را چک کن.
+گام ۴: وضعیت باید FAULT بماند و هیچ‌کدام از سه پایه نباید تغییر کرده باشند.</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
+        <is>
+          <t>valid true, fault ALL</t>
+        </is>
+      </c>
+      <c r="G9" s="50" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H9" s="48" t="inlineStr">
+        <is>
+          <t>state=FAULT، هیچ pin (PB11/PB5/PB7) تغییر نکند. PASS: همه fault‌ها → FAULT بدون pin. FAIL: هر تغییر pin.</t>
+        </is>
+      </c>
+      <c r="I9" s="48" t="inlineStr">
+        <is>
+          <t>PASS: همه fault → FAULT no pin. FAIL: pin change.</t>
+        </is>
+      </c>
+      <c r="J9" s="51" t="n"/>
+      <c r="K9" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L9" s="53" t="n"/>
+      <c r="M9" s="48" t="n"/>
+      <c r="N9" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O9" s="50" t="n"/>
+      <c r="P9" s="50" t="n"/>
+      <c r="Q9" s="54">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>CO-006</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>ورودی قطع → BATTERY</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>BOOT با snapshot معتبر</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BOOT با snapshot معتبر باشد.
+گام ۲: snapshot معتبر با v=24000، input=false (یعنی Vin حداکثر 20 ولت) و fault=0 اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت باید BATTERY شود و PB11 باید High و امن (متصل) باشد؛ رفتن به INPUT یا SAFE یا FAULT یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F10" s="57" t="inlineStr">
+        <is>
+          <t>valid true, v24000, input false</t>
+        </is>
+      </c>
+      <c r="G10" s="57" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H10" s="55" t="inlineStr">
+        <is>
+          <t>state=BATTERY, PB11 High-safe (متصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
+        </is>
+      </c>
+      <c r="I10" s="55" t="inlineStr">
+        <is>
+          <t>PASS: BATTERY. FAIL: otherwise.</t>
+        </is>
+      </c>
+      <c r="J10" s="55" t="n"/>
+      <c r="K10" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L10" s="58" t="n"/>
+      <c r="M10" s="55" t="n"/>
+      <c r="N10" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O10" s="57" t="n"/>
+      <c r="P10" s="57" t="n"/>
+      <c r="Q10" s="59">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>CO-007</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="inlineStr">
+        <is>
+          <t>ورودی حاضر → INPUT</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="inlineStr">
+        <is>
+          <t>BOOT/BATTERY</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BOOT یا BATTERY باشد.
+گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
+گام ۳: 500 میلی‌ثانیه صبر کن.
+گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
+        <is>
+          <t>valid true, v24000, input true</t>
+        </is>
+      </c>
+      <c r="G11" s="50" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H11" s="48" t="inlineStr">
+        <is>
+          <t>state=INPUT, PB11 High-safe. PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
+        </is>
+      </c>
+      <c r="I11" s="48" t="inlineStr">
+        <is>
+          <t>PASS: INPUT. FAIL: otherwise.</t>
+        </is>
+      </c>
+      <c r="J11" s="51" t="n"/>
+      <c r="K11" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L11" s="53" t="n"/>
+      <c r="M11" s="48" t="n"/>
+      <c r="N11" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O11" s="50" t="n"/>
+      <c r="P11" s="50" t="n"/>
+      <c r="Q11" s="54">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>CO-008</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>قطع با گیت / 21000 + flag</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>BATTERY/INPUT, PB11 High</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
+گام ۲: snapshot معتبر با v=20900 (کمتر از 21000)، flag=true و input=false اعمال کن.
+گام ۳: این شرط را 3500 میلی‌ثانیه پیوسته نگه دار و ساعت بگیر.
+گام ۴: در 2500 میلی‌ثانیه اول باید هنوز BATTERY/INPUT و PB11 وصل باشد؛ فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت SAFE شود. قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F12" s="57" t="inlineStr">
+        <is>
+          <t>v20900 (&lt;21000) flag true</t>
+        </is>
+      </c>
+      <c r="G12" s="57" t="inlineStr">
+        <is>
+          <t>3500ms (≥3000)</t>
+        </is>
+      </c>
+      <c r="H12" s="55" t="inlineStr">
+        <is>
+          <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 High؛ پس از 3000ms PB11 Low (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
+        </is>
+      </c>
+      <c r="I12" s="55" t="inlineStr">
+        <is>
+          <t>PASS: 2500 still no cut, 3000 SAFE. FAIL: early or no cut.</t>
+        </is>
+      </c>
+      <c r="J12" s="55" t="n"/>
+      <c r="K12" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L12" s="58" t="n"/>
+      <c r="M12" s="55" t="n"/>
+      <c r="N12" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O12" s="57" t="n"/>
+      <c r="P12" s="57" t="n"/>
+      <c r="Q12" s="59">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>CO-009</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="inlineStr">
+        <is>
+          <t>قطع مستقل / 20800</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>BATTERY, flag false</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BATTERY و flag=false باشد.
+گام ۲: snapshot معتبر با v=20700 (کمتر از 20800)، flag=false و input=false اعمال کن.
+گام ۳: 3500 میلی‌ثانیه پیوسته نگه دار.
+گام ۴: بعد از 3000 میلی‌ثانیه باید SAFE با PB11 قطع شود؛ این قطع به flag ربطی ندارد و با flag=false هم باید اتفاق بیفتد.</t>
+        </is>
+      </c>
+      <c r="F13" s="50" t="inlineStr">
+        <is>
+          <t>v20700 (&lt;20800) flag false</t>
+        </is>
+      </c>
+      <c r="G13" s="50" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H13" s="48" t="inlineStr">
+        <is>
+          <t>پس از 3000ms SAFE با PB11 Low مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
+        </is>
+      </c>
+      <c r="I13" s="48" t="inlineStr">
+        <is>
+          <t>PASS: independent cut. FAIL: no cut due flag.</t>
+        </is>
+      </c>
+      <c r="J13" s="51" t="n"/>
+      <c r="K13" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L13" s="53" t="n"/>
+      <c r="M13" s="48" t="n"/>
+      <c r="N13" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O13" s="50" t="n"/>
+      <c r="P13" s="50" t="n"/>
+      <c r="Q13" s="54">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>CO-010</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>مرز دقیق 21000 نباید cut</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BATTERY باشد.
+گام ۲: snapshot معتبر با v دقیقاً 21000 (مرز)، flag=true و input=true (Vin=24 ولت) اعمال کن.
+گام ۳: 3500 میلی‌ثانیه پایدار نگه دار.
+گام ۴: هیچ قطعی نباید رخ دهد (شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی»)؛ وضعیت باید INPUT شده باشد (چون ورودی حاضر است) و PB11 High و امن بماند.</t>
+        </is>
+      </c>
+      <c r="F14" s="57" t="inlineStr">
+        <is>
+          <t>valid=true, v=21000 (دقیق) flag=true, input=true (Vin≥21V)</t>
+        </is>
+      </c>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H14" s="55" t="inlineStr">
+        <is>
+          <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 High-safe بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
+        </is>
+      </c>
+      <c r="I14" s="55" t="inlineStr">
+        <is>
+          <t>PASS: با v=21000 و input true، state=INPUT و PB11 High. FAIL: هر cut یا BATTERY.</t>
+        </is>
+      </c>
+      <c r="J14" s="55" t="n"/>
+      <c r="K14" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L14" s="58" t="n"/>
+      <c r="M14" s="55" t="n"/>
+      <c r="N14" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O14" s="57" t="n"/>
+      <c r="P14" s="57" t="n"/>
+      <c r="Q14" s="59">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>CO-011</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="inlineStr">
+        <is>
+          <t>مرز دقیق 20800 نباید cut</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BATTERY باشد.
+گام ۲: snapshot معتبر با v دقیقاً 20800 و flag=false اعمال کن.
+گام ۳: 3500 میلی‌ثانیه نگه دار.
+گام ۴: هیچ قطعی نباید رخ دهد؛ قطع فقط برای «کمتر از 20800» است و روی خودِ مرز 20800 نباید اتفاق بیفتد.</t>
+        </is>
+      </c>
+      <c r="F15" s="50" t="inlineStr">
+        <is>
+          <t>v=20800 flag false</t>
+        </is>
+      </c>
+      <c r="G15" s="50" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H15" s="48" t="inlineStr">
+        <is>
+          <t>هیچ قطع نشود. PASS: need &lt;20800. FAIL: cut at exact.</t>
+        </is>
+      </c>
+      <c r="I15" s="48" t="inlineStr">
+        <is>
+          <t>PASS: 20800 no independent cut. FAIL: cut.</t>
+        </is>
+      </c>
+      <c r="J15" s="51" t="n"/>
+      <c r="K15" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L15" s="53" t="n"/>
+      <c r="M15" s="48" t="n"/>
+      <c r="N15" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O15" s="50" t="n"/>
+      <c r="P15" s="50" t="n"/>
+      <c r="Q15" s="54">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>CO-012</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>قطع &lt;3000ms نباید</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D16" s="55" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در BATTERY باشد.
+گام ۲: snapshot معتبر با v=20900، flag=true و input=true (Vin=24 ولت) بده.
+گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000) و بعد ولتاژ را به 24000 برگردان.
+گام ۴: تا 2500 میلی‌ثانیه باید هنوز INPUT و PB11 وصل باشد؛ SAFE شدن زودتر از 3000 میلی‌ثانیه یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F16" s="57" t="inlineStr">
+        <is>
+          <t>valid=true, v=20900 (&lt;21000) flag=true, input=true, فقط 2500ms (&lt;3000)</t>
+        </is>
+      </c>
+      <c r="G16" s="57" t="inlineStr">
+        <is>
+          <t>2500ms</t>
+        </is>
+      </c>
+      <c r="H16" s="55" t="inlineStr">
+        <is>
+          <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 High. PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
+        </is>
+      </c>
+      <c r="I16" s="55" t="inlineStr">
+        <is>
+          <t>PASS: 2500ms still INPUT (no cut). FAIL: early SAFE یا BATTERY.</t>
+        </is>
+      </c>
+      <c r="J16" s="55" t="n"/>
+      <c r="K16" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L16" s="58" t="n"/>
+      <c r="M16" s="55" t="n"/>
+      <c r="N16" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O16" s="57" t="n"/>
+      <c r="P16" s="57" t="n"/>
+      <c r="Q16" s="59">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>CO-013</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="inlineStr">
+        <is>
+          <t>وصل مجدد / 21200 + input</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>SAFE, PB11 Low</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
+گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
+گام ۳: 3500 میلی‌ثانیه نگه دار و PB11 را زیر نظر بگیر.
+گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F17" s="50" t="inlineStr">
+        <is>
+          <t>SAFE, input true, v21300</t>
+        </is>
+      </c>
+      <c r="G17" s="50" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H17" s="48" t="inlineStr">
+        <is>
+          <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
+        </is>
+      </c>
+      <c r="I17" s="48" t="inlineStr">
+        <is>
+          <t>PASS: قبل 3000 SAFE Low، بعد 3000 INPUT High. FAIL: early or no reconnect.</t>
+        </is>
+      </c>
+      <c r="J17" s="51" t="n"/>
+      <c r="K17" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L17" s="53" t="n"/>
+      <c r="M17" s="48" t="n"/>
+      <c r="N17" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="54">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>CO-014</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>مرز دقیق 21200 باید reconnect</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D18" s="55" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="E18" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در SAFE باشد.
+گام ۲: input=true و v دقیقاً 21200 اعمال کن (روی خودِ مرز).
+گام ۳: 3500 میلی‌ثانیه نگه دار.
+گام ۴: بعد از 3000 میلی‌ثانیه باید INPUT و PB11 وصل شده باشد؛ شرط وصل «دست‌کم 21200» است، پس روی مرز هم باید وصل شود.</t>
+        </is>
+      </c>
+      <c r="F18" s="57" t="inlineStr">
+        <is>
+          <t>v=21200 input true</t>
+        </is>
+      </c>
+      <c r="G18" s="57" t="inlineStr">
+        <is>
+          <t>3500ms</t>
+        </is>
+      </c>
+      <c r="H18" s="55" t="inlineStr">
+        <is>
+          <t>پس از 3000ms INPUT و PB11 High. PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
+        </is>
+      </c>
+      <c r="I18" s="55" t="inlineStr">
+        <is>
+          <t>PASS: 21200 reconnects (need ≥). FAIL: no.</t>
+        </is>
+      </c>
+      <c r="J18" s="55" t="n"/>
+      <c r="K18" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L18" s="58" t="n"/>
+      <c r="M18" s="55" t="n"/>
+      <c r="N18" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O18" s="57" t="n"/>
+      <c r="P18" s="57" t="n"/>
+      <c r="Q18" s="59">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>CO-015</t>
+        </is>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>reconnect &lt;3000 نباید</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D19" s="48" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="E19" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در SAFE باشد.
+گام ۲: input=true و v=21300 اعمال کن.
+گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000).
+گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F19" s="50" t="inlineStr">
+        <is>
+          <t>v21300 input true</t>
+        </is>
+      </c>
+      <c r="G19" s="50" t="inlineStr">
+        <is>
+          <t>2500ms</t>
+        </is>
+      </c>
+      <c r="H19" s="48" t="inlineStr">
+        <is>
+          <t>هنوز SAFE و PB11 Low. PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
+        </is>
+      </c>
+      <c r="I19" s="48" t="inlineStr">
+        <is>
+          <t>PASS: 2500 still SAFE. FAIL: INPUT early.</t>
+        </is>
+      </c>
+      <c r="J19" s="51" t="n"/>
+      <c r="K19" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L19" s="53" t="n"/>
+      <c r="M19" s="48" t="n"/>
+      <c r="N19" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O19" s="50" t="n"/>
+      <c r="P19" s="50" t="n"/>
+      <c r="Q19" s="54">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="40.5" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
+        <is>
+          <t>CO-016</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t>پس از reconnect state INPUT</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D20" s="61" t="inlineStr">
+        <is>
+          <t>پس از CO-013</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: تست CO-013 را انجام بده تا وصل مجدد موفق اتفاق بیفتد.
+گام ۲: بلافاصله (در حد 100 میلی‌ثانیه بعد) وضعیت را بخوان.
+گام ۳: وضعیت باید INPUT باشد؛ IDLE برای snapshot معتبر هرگز نباید دیده شود.</t>
+        </is>
+      </c>
+      <c r="F20" s="57" t="inlineStr">
+        <is>
+          <t>post-reconnect</t>
+        </is>
+      </c>
+      <c r="G20" s="57" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="H20" s="55" t="inlineStr">
+        <is>
+          <t>state=INPUT باشد، نه IDLE (IDLE برای معتبر ممنوع). PASS: INPUT. FAIL: IDLE.</t>
+        </is>
+      </c>
+      <c r="I20" s="55" t="inlineStr">
+        <is>
+          <t>PASS: INPUT not IDLE. FAIL: IDLE.</t>
+        </is>
+      </c>
+      <c r="J20" s="55" t="n"/>
+      <c r="K20" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L20" s="58" t="n"/>
+      <c r="M20" s="55" t="n"/>
+      <c r="N20" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O20" s="57" t="n"/>
+      <c r="P20" s="57" t="n"/>
+      <c r="Q20" s="59">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="40.5" customHeight="1">
+      <c r="A21" s="47" t="inlineStr">
+        <is>
+          <t>CO-017</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>PB11 در invalid حفظ</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>INPUT با PB11 High</t>
+        </is>
+      </c>
+      <c r="E21" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را با snapshot معتبر و input=true به INPUT ببر و PB11 را چک کن که وصل (High) است.
+گام ۲: حالا valid=false کن و 500 میلی‌ثانیه صبر کن.
+گام ۳: PB11 را دوباره بخوان: باید بدون تغییر همان High مانده باشد.</t>
+        </is>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
+        <is>
+          <t>valid true→false</t>
+        </is>
+      </c>
+      <c r="G21" s="50" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H21" s="48" t="inlineStr">
+        <is>
+          <t>PB11 Low-High بدون تغییر بماند (High). PASS: حفظ. FAIL: تغییر.</t>
+        </is>
+      </c>
+      <c r="I21" s="48" t="inlineStr">
+        <is>
+          <t>PASS: PB11 preserved in invalid. FAIL: change.</t>
+        </is>
+      </c>
+      <c r="J21" s="51" t="n"/>
+      <c r="K21" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L21" s="53" t="n"/>
+      <c r="M21" s="48" t="n"/>
+      <c r="N21" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O21" s="50" t="n"/>
+      <c r="P21" s="50" t="n"/>
+      <c r="Q21" s="54">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="inlineStr">
+        <is>
+          <t>CO-018</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>PB11 در fault حفظ</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D22" s="55" t="inlineStr">
+        <is>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="E22" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: برد در INPUT باشد.
+گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
+گام ۳: 500 میلی‌ثانیه صبر کن و PB11 را بخوان.
+گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F22" s="57" t="inlineStr">
+        <is>
+          <t>valid true fault1</t>
+        </is>
+      </c>
+      <c r="G22" s="57" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H22" s="55" t="inlineStr">
+        <is>
+          <t>PB11 حفظ (High). PASS. FAIL: Low شدن.</t>
+        </is>
+      </c>
+      <c r="I22" s="55" t="inlineStr">
+        <is>
+          <t>PASS: PB11 preserved in fault. FAIL: change.</t>
+        </is>
+      </c>
+      <c r="J22" s="55" t="n"/>
+      <c r="K22" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L22" s="58" t="n"/>
+      <c r="M22" s="55" t="n"/>
+      <c r="N22" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O22" s="57" t="n"/>
+      <c r="P22" s="57" t="n"/>
+      <c r="Q22" s="59">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="40.5" customHeight="1">
+      <c r="A23" s="47" t="inlineStr">
+        <is>
+          <t>CO-019</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>PB5 و PB7 هیچ‌گاه تغییر نکنند</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>هر حالت</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015 که انجام می‌دهی، علاوه بر PB11 دو پایهٔ PB5 (BAT_SWITCH) و PB7 (RELAY) را هم با اسیلوسکوپ یا لاگ BSP زیر نظر بگیر.
+گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
+گام ۳: PB5 باید همیشه High امن (active-low) و PB7 همیشه Low بماند؛ هر تغییر (toggle) روی این دو یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F23" s="50" t="inlineStr">
+        <is>
+          <t>تمام حالات</t>
+        </is>
+      </c>
+      <c r="G23" s="50" t="inlineStr">
+        <is>
+          <t>هر تست</t>
+        </is>
+      </c>
+      <c r="H23" s="48" t="inlineStr">
+        <is>
+          <t>PB5 و PB7 ثابت بمانند (PB5 High-safe active-low، PB7 Low). PASS: بدون تغییر. FAIL: هر toggle.</t>
+        </is>
+      </c>
+      <c r="I23" s="48" t="inlineStr">
+        <is>
+          <t>PASS: PB5/PB7 never change. FAIL: any toggle.</t>
+        </is>
+      </c>
+      <c r="J23" s="51" t="n"/>
+      <c r="K23" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L23" s="53" t="n"/>
+      <c r="M23" s="48" t="n"/>
+      <c r="N23" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O23" s="50" t="n"/>
+      <c r="P23" s="50" t="n"/>
+      <c r="Q23" s="54">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="inlineStr">
+        <is>
+          <t>CO-024</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>وصل مجدد 30s پایداری ورودی</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>برد در SAFE پس از قطع، v_bat=24V</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
+گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
+گام ۳: بعد از آن 3 ثانیه ولتاژ را روی 21200 نگه دار (در مجموع 33 ثانیه).
+گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
+        </is>
+      </c>
+      <c r="F24" s="57" t="inlineStr">
+        <is>
+          <t>input=true v=24000</t>
+        </is>
+      </c>
+      <c r="G24" s="57" t="inlineStr">
+        <is>
+          <t>33s</t>
+        </is>
+      </c>
+      <c r="H24" s="55" t="inlineStr">
+        <is>
+          <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
+        </is>
+      </c>
+      <c r="I24" s="55" t="inlineStr">
+        <is>
+          <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
+        </is>
+      </c>
+      <c r="J24" s="55" t="n"/>
+      <c r="K24" s="55" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="n"/>
+      <c r="M24" s="55" t="n"/>
+      <c r="N24" s="55" t="inlineStr">
+        <is>
+          <t>thermal+30s</t>
+        </is>
+      </c>
+      <c r="O24" s="57" t="n"/>
+      <c r="P24" s="57" t="n"/>
+      <c r="Q24" s="59">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="63">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="63">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="63">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="63">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="63">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="63">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="63">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="63">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="63">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="63">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="63">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="63">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="63">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="63">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q24"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E17" location="'تست‌های آزمایشگاهی'!A12"/>
+    <hyperlink ref="D20" location="'تست‌های آزمایشگاهی'!A17"/>
+    <hyperlink ref="E20" location="'تست‌های آزمایشگاهی'!A17"/>
+    <hyperlink ref="E23" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="E24" location="'تست‌های آزمایشگاهی'!A12"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3691,7 +4244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -4151,17 +4704,17 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
-    <hyperlink ref="F4" location="'برنامه تست'!A5"/>
-    <hyperlink ref="F5" location="'برنامه تست'!A8"/>
-    <hyperlink ref="F6" location="'برنامه تست'!A12"/>
-    <hyperlink ref="F7" location="'برنامه تست'!A13"/>
-    <hyperlink ref="F8" location="'برنامه تست'!A16"/>
-    <hyperlink ref="F9" location="'برنامه تست'!A17"/>
+    <hyperlink ref="F4" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="F5" location="'تست‌های آزمایشگاهی'!A8"/>
+    <hyperlink ref="F6" location="'تست‌های آزمایشگاهی'!A12"/>
+    <hyperlink ref="F7" location="'تست‌های آزمایشگاهی'!A13"/>
+    <hyperlink ref="F8" location="'تست‌های آزمایشگاهی'!A16"/>
+    <hyperlink ref="F9" location="'تست‌های آزمایشگاهی'!A17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId2"/>
-    <hyperlink ref="F10" location="'برنامه تست'!A20"/>
-    <hyperlink ref="F11" location="'برنامه تست'!A21"/>
+    <hyperlink ref="F10" location="'تست‌های آزمایشگاهی'!A20"/>
+    <hyperlink ref="F11" location="'تست‌های آزمایشگاهی'!A21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId3"/>
-    <hyperlink ref="F12" location="'برنامه تست'!A23"/>
+    <hyperlink ref="F12" location="'تست‌های آزمایشگاهی'!A23"/>
     <hyperlink ref="F13" location="'تست‌های برنامه‌نویسی'!A6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId4"/>
     <hyperlink ref="F14" location="'تست‌های برنامه‌نویسی'!A7"/>
@@ -4174,7 +4727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4453,7 +5006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -4959,7 +5512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -5175,7 +5728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -266,6 +266,100 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00C00000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="7"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -420,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -646,6 +740,137 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1036,317 +1261,614 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Changeover — منطق قطع/وصل باتری</t>
         </is>
       </c>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="82" t="n"/>
+      <c r="G1" s="82" t="n"/>
+      <c r="H1" s="82" t="n"/>
+      <c r="I1" s="82" t="n"/>
+      <c r="J1" s="82" t="n"/>
+      <c r="K1" s="82" t="n"/>
+      <c r="L1" s="82" t="n"/>
+      <c r="M1" s="82" t="n"/>
+      <c r="N1" s="82" t="n"/>
+      <c r="O1" s="82" t="n"/>
+      <c r="P1" s="82" t="n"/>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>ChangeOver | PB11 (BSP_GPIO_PROTECT_BATTERY) | آستانه‌ها: 21000/20800/21200 و فیلتر 3000ms | نسخه 2.1 — فقط PB11، زمان rtos_time</t>
         </is>
       </c>
+      <c r="B2" s="82" t="n"/>
+      <c r="C2" s="82" t="n"/>
+      <c r="D2" s="82" t="n"/>
+      <c r="E2" s="82" t="n"/>
+      <c r="F2" s="82" t="n"/>
+      <c r="G2" s="82" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="82" t="n"/>
+      <c r="J2" s="82" t="n"/>
+      <c r="K2" s="82" t="n"/>
+      <c r="L2" s="82" t="n"/>
+      <c r="M2" s="82" t="n"/>
+      <c r="N2" s="82" t="n"/>
+      <c r="O2" s="82" t="n"/>
+      <c r="P2" s="82" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8" t="n"/>
-      <c r="N3" s="8" t="n"/>
-      <c r="O3" s="8" t="n"/>
-      <c r="P3" s="9" t="n"/>
+      <c r="B3" s="85" t="n"/>
+      <c r="C3" s="85" t="n"/>
+      <c r="D3" s="85" t="n"/>
+      <c r="E3" s="85" t="n"/>
+      <c r="F3" s="85" t="n"/>
+      <c r="G3" s="85" t="n"/>
+      <c r="H3" s="85" t="n"/>
+      <c r="I3" s="85" t="n"/>
+      <c r="J3" s="85" t="n"/>
+      <c r="K3" s="85" t="n"/>
+      <c r="L3" s="85" t="n"/>
+      <c r="M3" s="85" t="n"/>
+      <c r="N3" s="85" t="n"/>
+      <c r="O3" s="85" t="n"/>
+      <c r="P3" s="86" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>این فایل برای اعتبارسنجی منطق Changeover تهیه شده است: بررسی snapshot.valid، fault_mask، input_present، v_bat24_mv، قفل داخلی باتری کم و تایمر 3000ms.</t>
         </is>
       </c>
+      <c r="B4" s="82" t="n"/>
+      <c r="C4" s="82" t="n"/>
+      <c r="D4" s="82" t="n"/>
+      <c r="E4" s="82" t="n"/>
+      <c r="F4" s="82" t="n"/>
+      <c r="G4" s="82" t="n"/>
+      <c r="H4" s="82" t="n"/>
+      <c r="I4" s="82" t="n"/>
+      <c r="J4" s="82" t="n"/>
+      <c r="K4" s="82" t="n"/>
+      <c r="L4" s="82" t="n"/>
+      <c r="M4" s="82" t="n"/>
+      <c r="N4" s="82" t="n"/>
+      <c r="O4" s="82" t="n"/>
+      <c r="P4" s="82" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار mV و ms و state/PB11 قابل اندازه‌گیری تعریف شده است.</t>
         </is>
       </c>
+      <c r="B5" s="82" t="n"/>
+      <c r="C5" s="82" t="n"/>
+      <c r="D5" s="82" t="n"/>
+      <c r="E5" s="82" t="n"/>
+      <c r="F5" s="82" t="n"/>
+      <c r="G5" s="82" t="n"/>
+      <c r="H5" s="82" t="n"/>
+      <c r="I5" s="82" t="n"/>
+      <c r="J5" s="82" t="n"/>
+      <c r="K5" s="82" t="n"/>
+      <c r="L5" s="82" t="n"/>
+      <c r="M5" s="82" t="n"/>
+      <c r="N5" s="82" t="n"/>
+      <c r="O5" s="82" t="n"/>
+      <c r="P5" s="82" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="87" t="inlineStr">
         <is>
           <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است. فقط یک Workbook برای Changeover باقی بماند.</t>
         </is>
       </c>
+      <c r="B6" s="82" t="n"/>
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="82" t="n"/>
+      <c r="F6" s="82" t="n"/>
+      <c r="G6" s="82" t="n"/>
+      <c r="H6" s="82" t="n"/>
+      <c r="I6" s="82" t="n"/>
+      <c r="J6" s="82" t="n"/>
+      <c r="K6" s="82" t="n"/>
+      <c r="L6" s="82" t="n"/>
+      <c r="M6" s="82" t="n"/>
+      <c r="N6" s="82" t="n"/>
+      <c r="O6" s="82" t="n"/>
+      <c r="P6" s="82" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>دامنه: فقط Changeover؛ Measurement برای snapshot، Fault برای fault_mask و UI برای فلگ</t>
         </is>
       </c>
+      <c r="B7" s="82" t="n"/>
+      <c r="C7" s="82" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="82" t="n"/>
+      <c r="F7" s="82" t="n"/>
+      <c r="G7" s="82" t="n"/>
+      <c r="H7" s="82" t="n"/>
+      <c r="I7" s="82" t="n"/>
+      <c r="J7" s="82" t="n"/>
+      <c r="K7" s="82" t="n"/>
+      <c r="L7" s="82" t="n"/>
+      <c r="M7" s="82" t="n"/>
+      <c r="N7" s="82" t="n"/>
+      <c r="O7" s="82" t="n"/>
+      <c r="P7" s="82" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="87" t="inlineStr">
         <is>
           <t>منطق (snapshot-first): اگر snapshot==NULL یا valid==false → هیچ تصمیمی، state حفظ، PB11 حفظ، تایمر reset، fault هم state را تغییر نمی‌دهد، زمان نامعتبر شمرده نشود.</t>
         </is>
       </c>
+      <c r="B8" s="82" t="n"/>
+      <c r="C8" s="82" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="82" t="n"/>
+      <c r="F8" s="82" t="n"/>
+      <c r="G8" s="82" t="n"/>
+      <c r="H8" s="82" t="n"/>
+      <c r="I8" s="82" t="n"/>
+      <c r="J8" s="82" t="n"/>
+      <c r="K8" s="82" t="n"/>
+      <c r="L8" s="82" t="n"/>
+      <c r="M8" s="82" t="n"/>
+      <c r="N8" s="82" t="n"/>
+      <c r="O8" s="82" t="n"/>
+      <c r="P8" s="82" t="n"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t>فقط وقتی snapshot معتبر و fault!=0 → state=FAULT بدون تغییر هیچ pin (PB11/PB5/PB7).</t>
         </is>
       </c>
+      <c r="B9" s="82" t="n"/>
+      <c r="C9" s="82" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="82" t="n"/>
+      <c r="F9" s="82" t="n"/>
+      <c r="G9" s="82" t="n"/>
+      <c r="H9" s="82" t="n"/>
+      <c r="I9" s="82" t="n"/>
+      <c r="J9" s="82" t="n"/>
+      <c r="K9" s="82" t="n"/>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
+      <c r="O9" s="82" t="n"/>
+      <c r="P9" s="82" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr">
         <is>
           <t>قطع با گیت: v_bat&lt;21000 و flag true به‌مدت پیوسته 3000ms → قطع (PB11 Low) → SAFE. قطع مستقل: v_bat&lt;20800 مستقل از فلگ 3000ms → SAFE.</t>
         </is>
       </c>
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="n"/>
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+      <c r="P10" s="82" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="87" t="inlineStr">
         <is>
           <t>وصل مجدد: input_present==true و v_bat≥21200 به‌مدت پیوسته 3000ms → وصل (PB11 High) → INPUT (هرگز IDLE).</t>
         </is>
       </c>
+      <c r="B11" s="82" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="82" t="n"/>
+      <c r="J11" s="82" t="n"/>
+      <c r="K11" s="82" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
+      <c r="O11" s="82" t="n"/>
+      <c r="P11" s="82" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>زمان فقط با func__Rtos_MillisecondsToTicks و osKernelGetTickCount؛ فرض tick=1ms ممنوع؛ durationTicks==0 → هیچ قطع/وصل فوری.</t>
         </is>
       </c>
+      <c r="B12" s="82" t="n"/>
+      <c r="C12" s="82" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="82" t="n"/>
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="82" t="n"/>
+      <c r="I12" s="82" t="n"/>
+      <c r="J12" s="82" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
+      <c r="N12" s="82" t="n"/>
+      <c r="O12" s="82" t="n"/>
+      <c r="P12" s="82" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>روش اجرای تست</t>
         </is>
       </c>
+      <c r="B13" s="82" t="n"/>
+      <c r="C13" s="82" t="n"/>
+      <c r="D13" s="82" t="n"/>
+      <c r="E13" s="82" t="n"/>
+      <c r="F13" s="82" t="n"/>
+      <c r="G13" s="82" t="n"/>
+      <c r="H13" s="82" t="n"/>
+      <c r="I13" s="82" t="n"/>
+      <c r="J13" s="82" t="n"/>
+      <c r="K13" s="82" t="n"/>
+      <c r="L13" s="82" t="n"/>
+      <c r="M13" s="82" t="n"/>
+      <c r="N13" s="82" t="n"/>
+      <c r="O13" s="82" t="n"/>
+      <c r="P13" s="82" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="87" t="inlineStr">
         <is>
           <t>۱) برد را با منبع آزمایشگاهی و رعایت ایمنی تغذیه کن؛ PB11 را با DMM/اسکوپ نسبت به GND اندازه بگیر (فعال Low). PB5/PB7 را هم هم‌زمان اسکوپ کن و مطمئن شو تغییری ندارند.</t>
         </is>
       </c>
+      <c r="B14" s="82" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
+      <c r="G14" s="82" t="n"/>
+      <c r="H14" s="82" t="n"/>
+      <c r="I14" s="82" t="n"/>
+      <c r="J14" s="82" t="n"/>
+      <c r="K14" s="82" t="n"/>
+      <c r="L14" s="82" t="n"/>
+      <c r="M14" s="82" t="n"/>
+      <c r="N14" s="82" t="n"/>
+      <c r="O14" s="82" t="n"/>
+      <c r="P14" s="82" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="87" t="inlineStr">
         <is>
           <t>۲) firmware موردنظر را پروگرام کن؛ commit و شناسه برد را در «تأیید نهایی» ثبت کن.</t>
         </is>
       </c>
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="82" t="n"/>
+      <c r="F15" s="82" t="n"/>
+      <c r="G15" s="82" t="n"/>
+      <c r="H15" s="82" t="n"/>
+      <c r="I15" s="82" t="n"/>
+      <c r="J15" s="82" t="n"/>
+      <c r="K15" s="82" t="n"/>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
+      <c r="N15" s="82" t="n"/>
+      <c r="O15" s="82" t="n"/>
+      <c r="P15" s="82" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="87" t="inlineStr">
         <is>
           <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present را ست کن؛ قفل داخلی باتری کم فقط با ولتاژ زیر ۲۱۰۰۰ میلی‌ولت بسته می‌شود (مستقیم ست نمی‌شود)؛ fault_mask را از Fault اعمال کن.</t>
         </is>
       </c>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="82" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="82" t="n"/>
+      <c r="F16" s="82" t="n"/>
+      <c r="G16" s="82" t="n"/>
+      <c r="H16" s="82" t="n"/>
+      <c r="I16" s="82" t="n"/>
+      <c r="J16" s="82" t="n"/>
+      <c r="K16" s="82" t="n"/>
+      <c r="L16" s="82" t="n"/>
+      <c r="M16" s="82" t="n"/>
+      <c r="N16" s="82" t="n"/>
+      <c r="O16" s="82" t="n"/>
+      <c r="P16" s="82" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t>۴) برای تست 3000ms: شرط را حداقل 3500ms پایدار نگه دار و سپس PB11 و state را بخوان؛ برای تست &lt;3000ms: پس از 2500ms بخوان و مطمئن شو هنوز تغییر نکرده.</t>
         </is>
       </c>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="82" t="n"/>
+      <c r="J17" s="82" t="n"/>
+      <c r="K17" s="82" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
+      <c r="O17" s="82" t="n"/>
+      <c r="P17" s="82" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="87" t="inlineStr">
         <is>
           <t>۵) برای snapshot نامعتبر: valid=false یا NULL تزریق کن و ببین state و PB11 حفظ می‌ماند (باید «state فعلی حفظ شود» نه IDLE ثابت).</t>
         </is>
       </c>
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
+      <c r="O18" s="82" t="n"/>
+      <c r="P18" s="82" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="87" t="inlineStr">
         <is>
           <t>۶) نتیجه واقعی را بنویس و در صورت رد، در «ثبت ایراد» ردیف بساز.</t>
         </is>
       </c>
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="82" t="n"/>
+      <c r="J19" s="82" t="n"/>
+      <c r="K19" s="82" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
+      <c r="O19" s="82" t="n"/>
+      <c r="P19" s="82" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="89" t="inlineStr">
         <is>
           <t>تاریخچه نسخه</t>
         </is>
       </c>
+      <c r="B20" s="82" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="82" t="n"/>
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="n"/>
+      <c r="K20" s="82" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
+      <c r="O20" s="82" t="n"/>
+      <c r="P20" s="82" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="90" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="90" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C21" s="41" t="inlineStr">
+      <c r="C21" s="90" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D21" s="41" t="inlineStr">
+      <c r="D21" s="90" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="85" t="n"/>
+      <c r="G21" s="85" t="n"/>
+      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="85" t="n"/>
+      <c r="J21" s="85" t="n"/>
+      <c r="K21" s="85" t="n"/>
+      <c r="L21" s="85" t="n"/>
+      <c r="M21" s="85" t="n"/>
+      <c r="N21" s="85" t="n"/>
+      <c r="O21" s="85" t="n"/>
+      <c r="P21" s="86" t="n"/>
     </row>
     <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="92" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="92" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>تکمیل ۲۲ تست مطابق لیست درخواستی، ستون‌های ۱۶گانه، PASS/FAIL per test، زمان rtos_time و duration0 guard</t>
         </is>
       </c>
-      <c r="D22" s="42" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
+      <c r="E22" s="93" t="n"/>
+      <c r="F22" s="85" t="n"/>
+      <c r="G22" s="85" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="86" t="n"/>
     </row>
     <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="92" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="92" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C23" s="42" t="inlineStr">
+      <c r="C23" s="92" t="inlineStr">
         <is>
           <t>snapshot-first با MillisecondsToTicks، نگاشت BATTERY/INPUT/SAFE/FAULT بدون IDLE</t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
+      <c r="D23" s="92" t="inlineStr">
         <is>
           <t>a4a5bf2</t>
         </is>
       </c>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8" t="n"/>
-      <c r="N23" s="8" t="n"/>
-      <c r="O23" s="8" t="n"/>
-      <c r="P23" s="9" t="n"/>
+      <c r="E23" s="93" t="n"/>
+      <c r="F23" s="85" t="n"/>
+      <c r="G23" s="85" t="n"/>
+      <c r="H23" s="85" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="85" t="n"/>
+      <c r="K23" s="85" t="n"/>
+      <c r="L23" s="85" t="n"/>
+      <c r="M23" s="85" t="n"/>
+      <c r="N23" s="85" t="n"/>
+      <c r="O23" s="85" t="n"/>
+      <c r="P23" s="86" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="92" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="92" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="92" t="inlineStr">
         <is>
           <t>پیاده‌سازی با 21 سناریو</t>
         </is>
       </c>
-      <c r="D24" s="42" t="inlineStr">
+      <c r="D24" s="92" t="inlineStr">
         <is>
           <t>d0adc6f</t>
         </is>
       </c>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="9" t="n"/>
+      <c r="E24" s="93" t="n"/>
+      <c r="F24" s="85" t="n"/>
+      <c r="G24" s="85" t="n"/>
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="86" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="94" t="inlineStr">
         <is>
           <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="D25" s="94" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
+      <c r="E25" s="82" t="n"/>
+      <c r="F25" s="82" t="n"/>
+      <c r="G25" s="82" t="n"/>
+      <c r="H25" s="82" t="n"/>
+      <c r="I25" s="82" t="n"/>
+      <c r="J25" s="82" t="n"/>
+      <c r="K25" s="82" t="n"/>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
+      <c r="N25" s="82" t="n"/>
+      <c r="O25" s="82" t="n"/>
+      <c r="P25" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1411,376 +1933,1063 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="95" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Changeover (قطع/وصل باتری با 3000ms)</t>
         </is>
       </c>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="82" t="n"/>
+      <c r="G1" s="82" t="n"/>
+      <c r="H1" s="82" t="n"/>
+      <c r="I1" s="82" t="n"/>
+      <c r="J1" s="82" t="n"/>
+      <c r="K1" s="82" t="n"/>
+      <c r="L1" s="82" t="n"/>
+      <c r="M1" s="82" t="n"/>
+      <c r="N1" s="82" t="n"/>
+      <c r="O1" s="82" t="n"/>
+      <c r="P1" s="82" t="n"/>
+      <c r="Q1" s="82" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="96" t="inlineStr">
         <is>
           <t>ورودی‌ها بر حسب mV؛ زمان‌ها بر حسب ms. PB11 فقط از BSP_GPIO_PROTECT_BATTERY (فعال Low) — PB5/PB7 ممنوع. ورودی‌ها: valid، v_bat، input_present، flag، fault.</t>
         </is>
       </c>
+      <c r="B2" s="82" t="n"/>
+      <c r="C2" s="82" t="n"/>
+      <c r="D2" s="82" t="n"/>
+      <c r="E2" s="82" t="n"/>
+      <c r="F2" s="82" t="n"/>
+      <c r="G2" s="82" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="82" t="n"/>
+      <c r="J2" s="82" t="n"/>
+      <c r="K2" s="82" t="n"/>
+      <c r="L2" s="82" t="n"/>
+      <c r="M2" s="82" t="n"/>
+      <c r="N2" s="82" t="n"/>
+      <c r="O2" s="82" t="n"/>
+      <c r="P2" s="82" t="n"/>
+      <c r="Q2" s="82" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="97" t="inlineStr">
         <is>
           <t>snapshot نامعتبر → «state فعلی حفظ شود» (نه IDLE ثابت). CO-010/012 باید INPUT باشد. معیار قبولی هر ردیف توضیح می‌دهد PASS چیست و FAIL چیست.</t>
         </is>
       </c>
+      <c r="B3" s="82" t="n"/>
+      <c r="C3" s="82" t="n"/>
+      <c r="D3" s="82" t="n"/>
+      <c r="E3" s="82" t="n"/>
+      <c r="F3" s="82" t="n"/>
+      <c r="G3" s="82" t="n"/>
+      <c r="H3" s="82" t="n"/>
+      <c r="I3" s="82" t="n"/>
+      <c r="J3" s="82" t="n"/>
+      <c r="K3" s="82" t="n"/>
+      <c r="L3" s="82" t="n"/>
+      <c r="M3" s="82" t="n"/>
+      <c r="N3" s="82" t="n"/>
+      <c r="O3" s="82" t="n"/>
+      <c r="P3" s="82" t="n"/>
+      <c r="Q3" s="82" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="84" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="84" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="84" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="84" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="84" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="84" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="84" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="84" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="84" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="84" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="84" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="84" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="n"/>
+      <c r="Q4" s="84" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="Q5" s="63">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="82" t="n"/>
+      <c r="C5" s="82" t="n"/>
+      <c r="D5" s="82" t="n"/>
+      <c r="E5" s="82" t="n"/>
+      <c r="F5" s="82" t="n"/>
+      <c r="G5" s="82" t="n"/>
+      <c r="H5" s="82" t="n"/>
+      <c r="I5" s="82" t="n"/>
+      <c r="J5" s="82" t="n"/>
+      <c r="K5" s="82" t="n"/>
+      <c r="L5" s="82" t="n"/>
+      <c r="M5" s="82" t="n"/>
+      <c r="N5" s="82" t="n"/>
+      <c r="O5" s="82" t="n"/>
+      <c r="P5" s="82" t="n"/>
+      <c r="Q5" s="98">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
-      <c r="Q6" s="63">
+      <c r="A6" s="82" t="n"/>
+      <c r="B6" s="82" t="n"/>
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="82" t="n"/>
+      <c r="F6" s="82" t="n"/>
+      <c r="G6" s="82" t="n"/>
+      <c r="H6" s="82" t="n"/>
+      <c r="I6" s="82" t="n"/>
+      <c r="J6" s="82" t="n"/>
+      <c r="K6" s="82" t="n"/>
+      <c r="L6" s="82" t="n"/>
+      <c r="M6" s="82" t="n"/>
+      <c r="N6" s="82" t="n"/>
+      <c r="O6" s="82" t="n"/>
+      <c r="P6" s="82" t="n"/>
+      <c r="Q6" s="98">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="Q7" s="63">
+      <c r="A7" s="82" t="n"/>
+      <c r="B7" s="82" t="n"/>
+      <c r="C7" s="82" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="82" t="n"/>
+      <c r="F7" s="82" t="n"/>
+      <c r="G7" s="82" t="n"/>
+      <c r="H7" s="82" t="n"/>
+      <c r="I7" s="82" t="n"/>
+      <c r="J7" s="82" t="n"/>
+      <c r="K7" s="82" t="n"/>
+      <c r="L7" s="82" t="n"/>
+      <c r="M7" s="82" t="n"/>
+      <c r="N7" s="82" t="n"/>
+      <c r="O7" s="82" t="n"/>
+      <c r="P7" s="82" t="n"/>
+      <c r="Q7" s="98">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="E8" t="inlineStr">
+      <c r="A8" s="82" t="n"/>
+      <c r="B8" s="82" t="n"/>
+      <c r="C8" s="82" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="82" t="inlineStr">
         <is>
           <t>#'برنامه تست'!A12</t>
         </is>
       </c>
-      <c r="Q8" s="63">
+      <c r="F8" s="82" t="n"/>
+      <c r="G8" s="82" t="n"/>
+      <c r="H8" s="82" t="n"/>
+      <c r="I8" s="82" t="n"/>
+      <c r="J8" s="82" t="n"/>
+      <c r="K8" s="82" t="n"/>
+      <c r="L8" s="82" t="n"/>
+      <c r="M8" s="82" t="n"/>
+      <c r="N8" s="82" t="n"/>
+      <c r="O8" s="82" t="n"/>
+      <c r="P8" s="82" t="n"/>
+      <c r="Q8" s="98">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="Q9" s="63">
+      <c r="A9" s="82" t="n"/>
+      <c r="B9" s="82" t="n"/>
+      <c r="C9" s="82" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="82" t="n"/>
+      <c r="F9" s="82" t="n"/>
+      <c r="G9" s="82" t="n"/>
+      <c r="H9" s="82" t="n"/>
+      <c r="I9" s="82" t="n"/>
+      <c r="J9" s="82" t="n"/>
+      <c r="K9" s="82" t="n"/>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
+      <c r="O9" s="82" t="n"/>
+      <c r="P9" s="82" t="n"/>
+      <c r="Q9" s="98">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="Q10" s="63">
+      <c r="A10" s="82" t="n"/>
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="n"/>
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+      <c r="P10" s="82" t="n"/>
+      <c r="Q10" s="98">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="Q11" s="63">
+      <c r="A11" s="82" t="n"/>
+      <c r="B11" s="82" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="82" t="n"/>
+      <c r="J11" s="82" t="n"/>
+      <c r="K11" s="82" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
+      <c r="O11" s="82" t="n"/>
+      <c r="P11" s="82" t="n"/>
+      <c r="Q11" s="98">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="Q12" s="63">
+      <c r="A12" s="82" t="n"/>
+      <c r="B12" s="82" t="n"/>
+      <c r="C12" s="82" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="82" t="n"/>
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="82" t="n"/>
+      <c r="I12" s="82" t="n"/>
+      <c r="J12" s="82" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
+      <c r="N12" s="82" t="n"/>
+      <c r="O12" s="82" t="n"/>
+      <c r="P12" s="82" t="n"/>
+      <c r="Q12" s="98">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="Q13" s="63">
+      <c r="A13" s="82" t="n"/>
+      <c r="B13" s="82" t="n"/>
+      <c r="C13" s="82" t="n"/>
+      <c r="D13" s="82" t="n"/>
+      <c r="E13" s="82" t="n"/>
+      <c r="F13" s="82" t="n"/>
+      <c r="G13" s="82" t="n"/>
+      <c r="H13" s="82" t="n"/>
+      <c r="I13" s="82" t="n"/>
+      <c r="J13" s="82" t="n"/>
+      <c r="K13" s="82" t="n"/>
+      <c r="L13" s="82" t="n"/>
+      <c r="M13" s="82" t="n"/>
+      <c r="N13" s="82" t="n"/>
+      <c r="O13" s="82" t="n"/>
+      <c r="P13" s="82" t="n"/>
+      <c r="Q13" s="98">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="Q14" s="63">
+      <c r="A14" s="82" t="n"/>
+      <c r="B14" s="82" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
+      <c r="G14" s="82" t="n"/>
+      <c r="H14" s="82" t="n"/>
+      <c r="I14" s="82" t="n"/>
+      <c r="J14" s="82" t="n"/>
+      <c r="K14" s="82" t="n"/>
+      <c r="L14" s="82" t="n"/>
+      <c r="M14" s="82" t="n"/>
+      <c r="N14" s="82" t="n"/>
+      <c r="O14" s="82" t="n"/>
+      <c r="P14" s="82" t="n"/>
+      <c r="Q14" s="98">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="Q15" s="63">
+      <c r="A15" s="82" t="n"/>
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="82" t="n"/>
+      <c r="F15" s="82" t="n"/>
+      <c r="G15" s="82" t="n"/>
+      <c r="H15" s="82" t="n"/>
+      <c r="I15" s="82" t="n"/>
+      <c r="J15" s="82" t="n"/>
+      <c r="K15" s="82" t="n"/>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
+      <c r="N15" s="82" t="n"/>
+      <c r="O15" s="82" t="n"/>
+      <c r="P15" s="82" t="n"/>
+      <c r="Q15" s="98">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="Q16" s="63">
+      <c r="A16" s="82" t="n"/>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="82" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="82" t="n"/>
+      <c r="F16" s="82" t="n"/>
+      <c r="G16" s="82" t="n"/>
+      <c r="H16" s="82" t="n"/>
+      <c r="I16" s="82" t="n"/>
+      <c r="J16" s="82" t="n"/>
+      <c r="K16" s="82" t="n"/>
+      <c r="L16" s="82" t="n"/>
+      <c r="M16" s="82" t="n"/>
+      <c r="N16" s="82" t="n"/>
+      <c r="O16" s="82" t="n"/>
+      <c r="P16" s="82" t="n"/>
+      <c r="Q16" s="98">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="Q17" s="63">
+      <c r="A17" s="82" t="n"/>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="82" t="n"/>
+      <c r="J17" s="82" t="n"/>
+      <c r="K17" s="82" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
+      <c r="O17" s="82" t="n"/>
+      <c r="P17" s="82" t="n"/>
+      <c r="Q17" s="98">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="Q18" s="63">
+      <c r="A18" s="82" t="n"/>
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
+      <c r="O18" s="82" t="n"/>
+      <c r="P18" s="82" t="n"/>
+      <c r="Q18" s="98">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="Q19" s="63">
+      <c r="A19" s="82" t="n"/>
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="82" t="n"/>
+      <c r="J19" s="82" t="n"/>
+      <c r="K19" s="82" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
+      <c r="O19" s="82" t="n"/>
+      <c r="P19" s="82" t="n"/>
+      <c r="Q19" s="98">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="40.5" customHeight="1">
-      <c r="Q20" s="63">
+      <c r="A20" s="82" t="n"/>
+      <c r="B20" s="82" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="82" t="n"/>
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="n"/>
+      <c r="K20" s="82" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
+      <c r="O20" s="82" t="n"/>
+      <c r="P20" s="82" t="n"/>
+      <c r="Q20" s="98">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="40.5" customHeight="1">
-      <c r="Q21" s="63">
+      <c r="A21" s="82" t="n"/>
+      <c r="B21" s="82" t="n"/>
+      <c r="C21" s="82" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="82" t="n"/>
+      <c r="F21" s="82" t="n"/>
+      <c r="G21" s="82" t="n"/>
+      <c r="H21" s="82" t="n"/>
+      <c r="I21" s="82" t="n"/>
+      <c r="J21" s="82" t="n"/>
+      <c r="K21" s="82" t="n"/>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
+      <c r="N21" s="82" t="n"/>
+      <c r="O21" s="82" t="n"/>
+      <c r="P21" s="82" t="n"/>
+      <c r="Q21" s="98">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="Q22" s="63">
+      <c r="A22" s="82" t="n"/>
+      <c r="B22" s="82" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="82" t="n"/>
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="82" t="n"/>
+      <c r="P22" s="82" t="n"/>
+      <c r="Q22" s="98">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="Q23" s="63">
+      <c r="A23" s="82" t="n"/>
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="82" t="n"/>
+      <c r="J23" s="82" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="82" t="n"/>
+      <c r="P23" s="82" t="n"/>
+      <c r="Q23" s="98">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="Q24" s="63">
+      <c r="A24" s="82" t="n"/>
+      <c r="B24" s="82" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="82" t="n"/>
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="82" t="n"/>
+      <c r="H24" s="82" t="n"/>
+      <c r="I24" s="82" t="n"/>
+      <c r="J24" s="82" t="n"/>
+      <c r="K24" s="82" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
+      <c r="O24" s="82" t="n"/>
+      <c r="P24" s="82" t="n"/>
+      <c r="Q24" s="98">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="Q25" s="63">
+      <c r="A25" s="82" t="n"/>
+      <c r="B25" s="82" t="n"/>
+      <c r="C25" s="82" t="n"/>
+      <c r="D25" s="82" t="n"/>
+      <c r="E25" s="82" t="n"/>
+      <c r="F25" s="82" t="n"/>
+      <c r="G25" s="82" t="n"/>
+      <c r="H25" s="82" t="n"/>
+      <c r="I25" s="82" t="n"/>
+      <c r="J25" s="82" t="n"/>
+      <c r="K25" s="82" t="n"/>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
+      <c r="N25" s="82" t="n"/>
+      <c r="O25" s="82" t="n"/>
+      <c r="P25" s="82" t="n"/>
+      <c r="Q25" s="98">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="Q26" s="63">
+      <c r="A26" s="82" t="n"/>
+      <c r="B26" s="82" t="n"/>
+      <c r="C26" s="82" t="n"/>
+      <c r="D26" s="82" t="n"/>
+      <c r="E26" s="82" t="n"/>
+      <c r="F26" s="82" t="n"/>
+      <c r="G26" s="82" t="n"/>
+      <c r="H26" s="82" t="n"/>
+      <c r="I26" s="82" t="n"/>
+      <c r="J26" s="82" t="n"/>
+      <c r="K26" s="82" t="n"/>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
+      <c r="N26" s="82" t="n"/>
+      <c r="O26" s="82" t="n"/>
+      <c r="P26" s="82" t="n"/>
+      <c r="Q26" s="98">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
-      <c r="Q27" s="63">
+      <c r="A27" s="82" t="n"/>
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="82" t="n"/>
+      <c r="D27" s="82" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
+      <c r="G27" s="82" t="n"/>
+      <c r="H27" s="82" t="n"/>
+      <c r="I27" s="82" t="n"/>
+      <c r="J27" s="82" t="n"/>
+      <c r="K27" s="82" t="n"/>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="82" t="n"/>
+      <c r="N27" s="82" t="n"/>
+      <c r="O27" s="82" t="n"/>
+      <c r="P27" s="82" t="n"/>
+      <c r="Q27" s="98">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
-      <c r="Q28" s="63">
+      <c r="A28" s="82" t="n"/>
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="82" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="82" t="n"/>
+      <c r="F28" s="82" t="n"/>
+      <c r="G28" s="82" t="n"/>
+      <c r="H28" s="82" t="n"/>
+      <c r="I28" s="82" t="n"/>
+      <c r="J28" s="82" t="n"/>
+      <c r="K28" s="82" t="n"/>
+      <c r="L28" s="82" t="n"/>
+      <c r="M28" s="82" t="n"/>
+      <c r="N28" s="82" t="n"/>
+      <c r="O28" s="82" t="n"/>
+      <c r="P28" s="82" t="n"/>
+      <c r="Q28" s="98">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="63">
+      <c r="A29" s="82" t="n"/>
+      <c r="B29" s="82" t="n"/>
+      <c r="C29" s="82" t="n"/>
+      <c r="D29" s="82" t="n"/>
+      <c r="E29" s="82" t="n"/>
+      <c r="F29" s="82" t="n"/>
+      <c r="G29" s="82" t="n"/>
+      <c r="H29" s="82" t="n"/>
+      <c r="I29" s="82" t="n"/>
+      <c r="J29" s="82" t="n"/>
+      <c r="K29" s="82" t="n"/>
+      <c r="L29" s="82" t="n"/>
+      <c r="M29" s="82" t="n"/>
+      <c r="N29" s="82" t="n"/>
+      <c r="O29" s="82" t="n"/>
+      <c r="P29" s="82" t="n"/>
+      <c r="Q29" s="98">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="63">
+      <c r="A30" s="82" t="n"/>
+      <c r="B30" s="82" t="n"/>
+      <c r="C30" s="82" t="n"/>
+      <c r="D30" s="82" t="n"/>
+      <c r="E30" s="82" t="n"/>
+      <c r="F30" s="82" t="n"/>
+      <c r="G30" s="82" t="n"/>
+      <c r="H30" s="82" t="n"/>
+      <c r="I30" s="82" t="n"/>
+      <c r="J30" s="82" t="n"/>
+      <c r="K30" s="82" t="n"/>
+      <c r="L30" s="82" t="n"/>
+      <c r="M30" s="82" t="n"/>
+      <c r="N30" s="82" t="n"/>
+      <c r="O30" s="82" t="n"/>
+      <c r="P30" s="82" t="n"/>
+      <c r="Q30" s="98">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="63">
+      <c r="A31" s="82" t="n"/>
+      <c r="B31" s="82" t="n"/>
+      <c r="C31" s="82" t="n"/>
+      <c r="D31" s="82" t="n"/>
+      <c r="E31" s="82" t="n"/>
+      <c r="F31" s="82" t="n"/>
+      <c r="G31" s="82" t="n"/>
+      <c r="H31" s="82" t="n"/>
+      <c r="I31" s="82" t="n"/>
+      <c r="J31" s="82" t="n"/>
+      <c r="K31" s="82" t="n"/>
+      <c r="L31" s="82" t="n"/>
+      <c r="M31" s="82" t="n"/>
+      <c r="N31" s="82" t="n"/>
+      <c r="O31" s="82" t="n"/>
+      <c r="P31" s="82" t="n"/>
+      <c r="Q31" s="98">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="63">
+      <c r="A32" s="82" t="n"/>
+      <c r="B32" s="82" t="n"/>
+      <c r="C32" s="82" t="n"/>
+      <c r="D32" s="82" t="n"/>
+      <c r="E32" s="82" t="n"/>
+      <c r="F32" s="82" t="n"/>
+      <c r="G32" s="82" t="n"/>
+      <c r="H32" s="82" t="n"/>
+      <c r="I32" s="82" t="n"/>
+      <c r="J32" s="82" t="n"/>
+      <c r="K32" s="82" t="n"/>
+      <c r="L32" s="82" t="n"/>
+      <c r="M32" s="82" t="n"/>
+      <c r="N32" s="82" t="n"/>
+      <c r="O32" s="82" t="n"/>
+      <c r="P32" s="82" t="n"/>
+      <c r="Q32" s="98">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="63">
+      <c r="A33" s="82" t="n"/>
+      <c r="B33" s="82" t="n"/>
+      <c r="C33" s="82" t="n"/>
+      <c r="D33" s="82" t="n"/>
+      <c r="E33" s="82" t="n"/>
+      <c r="F33" s="82" t="n"/>
+      <c r="G33" s="82" t="n"/>
+      <c r="H33" s="82" t="n"/>
+      <c r="I33" s="82" t="n"/>
+      <c r="J33" s="82" t="n"/>
+      <c r="K33" s="82" t="n"/>
+      <c r="L33" s="82" t="n"/>
+      <c r="M33" s="82" t="n"/>
+      <c r="N33" s="82" t="n"/>
+      <c r="O33" s="82" t="n"/>
+      <c r="P33" s="82" t="n"/>
+      <c r="Q33" s="98">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="63">
+      <c r="A34" s="82" t="n"/>
+      <c r="B34" s="82" t="n"/>
+      <c r="C34" s="82" t="n"/>
+      <c r="D34" s="82" t="n"/>
+      <c r="E34" s="82" t="n"/>
+      <c r="F34" s="82" t="n"/>
+      <c r="G34" s="82" t="n"/>
+      <c r="H34" s="82" t="n"/>
+      <c r="I34" s="82" t="n"/>
+      <c r="J34" s="82" t="n"/>
+      <c r="K34" s="82" t="n"/>
+      <c r="L34" s="82" t="n"/>
+      <c r="M34" s="82" t="n"/>
+      <c r="N34" s="82" t="n"/>
+      <c r="O34" s="82" t="n"/>
+      <c r="P34" s="82" t="n"/>
+      <c r="Q34" s="98">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="63">
+      <c r="A35" s="82" t="n"/>
+      <c r="B35" s="82" t="n"/>
+      <c r="C35" s="82" t="n"/>
+      <c r="D35" s="82" t="n"/>
+      <c r="E35" s="82" t="n"/>
+      <c r="F35" s="82" t="n"/>
+      <c r="G35" s="82" t="n"/>
+      <c r="H35" s="82" t="n"/>
+      <c r="I35" s="82" t="n"/>
+      <c r="J35" s="82" t="n"/>
+      <c r="K35" s="82" t="n"/>
+      <c r="L35" s="82" t="n"/>
+      <c r="M35" s="82" t="n"/>
+      <c r="N35" s="82" t="n"/>
+      <c r="O35" s="82" t="n"/>
+      <c r="P35" s="82" t="n"/>
+      <c r="Q35" s="98">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="63">
+      <c r="A36" s="82" t="n"/>
+      <c r="B36" s="82" t="n"/>
+      <c r="C36" s="82" t="n"/>
+      <c r="D36" s="82" t="n"/>
+      <c r="E36" s="82" t="n"/>
+      <c r="F36" s="82" t="n"/>
+      <c r="G36" s="82" t="n"/>
+      <c r="H36" s="82" t="n"/>
+      <c r="I36" s="82" t="n"/>
+      <c r="J36" s="82" t="n"/>
+      <c r="K36" s="82" t="n"/>
+      <c r="L36" s="82" t="n"/>
+      <c r="M36" s="82" t="n"/>
+      <c r="N36" s="82" t="n"/>
+      <c r="O36" s="82" t="n"/>
+      <c r="P36" s="82" t="n"/>
+      <c r="Q36" s="98">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="63">
+      <c r="A37" s="82" t="n"/>
+      <c r="B37" s="82" t="n"/>
+      <c r="C37" s="82" t="n"/>
+      <c r="D37" s="82" t="n"/>
+      <c r="E37" s="82" t="n"/>
+      <c r="F37" s="82" t="n"/>
+      <c r="G37" s="82" t="n"/>
+      <c r="H37" s="82" t="n"/>
+      <c r="I37" s="82" t="n"/>
+      <c r="J37" s="82" t="n"/>
+      <c r="K37" s="82" t="n"/>
+      <c r="L37" s="82" t="n"/>
+      <c r="M37" s="82" t="n"/>
+      <c r="N37" s="82" t="n"/>
+      <c r="O37" s="82" t="n"/>
+      <c r="P37" s="82" t="n"/>
+      <c r="Q37" s="98">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="63">
+      <c r="A38" s="82" t="n"/>
+      <c r="B38" s="82" t="n"/>
+      <c r="C38" s="82" t="n"/>
+      <c r="D38" s="82" t="n"/>
+      <c r="E38" s="82" t="n"/>
+      <c r="F38" s="82" t="n"/>
+      <c r="G38" s="82" t="n"/>
+      <c r="H38" s="82" t="n"/>
+      <c r="I38" s="82" t="n"/>
+      <c r="J38" s="82" t="n"/>
+      <c r="K38" s="82" t="n"/>
+      <c r="L38" s="82" t="n"/>
+      <c r="M38" s="82" t="n"/>
+      <c r="N38" s="82" t="n"/>
+      <c r="O38" s="82" t="n"/>
+      <c r="P38" s="82" t="n"/>
+      <c r="Q38" s="98">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="63">
+      <c r="A39" s="82" t="n"/>
+      <c r="B39" s="82" t="n"/>
+      <c r="C39" s="82" t="n"/>
+      <c r="D39" s="82" t="n"/>
+      <c r="E39" s="82" t="n"/>
+      <c r="F39" s="82" t="n"/>
+      <c r="G39" s="82" t="n"/>
+      <c r="H39" s="82" t="n"/>
+      <c r="I39" s="82" t="n"/>
+      <c r="J39" s="82" t="n"/>
+      <c r="K39" s="82" t="n"/>
+      <c r="L39" s="82" t="n"/>
+      <c r="M39" s="82" t="n"/>
+      <c r="N39" s="82" t="n"/>
+      <c r="O39" s="82" t="n"/>
+      <c r="P39" s="82" t="n"/>
+      <c r="Q39" s="98">
         <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="63">
+      <c r="A40" s="82" t="n"/>
+      <c r="B40" s="82" t="n"/>
+      <c r="C40" s="82" t="n"/>
+      <c r="D40" s="82" t="n"/>
+      <c r="E40" s="82" t="n"/>
+      <c r="F40" s="82" t="n"/>
+      <c r="G40" s="82" t="n"/>
+      <c r="H40" s="82" t="n"/>
+      <c r="I40" s="82" t="n"/>
+      <c r="J40" s="82" t="n"/>
+      <c r="K40" s="82" t="n"/>
+      <c r="L40" s="82" t="n"/>
+      <c r="M40" s="82" t="n"/>
+      <c r="N40" s="82" t="n"/>
+      <c r="O40" s="82" t="n"/>
+      <c r="P40" s="82" t="n"/>
+      <c r="Q40" s="98">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="63">
+      <c r="A41" s="82" t="n"/>
+      <c r="B41" s="82" t="n"/>
+      <c r="C41" s="82" t="n"/>
+      <c r="D41" s="82" t="n"/>
+      <c r="E41" s="82" t="n"/>
+      <c r="F41" s="82" t="n"/>
+      <c r="G41" s="82" t="n"/>
+      <c r="H41" s="82" t="n"/>
+      <c r="I41" s="82" t="n"/>
+      <c r="J41" s="82" t="n"/>
+      <c r="K41" s="82" t="n"/>
+      <c r="L41" s="82" t="n"/>
+      <c r="M41" s="82" t="n"/>
+      <c r="N41" s="82" t="n"/>
+      <c r="O41" s="82" t="n"/>
+      <c r="P41" s="82" t="n"/>
+      <c r="Q41" s="98">
         <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="63">
+      <c r="A42" s="82" t="n"/>
+      <c r="B42" s="82" t="n"/>
+      <c r="C42" s="82" t="n"/>
+      <c r="D42" s="82" t="n"/>
+      <c r="E42" s="82" t="n"/>
+      <c r="F42" s="82" t="n"/>
+      <c r="G42" s="82" t="n"/>
+      <c r="H42" s="82" t="n"/>
+      <c r="I42" s="82" t="n"/>
+      <c r="J42" s="82" t="n"/>
+      <c r="K42" s="82" t="n"/>
+      <c r="L42" s="82" t="n"/>
+      <c r="M42" s="82" t="n"/>
+      <c r="N42" s="82" t="n"/>
+      <c r="O42" s="82" t="n"/>
+      <c r="P42" s="82" t="n"/>
+      <c r="Q42" s="98">
         <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="63">
+      <c r="A43" s="82" t="n"/>
+      <c r="B43" s="82" t="n"/>
+      <c r="C43" s="82" t="n"/>
+      <c r="D43" s="82" t="n"/>
+      <c r="E43" s="82" t="n"/>
+      <c r="F43" s="82" t="n"/>
+      <c r="G43" s="82" t="n"/>
+      <c r="H43" s="82" t="n"/>
+      <c r="I43" s="82" t="n"/>
+      <c r="J43" s="82" t="n"/>
+      <c r="K43" s="82" t="n"/>
+      <c r="L43" s="82" t="n"/>
+      <c r="M43" s="82" t="n"/>
+      <c r="N43" s="82" t="n"/>
+      <c r="O43" s="82" t="n"/>
+      <c r="P43" s="82" t="n"/>
+      <c r="Q43" s="98">
         <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="63">
+      <c r="A44" s="82" t="n"/>
+      <c r="B44" s="82" t="n"/>
+      <c r="C44" s="82" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="82" t="n"/>
+      <c r="F44" s="82" t="n"/>
+      <c r="G44" s="82" t="n"/>
+      <c r="H44" s="82" t="n"/>
+      <c r="I44" s="82" t="n"/>
+      <c r="J44" s="82" t="n"/>
+      <c r="K44" s="82" t="n"/>
+      <c r="L44" s="82" t="n"/>
+      <c r="M44" s="82" t="n"/>
+      <c r="N44" s="82" t="n"/>
+      <c r="O44" s="82" t="n"/>
+      <c r="P44" s="82" t="n"/>
+      <c r="Q44" s="98">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="54" customHeight="1">
-      <c r="A45" s="47" t="inlineStr">
+      <c r="A45" s="99" t="inlineStr">
         <is>
           <t>CO-025</t>
         </is>
       </c>
-      <c r="B45" s="48" t="inlineStr">
+      <c r="B45" s="100" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C45" s="50" t="inlineStr">
+      <c r="C45" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D45" s="48" t="inlineStr">
+      <c r="D45" s="100" t="inlineStr">
         <is>
           <t>دستگاه روشن، باتری وصل و یک بار (مثلاً لامپ) روی خروجی</t>
         </is>
       </c>
-      <c r="E45" s="48" t="inlineStr">
+      <c r="E45" s="100" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را فقط با باتری روشن کن و مطمئن شو بار روشن است.
 گام ۲: ولتاژ باتری را با منبع آزمایشگاهی آرام پایین بیاور تا زیر 21 ولت برسد.
@@ -1788,68 +2997,68 @@
 گام ۴: بار باید خاموش شود (خروجی قطع شود)؛ تا وقتی باتری بالای 21 ولت است بار نباید قطع شود.</t>
         </is>
       </c>
-      <c r="F45" s="48" t="inlineStr">
+      <c r="F45" s="100" t="inlineStr">
         <is>
           <t>باتری از 24 ولت تا زیر 21 ولت</t>
         </is>
       </c>
-      <c r="G45" s="50" t="inlineStr">
+      <c r="G45" s="101" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H45" s="48" t="inlineStr">
+      <c r="H45" s="100" t="inlineStr">
         <is>
           <t>با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود</t>
         </is>
       </c>
-      <c r="I45" s="48" t="inlineStr">
+      <c r="I45" s="100" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J45" s="48" t="inlineStr">
+      <c r="J45" s="100" t="inlineStr">
         <is>
           <t>بار قطع شود؛ قطع زودهنگام وقتی باتری هنوز بالای حد است = رد</t>
         </is>
       </c>
-      <c r="K45" s="48" t="inlineStr"/>
-      <c r="L45" s="80" t="inlineStr">
+      <c r="K45" s="100" t="inlineStr"/>
+      <c r="L45" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M45" s="48" t="n"/>
-      <c r="N45" s="48" t="n"/>
-      <c r="O45" s="50" t="n"/>
-      <c r="P45" s="50" t="n"/>
-      <c r="Q45" s="54">
+      <c r="M45" s="100" t="n"/>
+      <c r="N45" s="100" t="n"/>
+      <c r="O45" s="101" t="n"/>
+      <c r="P45" s="101" t="n"/>
+      <c r="Q45" s="103">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="54" customHeight="1">
-      <c r="A46" s="47" t="inlineStr">
+      <c r="A46" s="99" t="inlineStr">
         <is>
           <t>CO-026</t>
         </is>
       </c>
-      <c r="B46" s="55" t="inlineStr">
+      <c r="B46" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C46" s="57" t="inlineStr">
+      <c r="C46" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D46" s="61" t="inlineStr">
+      <c r="D46" s="106" t="inlineStr">
         <is>
           <t>پایان CO-025 (خروجی قطع است)</t>
         </is>
       </c>
-      <c r="E46" s="61" t="inlineStr">
+      <c r="E46" s="106" t="inlineStr">
         <is>
           <t>گام ۱: از پایان CO-025 شروع کن که خروجی قطع و بار خاموش است.
 گام ۲: برق شهر (ورودی) را وصل کن و ولتاژ باتری را به بالای 21.2 ولت برگردان (با شارژ یا منبع).
@@ -1857,68 +3066,68 @@
 گام ۴: بار باید دوباره روشن شود؛ اگر ولتاژ باتری هنوز پایین است نباید وصل شود.</t>
         </is>
       </c>
-      <c r="F46" s="55" t="inlineStr">
+      <c r="F46" s="104" t="inlineStr">
         <is>
           <t>ورودی حاضر + باتری بالای 21.2 ولت</t>
         </is>
       </c>
-      <c r="G46" s="57" t="inlineStr">
+      <c r="G46" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H46" s="55" t="inlineStr">
+      <c r="H46" s="104" t="inlineStr">
         <is>
           <t>خروجی وصل و بار روشن می‌شود</t>
         </is>
       </c>
-      <c r="I46" s="55" t="inlineStr">
+      <c r="I46" s="104" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="55" t="inlineStr">
+      <c r="J46" s="104" t="inlineStr">
         <is>
           <t>بار دوباره روشن شود؛ وصل شدن با باتری پایین = رد</t>
         </is>
       </c>
-      <c r="K46" s="55" t="inlineStr"/>
-      <c r="L46" s="80" t="inlineStr">
+      <c r="K46" s="104" t="inlineStr"/>
+      <c r="L46" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="57" t="n"/>
-      <c r="P46" s="57" t="n"/>
-      <c r="Q46" s="59">
+      <c r="M46" s="104" t="n"/>
+      <c r="N46" s="104" t="n"/>
+      <c r="O46" s="105" t="n"/>
+      <c r="P46" s="105" t="n"/>
+      <c r="Q46" s="107">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="54" customHeight="1">
-      <c r="A47" s="47" t="inlineStr">
+      <c r="A47" s="99" t="inlineStr">
         <is>
           <t>CO-027</t>
         </is>
       </c>
-      <c r="B47" s="48" t="inlineStr">
+      <c r="B47" s="100" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C47" s="50" t="inlineStr">
+      <c r="C47" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D47" s="48" t="inlineStr">
+      <c r="D47" s="100" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر و باتری وصل، بار روشن</t>
         </is>
       </c>
-      <c r="E47" s="48" t="inlineStr">
+      <c r="E47" s="100" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را با برق شهر و باتری روشن کن و بار را روشن ببین.
 گام ۲: برق شهر را بکش؛ دستگاه نباید خاموش شود و بار باید بی‌وقفه روشن بماند (کار روی باتری).
@@ -1926,68 +3135,68 @@
 گام ۴: در هیچ‌کدام از این دو جابه‌جایی نباید دستگاه در وضعیت خطا گیر کند.</t>
         </is>
       </c>
-      <c r="F47" s="48" t="inlineStr">
+      <c r="F47" s="100" t="inlineStr">
         <is>
           <t>قطع و وصل برق شهر</t>
         </is>
       </c>
-      <c r="G47" s="50" t="inlineStr">
+      <c r="G47" s="101" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H47" s="48" t="inlineStr">
+      <c r="H47" s="100" t="inlineStr">
         <is>
           <t>ادامهٔ بی‌وقفهٔ کار بار و برگشت عادی</t>
         </is>
       </c>
-      <c r="I47" s="48" t="inlineStr">
+      <c r="I47" s="100" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J47" s="48" t="inlineStr">
+      <c r="J47" s="100" t="inlineStr">
         <is>
           <t>بار هرگز خاموش نشود و دستگاه بعد از برگشت شهر عادی کار کند</t>
         </is>
       </c>
-      <c r="K47" s="48" t="inlineStr"/>
-      <c r="L47" s="80" t="inlineStr">
+      <c r="K47" s="100" t="inlineStr"/>
+      <c r="L47" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M47" s="48" t="n"/>
-      <c r="N47" s="48" t="n"/>
-      <c r="O47" s="50" t="n"/>
-      <c r="P47" s="50" t="n"/>
-      <c r="Q47" s="54">
+      <c r="M47" s="100" t="n"/>
+      <c r="N47" s="100" t="n"/>
+      <c r="O47" s="101" t="n"/>
+      <c r="P47" s="101" t="n"/>
+      <c r="Q47" s="103">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="47" t="inlineStr">
+      <c r="A48" s="99" t="inlineStr">
         <is>
           <t>CO-028</t>
         </is>
       </c>
-      <c r="B48" s="55" t="inlineStr">
+      <c r="B48" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C48" s="57" t="inlineStr">
+      <c r="C48" s="105" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D48" s="55" t="inlineStr">
+      <c r="D48" s="104" t="inlineStr">
         <is>
           <t>دستگاه در حال کار عادی با بار روشن</t>
         </is>
       </c>
-      <c r="E48" s="55" t="inlineStr">
+      <c r="E48" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه در حال کار عادی باشد و بار روشن.
 گام ۲: یک خطای شارژر بساز (حین شارژ سیم باتری را قطع کن تا آلارم قطع باتری بیاید).
@@ -1995,42 +3204,42 @@
 گام ۴: بار نباید قطع‌ووصل یا چشمک بزند؛ خروجی باید همان وضعیت قبل از خطا را نگه دارد.</t>
         </is>
       </c>
-      <c r="F48" s="55" t="inlineStr">
+      <c r="F48" s="104" t="inlineStr">
         <is>
           <t>خطای قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G48" s="57" t="inlineStr">
+      <c r="G48" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H48" s="55" t="inlineStr">
+      <c r="H48" s="104" t="inlineStr">
         <is>
           <t>آلارم خطا می‌آید ولی خروجی تکان نمی‌خورد</t>
         </is>
       </c>
-      <c r="I48" s="55" t="inlineStr">
+      <c r="I48" s="104" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J48" s="55" t="inlineStr">
+      <c r="J48" s="104" t="inlineStr">
         <is>
           <t>بار بدون هیچ تکانی روشن بماند</t>
         </is>
       </c>
-      <c r="K48" s="55" t="inlineStr"/>
-      <c r="L48" s="80" t="inlineStr">
+      <c r="K48" s="104" t="inlineStr"/>
+      <c r="L48" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="57" t="n"/>
-      <c r="P48" s="57" t="n"/>
-      <c r="Q48" s="59">
+      <c r="M48" s="104" t="n"/>
+      <c r="N48" s="104" t="n"/>
+      <c r="O48" s="105" t="n"/>
+      <c r="P48" s="105" t="n"/>
+      <c r="Q48" s="107">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
@@ -2090,125 +3299,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="82" t="n"/>
+      <c r="G1" s="82" t="n"/>
+      <c r="H1" s="82" t="n"/>
+      <c r="I1" s="82" t="n"/>
+      <c r="J1" s="82" t="n"/>
+      <c r="K1" s="82" t="n"/>
+      <c r="L1" s="82" t="n"/>
+      <c r="M1" s="82" t="n"/>
+      <c r="N1" s="82" t="n"/>
+      <c r="O1" s="82" t="n"/>
+      <c r="P1" s="82" t="n"/>
+      <c r="Q1" s="82" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="82" t="n"/>
+      <c r="C2" s="82" t="n"/>
+      <c r="D2" s="82" t="n"/>
+      <c r="E2" s="82" t="n"/>
+      <c r="F2" s="82" t="n"/>
+      <c r="G2" s="82" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="82" t="n"/>
+      <c r="J2" s="82" t="n"/>
+      <c r="K2" s="82" t="n"/>
+      <c r="L2" s="82" t="n"/>
+      <c r="M2" s="82" t="n"/>
+      <c r="N2" s="82" t="n"/>
+      <c r="O2" s="82" t="n"/>
+      <c r="P2" s="82" t="n"/>
+      <c r="Q2" s="82" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="82" t="n"/>
+      <c r="B3" s="82" t="n"/>
+      <c r="C3" s="82" t="n"/>
+      <c r="D3" s="82" t="n"/>
+      <c r="E3" s="82" t="n"/>
+      <c r="F3" s="82" t="n"/>
+      <c r="G3" s="82" t="n"/>
+      <c r="H3" s="82" t="n"/>
+      <c r="I3" s="82" t="n"/>
+      <c r="J3" s="82" t="n"/>
+      <c r="K3" s="82" t="n"/>
+      <c r="L3" s="82" t="n"/>
+      <c r="M3" s="82" t="n"/>
+      <c r="N3" s="82" t="n"/>
+      <c r="O3" s="82" t="n"/>
+      <c r="P3" s="82" t="n"/>
+      <c r="Q3" s="82" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="84" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="84" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="84" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="84" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="84" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="84" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="84" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="84" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="84" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="84" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="84" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="84" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="n"/>
+      <c r="Q4" s="84" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>CO-001</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="100" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر / حفظ</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="100" t="inlineStr">
         <is>
           <t>Init → BOOT, PB11 High-safe</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد؛ PB11 باید High و امن باشد.
 گام ۲: یک snapshot نامعتبر اعمال کن: valid=false ولی v_bat=24000، input=false و fault=0.
@@ -2216,68 +3475,68 @@
 گام ۴: وضعیت قبلی (BOOT یا هر وضعیت قبلی) و PB11 باید بدون هیچ تغییری حفظ شده باشند؛ رفتن به FAULT یا IDLE یا تغییر PB11 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="101" t="inlineStr">
         <is>
           <t>valid=false, v=24000, input=false, flag false, fault0</t>
         </is>
       </c>
-      <c r="G5" s="50" t="inlineStr">
+      <c r="G5" s="101" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="100" t="inlineStr">
         <is>
           <t>state حفظ شود: «state فعلی حفظ شود» (BOOT/BATTERY/INPUT/SAFE قبلی) و PB11 حفظ (High-safe). PASS: state و PB11 بدون تغییر. FAIL: هر تغییر به FAULT یا IDLE یا تغییر PB11.</t>
         </is>
       </c>
-      <c r="I5" s="48" t="inlineStr">
+      <c r="I5" s="100" t="inlineStr">
         <is>
           <t>PASS: state فعلی حفظ. FAIL: تغییر خودبه‌خود.</t>
         </is>
       </c>
-      <c r="J5" s="51" t="n"/>
-      <c r="K5" s="52" t="inlineStr">
+      <c r="J5" s="111" t="n"/>
+      <c r="K5" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="53" t="n"/>
-      <c r="M5" s="48" t="n"/>
-      <c r="N5" s="48" t="inlineStr">
+      <c r="L5" s="113" t="n"/>
+      <c r="M5" s="100" t="n"/>
+      <c r="N5" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="50" t="n"/>
-      <c r="P5" s="50" t="n"/>
-      <c r="Q5" s="54">
+      <c r="O5" s="101" t="n"/>
+      <c r="P5" s="101" t="n"/>
+      <c r="Q5" s="103">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="99" t="inlineStr">
         <is>
           <t>CO-002</t>
         </is>
       </c>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر / تایمر reset</t>
         </is>
       </c>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="55" t="inlineStr">
+      <c r="D6" s="104" t="inlineStr">
         <is>
           <t>BATTERY با شرط قطع نیمه‌کاره</t>
         </is>
       </c>
-      <c r="E6" s="55" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
 گام ۲: دو ثانیه شرط قطع را اعمال کن: snapshot معتبر با v=20900 و flag=true.
@@ -2286,68 +3545,68 @@
 گام ۵: PB11 نباید قطع شود؛ آن یک ثانیهٔ نامعتبر تایمر 3 ثانیه‌ای را از نو شروع می‌کند، پس در هیچ‌کدام از دو بازهٔ 2 ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="57" t="inlineStr">
+      <c r="F6" s="105" t="inlineStr">
         <is>
           <t>valid true 2s → false 1s → true 2s, v20900 flag true</t>
         </is>
       </c>
-      <c r="G6" s="57" t="inlineStr">
+      <c r="G6" s="105" t="inlineStr">
         <is>
           <t>2+1+2s</t>
         </is>
       </c>
-      <c r="H6" s="55" t="inlineStr">
+      <c r="H6" s="104" t="inlineStr">
         <is>
           <t>PB11 نباید پس از 2s اول قطع شود؛ پس از 1s invalid، تایمر reset و 2s بعدی هم هنوز قطع نشود (نیاز به 3s پیوسته). PASS: invalid تایمر را reset. FAIL: قطع زود در 2s.</t>
         </is>
       </c>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="104" t="inlineStr">
         <is>
           <t>PASS: reset پس از invalid. FAIL: قطع زود.</t>
         </is>
       </c>
-      <c r="J6" s="55" t="n"/>
-      <c r="K6" s="55" t="inlineStr">
+      <c r="J6" s="104" t="n"/>
+      <c r="K6" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="58" t="n"/>
-      <c r="M6" s="55" t="n"/>
-      <c r="N6" s="55" t="inlineStr">
+      <c r="L6" s="115" t="n"/>
+      <c r="M6" s="104" t="n"/>
+      <c r="N6" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="57" t="n"/>
-      <c r="P6" s="57" t="n"/>
-      <c r="Q6" s="59">
+      <c r="O6" s="105" t="n"/>
+      <c r="P6" s="105" t="n"/>
+      <c r="Q6" s="107">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="99" t="inlineStr">
         <is>
           <t>CO-003</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="100" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر + Fault</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="48" t="inlineStr">
+      <c r="D7" s="100" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E7" s="48" t="inlineStr">
+      <c r="E7" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
 گام ۲: snapshot نامعتبر با fault=FAULT_ADC (مقدار 1) و v=25000 اعمال کن.
@@ -2355,68 +3614,68 @@
 گام ۴: وضعیت نباید FAULT شود و PB11 نباید تغییر کند؛ fault همراه snapshot نامعتبر شمرده نمی‌شود و تایمر قطع هم reset می‌شود.</t>
         </is>
       </c>
-      <c r="F7" s="50" t="inlineStr">
+      <c r="F7" s="101" t="inlineStr">
         <is>
           <t>valid=false, fault=1 (ADC), v25000</t>
         </is>
       </c>
-      <c r="G7" s="50" t="inlineStr">
+      <c r="G7" s="101" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H7" s="48" t="inlineStr">
+      <c r="H7" s="100" t="inlineStr">
         <is>
           <t>state حفظ شود (نه FAULT)، PB11 حفظ، تایمر reset. PASS: fault همراه invalid نباید FAULT شود. FAIL: FAULT شدن.</t>
         </is>
       </c>
-      <c r="I7" s="48" t="inlineStr">
+      <c r="I7" s="100" t="inlineStr">
         <is>
           <t>PASS: حفظ state قبلی. FAIL: FAULT.</t>
         </is>
       </c>
-      <c r="J7" s="51" t="n"/>
-      <c r="K7" s="52" t="inlineStr">
+      <c r="J7" s="111" t="n"/>
+      <c r="K7" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="53" t="n"/>
-      <c r="M7" s="48" t="n"/>
-      <c r="N7" s="48" t="inlineStr">
+      <c r="L7" s="113" t="n"/>
+      <c r="M7" s="100" t="n"/>
+      <c r="N7" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="50" t="n"/>
-      <c r="P7" s="50" t="n"/>
-      <c r="Q7" s="54">
+      <c r="O7" s="101" t="n"/>
+      <c r="P7" s="101" t="n"/>
+      <c r="Q7" s="103">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="99" t="inlineStr">
         <is>
           <t>CO-004</t>
         </is>
       </c>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>Fault با snapshot معتبر</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="55" t="inlineStr">
+      <c r="D8" s="104" t="inlineStr">
         <is>
           <t>INPUT/BATTERY</t>
         </is>
       </c>
-      <c r="E8" s="55" t="inlineStr">
+      <c r="E8" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت INPUT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true و fault=FAULT_ADC (مقدار 1) اعمال کن.
@@ -2424,68 +3683,68 @@
 گام ۴: وضعیت باید FAULT شود ولی PB11 دقیقاً همان قبلی بماند (از High به Low نرود) و تایمر قطع reset شود.</t>
         </is>
       </c>
-      <c r="F8" s="57" t="inlineStr">
+      <c r="F8" s="105" t="inlineStr">
         <is>
           <t>valid=true, v24000, input true, fault 1</t>
         </is>
       </c>
-      <c r="G8" s="57" t="inlineStr">
+      <c r="G8" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H8" s="55" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>state=FAULT، PB11 حفظ (بدون تغییر High→Low)، تایمر reset. PASS: FAULT بدون تغییر PB11. FAIL: تغییر PB11 یا ماندن در INPUT.</t>
         </is>
       </c>
-      <c r="I8" s="55" t="inlineStr">
+      <c r="I8" s="104" t="inlineStr">
         <is>
           <t>PASS: FAULT و PB11 حفظ. FAIL: تغییر PB11.</t>
         </is>
       </c>
-      <c r="J8" s="55" t="n"/>
-      <c r="K8" s="55" t="inlineStr">
+      <c r="J8" s="104" t="n"/>
+      <c r="K8" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="58" t="n"/>
-      <c r="M8" s="55" t="n"/>
-      <c r="N8" s="55" t="inlineStr">
+      <c r="L8" s="115" t="n"/>
+      <c r="M8" s="104" t="n"/>
+      <c r="N8" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O8" s="57" t="n"/>
-      <c r="P8" s="57" t="n"/>
-      <c r="Q8" s="59">
+      <c r="O8" s="105" t="n"/>
+      <c r="P8" s="105" t="n"/>
+      <c r="Q8" s="107">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="99" t="inlineStr">
         <is>
           <t>CO-005</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="100" t="inlineStr">
         <is>
           <t>Fault چند بیتی</t>
         </is>
       </c>
-      <c r="C9" s="50" t="inlineStr">
+      <c r="C9" s="101" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="48" t="inlineStr">
+      <c r="D9" s="100" t="inlineStr">
         <is>
           <t>FAULT قبلی</t>
         </is>
       </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="E9" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد از قبل در وضعیت FAULT باشد.
 گام ۲: snapshot معتبر با fault برابر 63 (همهٔ بیت‌های خطا با هم) اعمال کن.
@@ -2493,68 +3752,68 @@
 گام ۴: وضعیت باید FAULT بماند و هیچ‌کدام از سه پایه نباید تغییر کرده باشند.</t>
         </is>
       </c>
-      <c r="F9" s="50" t="inlineStr">
+      <c r="F9" s="101" t="inlineStr">
         <is>
           <t>valid true, fault ALL</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="G9" s="101" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H9" s="48" t="inlineStr">
+      <c r="H9" s="100" t="inlineStr">
         <is>
           <t>state=FAULT، هیچ pin (PB11/PB5/PB7) تغییر نکند. PASS: همه fault‌ها → FAULT بدون pin. FAIL: هر تغییر pin.</t>
         </is>
       </c>
-      <c r="I9" s="48" t="inlineStr">
+      <c r="I9" s="100" t="inlineStr">
         <is>
           <t>PASS: همه fault → FAULT no pin. FAIL: pin change.</t>
         </is>
       </c>
-      <c r="J9" s="51" t="n"/>
-      <c r="K9" s="52" t="inlineStr">
+      <c r="J9" s="111" t="n"/>
+      <c r="K9" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="53" t="n"/>
-      <c r="M9" s="48" t="n"/>
-      <c r="N9" s="48" t="inlineStr">
+      <c r="L9" s="113" t="n"/>
+      <c r="M9" s="100" t="n"/>
+      <c r="N9" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O9" s="50" t="n"/>
-      <c r="P9" s="50" t="n"/>
-      <c r="Q9" s="54">
+      <c r="O9" s="101" t="n"/>
+      <c r="P9" s="101" t="n"/>
+      <c r="Q9" s="103">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>CO-006</t>
         </is>
       </c>
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="104" t="inlineStr">
         <is>
           <t>ورودی قطع → BATTERY</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="55" t="inlineStr">
+      <c r="D10" s="104" t="inlineStr">
         <is>
           <t>BOOT با snapshot معتبر</t>
         </is>
       </c>
-      <c r="E10" s="55" t="inlineStr">
+      <c r="E10" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BOOT با snapshot معتبر باشد.
 گام ۲: snapshot معتبر با v=24000، input=false (یعنی Vin حداکثر 20 ولت) و fault=0 اعمال کن.
@@ -2562,68 +3821,68 @@
 گام ۴: وضعیت باید BATTERY شود و PB11 باید High و امن (متصل) باشد؛ رفتن به INPUT یا SAFE یا FAULT یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F10" s="57" t="inlineStr">
+      <c r="F10" s="105" t="inlineStr">
         <is>
           <t>valid true, v24000, input false</t>
         </is>
       </c>
-      <c r="G10" s="57" t="inlineStr">
+      <c r="G10" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H10" s="55" t="inlineStr">
+      <c r="H10" s="104" t="inlineStr">
         <is>
           <t>state=BATTERY, PB11 High-safe (متصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
         </is>
       </c>
-      <c r="I10" s="55" t="inlineStr">
+      <c r="I10" s="104" t="inlineStr">
         <is>
           <t>PASS: BATTERY. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J10" s="55" t="n"/>
-      <c r="K10" s="55" t="inlineStr">
+      <c r="J10" s="104" t="n"/>
+      <c r="K10" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="58" t="n"/>
-      <c r="M10" s="55" t="n"/>
-      <c r="N10" s="55" t="inlineStr">
+      <c r="L10" s="115" t="n"/>
+      <c r="M10" s="104" t="n"/>
+      <c r="N10" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O10" s="57" t="n"/>
-      <c r="P10" s="57" t="n"/>
-      <c r="Q10" s="59">
+      <c r="O10" s="105" t="n"/>
+      <c r="P10" s="105" t="n"/>
+      <c r="Q10" s="107">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="99" t="inlineStr">
         <is>
           <t>CO-007</t>
         </is>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="100" t="inlineStr">
         <is>
           <t>ورودی حاضر → INPUT</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="48" t="inlineStr">
+      <c r="D11" s="100" t="inlineStr">
         <is>
           <t>BOOT/BATTERY</t>
         </is>
       </c>
-      <c r="E11" s="48" t="inlineStr">
+      <c r="E11" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد در BOOT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
@@ -2631,68 +3890,68 @@
 گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
         </is>
       </c>
-      <c r="F11" s="50" t="inlineStr">
+      <c r="F11" s="101" t="inlineStr">
         <is>
           <t>valid true, v24000, input true</t>
         </is>
       </c>
-      <c r="G11" s="50" t="inlineStr">
+      <c r="G11" s="101" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H11" s="48" t="inlineStr">
+      <c r="H11" s="100" t="inlineStr">
         <is>
           <t>state=INPUT, PB11 High-safe. PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
         </is>
       </c>
-      <c r="I11" s="48" t="inlineStr">
+      <c r="I11" s="100" t="inlineStr">
         <is>
           <t>PASS: INPUT. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J11" s="51" t="n"/>
-      <c r="K11" s="52" t="inlineStr">
+      <c r="J11" s="111" t="n"/>
+      <c r="K11" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="53" t="n"/>
-      <c r="M11" s="48" t="n"/>
-      <c r="N11" s="48" t="inlineStr">
+      <c r="L11" s="113" t="n"/>
+      <c r="M11" s="100" t="n"/>
+      <c r="N11" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O11" s="50" t="n"/>
-      <c r="P11" s="50" t="n"/>
-      <c r="Q11" s="54">
+      <c r="O11" s="101" t="n"/>
+      <c r="P11" s="101" t="n"/>
+      <c r="Q11" s="103">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="99" t="inlineStr">
         <is>
           <t>CO-008</t>
         </is>
       </c>
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>قطع با گیت / 21000 + flag</t>
         </is>
       </c>
-      <c r="C12" s="56" t="inlineStr">
+      <c r="C12" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="55" t="inlineStr">
+      <c r="D12" s="104" t="inlineStr">
         <is>
           <t>BATTERY/INPUT, PB11 High</t>
         </is>
       </c>
-      <c r="E12" s="55" t="inlineStr">
+      <c r="E12" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
 گام ۲: snapshot معتبر با v=20900 (کمتر از 21000)، flag=true و input=false اعمال کن.
@@ -2700,68 +3959,68 @@
 گام ۴: در 2500 میلی‌ثانیه اول باید هنوز BATTERY/INPUT و PB11 وصل باشد؛ فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت SAFE شود. قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="57" t="inlineStr">
+      <c r="F12" s="105" t="inlineStr">
         <is>
           <t>v20900 (&lt;21000) flag true</t>
         </is>
       </c>
-      <c r="G12" s="57" t="inlineStr">
+      <c r="G12" s="105" t="inlineStr">
         <is>
           <t>3500ms (≥3000)</t>
         </is>
       </c>
-      <c r="H12" s="55" t="inlineStr">
+      <c r="H12" s="104" t="inlineStr">
         <is>
           <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 High؛ پس از 3000ms PB11 Low (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
         </is>
       </c>
-      <c r="I12" s="55" t="inlineStr">
+      <c r="I12" s="104" t="inlineStr">
         <is>
           <t>PASS: 2500 still no cut, 3000 SAFE. FAIL: early or no cut.</t>
         </is>
       </c>
-      <c r="J12" s="55" t="n"/>
-      <c r="K12" s="55" t="inlineStr">
+      <c r="J12" s="104" t="n"/>
+      <c r="K12" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="58" t="n"/>
-      <c r="M12" s="55" t="n"/>
-      <c r="N12" s="55" t="inlineStr">
+      <c r="L12" s="115" t="n"/>
+      <c r="M12" s="104" t="n"/>
+      <c r="N12" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O12" s="57" t="n"/>
-      <c r="P12" s="57" t="n"/>
-      <c r="Q12" s="59">
+      <c r="O12" s="105" t="n"/>
+      <c r="P12" s="105" t="n"/>
+      <c r="Q12" s="107">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="99" t="inlineStr">
         <is>
           <t>CO-009</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="100" t="inlineStr">
         <is>
           <t>قطع مستقل / 20800</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="48" t="inlineStr">
+      <c r="D13" s="100" t="inlineStr">
         <is>
           <t>BATTERY, flag false</t>
         </is>
       </c>
-      <c r="E13" s="48" t="inlineStr">
+      <c r="E13" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY و flag=false باشد.
 گام ۲: snapshot معتبر با v=20700 (کمتر از 20800)، flag=false و input=false اعمال کن.
@@ -2769,68 +4028,68 @@
 گام ۴: بعد از 3000 میلی‌ثانیه باید SAFE با PB11 قطع شود؛ این قطع به flag ربطی ندارد و با flag=false هم باید اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F13" s="50" t="inlineStr">
+      <c r="F13" s="101" t="inlineStr">
         <is>
           <t>v20700 (&lt;20800) flag false</t>
         </is>
       </c>
-      <c r="G13" s="50" t="inlineStr">
+      <c r="G13" s="101" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H13" s="48" t="inlineStr">
+      <c r="H13" s="100" t="inlineStr">
         <is>
           <t>پس از 3000ms SAFE با PB11 Low مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
         </is>
       </c>
-      <c r="I13" s="48" t="inlineStr">
+      <c r="I13" s="100" t="inlineStr">
         <is>
           <t>PASS: independent cut. FAIL: no cut due flag.</t>
         </is>
       </c>
-      <c r="J13" s="51" t="n"/>
-      <c r="K13" s="52" t="inlineStr">
+      <c r="J13" s="111" t="n"/>
+      <c r="K13" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="53" t="n"/>
-      <c r="M13" s="48" t="n"/>
-      <c r="N13" s="48" t="inlineStr">
+      <c r="L13" s="113" t="n"/>
+      <c r="M13" s="100" t="n"/>
+      <c r="N13" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O13" s="50" t="n"/>
-      <c r="P13" s="50" t="n"/>
-      <c r="Q13" s="54">
+      <c r="O13" s="101" t="n"/>
+      <c r="P13" s="101" t="n"/>
+      <c r="Q13" s="103">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>CO-010</t>
         </is>
       </c>
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="104" t="inlineStr">
         <is>
           <t>مرز دقیق 21000 نباید cut</t>
         </is>
       </c>
-      <c r="C14" s="56" t="inlineStr">
+      <c r="C14" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr">
+      <c r="D14" s="104" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E14" s="55" t="inlineStr">
+      <c r="E14" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v دقیقاً 21000 (مرز)، flag=true و input=true (Vin=24 ولت) اعمال کن.
@@ -2838,68 +4097,68 @@
 گام ۴: هیچ قطعی نباید رخ دهد (شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی»)؛ وضعیت باید INPUT شده باشد (چون ورودی حاضر است) و PB11 High و امن بماند.</t>
         </is>
       </c>
-      <c r="F14" s="57" t="inlineStr">
+      <c r="F14" s="105" t="inlineStr">
         <is>
           <t>valid=true, v=21000 (دقیق) flag=true, input=true (Vin≥21V)</t>
         </is>
       </c>
-      <c r="G14" s="57" t="inlineStr">
+      <c r="G14" s="105" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H14" s="55" t="inlineStr">
+      <c r="H14" s="104" t="inlineStr">
         <is>
           <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 High-safe بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
         </is>
       </c>
-      <c r="I14" s="55" t="inlineStr">
+      <c r="I14" s="104" t="inlineStr">
         <is>
           <t>PASS: با v=21000 و input true، state=INPUT و PB11 High. FAIL: هر cut یا BATTERY.</t>
         </is>
       </c>
-      <c r="J14" s="55" t="n"/>
-      <c r="K14" s="55" t="inlineStr">
+      <c r="J14" s="104" t="n"/>
+      <c r="K14" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="58" t="n"/>
-      <c r="M14" s="55" t="n"/>
-      <c r="N14" s="55" t="inlineStr">
+      <c r="L14" s="115" t="n"/>
+      <c r="M14" s="104" t="n"/>
+      <c r="N14" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O14" s="57" t="n"/>
-      <c r="P14" s="57" t="n"/>
-      <c r="Q14" s="59">
+      <c r="O14" s="105" t="n"/>
+      <c r="P14" s="105" t="n"/>
+      <c r="Q14" s="107">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="99" t="inlineStr">
         <is>
           <t>CO-011</t>
         </is>
       </c>
-      <c r="B15" s="48" t="inlineStr">
+      <c r="B15" s="100" t="inlineStr">
         <is>
           <t>مرز دقیق 20800 نباید cut</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="48" t="inlineStr">
+      <c r="D15" s="100" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E15" s="48" t="inlineStr">
+      <c r="E15" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v دقیقاً 20800 و flag=false اعمال کن.
@@ -2907,68 +4166,68 @@
 گام ۴: هیچ قطعی نباید رخ دهد؛ قطع فقط برای «کمتر از 20800» است و روی خودِ مرز 20800 نباید اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F15" s="50" t="inlineStr">
+      <c r="F15" s="101" t="inlineStr">
         <is>
           <t>v=20800 flag false</t>
         </is>
       </c>
-      <c r="G15" s="50" t="inlineStr">
+      <c r="G15" s="101" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H15" s="48" t="inlineStr">
+      <c r="H15" s="100" t="inlineStr">
         <is>
           <t>هیچ قطع نشود. PASS: need &lt;20800. FAIL: cut at exact.</t>
         </is>
       </c>
-      <c r="I15" s="48" t="inlineStr">
+      <c r="I15" s="100" t="inlineStr">
         <is>
           <t>PASS: 20800 no independent cut. FAIL: cut.</t>
         </is>
       </c>
-      <c r="J15" s="51" t="n"/>
-      <c r="K15" s="52" t="inlineStr">
+      <c r="J15" s="111" t="n"/>
+      <c r="K15" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="53" t="n"/>
-      <c r="M15" s="48" t="n"/>
-      <c r="N15" s="48" t="inlineStr">
+      <c r="L15" s="113" t="n"/>
+      <c r="M15" s="100" t="n"/>
+      <c r="N15" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O15" s="50" t="n"/>
-      <c r="P15" s="50" t="n"/>
-      <c r="Q15" s="54">
+      <c r="O15" s="101" t="n"/>
+      <c r="P15" s="101" t="n"/>
+      <c r="Q15" s="103">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="99" t="inlineStr">
         <is>
           <t>CO-012</t>
         </is>
       </c>
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="104" t="inlineStr">
         <is>
           <t>قطع &lt;3000ms نباید</t>
         </is>
       </c>
-      <c r="C16" s="56" t="inlineStr">
+      <c r="C16" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="55" t="inlineStr">
+      <c r="D16" s="104" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E16" s="55" t="inlineStr">
+      <c r="E16" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v=20900، flag=true و input=true (Vin=24 ولت) بده.
@@ -2976,68 +4235,68 @@
 گام ۴: تا 2500 میلی‌ثانیه باید هنوز INPUT و PB11 وصل باشد؛ SAFE شدن زودتر از 3000 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="57" t="inlineStr">
+      <c r="F16" s="105" t="inlineStr">
         <is>
           <t>valid=true, v=20900 (&lt;21000) flag=true, input=true, فقط 2500ms (&lt;3000)</t>
         </is>
       </c>
-      <c r="G16" s="57" t="inlineStr">
+      <c r="G16" s="105" t="inlineStr">
         <is>
           <t>2500ms</t>
         </is>
       </c>
-      <c r="H16" s="55" t="inlineStr">
+      <c r="H16" s="104" t="inlineStr">
         <is>
           <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 High. PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
         </is>
       </c>
-      <c r="I16" s="55" t="inlineStr">
+      <c r="I16" s="104" t="inlineStr">
         <is>
           <t>PASS: 2500ms still INPUT (no cut). FAIL: early SAFE یا BATTERY.</t>
         </is>
       </c>
-      <c r="J16" s="55" t="n"/>
-      <c r="K16" s="55" t="inlineStr">
+      <c r="J16" s="104" t="n"/>
+      <c r="K16" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="58" t="n"/>
-      <c r="M16" s="55" t="n"/>
-      <c r="N16" s="55" t="inlineStr">
+      <c r="L16" s="115" t="n"/>
+      <c r="M16" s="104" t="n"/>
+      <c r="N16" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O16" s="57" t="n"/>
-      <c r="P16" s="57" t="n"/>
-      <c r="Q16" s="59">
+      <c r="O16" s="105" t="n"/>
+      <c r="P16" s="105" t="n"/>
+      <c r="Q16" s="107">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="99" t="inlineStr">
         <is>
           <t>CO-013</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="100" t="inlineStr">
         <is>
           <t>وصل مجدد / 21200 + input</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="48" t="inlineStr">
+      <c r="D17" s="100" t="inlineStr">
         <is>
           <t>SAFE, PB11 Low</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="116" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
 گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
@@ -3045,68 +4304,68 @@
 گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="50" t="inlineStr">
+      <c r="F17" s="101" t="inlineStr">
         <is>
           <t>SAFE, input true, v21300</t>
         </is>
       </c>
-      <c r="G17" s="50" t="inlineStr">
+      <c r="G17" s="101" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H17" s="48" t="inlineStr">
+      <c r="H17" s="100" t="inlineStr">
         <is>
           <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
         </is>
       </c>
-      <c r="I17" s="48" t="inlineStr">
+      <c r="I17" s="100" t="inlineStr">
         <is>
           <t>PASS: قبل 3000 SAFE Low، بعد 3000 INPUT High. FAIL: early or no reconnect.</t>
         </is>
       </c>
-      <c r="J17" s="51" t="n"/>
-      <c r="K17" s="52" t="inlineStr">
+      <c r="J17" s="111" t="n"/>
+      <c r="K17" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="53" t="n"/>
-      <c r="M17" s="48" t="n"/>
-      <c r="N17" s="48" t="inlineStr">
+      <c r="L17" s="113" t="n"/>
+      <c r="M17" s="100" t="n"/>
+      <c r="N17" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O17" s="50" t="n"/>
-      <c r="P17" s="50" t="n"/>
-      <c r="Q17" s="54">
+      <c r="O17" s="101" t="n"/>
+      <c r="P17" s="101" t="n"/>
+      <c r="Q17" s="103">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="47" t="inlineStr">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>CO-014</t>
         </is>
       </c>
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B18" s="104" t="inlineStr">
         <is>
           <t>مرز دقیق 21200 باید reconnect</t>
         </is>
       </c>
-      <c r="C18" s="56" t="inlineStr">
+      <c r="C18" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="104" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E18" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در SAFE باشد.
 گام ۲: input=true و v دقیقاً 21200 اعمال کن (روی خودِ مرز).
@@ -3114,68 +4373,68 @@
 گام ۴: بعد از 3000 میلی‌ثانیه باید INPUT و PB11 وصل شده باشد؛ شرط وصل «دست‌کم 21200» است، پس روی مرز هم باید وصل شود.</t>
         </is>
       </c>
-      <c r="F18" s="57" t="inlineStr">
+      <c r="F18" s="105" t="inlineStr">
         <is>
           <t>v=21200 input true</t>
         </is>
       </c>
-      <c r="G18" s="57" t="inlineStr">
+      <c r="G18" s="105" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H18" s="55" t="inlineStr">
+      <c r="H18" s="104" t="inlineStr">
         <is>
           <t>پس از 3000ms INPUT و PB11 High. PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
         </is>
       </c>
-      <c r="I18" s="55" t="inlineStr">
+      <c r="I18" s="104" t="inlineStr">
         <is>
           <t>PASS: 21200 reconnects (need ≥). FAIL: no.</t>
         </is>
       </c>
-      <c r="J18" s="55" t="n"/>
-      <c r="K18" s="55" t="inlineStr">
+      <c r="J18" s="104" t="n"/>
+      <c r="K18" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="58" t="n"/>
-      <c r="M18" s="55" t="n"/>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="L18" s="115" t="n"/>
+      <c r="M18" s="104" t="n"/>
+      <c r="N18" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O18" s="57" t="n"/>
-      <c r="P18" s="57" t="n"/>
-      <c r="Q18" s="59">
+      <c r="O18" s="105" t="n"/>
+      <c r="P18" s="105" t="n"/>
+      <c r="Q18" s="107">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="A19" s="99" t="inlineStr">
         <is>
           <t>CO-015</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr">
+      <c r="B19" s="100" t="inlineStr">
         <is>
           <t>reconnect &lt;3000 نباید</t>
         </is>
       </c>
-      <c r="C19" s="49" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="48" t="inlineStr">
+      <c r="D19" s="100" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="E19" s="48" t="inlineStr">
+      <c r="E19" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد در SAFE باشد.
 گام ۲: input=true و v=21300 اعمال کن.
@@ -3183,204 +4442,204 @@
 گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F19" s="50" t="inlineStr">
+      <c r="F19" s="101" t="inlineStr">
         <is>
           <t>v21300 input true</t>
         </is>
       </c>
-      <c r="G19" s="50" t="inlineStr">
+      <c r="G19" s="101" t="inlineStr">
         <is>
           <t>2500ms</t>
         </is>
       </c>
-      <c r="H19" s="48" t="inlineStr">
+      <c r="H19" s="100" t="inlineStr">
         <is>
           <t>هنوز SAFE و PB11 Low. PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
         </is>
       </c>
-      <c r="I19" s="48" t="inlineStr">
+      <c r="I19" s="100" t="inlineStr">
         <is>
           <t>PASS: 2500 still SAFE. FAIL: INPUT early.</t>
         </is>
       </c>
-      <c r="J19" s="51" t="n"/>
-      <c r="K19" s="52" t="inlineStr">
+      <c r="J19" s="111" t="n"/>
+      <c r="K19" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L19" s="53" t="n"/>
-      <c r="M19" s="48" t="n"/>
-      <c r="N19" s="48" t="inlineStr">
+      <c r="L19" s="113" t="n"/>
+      <c r="M19" s="100" t="n"/>
+      <c r="N19" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O19" s="50" t="n"/>
-      <c r="P19" s="50" t="n"/>
-      <c r="Q19" s="54">
+      <c r="O19" s="101" t="n"/>
+      <c r="P19" s="101" t="n"/>
+      <c r="Q19" s="103">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="40.5" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="99" t="inlineStr">
         <is>
           <t>CO-016</t>
         </is>
       </c>
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="104" t="inlineStr">
         <is>
           <t>پس از reconnect state INPUT</t>
         </is>
       </c>
-      <c r="C20" s="56" t="inlineStr">
+      <c r="C20" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="106" t="inlineStr">
         <is>
           <t>پس از CO-013</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="106" t="inlineStr">
         <is>
           <t>گام ۱: تست CO-013 را انجام بده تا وصل مجدد موفق اتفاق بیفتد.
 گام ۲: بلافاصله (در حد 100 میلی‌ثانیه بعد) وضعیت را بخوان.
 گام ۳: وضعیت باید INPUT باشد؛ IDLE برای snapshot معتبر هرگز نباید دیده شود.</t>
         </is>
       </c>
-      <c r="F20" s="57" t="inlineStr">
+      <c r="F20" s="105" t="inlineStr">
         <is>
           <t>post-reconnect</t>
         </is>
       </c>
-      <c r="G20" s="57" t="inlineStr">
+      <c r="G20" s="105" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H20" s="55" t="inlineStr">
+      <c r="H20" s="104" t="inlineStr">
         <is>
           <t>state=INPUT باشد، نه IDLE (IDLE برای معتبر ممنوع). PASS: INPUT. FAIL: IDLE.</t>
         </is>
       </c>
-      <c r="I20" s="55" t="inlineStr">
+      <c r="I20" s="104" t="inlineStr">
         <is>
           <t>PASS: INPUT not IDLE. FAIL: IDLE.</t>
         </is>
       </c>
-      <c r="J20" s="55" t="n"/>
-      <c r="K20" s="55" t="inlineStr">
+      <c r="J20" s="104" t="n"/>
+      <c r="K20" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L20" s="58" t="n"/>
-      <c r="M20" s="55" t="n"/>
-      <c r="N20" s="55" t="inlineStr">
+      <c r="L20" s="115" t="n"/>
+      <c r="M20" s="104" t="n"/>
+      <c r="N20" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O20" s="57" t="n"/>
-      <c r="P20" s="57" t="n"/>
-      <c r="Q20" s="59">
+      <c r="O20" s="105" t="n"/>
+      <c r="P20" s="105" t="n"/>
+      <c r="Q20" s="107">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="40.5" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="A21" s="99" t="inlineStr">
         <is>
           <t>CO-017</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="100" t="inlineStr">
         <is>
           <t>PB11 در invalid حفظ</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D21" s="100" t="inlineStr">
         <is>
           <t>INPUT با PB11 High</t>
         </is>
       </c>
-      <c r="E21" s="48" t="inlineStr">
+      <c r="E21" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد را با snapshot معتبر و input=true به INPUT ببر و PB11 را چک کن که وصل (High) است.
 گام ۲: حالا valid=false کن و 500 میلی‌ثانیه صبر کن.
 گام ۳: PB11 را دوباره بخوان: باید بدون تغییر همان High مانده باشد.</t>
         </is>
       </c>
-      <c r="F21" s="50" t="inlineStr">
+      <c r="F21" s="101" t="inlineStr">
         <is>
           <t>valid true→false</t>
         </is>
       </c>
-      <c r="G21" s="50" t="inlineStr">
+      <c r="G21" s="101" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H21" s="48" t="inlineStr">
+      <c r="H21" s="100" t="inlineStr">
         <is>
           <t>PB11 Low-High بدون تغییر بماند (High). PASS: حفظ. FAIL: تغییر.</t>
         </is>
       </c>
-      <c r="I21" s="48" t="inlineStr">
+      <c r="I21" s="100" t="inlineStr">
         <is>
           <t>PASS: PB11 preserved in invalid. FAIL: change.</t>
         </is>
       </c>
-      <c r="J21" s="51" t="n"/>
-      <c r="K21" s="52" t="inlineStr">
+      <c r="J21" s="111" t="n"/>
+      <c r="K21" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L21" s="53" t="n"/>
-      <c r="M21" s="48" t="n"/>
-      <c r="N21" s="48" t="inlineStr">
+      <c r="L21" s="113" t="n"/>
+      <c r="M21" s="100" t="n"/>
+      <c r="N21" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O21" s="50" t="n"/>
-      <c r="P21" s="50" t="n"/>
-      <c r="Q21" s="54">
+      <c r="O21" s="101" t="n"/>
+      <c r="P21" s="101" t="n"/>
+      <c r="Q21" s="103">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="47" t="inlineStr">
+      <c r="A22" s="99" t="inlineStr">
         <is>
           <t>CO-018</t>
         </is>
       </c>
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="104" t="inlineStr">
         <is>
           <t>PB11 در fault حفظ</t>
         </is>
       </c>
-      <c r="C22" s="56" t="inlineStr">
+      <c r="C22" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="104" t="inlineStr">
         <is>
           <t>INPUT</t>
         </is>
       </c>
-      <c r="E22" s="55" t="inlineStr">
+      <c r="E22" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در INPUT باشد.
 گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
@@ -3388,136 +4647,136 @@
 گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F22" s="57" t="inlineStr">
+      <c r="F22" s="105" t="inlineStr">
         <is>
           <t>valid true fault1</t>
         </is>
       </c>
-      <c r="G22" s="57" t="inlineStr">
+      <c r="G22" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H22" s="55" t="inlineStr">
+      <c r="H22" s="104" t="inlineStr">
         <is>
           <t>PB11 حفظ (High). PASS. FAIL: Low شدن.</t>
         </is>
       </c>
-      <c r="I22" s="55" t="inlineStr">
+      <c r="I22" s="104" t="inlineStr">
         <is>
           <t>PASS: PB11 preserved in fault. FAIL: change.</t>
         </is>
       </c>
-      <c r="J22" s="55" t="n"/>
-      <c r="K22" s="55" t="inlineStr">
+      <c r="J22" s="104" t="n"/>
+      <c r="K22" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L22" s="58" t="n"/>
-      <c r="M22" s="55" t="n"/>
-      <c r="N22" s="55" t="inlineStr">
+      <c r="L22" s="115" t="n"/>
+      <c r="M22" s="104" t="n"/>
+      <c r="N22" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O22" s="57" t="n"/>
-      <c r="P22" s="57" t="n"/>
-      <c r="Q22" s="59">
+      <c r="O22" s="105" t="n"/>
+      <c r="P22" s="105" t="n"/>
+      <c r="Q22" s="107">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="47" t="inlineStr">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>CO-019</t>
         </is>
       </c>
-      <c r="B23" s="48" t="inlineStr">
+      <c r="B23" s="100" t="inlineStr">
         <is>
           <t>PB5 و PB7 هیچ‌گاه تغییر نکنند</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="48" t="inlineStr">
+      <c r="D23" s="100" t="inlineStr">
         <is>
           <t>هر حالت</t>
         </is>
       </c>
-      <c r="E23" s="60" t="inlineStr">
+      <c r="E23" s="116" t="inlineStr">
         <is>
           <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015 که انجام می‌دهی، علاوه بر PB11 دو پایهٔ PB5 (BAT_SWITCH) و PB7 (RELAY) را هم با اسیلوسکوپ یا لاگ BSP زیر نظر بگیر.
 گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
 گام ۳: PB5 باید همیشه High امن (active-low) و PB7 همیشه Low بماند؛ هر تغییر (toggle) روی این دو یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="50" t="inlineStr">
+      <c r="F23" s="101" t="inlineStr">
         <is>
           <t>تمام حالات</t>
         </is>
       </c>
-      <c r="G23" s="50" t="inlineStr">
+      <c r="G23" s="101" t="inlineStr">
         <is>
           <t>هر تست</t>
         </is>
       </c>
-      <c r="H23" s="48" t="inlineStr">
+      <c r="H23" s="100" t="inlineStr">
         <is>
           <t>PB5 و PB7 ثابت بمانند (PB5 High-safe active-low، PB7 Low). PASS: بدون تغییر. FAIL: هر toggle.</t>
         </is>
       </c>
-      <c r="I23" s="48" t="inlineStr">
+      <c r="I23" s="100" t="inlineStr">
         <is>
           <t>PASS: PB5/PB7 never change. FAIL: any toggle.</t>
         </is>
       </c>
-      <c r="J23" s="51" t="n"/>
-      <c r="K23" s="52" t="inlineStr">
+      <c r="J23" s="111" t="n"/>
+      <c r="K23" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L23" s="53" t="n"/>
-      <c r="M23" s="48" t="n"/>
-      <c r="N23" s="48" t="inlineStr">
+      <c r="L23" s="113" t="n"/>
+      <c r="M23" s="100" t="n"/>
+      <c r="N23" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O23" s="50" t="n"/>
-      <c r="P23" s="50" t="n"/>
-      <c r="Q23" s="54">
+      <c r="O23" s="101" t="n"/>
+      <c r="P23" s="101" t="n"/>
+      <c r="Q23" s="103">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="47" t="inlineStr">
+      <c r="A24" s="99" t="inlineStr">
         <is>
           <t>CO-024</t>
         </is>
       </c>
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="104" t="inlineStr">
         <is>
           <t>وصل مجدد 30s پایداری ورودی</t>
         </is>
       </c>
-      <c r="C24" s="56" t="inlineStr">
+      <c r="C24" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="104" t="inlineStr">
         <is>
           <t>برد در SAFE پس از قطع، v_bat=24V</t>
         </is>
       </c>
-      <c r="E24" s="61" t="inlineStr">
+      <c r="E24" s="106" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
 گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
@@ -3525,162 +4784,482 @@
 گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
         </is>
       </c>
-      <c r="F24" s="57" t="inlineStr">
+      <c r="F24" s="105" t="inlineStr">
         <is>
           <t>input=true v=24000</t>
         </is>
       </c>
-      <c r="G24" s="57" t="inlineStr">
+      <c r="G24" s="105" t="inlineStr">
         <is>
           <t>33s</t>
         </is>
       </c>
-      <c r="H24" s="55" t="inlineStr">
+      <c r="H24" s="104" t="inlineStr">
         <is>
           <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
         </is>
       </c>
-      <c r="I24" s="55" t="inlineStr">
+      <c r="I24" s="104" t="inlineStr">
         <is>
           <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
         </is>
       </c>
-      <c r="J24" s="55" t="n"/>
-      <c r="K24" s="55" t="inlineStr">
+      <c r="J24" s="104" t="n"/>
+      <c r="K24" s="104" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="L24" s="58" t="n"/>
-      <c r="M24" s="55" t="n"/>
-      <c r="N24" s="55" t="inlineStr">
+      <c r="L24" s="115" t="n"/>
+      <c r="M24" s="104" t="n"/>
+      <c r="N24" s="104" t="inlineStr">
         <is>
           <t>thermal+30s</t>
         </is>
       </c>
-      <c r="O24" s="57" t="n"/>
-      <c r="P24" s="57" t="n"/>
-      <c r="Q24" s="59">
+      <c r="O24" s="105" t="n"/>
+      <c r="P24" s="105" t="n"/>
+      <c r="Q24" s="107">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="63">
+      <c r="A25" s="82" t="n"/>
+      <c r="B25" s="82" t="n"/>
+      <c r="C25" s="82" t="n"/>
+      <c r="D25" s="82" t="n"/>
+      <c r="E25" s="82" t="n"/>
+      <c r="F25" s="82" t="n"/>
+      <c r="G25" s="82" t="n"/>
+      <c r="H25" s="82" t="n"/>
+      <c r="I25" s="82" t="n"/>
+      <c r="J25" s="82" t="n"/>
+      <c r="K25" s="82" t="n"/>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
+      <c r="N25" s="82" t="n"/>
+      <c r="O25" s="82" t="n"/>
+      <c r="P25" s="82" t="n"/>
+      <c r="Q25" s="98">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="63">
+      <c r="A26" s="82" t="n"/>
+      <c r="B26" s="82" t="n"/>
+      <c r="C26" s="82" t="n"/>
+      <c r="D26" s="82" t="n"/>
+      <c r="E26" s="82" t="n"/>
+      <c r="F26" s="82" t="n"/>
+      <c r="G26" s="82" t="n"/>
+      <c r="H26" s="82" t="n"/>
+      <c r="I26" s="82" t="n"/>
+      <c r="J26" s="82" t="n"/>
+      <c r="K26" s="82" t="n"/>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
+      <c r="N26" s="82" t="n"/>
+      <c r="O26" s="82" t="n"/>
+      <c r="P26" s="82" t="n"/>
+      <c r="Q26" s="98">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="63">
+      <c r="A27" s="82" t="n"/>
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="82" t="n"/>
+      <c r="D27" s="82" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
+      <c r="G27" s="82" t="n"/>
+      <c r="H27" s="82" t="n"/>
+      <c r="I27" s="82" t="n"/>
+      <c r="J27" s="82" t="n"/>
+      <c r="K27" s="82" t="n"/>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="82" t="n"/>
+      <c r="N27" s="82" t="n"/>
+      <c r="O27" s="82" t="n"/>
+      <c r="P27" s="82" t="n"/>
+      <c r="Q27" s="98">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="63">
+      <c r="A28" s="82" t="n"/>
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="82" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="82" t="n"/>
+      <c r="F28" s="82" t="n"/>
+      <c r="G28" s="82" t="n"/>
+      <c r="H28" s="82" t="n"/>
+      <c r="I28" s="82" t="n"/>
+      <c r="J28" s="82" t="n"/>
+      <c r="K28" s="82" t="n"/>
+      <c r="L28" s="82" t="n"/>
+      <c r="M28" s="82" t="n"/>
+      <c r="N28" s="82" t="n"/>
+      <c r="O28" s="82" t="n"/>
+      <c r="P28" s="82" t="n"/>
+      <c r="Q28" s="98">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="63">
+      <c r="A29" s="82" t="n"/>
+      <c r="B29" s="82" t="n"/>
+      <c r="C29" s="82" t="n"/>
+      <c r="D29" s="82" t="n"/>
+      <c r="E29" s="82" t="n"/>
+      <c r="F29" s="82" t="n"/>
+      <c r="G29" s="82" t="n"/>
+      <c r="H29" s="82" t="n"/>
+      <c r="I29" s="82" t="n"/>
+      <c r="J29" s="82" t="n"/>
+      <c r="K29" s="82" t="n"/>
+      <c r="L29" s="82" t="n"/>
+      <c r="M29" s="82" t="n"/>
+      <c r="N29" s="82" t="n"/>
+      <c r="O29" s="82" t="n"/>
+      <c r="P29" s="82" t="n"/>
+      <c r="Q29" s="98">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="63">
+      <c r="A30" s="82" t="n"/>
+      <c r="B30" s="82" t="n"/>
+      <c r="C30" s="82" t="n"/>
+      <c r="D30" s="82" t="n"/>
+      <c r="E30" s="82" t="n"/>
+      <c r="F30" s="82" t="n"/>
+      <c r="G30" s="82" t="n"/>
+      <c r="H30" s="82" t="n"/>
+      <c r="I30" s="82" t="n"/>
+      <c r="J30" s="82" t="n"/>
+      <c r="K30" s="82" t="n"/>
+      <c r="L30" s="82" t="n"/>
+      <c r="M30" s="82" t="n"/>
+      <c r="N30" s="82" t="n"/>
+      <c r="O30" s="82" t="n"/>
+      <c r="P30" s="82" t="n"/>
+      <c r="Q30" s="98">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="63">
+      <c r="A31" s="82" t="n"/>
+      <c r="B31" s="82" t="n"/>
+      <c r="C31" s="82" t="n"/>
+      <c r="D31" s="82" t="n"/>
+      <c r="E31" s="82" t="n"/>
+      <c r="F31" s="82" t="n"/>
+      <c r="G31" s="82" t="n"/>
+      <c r="H31" s="82" t="n"/>
+      <c r="I31" s="82" t="n"/>
+      <c r="J31" s="82" t="n"/>
+      <c r="K31" s="82" t="n"/>
+      <c r="L31" s="82" t="n"/>
+      <c r="M31" s="82" t="n"/>
+      <c r="N31" s="82" t="n"/>
+      <c r="O31" s="82" t="n"/>
+      <c r="P31" s="82" t="n"/>
+      <c r="Q31" s="98">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="63">
+      <c r="A32" s="82" t="n"/>
+      <c r="B32" s="82" t="n"/>
+      <c r="C32" s="82" t="n"/>
+      <c r="D32" s="82" t="n"/>
+      <c r="E32" s="82" t="n"/>
+      <c r="F32" s="82" t="n"/>
+      <c r="G32" s="82" t="n"/>
+      <c r="H32" s="82" t="n"/>
+      <c r="I32" s="82" t="n"/>
+      <c r="J32" s="82" t="n"/>
+      <c r="K32" s="82" t="n"/>
+      <c r="L32" s="82" t="n"/>
+      <c r="M32" s="82" t="n"/>
+      <c r="N32" s="82" t="n"/>
+      <c r="O32" s="82" t="n"/>
+      <c r="P32" s="82" t="n"/>
+      <c r="Q32" s="98">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="63">
+      <c r="A33" s="82" t="n"/>
+      <c r="B33" s="82" t="n"/>
+      <c r="C33" s="82" t="n"/>
+      <c r="D33" s="82" t="n"/>
+      <c r="E33" s="82" t="n"/>
+      <c r="F33" s="82" t="n"/>
+      <c r="G33" s="82" t="n"/>
+      <c r="H33" s="82" t="n"/>
+      <c r="I33" s="82" t="n"/>
+      <c r="J33" s="82" t="n"/>
+      <c r="K33" s="82" t="n"/>
+      <c r="L33" s="82" t="n"/>
+      <c r="M33" s="82" t="n"/>
+      <c r="N33" s="82" t="n"/>
+      <c r="O33" s="82" t="n"/>
+      <c r="P33" s="82" t="n"/>
+      <c r="Q33" s="98">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="63">
+      <c r="A34" s="82" t="n"/>
+      <c r="B34" s="82" t="n"/>
+      <c r="C34" s="82" t="n"/>
+      <c r="D34" s="82" t="n"/>
+      <c r="E34" s="82" t="n"/>
+      <c r="F34" s="82" t="n"/>
+      <c r="G34" s="82" t="n"/>
+      <c r="H34" s="82" t="n"/>
+      <c r="I34" s="82" t="n"/>
+      <c r="J34" s="82" t="n"/>
+      <c r="K34" s="82" t="n"/>
+      <c r="L34" s="82" t="n"/>
+      <c r="M34" s="82" t="n"/>
+      <c r="N34" s="82" t="n"/>
+      <c r="O34" s="82" t="n"/>
+      <c r="P34" s="82" t="n"/>
+      <c r="Q34" s="98">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="63">
+      <c r="A35" s="82" t="n"/>
+      <c r="B35" s="82" t="n"/>
+      <c r="C35" s="82" t="n"/>
+      <c r="D35" s="82" t="n"/>
+      <c r="E35" s="82" t="n"/>
+      <c r="F35" s="82" t="n"/>
+      <c r="G35" s="82" t="n"/>
+      <c r="H35" s="82" t="n"/>
+      <c r="I35" s="82" t="n"/>
+      <c r="J35" s="82" t="n"/>
+      <c r="K35" s="82" t="n"/>
+      <c r="L35" s="82" t="n"/>
+      <c r="M35" s="82" t="n"/>
+      <c r="N35" s="82" t="n"/>
+      <c r="O35" s="82" t="n"/>
+      <c r="P35" s="82" t="n"/>
+      <c r="Q35" s="98">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="63">
+      <c r="A36" s="82" t="n"/>
+      <c r="B36" s="82" t="n"/>
+      <c r="C36" s="82" t="n"/>
+      <c r="D36" s="82" t="n"/>
+      <c r="E36" s="82" t="n"/>
+      <c r="F36" s="82" t="n"/>
+      <c r="G36" s="82" t="n"/>
+      <c r="H36" s="82" t="n"/>
+      <c r="I36" s="82" t="n"/>
+      <c r="J36" s="82" t="n"/>
+      <c r="K36" s="82" t="n"/>
+      <c r="L36" s="82" t="n"/>
+      <c r="M36" s="82" t="n"/>
+      <c r="N36" s="82" t="n"/>
+      <c r="O36" s="82" t="n"/>
+      <c r="P36" s="82" t="n"/>
+      <c r="Q36" s="98">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="63">
+      <c r="A37" s="82" t="n"/>
+      <c r="B37" s="82" t="n"/>
+      <c r="C37" s="82" t="n"/>
+      <c r="D37" s="82" t="n"/>
+      <c r="E37" s="82" t="n"/>
+      <c r="F37" s="82" t="n"/>
+      <c r="G37" s="82" t="n"/>
+      <c r="H37" s="82" t="n"/>
+      <c r="I37" s="82" t="n"/>
+      <c r="J37" s="82" t="n"/>
+      <c r="K37" s="82" t="n"/>
+      <c r="L37" s="82" t="n"/>
+      <c r="M37" s="82" t="n"/>
+      <c r="N37" s="82" t="n"/>
+      <c r="O37" s="82" t="n"/>
+      <c r="P37" s="82" t="n"/>
+      <c r="Q37" s="98">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="63">
+      <c r="A38" s="82" t="n"/>
+      <c r="B38" s="82" t="n"/>
+      <c r="C38" s="82" t="n"/>
+      <c r="D38" s="82" t="n"/>
+      <c r="E38" s="82" t="n"/>
+      <c r="F38" s="82" t="n"/>
+      <c r="G38" s="82" t="n"/>
+      <c r="H38" s="82" t="n"/>
+      <c r="I38" s="82" t="n"/>
+      <c r="J38" s="82" t="n"/>
+      <c r="K38" s="82" t="n"/>
+      <c r="L38" s="82" t="n"/>
+      <c r="M38" s="82" t="n"/>
+      <c r="N38" s="82" t="n"/>
+      <c r="O38" s="82" t="n"/>
+      <c r="P38" s="82" t="n"/>
+      <c r="Q38" s="98">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="63">
+      <c r="A39" s="82" t="n"/>
+      <c r="B39" s="82" t="n"/>
+      <c r="C39" s="82" t="n"/>
+      <c r="D39" s="82" t="n"/>
+      <c r="E39" s="82" t="n"/>
+      <c r="F39" s="82" t="n"/>
+      <c r="G39" s="82" t="n"/>
+      <c r="H39" s="82" t="n"/>
+      <c r="I39" s="82" t="n"/>
+      <c r="J39" s="82" t="n"/>
+      <c r="K39" s="82" t="n"/>
+      <c r="L39" s="82" t="n"/>
+      <c r="M39" s="82" t="n"/>
+      <c r="N39" s="82" t="n"/>
+      <c r="O39" s="82" t="n"/>
+      <c r="P39" s="82" t="n"/>
+      <c r="Q39" s="98">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="63">
+      <c r="A40" s="82" t="n"/>
+      <c r="B40" s="82" t="n"/>
+      <c r="C40" s="82" t="n"/>
+      <c r="D40" s="82" t="n"/>
+      <c r="E40" s="82" t="n"/>
+      <c r="F40" s="82" t="n"/>
+      <c r="G40" s="82" t="n"/>
+      <c r="H40" s="82" t="n"/>
+      <c r="I40" s="82" t="n"/>
+      <c r="J40" s="82" t="n"/>
+      <c r="K40" s="82" t="n"/>
+      <c r="L40" s="82" t="n"/>
+      <c r="M40" s="82" t="n"/>
+      <c r="N40" s="82" t="n"/>
+      <c r="O40" s="82" t="n"/>
+      <c r="P40" s="82" t="n"/>
+      <c r="Q40" s="98">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="63">
+      <c r="A41" s="82" t="n"/>
+      <c r="B41" s="82" t="n"/>
+      <c r="C41" s="82" t="n"/>
+      <c r="D41" s="82" t="n"/>
+      <c r="E41" s="82" t="n"/>
+      <c r="F41" s="82" t="n"/>
+      <c r="G41" s="82" t="n"/>
+      <c r="H41" s="82" t="n"/>
+      <c r="I41" s="82" t="n"/>
+      <c r="J41" s="82" t="n"/>
+      <c r="K41" s="82" t="n"/>
+      <c r="L41" s="82" t="n"/>
+      <c r="M41" s="82" t="n"/>
+      <c r="N41" s="82" t="n"/>
+      <c r="O41" s="82" t="n"/>
+      <c r="P41" s="82" t="n"/>
+      <c r="Q41" s="98">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="63">
+      <c r="A42" s="82" t="n"/>
+      <c r="B42" s="82" t="n"/>
+      <c r="C42" s="82" t="n"/>
+      <c r="D42" s="82" t="n"/>
+      <c r="E42" s="82" t="n"/>
+      <c r="F42" s="82" t="n"/>
+      <c r="G42" s="82" t="n"/>
+      <c r="H42" s="82" t="n"/>
+      <c r="I42" s="82" t="n"/>
+      <c r="J42" s="82" t="n"/>
+      <c r="K42" s="82" t="n"/>
+      <c r="L42" s="82" t="n"/>
+      <c r="M42" s="82" t="n"/>
+      <c r="N42" s="82" t="n"/>
+      <c r="O42" s="82" t="n"/>
+      <c r="P42" s="82" t="n"/>
+      <c r="Q42" s="98">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="63">
+      <c r="A43" s="82" t="n"/>
+      <c r="B43" s="82" t="n"/>
+      <c r="C43" s="82" t="n"/>
+      <c r="D43" s="82" t="n"/>
+      <c r="E43" s="82" t="n"/>
+      <c r="F43" s="82" t="n"/>
+      <c r="G43" s="82" t="n"/>
+      <c r="H43" s="82" t="n"/>
+      <c r="I43" s="82" t="n"/>
+      <c r="J43" s="82" t="n"/>
+      <c r="K43" s="82" t="n"/>
+      <c r="L43" s="82" t="n"/>
+      <c r="M43" s="82" t="n"/>
+      <c r="N43" s="82" t="n"/>
+      <c r="O43" s="82" t="n"/>
+      <c r="P43" s="82" t="n"/>
+      <c r="Q43" s="98">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="63">
+      <c r="A44" s="82" t="n"/>
+      <c r="B44" s="82" t="n"/>
+      <c r="C44" s="82" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="82" t="n"/>
+      <c r="F44" s="82" t="n"/>
+      <c r="G44" s="82" t="n"/>
+      <c r="H44" s="82" t="n"/>
+      <c r="I44" s="82" t="n"/>
+      <c r="J44" s="82" t="n"/>
+      <c r="K44" s="82" t="n"/>
+      <c r="L44" s="82" t="n"/>
+      <c r="M44" s="82" t="n"/>
+      <c r="N44" s="82" t="n"/>
+      <c r="O44" s="82" t="n"/>
+      <c r="P44" s="82" t="n"/>
+      <c r="Q44" s="98">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
@@ -3734,125 +5313,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="82" t="n"/>
+      <c r="G1" s="82" t="n"/>
+      <c r="H1" s="82" t="n"/>
+      <c r="I1" s="82" t="n"/>
+      <c r="J1" s="82" t="n"/>
+      <c r="K1" s="82" t="n"/>
+      <c r="L1" s="82" t="n"/>
+      <c r="M1" s="82" t="n"/>
+      <c r="N1" s="82" t="n"/>
+      <c r="O1" s="82" t="n"/>
+      <c r="P1" s="82" t="n"/>
+      <c r="Q1" s="82" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="78" t="inlineStr">
+      <c r="A2" s="82" t="n"/>
+      <c r="B2" s="109" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="82" t="n"/>
+      <c r="D2" s="82" t="n"/>
+      <c r="E2" s="82" t="n"/>
+      <c r="F2" s="82" t="n"/>
+      <c r="G2" s="82" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="82" t="n"/>
+      <c r="J2" s="82" t="n"/>
+      <c r="K2" s="82" t="n"/>
+      <c r="L2" s="82" t="n"/>
+      <c r="M2" s="82" t="n"/>
+      <c r="N2" s="82" t="n"/>
+      <c r="O2" s="82" t="n"/>
+      <c r="P2" s="82" t="n"/>
+      <c r="Q2" s="82" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="82" t="n"/>
+      <c r="B3" s="82" t="n"/>
+      <c r="C3" s="82" t="n"/>
+      <c r="D3" s="82" t="n"/>
+      <c r="E3" s="82" t="n"/>
+      <c r="F3" s="82" t="n"/>
+      <c r="G3" s="82" t="n"/>
+      <c r="H3" s="82" t="n"/>
+      <c r="I3" s="82" t="n"/>
+      <c r="J3" s="82" t="n"/>
+      <c r="K3" s="82" t="n"/>
+      <c r="L3" s="82" t="n"/>
+      <c r="M3" s="82" t="n"/>
+      <c r="N3" s="82" t="n"/>
+      <c r="O3" s="82" t="n"/>
+      <c r="P3" s="82" t="n"/>
+      <c r="Q3" s="82" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="84" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="84" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="84" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="84" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="84" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="84" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="84" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="84" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="84" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="84" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="84" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="84" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="n"/>
+      <c r="Q4" s="84" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>CO-020</t>
         </is>
       </c>
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="104" t="inlineStr">
         <is>
           <t>فقط PROTECT_BATTERY مجاز</t>
         </is>
       </c>
-      <c r="C5" s="56" t="inlineStr">
+      <c r="C5" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="55" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>کد review + تست</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr">
+      <c r="E5" s="106" t="inlineStr">
         <is>
           <t>گام ۱: کد changeover.c را بازبینی کن: تنها جایی که اجازهٔ نوشتن روی خروجی دارد باید func__BspGpio_Write با BSP_GPIO_PROTECT_BATTERY (همان PB11) باشد.
 گام ۲: دنبال هر ارجاع مستقیم به board_pins یا HAL یا PB5/PB7 در این مسیر بگرد؛ نباید هیچ‌کدام باشد.
@@ -3860,68 +5489,68 @@
 گام ۴: اگر PB5 یا PB7 در هیچ تستی تغییر نکرد، قبول است.</t>
         </is>
       </c>
-      <c r="F5" s="57" t="inlineStr">
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>کد + PB11</t>
         </is>
       </c>
-      <c r="G5" s="57" t="inlineStr">
+      <c r="G5" s="105" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="55" t="inlineStr">
+      <c r="H5" s="104" t="inlineStr">
         <is>
           <t>هیچ کد board_pins/HAL/PB5/PB7 نباشد، فقط PB11 تغییر کند. PASS: فقط PB11. FAIL: PB5/7.</t>
         </is>
       </c>
-      <c r="I5" s="55" t="inlineStr">
+      <c r="I5" s="104" t="inlineStr">
         <is>
           <t>PASS: only PB11. FAIL: PB5/7 usage.</t>
         </is>
       </c>
-      <c r="J5" s="55" t="n"/>
-      <c r="K5" s="55" t="inlineStr">
+      <c r="J5" s="104" t="n"/>
+      <c r="K5" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="58" t="n"/>
-      <c r="M5" s="55" t="n"/>
-      <c r="N5" s="55" t="inlineStr">
+      <c r="L5" s="115" t="n"/>
+      <c r="M5" s="104" t="n"/>
+      <c r="N5" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="57" t="n"/>
-      <c r="P5" s="57" t="n"/>
-      <c r="Q5" s="59">
+      <c r="O5" s="105" t="n"/>
+      <c r="P5" s="105" t="n"/>
+      <c r="Q5" s="107">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="99" t="inlineStr">
         <is>
           <t>CO-021</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="100" t="inlineStr">
         <is>
           <t>زمان از rtos_time</t>
         </is>
       </c>
-      <c r="C6" s="50" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="100" t="inlineStr">
         <is>
           <t>هر زمان</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="100" t="inlineStr">
         <is>
           <t>گام ۱: کد را بازبینی کن: همهٔ تبدیل‌های میلی‌ثانیه به تیک باید فقط از func__Rtos_MillisecondsToTicks و زمان فعلی از osKernelGetTickCount گرفته شود.
 گام ۲: دنبال هر جا که «تیک برابر 1 میلی‌ثانیه» فرض شده باشد بگرد؛ نباید هیچ جا باشد.
@@ -3929,68 +5558,68 @@
 گام ۴: رفتار باید با هر فرکانس تیک درست بماند؛ وابستگی به فرض 1 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F6" s="101" t="inlineStr">
         <is>
           <t>کد review</t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
+      <c r="G6" s="101" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="100" t="inlineStr">
         <is>
           <t>زمان با rtos_time قابل‌حمل باشد، 3000ms با هر فرکانس تیک درست کار کند. PASS: portable. FAIL: فرض 1ms.</t>
         </is>
       </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="I6" s="100" t="inlineStr">
         <is>
           <t>PASS: portable via rtos_time. FAIL: hardcoded 1ms.</t>
         </is>
       </c>
-      <c r="J6" s="51" t="n"/>
-      <c r="K6" s="52" t="inlineStr">
+      <c r="J6" s="111" t="n"/>
+      <c r="K6" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="53" t="n"/>
-      <c r="M6" s="48" t="n"/>
-      <c r="N6" s="48" t="inlineStr">
+      <c r="L6" s="113" t="n"/>
+      <c r="M6" s="100" t="n"/>
+      <c r="N6" s="100" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="50" t="n"/>
-      <c r="P6" s="50" t="n"/>
-      <c r="Q6" s="54">
+      <c r="O6" s="101" t="n"/>
+      <c r="P6" s="101" t="n"/>
+      <c r="Q6" s="103">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="99" t="inlineStr">
         <is>
           <t>CO-022</t>
         </is>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="104" t="inlineStr">
         <is>
           <t>durationTicks صفر → no immediate cut</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="55" t="inlineStr">
+      <c r="D7" s="104" t="inlineStr">
         <is>
           <t>BATTERY با شرط قطع</t>
         </is>
       </c>
-      <c r="E7" s="55" t="inlineStr">
+      <c r="E7" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY و شرط قطع برقرار باشد.
 گام ۲: در شبیه‌سازی کاری کن فرکانس تیک صفر شود، طوری که func__Rtos_MillisecondsToTicks مقدار 0 برگرداند.
@@ -3998,68 +5627,68 @@
 گام ۴: هیچ قطع یا وصل فوری نباید اتفاق بیفتد؛ وضعیت و PB11 باید حفظ شوند و فقط تایمر reset شود. قطع فوری یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="57" t="inlineStr">
+      <c r="F7" s="105" t="inlineStr">
         <is>
           <t>valid true v20700 durTicks0</t>
         </is>
       </c>
-      <c r="G7" s="57" t="inlineStr">
+      <c r="G7" s="105" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H7" s="55" t="inlineStr">
+      <c r="H7" s="104" t="inlineStr">
         <is>
           <t>هیچ قطع/وصل فوری انجام نشود، state و PB11 حفظ، تایمر reset. PASS: guard بدون تصمیم. FAIL: قطع فوری.</t>
         </is>
       </c>
-      <c r="I7" s="55" t="inlineStr">
+      <c r="I7" s="104" t="inlineStr">
         <is>
           <t>PASS: guard preserves. FAIL: immediate cut.</t>
         </is>
       </c>
-      <c r="J7" s="55" t="n"/>
-      <c r="K7" s="55" t="inlineStr">
+      <c r="J7" s="104" t="n"/>
+      <c r="K7" s="104" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="58" t="n"/>
-      <c r="M7" s="55" t="n"/>
-      <c r="N7" s="55" t="inlineStr">
+      <c r="L7" s="115" t="n"/>
+      <c r="M7" s="104" t="n"/>
+      <c r="N7" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="57" t="n"/>
-      <c r="P7" s="57" t="n"/>
-      <c r="Q7" s="59">
+      <c r="O7" s="105" t="n"/>
+      <c r="P7" s="105" t="n"/>
+      <c r="Q7" s="107">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="99" t="inlineStr">
         <is>
           <t>CO-023</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="100" t="inlineStr">
         <is>
           <t>snapshot zeroing task_control</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="110" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="48" t="inlineStr">
+      <c r="D8" s="100" t="inlineStr">
         <is>
           <t>MODULE_MEASUREMENT=0 یا GetSnapshot=false</t>
         </is>
       </c>
-      <c r="E8" s="48" t="inlineStr">
+      <c r="E8" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن (یا ADC را نگه دار تا valid=false بماند).
 گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
@@ -4067,167 +5696,487 @@
 گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند؛ هیچ تصمیمی بر اساس زباله قبول نیست.</t>
         </is>
       </c>
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" s="50" t="inlineStr">
+      <c r="G8" s="101" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H8" s="48" t="inlineStr">
+      <c r="H8" s="100" t="inlineStr">
         <is>
           <t>هیچ فیلد snapshot حاوی زباله پشته نباشد؛ Changeover باید فقط روی valid گیت بزند و PB11 امن بماند؛ task_control مانند task_comm/task_ui/task_protection هر 9 فیلد را صفر کند</t>
         </is>
       </c>
-      <c r="I8" s="48" t="inlineStr">
+      <c r="I8" s="100" t="inlineStr">
         <is>
           <t>امن</t>
         </is>
       </c>
-      <c r="J8" s="48" t="inlineStr">
+      <c r="J8" s="100" t="inlineStr">
         <is>
           <t>بدون تصمیم بر اساس زباله؛ PB11 حفظ</t>
         </is>
       </c>
-      <c r="K8" s="48" t="n"/>
-      <c r="L8" s="62" t="inlineStr">
+      <c r="K8" s="100" t="n"/>
+      <c r="L8" s="117" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M8" s="48" t="n"/>
-      <c r="N8" s="48" t="n"/>
-      <c r="O8" s="50" t="inlineStr">
+      <c r="M8" s="100" t="n"/>
+      <c r="N8" s="100" t="n"/>
+      <c r="O8" s="101" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P8" s="50" t="n"/>
-      <c r="Q8" s="54" t="inlineStr">
+      <c r="P8" s="101" t="n"/>
+      <c r="Q8" s="103" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="63">
+      <c r="A9" s="82" t="n"/>
+      <c r="B9" s="82" t="n"/>
+      <c r="C9" s="82" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="82" t="n"/>
+      <c r="F9" s="82" t="n"/>
+      <c r="G9" s="82" t="n"/>
+      <c r="H9" s="82" t="n"/>
+      <c r="I9" s="82" t="n"/>
+      <c r="J9" s="82" t="n"/>
+      <c r="K9" s="82" t="n"/>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
+      <c r="O9" s="82" t="n"/>
+      <c r="P9" s="82" t="n"/>
+      <c r="Q9" s="98">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="63">
+      <c r="A10" s="82" t="n"/>
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="n"/>
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+      <c r="P10" s="82" t="n"/>
+      <c r="Q10" s="98">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="63">
+      <c r="A11" s="82" t="n"/>
+      <c r="B11" s="82" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="82" t="n"/>
+      <c r="J11" s="82" t="n"/>
+      <c r="K11" s="82" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
+      <c r="O11" s="82" t="n"/>
+      <c r="P11" s="82" t="n"/>
+      <c r="Q11" s="98">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="63">
+      <c r="A12" s="82" t="n"/>
+      <c r="B12" s="82" t="n"/>
+      <c r="C12" s="82" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="82" t="n"/>
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="82" t="n"/>
+      <c r="I12" s="82" t="n"/>
+      <c r="J12" s="82" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
+      <c r="N12" s="82" t="n"/>
+      <c r="O12" s="82" t="n"/>
+      <c r="P12" s="82" t="n"/>
+      <c r="Q12" s="98">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="63">
+      <c r="A13" s="82" t="n"/>
+      <c r="B13" s="82" t="n"/>
+      <c r="C13" s="82" t="n"/>
+      <c r="D13" s="82" t="n"/>
+      <c r="E13" s="82" t="n"/>
+      <c r="F13" s="82" t="n"/>
+      <c r="G13" s="82" t="n"/>
+      <c r="H13" s="82" t="n"/>
+      <c r="I13" s="82" t="n"/>
+      <c r="J13" s="82" t="n"/>
+      <c r="K13" s="82" t="n"/>
+      <c r="L13" s="82" t="n"/>
+      <c r="M13" s="82" t="n"/>
+      <c r="N13" s="82" t="n"/>
+      <c r="O13" s="82" t="n"/>
+      <c r="P13" s="82" t="n"/>
+      <c r="Q13" s="98">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="63">
+      <c r="A14" s="82" t="n"/>
+      <c r="B14" s="82" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
+      <c r="G14" s="82" t="n"/>
+      <c r="H14" s="82" t="n"/>
+      <c r="I14" s="82" t="n"/>
+      <c r="J14" s="82" t="n"/>
+      <c r="K14" s="82" t="n"/>
+      <c r="L14" s="82" t="n"/>
+      <c r="M14" s="82" t="n"/>
+      <c r="N14" s="82" t="n"/>
+      <c r="O14" s="82" t="n"/>
+      <c r="P14" s="82" t="n"/>
+      <c r="Q14" s="98">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="63">
+      <c r="A15" s="82" t="n"/>
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="82" t="n"/>
+      <c r="F15" s="82" t="n"/>
+      <c r="G15" s="82" t="n"/>
+      <c r="H15" s="82" t="n"/>
+      <c r="I15" s="82" t="n"/>
+      <c r="J15" s="82" t="n"/>
+      <c r="K15" s="82" t="n"/>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
+      <c r="N15" s="82" t="n"/>
+      <c r="O15" s="82" t="n"/>
+      <c r="P15" s="82" t="n"/>
+      <c r="Q15" s="98">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="63">
+      <c r="A16" s="82" t="n"/>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="82" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="82" t="n"/>
+      <c r="F16" s="82" t="n"/>
+      <c r="G16" s="82" t="n"/>
+      <c r="H16" s="82" t="n"/>
+      <c r="I16" s="82" t="n"/>
+      <c r="J16" s="82" t="n"/>
+      <c r="K16" s="82" t="n"/>
+      <c r="L16" s="82" t="n"/>
+      <c r="M16" s="82" t="n"/>
+      <c r="N16" s="82" t="n"/>
+      <c r="O16" s="82" t="n"/>
+      <c r="P16" s="82" t="n"/>
+      <c r="Q16" s="98">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="63">
+      <c r="A17" s="82" t="n"/>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="82" t="n"/>
+      <c r="J17" s="82" t="n"/>
+      <c r="K17" s="82" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
+      <c r="O17" s="82" t="n"/>
+      <c r="P17" s="82" t="n"/>
+      <c r="Q17" s="98">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="63">
+      <c r="A18" s="82" t="n"/>
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
+      <c r="O18" s="82" t="n"/>
+      <c r="P18" s="82" t="n"/>
+      <c r="Q18" s="98">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="63">
+      <c r="A19" s="82" t="n"/>
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="82" t="n"/>
+      <c r="J19" s="82" t="n"/>
+      <c r="K19" s="82" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
+      <c r="O19" s="82" t="n"/>
+      <c r="P19" s="82" t="n"/>
+      <c r="Q19" s="98">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="63">
+      <c r="A20" s="82" t="n"/>
+      <c r="B20" s="82" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="82" t="n"/>
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="n"/>
+      <c r="K20" s="82" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
+      <c r="O20" s="82" t="n"/>
+      <c r="P20" s="82" t="n"/>
+      <c r="Q20" s="98">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="63">
+      <c r="A21" s="82" t="n"/>
+      <c r="B21" s="82" t="n"/>
+      <c r="C21" s="82" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="82" t="n"/>
+      <c r="F21" s="82" t="n"/>
+      <c r="G21" s="82" t="n"/>
+      <c r="H21" s="82" t="n"/>
+      <c r="I21" s="82" t="n"/>
+      <c r="J21" s="82" t="n"/>
+      <c r="K21" s="82" t="n"/>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
+      <c r="N21" s="82" t="n"/>
+      <c r="O21" s="82" t="n"/>
+      <c r="P21" s="82" t="n"/>
+      <c r="Q21" s="98">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="63">
+      <c r="A22" s="82" t="n"/>
+      <c r="B22" s="82" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="82" t="n"/>
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="82" t="n"/>
+      <c r="P22" s="82" t="n"/>
+      <c r="Q22" s="98">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="63">
+      <c r="A23" s="82" t="n"/>
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="82" t="n"/>
+      <c r="J23" s="82" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="82" t="n"/>
+      <c r="P23" s="82" t="n"/>
+      <c r="Q23" s="98">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="63">
+      <c r="A24" s="82" t="n"/>
+      <c r="B24" s="82" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="82" t="n"/>
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="82" t="n"/>
+      <c r="H24" s="82" t="n"/>
+      <c r="I24" s="82" t="n"/>
+      <c r="J24" s="82" t="n"/>
+      <c r="K24" s="82" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
+      <c r="O24" s="82" t="n"/>
+      <c r="P24" s="82" t="n"/>
+      <c r="Q24" s="98">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="63">
+      <c r="A25" s="82" t="n"/>
+      <c r="B25" s="82" t="n"/>
+      <c r="C25" s="82" t="n"/>
+      <c r="D25" s="82" t="n"/>
+      <c r="E25" s="82" t="n"/>
+      <c r="F25" s="82" t="n"/>
+      <c r="G25" s="82" t="n"/>
+      <c r="H25" s="82" t="n"/>
+      <c r="I25" s="82" t="n"/>
+      <c r="J25" s="82" t="n"/>
+      <c r="K25" s="82" t="n"/>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
+      <c r="N25" s="82" t="n"/>
+      <c r="O25" s="82" t="n"/>
+      <c r="P25" s="82" t="n"/>
+      <c r="Q25" s="98">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="63">
+      <c r="A26" s="82" t="n"/>
+      <c r="B26" s="82" t="n"/>
+      <c r="C26" s="82" t="n"/>
+      <c r="D26" s="82" t="n"/>
+      <c r="E26" s="82" t="n"/>
+      <c r="F26" s="82" t="n"/>
+      <c r="G26" s="82" t="n"/>
+      <c r="H26" s="82" t="n"/>
+      <c r="I26" s="82" t="n"/>
+      <c r="J26" s="82" t="n"/>
+      <c r="K26" s="82" t="n"/>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
+      <c r="N26" s="82" t="n"/>
+      <c r="O26" s="82" t="n"/>
+      <c r="P26" s="82" t="n"/>
+      <c r="Q26" s="98">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="63">
+      <c r="A27" s="82" t="n"/>
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="82" t="n"/>
+      <c r="D27" s="82" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
+      <c r="G27" s="82" t="n"/>
+      <c r="H27" s="82" t="n"/>
+      <c r="I27" s="82" t="n"/>
+      <c r="J27" s="82" t="n"/>
+      <c r="K27" s="82" t="n"/>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="82" t="n"/>
+      <c r="N27" s="82" t="n"/>
+      <c r="O27" s="82" t="n"/>
+      <c r="P27" s="82" t="n"/>
+      <c r="Q27" s="98">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="63">
+      <c r="A28" s="82" t="n"/>
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="82" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="82" t="n"/>
+      <c r="F28" s="82" t="n"/>
+      <c r="G28" s="82" t="n"/>
+      <c r="H28" s="82" t="n"/>
+      <c r="I28" s="82" t="n"/>
+      <c r="J28" s="82" t="n"/>
+      <c r="K28" s="82" t="n"/>
+      <c r="L28" s="82" t="n"/>
+      <c r="M28" s="82" t="n"/>
+      <c r="N28" s="82" t="n"/>
+      <c r="O28" s="82" t="n"/>
+      <c r="P28" s="82" t="n"/>
+      <c r="Q28" s="98">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
@@ -4263,435 +6212,440 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوهای Changeover</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
-      <c r="C1" s="8" t="n"/>
-      <c r="D1" s="8" t="n"/>
-      <c r="E1" s="8" t="n"/>
-      <c r="F1" s="9" t="n"/>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="86" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="118" t="inlineStr">
         <is>
           <t>این صفحه مرجع انتظار است؛ نتیجه واقعی فقط در «برنامه تست» ثبت شود. مقادیر از کد واقعی استخراج شده؛ مقدار حدسی وجود ندارد.</t>
         </is>
       </c>
+      <c r="B2" s="82" t="n"/>
+      <c r="C2" s="82" t="n"/>
+      <c r="D2" s="82" t="n"/>
+      <c r="E2" s="82" t="n"/>
+      <c r="F2" s="82" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="90" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="90" t="inlineStr">
         <is>
           <t>شرط / مقدار (از کد)</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="90" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="90" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="90" t="inlineStr">
         <is>
           <t>توضیح تکمیلی</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
+      <c r="F3" s="90" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="119" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="119" t="inlineStr">
         <is>
           <t>valid==false یا NULL</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="119" t="inlineStr">
         <is>
           <t>state حفظ، PB11 حفظ، تایمر reset</t>
         </is>
       </c>
-      <c r="D4" s="66" t="inlineStr">
+      <c r="D4" s="120" t="inlineStr">
         <is>
           <t>changeover.c:valid check</t>
         </is>
       </c>
-      <c r="E4" s="65" t="inlineStr">
+      <c r="E4" s="119" t="inlineStr">
         <is>
           <t>زمان نامعتبر شمرده نشود</t>
         </is>
       </c>
-      <c r="F4" s="66" t="inlineStr">
+      <c r="F4" s="120" t="inlineStr">
         <is>
           <t>CO-001,002,017</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="119" t="inlineStr">
         <is>
           <t>Fault</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="119" t="inlineStr">
         <is>
           <t>fault_mask !=0</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="119" t="inlineStr">
         <is>
           <t>state=FAULT، هیچ pin تغییر نکند</t>
         </is>
       </c>
-      <c r="D5" s="65" t="inlineStr">
+      <c r="D5" s="119" t="inlineStr">
         <is>
           <t>FAULT_NONE</t>
         </is>
       </c>
-      <c r="E5" s="65" t="inlineStr">
+      <c r="E5" s="119" t="inlineStr">
         <is>
           <t>بالاترین اولویت پس از valid</t>
         </is>
       </c>
-      <c r="F5" s="66" t="inlineStr">
+      <c r="F5" s="120" t="inlineStr">
         <is>
           <t>CO-004,005,018</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="119" t="inlineStr">
         <is>
           <t>قطع با آلارم</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="119" t="inlineStr">
         <is>
           <t>v&lt;21000 و فلگ true</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="119" t="inlineStr">
         <is>
           <t>پس از 3000ms PB11 Low (قطع) → SAFE</t>
         </is>
       </c>
-      <c r="D6" s="65" t="inlineStr">
+      <c r="D6" s="119" t="inlineStr">
         <is>
           <t>CHANGEOVER_BAT_LOW_ALARM_CUT_MV=21000</t>
         </is>
       </c>
-      <c r="E6" s="65" t="inlineStr">
+      <c r="E6" s="119" t="inlineStr">
         <is>
           <t>پیوسته</t>
         </is>
       </c>
-      <c r="F6" s="66" t="inlineStr">
+      <c r="F6" s="120" t="inlineStr">
         <is>
           <t>CO-008,010,012</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="119" t="inlineStr">
         <is>
           <t>قطع مستقل</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="119" t="inlineStr">
         <is>
           <t>v&lt;20800 (بدون فلگ)</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="119" t="inlineStr">
         <is>
           <t>پس از 3000ms PB11 Low</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="119" t="inlineStr">
         <is>
           <t>CHANGEOVER_BAT_CRITICAL_CUT_MV=20800</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr">
+      <c r="E7" s="119" t="inlineStr">
         <is>
           <t>مستقل</t>
         </is>
       </c>
-      <c r="F7" s="66" t="inlineStr">
+      <c r="F7" s="120" t="inlineStr">
         <is>
           <t>CO-009,011</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="119" t="inlineStr">
         <is>
           <t>فیلتر زمان</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="119" t="inlineStr">
         <is>
           <t>هر شرط &lt;3000ms</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="119" t="inlineStr">
         <is>
           <t>عدم قطع/وصل</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="119" t="inlineStr">
         <is>
           <t>CHANGEOVER_DURATION_MS=3000</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E8" s="119" t="inlineStr">
         <is>
           <t>از rtos_time</t>
         </is>
       </c>
-      <c r="F8" s="66" t="inlineStr">
+      <c r="F8" s="120" t="inlineStr">
         <is>
           <t>CO-012,015</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="119" t="inlineStr">
         <is>
           <t>وصل مجدد</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="119" t="inlineStr">
         <is>
           <t>input==true و v≥21200</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="119" t="inlineStr">
         <is>
           <t>پس از 3000ms PB11 High → INPUT</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="119" t="inlineStr">
         <is>
           <t>CHANGEOVER_BAT_RECONNECT_MV=21200</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="119" t="inlineStr">
         <is>
           <t>هر دو پیوسته</t>
         </is>
       </c>
-      <c r="F9" s="66" t="inlineStr">
+      <c r="F9" s="120" t="inlineStr">
         <is>
           <t>CO-013,014,016</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="119" t="inlineStr">
         <is>
           <t>پس از reconnect</t>
         </is>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="119" t="inlineStr">
         <is>
           <t>state=INPUT</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="119" t="inlineStr">
         <is>
           <t>نه IDLE</t>
         </is>
       </c>
-      <c r="D10" s="66" t="inlineStr">
+      <c r="D10" s="120" t="inlineStr">
         <is>
           <t>app_types.h</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
+      <c r="E10" s="119" t="inlineStr">
         <is>
           <t>IDLE ممنوع برای valid</t>
         </is>
       </c>
-      <c r="F10" s="66" t="inlineStr">
+      <c r="F10" s="120" t="inlineStr">
         <is>
           <t>CO-016</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="119" t="inlineStr">
         <is>
           <t>PB11 حفظ</t>
         </is>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="119" t="inlineStr">
         <is>
           <t>invalid/fault</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="119" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="D11" s="65" t="inlineStr">
+      <c r="D11" s="119" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="65" t="inlineStr">
+      <c r="E11" s="119" t="inlineStr">
         <is>
           <t>snapshot-first</t>
         </is>
       </c>
-      <c r="F11" s="66" t="inlineStr">
+      <c r="F11" s="120" t="inlineStr">
         <is>
           <t>CO-017,018</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="119" t="inlineStr">
         <is>
           <t>PB5/PB7</t>
         </is>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="119" t="inlineStr">
         <is>
           <t>هیچ‌گاه</t>
         </is>
       </c>
-      <c r="C12" s="65" t="inlineStr">
+      <c r="C12" s="119" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="D12" s="66" t="inlineStr">
+      <c r="D12" s="120" t="inlineStr">
         <is>
           <t>bsp_gpio.h:Forbidden</t>
         </is>
       </c>
-      <c r="E12" s="65" t="inlineStr">
+      <c r="E12" s="119" t="inlineStr">
         <is>
           <t>فقط PROTECT_BATTERY</t>
         </is>
       </c>
-      <c r="F12" s="66" t="inlineStr">
+      <c r="F12" s="120" t="inlineStr">
         <is>
           <t>CO-019,020</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="119" t="inlineStr">
         <is>
           <t>زمان</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="119" t="inlineStr">
         <is>
           <t>ticks→ms via rtos_time</t>
         </is>
       </c>
-      <c r="C13" s="65" t="inlineStr">
+      <c r="C13" s="119" t="inlineStr">
         <is>
           <t>بدون فرض 1ms</t>
         </is>
       </c>
-      <c r="D13" s="65" t="inlineStr">
+      <c r="D13" s="119" t="inlineStr">
         <is>
           <t>func__Rtos_MillisecondsToTicks</t>
         </is>
       </c>
-      <c r="E13" s="65" t="inlineStr">
+      <c r="E13" s="119" t="inlineStr">
         <is>
           <t>قابل‌حمل</t>
         </is>
       </c>
-      <c r="F13" s="66" t="inlineStr">
+      <c r="F13" s="120" t="inlineStr">
         <is>
           <t>CO-021</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="119" t="inlineStr">
         <is>
           <t>duration0</t>
         </is>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="119" t="inlineStr">
         <is>
           <t>Ticks==0</t>
         </is>
       </c>
-      <c r="C14" s="65" t="inlineStr">
+      <c r="C14" s="119" t="inlineStr">
         <is>
           <t>بدون تصمیم، حفظ state/PB11</t>
         </is>
       </c>
-      <c r="D14" s="66" t="inlineStr">
+      <c r="D14" s="120" t="inlineStr">
         <is>
           <t>changeover.c guard</t>
         </is>
       </c>
-      <c r="E14" s="65" t="inlineStr">
+      <c r="E14" s="119" t="inlineStr">
         <is>
           <t>frequency 0</t>
         </is>
       </c>
-      <c r="F14" s="66" t="inlineStr">
+      <c r="F14" s="120" t="inlineStr">
         <is>
           <t>CO-022</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="65" t="inlineStr">
+      <c r="A15" s="119" t="inlineStr">
         <is>
           <t>منبع داده</t>
         </is>
       </c>
-      <c r="B15" s="65" t="inlineStr">
+      <c r="B15" s="119" t="inlineStr">
         <is>
           <t>فقط 5 ورودی مجاز</t>
         </is>
       </c>
-      <c r="C15" s="65" t="inlineStr">
+      <c r="C15" s="119" t="inlineStr">
         <is>
           <t>عدم استفاده از v_in/v_bat12 و ...</t>
         </is>
       </c>
-      <c r="D15" s="66" t="inlineStr">
+      <c r="D15" s="120" t="inlineStr">
         <is>
           <t>app_types.h</t>
         </is>
       </c>
-      <c r="E15" s="65" t="inlineStr">
+      <c r="E15" s="119" t="inlineStr">
         <is>
           <t>محدودیت</t>
         </is>
       </c>
-      <c r="F15" s="66" t="inlineStr">
+      <c r="F15" s="120" t="inlineStr">
         <is>
           <t>CO-020</t>
         </is>
@@ -4753,247 +6707,259 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="82" t="n"/>
+      <c r="G1" s="82" t="n"/>
+      <c r="H1" s="82" t="n"/>
+      <c r="I1" s="82" t="n"/>
+      <c r="J1" s="82" t="n"/>
+      <c r="K1" s="82" t="n"/>
+      <c r="L1" s="82" t="n"/>
+      <c r="M1" s="82" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="9" t="n"/>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
+      <c r="G2" s="85" t="n"/>
+      <c r="H2" s="85" t="n"/>
+      <c r="I2" s="85" t="n"/>
+      <c r="J2" s="85" t="n"/>
+      <c r="K2" s="85" t="n"/>
+      <c r="L2" s="85" t="n"/>
+      <c r="M2" s="86" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="90" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="90" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="90" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="90" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="90" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
+      <c r="F3" s="90" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="41" t="inlineStr">
+      <c r="G3" s="90" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="41" t="inlineStr">
+      <c r="H3" s="90" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="41" t="inlineStr">
+      <c r="I3" s="90" t="inlineStr">
         <is>
           <t>مدرک / مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="41" t="inlineStr">
+      <c r="J3" s="90" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="41" t="inlineStr">
+      <c r="K3" s="90" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="41" t="inlineStr">
+      <c r="L3" s="90" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="41" t="inlineStr">
+      <c r="M3" s="90" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="23" t="inlineStr"/>
-      <c r="B4" s="23" t="inlineStr"/>
-      <c r="C4" s="23" t="inlineStr"/>
-      <c r="D4" s="23" t="inlineStr"/>
-      <c r="E4" s="23" t="inlineStr"/>
-      <c r="F4" s="23" t="inlineStr"/>
-      <c r="G4" s="23" t="inlineStr"/>
-      <c r="H4" s="23" t="inlineStr"/>
-      <c r="I4" s="23" t="inlineStr"/>
-      <c r="J4" s="23" t="inlineStr"/>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="23" t="inlineStr"/>
-      <c r="M4" s="23" t="inlineStr"/>
+      <c r="A4" s="122" t="inlineStr"/>
+      <c r="B4" s="122" t="inlineStr"/>
+      <c r="C4" s="122" t="inlineStr"/>
+      <c r="D4" s="122" t="inlineStr"/>
+      <c r="E4" s="122" t="inlineStr"/>
+      <c r="F4" s="122" t="inlineStr"/>
+      <c r="G4" s="122" t="inlineStr"/>
+      <c r="H4" s="122" t="inlineStr"/>
+      <c r="I4" s="122" t="inlineStr"/>
+      <c r="J4" s="122" t="inlineStr"/>
+      <c r="K4" s="122" t="inlineStr"/>
+      <c r="L4" s="122" t="inlineStr"/>
+      <c r="M4" s="122" t="inlineStr"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="24" t="inlineStr"/>
-      <c r="B5" s="24" t="inlineStr"/>
-      <c r="C5" s="24" t="inlineStr"/>
-      <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="24" t="inlineStr"/>
-      <c r="F5" s="24" t="inlineStr"/>
-      <c r="G5" s="24" t="inlineStr"/>
-      <c r="H5" s="24" t="inlineStr"/>
-      <c r="I5" s="24" t="inlineStr"/>
-      <c r="J5" s="24" t="inlineStr"/>
-      <c r="K5" s="24" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr"/>
-      <c r="M5" s="24" t="inlineStr"/>
+      <c r="A5" s="123" t="inlineStr"/>
+      <c r="B5" s="123" t="inlineStr"/>
+      <c r="C5" s="123" t="inlineStr"/>
+      <c r="D5" s="123" t="inlineStr"/>
+      <c r="E5" s="123" t="inlineStr"/>
+      <c r="F5" s="123" t="inlineStr"/>
+      <c r="G5" s="123" t="inlineStr"/>
+      <c r="H5" s="123" t="inlineStr"/>
+      <c r="I5" s="123" t="inlineStr"/>
+      <c r="J5" s="123" t="inlineStr"/>
+      <c r="K5" s="123" t="inlineStr"/>
+      <c r="L5" s="123" t="inlineStr"/>
+      <c r="M5" s="123" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="23" t="inlineStr"/>
-      <c r="B6" s="23" t="inlineStr"/>
-      <c r="C6" s="23" t="inlineStr"/>
-      <c r="D6" s="23" t="inlineStr"/>
-      <c r="E6" s="23" t="inlineStr"/>
-      <c r="F6" s="23" t="inlineStr"/>
-      <c r="G6" s="23" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr"/>
-      <c r="I6" s="23" t="inlineStr"/>
-      <c r="J6" s="23" t="inlineStr"/>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="23" t="inlineStr"/>
-      <c r="M6" s="23" t="inlineStr"/>
+      <c r="A6" s="122" t="inlineStr"/>
+      <c r="B6" s="122" t="inlineStr"/>
+      <c r="C6" s="122" t="inlineStr"/>
+      <c r="D6" s="122" t="inlineStr"/>
+      <c r="E6" s="122" t="inlineStr"/>
+      <c r="F6" s="122" t="inlineStr"/>
+      <c r="G6" s="122" t="inlineStr"/>
+      <c r="H6" s="122" t="inlineStr"/>
+      <c r="I6" s="122" t="inlineStr"/>
+      <c r="J6" s="122" t="inlineStr"/>
+      <c r="K6" s="122" t="inlineStr"/>
+      <c r="L6" s="122" t="inlineStr"/>
+      <c r="M6" s="122" t="inlineStr"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="24" t="inlineStr"/>
-      <c r="B7" s="24" t="inlineStr"/>
-      <c r="C7" s="24" t="inlineStr"/>
-      <c r="D7" s="24" t="inlineStr"/>
-      <c r="E7" s="24" t="inlineStr"/>
-      <c r="F7" s="24" t="inlineStr"/>
-      <c r="G7" s="24" t="inlineStr"/>
-      <c r="H7" s="24" t="inlineStr"/>
-      <c r="I7" s="24" t="inlineStr"/>
-      <c r="J7" s="24" t="inlineStr"/>
-      <c r="K7" s="24" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr"/>
-      <c r="M7" s="24" t="inlineStr"/>
+      <c r="A7" s="123" t="inlineStr"/>
+      <c r="B7" s="123" t="inlineStr"/>
+      <c r="C7" s="123" t="inlineStr"/>
+      <c r="D7" s="123" t="inlineStr"/>
+      <c r="E7" s="123" t="inlineStr"/>
+      <c r="F7" s="123" t="inlineStr"/>
+      <c r="G7" s="123" t="inlineStr"/>
+      <c r="H7" s="123" t="inlineStr"/>
+      <c r="I7" s="123" t="inlineStr"/>
+      <c r="J7" s="123" t="inlineStr"/>
+      <c r="K7" s="123" t="inlineStr"/>
+      <c r="L7" s="123" t="inlineStr"/>
+      <c r="M7" s="123" t="inlineStr"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="23" t="inlineStr"/>
-      <c r="B8" s="23" t="inlineStr"/>
-      <c r="C8" s="23" t="inlineStr"/>
-      <c r="D8" s="23" t="inlineStr"/>
-      <c r="E8" s="23" t="inlineStr"/>
-      <c r="F8" s="23" t="inlineStr"/>
-      <c r="G8" s="23" t="inlineStr"/>
-      <c r="H8" s="23" t="inlineStr"/>
-      <c r="I8" s="23" t="inlineStr"/>
-      <c r="J8" s="23" t="inlineStr"/>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="23" t="inlineStr"/>
-      <c r="M8" s="23" t="inlineStr"/>
+      <c r="A8" s="122" t="inlineStr"/>
+      <c r="B8" s="122" t="inlineStr"/>
+      <c r="C8" s="122" t="inlineStr"/>
+      <c r="D8" s="122" t="inlineStr"/>
+      <c r="E8" s="122" t="inlineStr"/>
+      <c r="F8" s="122" t="inlineStr"/>
+      <c r="G8" s="122" t="inlineStr"/>
+      <c r="H8" s="122" t="inlineStr"/>
+      <c r="I8" s="122" t="inlineStr"/>
+      <c r="J8" s="122" t="inlineStr"/>
+      <c r="K8" s="122" t="inlineStr"/>
+      <c r="L8" s="122" t="inlineStr"/>
+      <c r="M8" s="122" t="inlineStr"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="24" t="inlineStr"/>
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr"/>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr"/>
-      <c r="F9" s="24" t="inlineStr"/>
-      <c r="G9" s="24" t="inlineStr"/>
-      <c r="H9" s="24" t="inlineStr"/>
-      <c r="I9" s="24" t="inlineStr"/>
-      <c r="J9" s="24" t="inlineStr"/>
-      <c r="K9" s="24" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr"/>
-      <c r="M9" s="24" t="inlineStr"/>
+      <c r="A9" s="123" t="inlineStr"/>
+      <c r="B9" s="123" t="inlineStr"/>
+      <c r="C9" s="123" t="inlineStr"/>
+      <c r="D9" s="123" t="inlineStr"/>
+      <c r="E9" s="123" t="inlineStr"/>
+      <c r="F9" s="123" t="inlineStr"/>
+      <c r="G9" s="123" t="inlineStr"/>
+      <c r="H9" s="123" t="inlineStr"/>
+      <c r="I9" s="123" t="inlineStr"/>
+      <c r="J9" s="123" t="inlineStr"/>
+      <c r="K9" s="123" t="inlineStr"/>
+      <c r="L9" s="123" t="inlineStr"/>
+      <c r="M9" s="123" t="inlineStr"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="23" t="inlineStr"/>
-      <c r="B10" s="23" t="inlineStr"/>
-      <c r="C10" s="23" t="inlineStr"/>
-      <c r="D10" s="23" t="inlineStr"/>
-      <c r="E10" s="23" t="inlineStr"/>
-      <c r="F10" s="23" t="inlineStr"/>
-      <c r="G10" s="23" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr"/>
-      <c r="I10" s="23" t="inlineStr"/>
-      <c r="J10" s="23" t="inlineStr"/>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="23" t="inlineStr"/>
-      <c r="M10" s="23" t="inlineStr"/>
+      <c r="A10" s="122" t="inlineStr"/>
+      <c r="B10" s="122" t="inlineStr"/>
+      <c r="C10" s="122" t="inlineStr"/>
+      <c r="D10" s="122" t="inlineStr"/>
+      <c r="E10" s="122" t="inlineStr"/>
+      <c r="F10" s="122" t="inlineStr"/>
+      <c r="G10" s="122" t="inlineStr"/>
+      <c r="H10" s="122" t="inlineStr"/>
+      <c r="I10" s="122" t="inlineStr"/>
+      <c r="J10" s="122" t="inlineStr"/>
+      <c r="K10" s="122" t="inlineStr"/>
+      <c r="L10" s="122" t="inlineStr"/>
+      <c r="M10" s="122" t="inlineStr"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="24" t="inlineStr"/>
-      <c r="B11" s="24" t="inlineStr"/>
-      <c r="C11" s="24" t="inlineStr"/>
-      <c r="D11" s="24" t="inlineStr"/>
-      <c r="E11" s="24" t="inlineStr"/>
-      <c r="F11" s="24" t="inlineStr"/>
-      <c r="G11" s="24" t="inlineStr"/>
-      <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="24" t="inlineStr"/>
-      <c r="J11" s="24" t="inlineStr"/>
-      <c r="K11" s="24" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr"/>
-      <c r="M11" s="24" t="inlineStr"/>
+      <c r="A11" s="123" t="inlineStr"/>
+      <c r="B11" s="123" t="inlineStr"/>
+      <c r="C11" s="123" t="inlineStr"/>
+      <c r="D11" s="123" t="inlineStr"/>
+      <c r="E11" s="123" t="inlineStr"/>
+      <c r="F11" s="123" t="inlineStr"/>
+      <c r="G11" s="123" t="inlineStr"/>
+      <c r="H11" s="123" t="inlineStr"/>
+      <c r="I11" s="123" t="inlineStr"/>
+      <c r="J11" s="123" t="inlineStr"/>
+      <c r="K11" s="123" t="inlineStr"/>
+      <c r="L11" s="123" t="inlineStr"/>
+      <c r="M11" s="123" t="inlineStr"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="23" t="inlineStr"/>
-      <c r="B12" s="23" t="inlineStr"/>
-      <c r="C12" s="23" t="inlineStr"/>
-      <c r="D12" s="23" t="inlineStr"/>
-      <c r="E12" s="23" t="inlineStr"/>
-      <c r="F12" s="23" t="inlineStr"/>
-      <c r="G12" s="23" t="inlineStr"/>
-      <c r="H12" s="23" t="inlineStr"/>
-      <c r="I12" s="23" t="inlineStr"/>
-      <c r="J12" s="23" t="inlineStr"/>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="23" t="inlineStr"/>
-      <c r="M12" s="23" t="inlineStr"/>
+      <c r="A12" s="122" t="inlineStr"/>
+      <c r="B12" s="122" t="inlineStr"/>
+      <c r="C12" s="122" t="inlineStr"/>
+      <c r="D12" s="122" t="inlineStr"/>
+      <c r="E12" s="122" t="inlineStr"/>
+      <c r="F12" s="122" t="inlineStr"/>
+      <c r="G12" s="122" t="inlineStr"/>
+      <c r="H12" s="122" t="inlineStr"/>
+      <c r="I12" s="122" t="inlineStr"/>
+      <c r="J12" s="122" t="inlineStr"/>
+      <c r="K12" s="122" t="inlineStr"/>
+      <c r="L12" s="122" t="inlineStr"/>
+      <c r="M12" s="122" t="inlineStr"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="24" t="inlineStr"/>
-      <c r="B13" s="24" t="inlineStr"/>
-      <c r="C13" s="24" t="inlineStr"/>
-      <c r="D13" s="24" t="inlineStr"/>
-      <c r="E13" s="24" t="inlineStr"/>
-      <c r="F13" s="24" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr"/>
-      <c r="H13" s="24" t="inlineStr"/>
-      <c r="I13" s="24" t="inlineStr"/>
-      <c r="J13" s="24" t="inlineStr"/>
-      <c r="K13" s="24" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr"/>
-      <c r="M13" s="24" t="inlineStr"/>
+      <c r="A13" s="123" t="inlineStr"/>
+      <c r="B13" s="123" t="inlineStr"/>
+      <c r="C13" s="123" t="inlineStr"/>
+      <c r="D13" s="123" t="inlineStr"/>
+      <c r="E13" s="123" t="inlineStr"/>
+      <c r="F13" s="123" t="inlineStr"/>
+      <c r="G13" s="123" t="inlineStr"/>
+      <c r="H13" s="123" t="inlineStr"/>
+      <c r="I13" s="123" t="inlineStr"/>
+      <c r="J13" s="123" t="inlineStr"/>
+      <c r="K13" s="123" t="inlineStr"/>
+      <c r="L13" s="123" t="inlineStr"/>
+      <c r="M13" s="123" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5025,460 +6991,490 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
+      <c r="A1" s="124" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — Changeover — PB11</t>
         </is>
       </c>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="82" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="125" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بستن ایرادهای باز امضا شود. بدون تکمیل این صفحه، اعتبارسنجی ناقص است.</t>
         </is>
       </c>
+      <c r="B2" s="82" t="n"/>
+      <c r="C2" s="82" t="n"/>
+      <c r="D2" s="82" t="n"/>
+      <c r="E2" s="82" t="n"/>
+      <c r="F2" s="82" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="40" t="inlineStr">
+      <c r="A3" s="89" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="82" t="n"/>
+      <c r="C3" s="82" t="n"/>
+      <c r="D3" s="82" t="n"/>
+      <c r="E3" s="82" t="n"/>
+      <c r="F3" s="82" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="126" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="C4" s="70" t="inlineStr">
+      <c r="C4" s="126" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="92" t="inlineStr">
         <is>
           <t>Changeover — PB11</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="9" t="n"/>
+      <c r="E4" s="93" t="n"/>
+      <c r="F4" s="86" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="126" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="92" t="inlineStr">
         <is>
           <t>2026-09-16 (2.1 — فیلتر 3000ms)</t>
         </is>
       </c>
-      <c r="C5" s="70" t="inlineStr">
+      <c r="C5" s="126" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="92" t="inlineStr">
         <is>
           <t>2.1 — فیلتر 3000ms</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="9" t="n"/>
+      <c r="E5" s="93" t="n"/>
+      <c r="F5" s="86" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="126" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="126" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="9" t="n"/>
+      <c r="D6" s="127" t="inlineStr"/>
+      <c r="E6" s="93" t="n"/>
+      <c r="F6" s="86" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="126" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr"/>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="B7" s="127" t="inlineStr"/>
+      <c r="C7" s="126" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="9" t="n"/>
+      <c r="D7" s="127" t="inlineStr"/>
+      <c r="E7" s="93" t="n"/>
+      <c r="F7" s="86" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="126" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr"/>
-      <c r="C8" s="70" t="inlineStr">
+      <c r="B8" s="127" t="inlineStr"/>
+      <c r="C8" s="126" t="inlineStr">
         <is>
           <t>ابزار اندازه‌گیری</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="92" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسیلوسکوپ + تایمر RTOS</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="E8" s="93" t="n"/>
+      <c r="F8" s="86" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="126" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="92" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr"/>
-      <c r="D9" s="27" t="inlineStr"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="9" t="n"/>
+      <c r="C9" s="126" t="inlineStr"/>
+      <c r="D9" s="127" t="inlineStr"/>
+      <c r="E9" s="93" t="n"/>
+      <c r="F9" s="86" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="70" t="inlineStr">
+      <c r="A10" s="126" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="92" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr"/>
-      <c r="D10" s="27" t="inlineStr"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
+      <c r="C10" s="126" t="inlineStr"/>
+      <c r="D10" s="127" t="inlineStr"/>
+      <c r="E10" s="93" t="n"/>
+      <c r="F10" s="93" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="A11" s="126" t="inlineStr">
         <is>
           <t>آستانه‌ها</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="92" t="inlineStr">
         <is>
           <t>21000/20800/21200</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr"/>
-      <c r="D11" s="27" t="inlineStr"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="C11" s="126" t="inlineStr"/>
+      <c r="D11" s="127" t="inlineStr"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="126" t="inlineStr">
         <is>
           <t>فیلتر</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>3000ms</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr"/>
-      <c r="D12" s="27" t="inlineStr"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="C12" s="126" t="inlineStr"/>
+      <c r="D12" s="127" t="inlineStr"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="126" t="inlineStr">
         <is>
           <t>مجاز pin</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="92" t="inlineStr">
         <is>
           <t>فقط BSP_GPIO_PROTECT_BATTERY</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr"/>
-      <c r="D13" s="27" t="inlineStr"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
+      <c r="C13" s="126" t="inlineStr"/>
+      <c r="D13" s="127" t="inlineStr"/>
+      <c r="E13" s="93" t="n"/>
+      <c r="F13" s="93" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="70" t="inlineStr">
+      <c r="A14" s="126" t="inlineStr">
         <is>
           <t>ممنوع</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="92" t="inlineStr">
         <is>
           <t>PB5/PB7/HAL/board_pins</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr"/>
-      <c r="D14" s="27" t="inlineStr"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
+      <c r="C14" s="126" t="inlineStr"/>
+      <c r="D14" s="127" t="inlineStr"/>
+      <c r="E14" s="93" t="n"/>
+      <c r="F14" s="93" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="89" t="inlineStr">
         <is>
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="82" t="n"/>
+      <c r="F15" s="82" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="90" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="90" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C16" s="41" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="90" t="inlineStr">
         <is>
           <t>فرمول پیشنهادی</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="9" t="n"/>
+      <c r="E16" s="85" t="n"/>
+      <c r="F16" s="86" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="92" t="inlineStr">
         <is>
           <t>تعداد کل تست‌ها</t>
         </is>
       </c>
-      <c r="B17" s="71">
+      <c r="B17" s="128">
         <f>COUNTA('برنامه تست'!A5:A200)</f>
         <v/>
       </c>
-      <c r="C17" s="42" t="inlineStr">
+      <c r="C17" s="92" t="inlineStr">
         <is>
           <t>کل ردیف‌های برنامه تست</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="9" t="n"/>
+      <c r="D17" s="92" t="inlineStr"/>
+      <c r="E17" s="85" t="n"/>
+      <c r="F17" s="86" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="92" t="inlineStr">
         <is>
           <t>تعداد قبول (PASS)</t>
         </is>
       </c>
-      <c r="B18" s="71">
+      <c r="B18" s="128">
         <f>COUNTIF('برنامه تست'!K5:K200,"قبول")</f>
         <v/>
       </c>
-      <c r="C18" s="42" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = قبول</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="E18" s="85" t="n"/>
+      <c r="F18" s="86" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="92" t="inlineStr">
         <is>
           <t>تعداد رد (FAIL)</t>
         </is>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="128">
         <f>COUNTIF('برنامه تست'!K5:K200,"رد")</f>
         <v/>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="92" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = رد</t>
         </is>
       </c>
-      <c r="D19" s="42" t="inlineStr">
+      <c r="D19" s="92" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n"/>
+      <c r="E19" s="85" t="n"/>
+      <c r="F19" s="86" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="A20" s="92" t="inlineStr">
         <is>
           <t>تعداد در انتظار</t>
         </is>
       </c>
-      <c r="B20" s="71">
+      <c r="B20" s="128">
         <f>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C20" s="42" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = در انتظار</t>
         </is>
       </c>
-      <c r="D20" s="42" t="inlineStr">
+      <c r="D20" s="92" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="86" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="92" t="inlineStr">
         <is>
           <t>تعداد مسدود</t>
         </is>
       </c>
-      <c r="B21" s="71">
+      <c r="B21" s="128">
         <f>COUNTIF('برنامه تست'!K5:K200,"مسدود")</f>
         <v/>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="C21" s="92" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = مسدود</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="9" t="n"/>
+      <c r="D21" s="92" t="inlineStr"/>
+      <c r="E21" s="85" t="n"/>
+      <c r="F21" s="86" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="92" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B22" s="71">
+      <c r="B22" s="128">
         <f>IF(B17=0,"",TEXT(B18/B17,"0%"))</f>
         <v/>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>PASS / TOTAL</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="9" t="n"/>
+      <c r="D22" s="92" t="inlineStr"/>
+      <c r="E22" s="85" t="n"/>
+      <c r="F22" s="86" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="89" t="inlineStr">
         <is>
           <t>امضاها</t>
         </is>
       </c>
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="90" t="inlineStr">
         <is>
           <t>نقش</t>
         </is>
       </c>
-      <c r="B24" s="41" t="inlineStr">
+      <c r="B24" s="90" t="inlineStr">
         <is>
           <t>نام و نام خانوادگی</t>
         </is>
       </c>
-      <c r="C24" s="41" t="inlineStr">
+      <c r="C24" s="90" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="D24" s="41" t="inlineStr">
+      <c r="D24" s="90" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
-      <c r="E24" s="41" t="inlineStr">
+      <c r="E24" s="90" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
       </c>
-      <c r="F24" s="9" t="n"/>
+      <c r="F24" s="86" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="92" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="9" t="n"/>
+      <c r="B25" s="92" t="inlineStr"/>
+      <c r="C25" s="92" t="inlineStr"/>
+      <c r="D25" s="92" t="inlineStr"/>
+      <c r="E25" s="92" t="inlineStr"/>
+      <c r="F25" s="86" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="92" t="inlineStr">
         <is>
           <t>بازبین فنی</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="9" t="n"/>
+      <c r="B26" s="92" t="inlineStr"/>
+      <c r="C26" s="92" t="inlineStr"/>
+      <c r="D26" s="92" t="inlineStr"/>
+      <c r="E26" s="92" t="inlineStr"/>
+      <c r="F26" s="86" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="42" t="inlineStr">
+      <c r="A27" s="92" t="inlineStr">
         <is>
           <t>تأیید نهایی</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="10" t="inlineStr"/>
-      <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="9" t="n"/>
+      <c r="B27" s="92" t="inlineStr"/>
+      <c r="C27" s="92" t="inlineStr"/>
+      <c r="D27" s="92" t="inlineStr"/>
+      <c r="E27" s="92" t="inlineStr"/>
+      <c r="F27" s="86" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="69" t="inlineStr">
+      <c r="A28" s="125" t="inlineStr">
         <is>
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
       </c>
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="82" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="82" t="n"/>
+      <c r="F28" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -5526,198 +7522,202 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="129" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="129" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="129" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="129" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="82" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="89" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="129" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="129" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="129" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="129" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" s="82" t="n"/>
+    </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="89" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="129" t="inlineStr">
         <is>
           <t>BoardTest</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="72" t="inlineStr">
+      <c r="A16" s="129" t="inlineStr">
         <is>
           <t>InputOk</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="129" t="inlineStr">
         <is>
           <t>Charging</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="72" t="inlineStr">
+      <c r="A18" s="129" t="inlineStr">
         <is>
           <t>BatteryRun</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="129" t="inlineStr">
         <is>
           <t>هیسترزیس</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="A20" s="129" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A21" s="129" t="inlineStr">
         <is>
           <t>Snapshot</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="A22" s="129" t="inlineStr">
         <is>
           <t>Buzzer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="inlineStr">
+      <c r="A23" s="129" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="72" t="inlineStr">
+      <c r="A24" s="129" t="inlineStr">
         <is>
           <t>Changeover</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="82" t="n"/>
+    </row>
     <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="89" t="inlineStr">
         <is>
           <t>نتیجه ایراد</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="129" t="inlineStr">
         <is>
           <t>باز</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="129" t="inlineStr">
         <is>
           <t>در حال بررسی</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="129" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="72" t="inlineStr">
+      <c r="A30" s="129" t="inlineStr">
         <is>
           <t>بسته</t>
         </is>
@@ -5743,60 +7743,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول تغییر مسیر (Changeover)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="82" t="n"/>
+      <c r="C1" s="82" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="82" t="n"/>
+      <c r="B2" s="82" t="n"/>
+      <c r="C2" s="82" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Changeover_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="82" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="82" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="82" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="61">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -360,6 +360,10 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -430,7 +434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -510,11 +514,12 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -871,6 +876,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1239,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1266,21 +1286,6 @@
           <t>برگه تست و اعتبارسنجی عملی ماژول Changeover — منطق قطع/وصل باتری</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="82" t="n"/>
-      <c r="D1" s="82" t="n"/>
-      <c r="E1" s="82" t="n"/>
-      <c r="F1" s="82" t="n"/>
-      <c r="G1" s="82" t="n"/>
-      <c r="H1" s="82" t="n"/>
-      <c r="I1" s="82" t="n"/>
-      <c r="J1" s="82" t="n"/>
-      <c r="K1" s="82" t="n"/>
-      <c r="L1" s="82" t="n"/>
-      <c r="M1" s="82" t="n"/>
-      <c r="N1" s="82" t="n"/>
-      <c r="O1" s="82" t="n"/>
-      <c r="P1" s="82" t="n"/>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="83" t="inlineStr">
@@ -1288,21 +1293,6 @@
           <t>ChangeOver | PB11 (BSP_GPIO_PROTECT_BATTERY) | آستانه‌ها: 21000/20800/21200 و فیلتر 3000ms | نسخه 2.1 — فقط PB11، زمان rtos_time</t>
         </is>
       </c>
-      <c r="B2" s="82" t="n"/>
-      <c r="C2" s="82" t="n"/>
-      <c r="D2" s="82" t="n"/>
-      <c r="E2" s="82" t="n"/>
-      <c r="F2" s="82" t="n"/>
-      <c r="G2" s="82" t="n"/>
-      <c r="H2" s="82" t="n"/>
-      <c r="I2" s="82" t="n"/>
-      <c r="J2" s="82" t="n"/>
-      <c r="K2" s="82" t="n"/>
-      <c r="L2" s="82" t="n"/>
-      <c r="M2" s="82" t="n"/>
-      <c r="N2" s="82" t="n"/>
-      <c r="O2" s="82" t="n"/>
-      <c r="P2" s="82" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="84" t="inlineStr">
@@ -1310,21 +1300,21 @@
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="85" t="n"/>
-      <c r="C3" s="85" t="n"/>
-      <c r="D3" s="85" t="n"/>
-      <c r="E3" s="85" t="n"/>
-      <c r="F3" s="85" t="n"/>
-      <c r="G3" s="85" t="n"/>
-      <c r="H3" s="85" t="n"/>
-      <c r="I3" s="85" t="n"/>
-      <c r="J3" s="85" t="n"/>
-      <c r="K3" s="85" t="n"/>
-      <c r="L3" s="85" t="n"/>
-      <c r="M3" s="85" t="n"/>
-      <c r="N3" s="85" t="n"/>
-      <c r="O3" s="85" t="n"/>
-      <c r="P3" s="86" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="9" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="87" t="inlineStr">
@@ -1332,21 +1322,6 @@
           <t>این فایل برای اعتبارسنجی منطق Changeover تهیه شده است: بررسی snapshot.valid، fault_mask، input_present، v_bat24_mv، قفل داخلی باتری کم و تایمر 3000ms.</t>
         </is>
       </c>
-      <c r="B4" s="82" t="n"/>
-      <c r="C4" s="82" t="n"/>
-      <c r="D4" s="82" t="n"/>
-      <c r="E4" s="82" t="n"/>
-      <c r="F4" s="82" t="n"/>
-      <c r="G4" s="82" t="n"/>
-      <c r="H4" s="82" t="n"/>
-      <c r="I4" s="82" t="n"/>
-      <c r="J4" s="82" t="n"/>
-      <c r="K4" s="82" t="n"/>
-      <c r="L4" s="82" t="n"/>
-      <c r="M4" s="82" t="n"/>
-      <c r="N4" s="82" t="n"/>
-      <c r="O4" s="82" t="n"/>
-      <c r="P4" s="82" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="87" t="inlineStr">
@@ -1354,21 +1329,6 @@
           <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار mV و ms و state/PB11 قابل اندازه‌گیری تعریف شده است.</t>
         </is>
       </c>
-      <c r="B5" s="82" t="n"/>
-      <c r="C5" s="82" t="n"/>
-      <c r="D5" s="82" t="n"/>
-      <c r="E5" s="82" t="n"/>
-      <c r="F5" s="82" t="n"/>
-      <c r="G5" s="82" t="n"/>
-      <c r="H5" s="82" t="n"/>
-      <c r="I5" s="82" t="n"/>
-      <c r="J5" s="82" t="n"/>
-      <c r="K5" s="82" t="n"/>
-      <c r="L5" s="82" t="n"/>
-      <c r="M5" s="82" t="n"/>
-      <c r="N5" s="82" t="n"/>
-      <c r="O5" s="82" t="n"/>
-      <c r="P5" s="82" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="87" t="inlineStr">
@@ -1376,21 +1336,6 @@
           <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است. فقط یک Workbook برای Changeover باقی بماند.</t>
         </is>
       </c>
-      <c r="B6" s="82" t="n"/>
-      <c r="C6" s="82" t="n"/>
-      <c r="D6" s="82" t="n"/>
-      <c r="E6" s="82" t="n"/>
-      <c r="F6" s="82" t="n"/>
-      <c r="G6" s="82" t="n"/>
-      <c r="H6" s="82" t="n"/>
-      <c r="I6" s="82" t="n"/>
-      <c r="J6" s="82" t="n"/>
-      <c r="K6" s="82" t="n"/>
-      <c r="L6" s="82" t="n"/>
-      <c r="M6" s="82" t="n"/>
-      <c r="N6" s="82" t="n"/>
-      <c r="O6" s="82" t="n"/>
-      <c r="P6" s="82" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="88" t="inlineStr">
@@ -1398,21 +1343,6 @@
           <t>دامنه: فقط Changeover؛ Measurement برای snapshot، Fault برای fault_mask و UI برای فلگ</t>
         </is>
       </c>
-      <c r="B7" s="82" t="n"/>
-      <c r="C7" s="82" t="n"/>
-      <c r="D7" s="82" t="n"/>
-      <c r="E7" s="82" t="n"/>
-      <c r="F7" s="82" t="n"/>
-      <c r="G7" s="82" t="n"/>
-      <c r="H7" s="82" t="n"/>
-      <c r="I7" s="82" t="n"/>
-      <c r="J7" s="82" t="n"/>
-      <c r="K7" s="82" t="n"/>
-      <c r="L7" s="82" t="n"/>
-      <c r="M7" s="82" t="n"/>
-      <c r="N7" s="82" t="n"/>
-      <c r="O7" s="82" t="n"/>
-      <c r="P7" s="82" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="87" t="inlineStr">
@@ -1420,21 +1350,6 @@
           <t>منطق (snapshot-first): اگر snapshot==NULL یا valid==false → هیچ تصمیمی، state حفظ، PB11 حفظ، تایمر reset، fault هم state را تغییر نمی‌دهد، زمان نامعتبر شمرده نشود.</t>
         </is>
       </c>
-      <c r="B8" s="82" t="n"/>
-      <c r="C8" s="82" t="n"/>
-      <c r="D8" s="82" t="n"/>
-      <c r="E8" s="82" t="n"/>
-      <c r="F8" s="82" t="n"/>
-      <c r="G8" s="82" t="n"/>
-      <c r="H8" s="82" t="n"/>
-      <c r="I8" s="82" t="n"/>
-      <c r="J8" s="82" t="n"/>
-      <c r="K8" s="82" t="n"/>
-      <c r="L8" s="82" t="n"/>
-      <c r="M8" s="82" t="n"/>
-      <c r="N8" s="82" t="n"/>
-      <c r="O8" s="82" t="n"/>
-      <c r="P8" s="82" t="n"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="87" t="inlineStr">
@@ -1442,21 +1357,6 @@
           <t>فقط وقتی snapshot معتبر و fault!=0 → state=FAULT بدون تغییر هیچ pin (PB11/PB5/PB7).</t>
         </is>
       </c>
-      <c r="B9" s="82" t="n"/>
-      <c r="C9" s="82" t="n"/>
-      <c r="D9" s="82" t="n"/>
-      <c r="E9" s="82" t="n"/>
-      <c r="F9" s="82" t="n"/>
-      <c r="G9" s="82" t="n"/>
-      <c r="H9" s="82" t="n"/>
-      <c r="I9" s="82" t="n"/>
-      <c r="J9" s="82" t="n"/>
-      <c r="K9" s="82" t="n"/>
-      <c r="L9" s="82" t="n"/>
-      <c r="M9" s="82" t="n"/>
-      <c r="N9" s="82" t="n"/>
-      <c r="O9" s="82" t="n"/>
-      <c r="P9" s="82" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="87" t="inlineStr">
@@ -1464,21 +1364,6 @@
           <t>قطع با گیت: v_bat&lt;21000 و flag true به‌مدت پیوسته 3000ms → قطع (PB11 Low) → SAFE. قطع مستقل: v_bat&lt;20800 مستقل از فلگ 3000ms → SAFE.</t>
         </is>
       </c>
-      <c r="B10" s="82" t="n"/>
-      <c r="C10" s="82" t="n"/>
-      <c r="D10" s="82" t="n"/>
-      <c r="E10" s="82" t="n"/>
-      <c r="F10" s="82" t="n"/>
-      <c r="G10" s="82" t="n"/>
-      <c r="H10" s="82" t="n"/>
-      <c r="I10" s="82" t="n"/>
-      <c r="J10" s="82" t="n"/>
-      <c r="K10" s="82" t="n"/>
-      <c r="L10" s="82" t="n"/>
-      <c r="M10" s="82" t="n"/>
-      <c r="N10" s="82" t="n"/>
-      <c r="O10" s="82" t="n"/>
-      <c r="P10" s="82" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="87" t="inlineStr">
@@ -1486,21 +1371,6 @@
           <t>وصل مجدد: input_present==true و v_bat≥21200 به‌مدت پیوسته 3000ms → وصل (PB11 High) → INPUT (هرگز IDLE).</t>
         </is>
       </c>
-      <c r="B11" s="82" t="n"/>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="82" t="n"/>
-      <c r="F11" s="82" t="n"/>
-      <c r="G11" s="82" t="n"/>
-      <c r="H11" s="82" t="n"/>
-      <c r="I11" s="82" t="n"/>
-      <c r="J11" s="82" t="n"/>
-      <c r="K11" s="82" t="n"/>
-      <c r="L11" s="82" t="n"/>
-      <c r="M11" s="82" t="n"/>
-      <c r="N11" s="82" t="n"/>
-      <c r="O11" s="82" t="n"/>
-      <c r="P11" s="82" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="87" t="inlineStr">
@@ -1508,21 +1378,6 @@
           <t>زمان فقط با func__Rtos_MillisecondsToTicks و osKernelGetTickCount؛ فرض tick=1ms ممنوع؛ durationTicks==0 → هیچ قطع/وصل فوری.</t>
         </is>
       </c>
-      <c r="B12" s="82" t="n"/>
-      <c r="C12" s="82" t="n"/>
-      <c r="D12" s="82" t="n"/>
-      <c r="E12" s="82" t="n"/>
-      <c r="F12" s="82" t="n"/>
-      <c r="G12" s="82" t="n"/>
-      <c r="H12" s="82" t="n"/>
-      <c r="I12" s="82" t="n"/>
-      <c r="J12" s="82" t="n"/>
-      <c r="K12" s="82" t="n"/>
-      <c r="L12" s="82" t="n"/>
-      <c r="M12" s="82" t="n"/>
-      <c r="N12" s="82" t="n"/>
-      <c r="O12" s="82" t="n"/>
-      <c r="P12" s="82" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="88" t="inlineStr">
@@ -1530,21 +1385,6 @@
           <t>روش اجرای تست</t>
         </is>
       </c>
-      <c r="B13" s="82" t="n"/>
-      <c r="C13" s="82" t="n"/>
-      <c r="D13" s="82" t="n"/>
-      <c r="E13" s="82" t="n"/>
-      <c r="F13" s="82" t="n"/>
-      <c r="G13" s="82" t="n"/>
-      <c r="H13" s="82" t="n"/>
-      <c r="I13" s="82" t="n"/>
-      <c r="J13" s="82" t="n"/>
-      <c r="K13" s="82" t="n"/>
-      <c r="L13" s="82" t="n"/>
-      <c r="M13" s="82" t="n"/>
-      <c r="N13" s="82" t="n"/>
-      <c r="O13" s="82" t="n"/>
-      <c r="P13" s="82" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="87" t="inlineStr">
@@ -1552,21 +1392,6 @@
           <t>۱) برد را با منبع آزمایشگاهی و رعایت ایمنی تغذیه کن؛ PB11 را با DMM/اسکوپ نسبت به GND اندازه بگیر (فعال Low). PB5/PB7 را هم هم‌زمان اسکوپ کن و مطمئن شو تغییری ندارند.</t>
         </is>
       </c>
-      <c r="B14" s="82" t="n"/>
-      <c r="C14" s="82" t="n"/>
-      <c r="D14" s="82" t="n"/>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="n"/>
-      <c r="G14" s="82" t="n"/>
-      <c r="H14" s="82" t="n"/>
-      <c r="I14" s="82" t="n"/>
-      <c r="J14" s="82" t="n"/>
-      <c r="K14" s="82" t="n"/>
-      <c r="L14" s="82" t="n"/>
-      <c r="M14" s="82" t="n"/>
-      <c r="N14" s="82" t="n"/>
-      <c r="O14" s="82" t="n"/>
-      <c r="P14" s="82" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="87" t="inlineStr">
@@ -1574,21 +1399,6 @@
           <t>۲) firmware موردنظر را پروگرام کن؛ commit و شناسه برد را در «تأیید نهایی» ثبت کن.</t>
         </is>
       </c>
-      <c r="B15" s="82" t="n"/>
-      <c r="C15" s="82" t="n"/>
-      <c r="D15" s="82" t="n"/>
-      <c r="E15" s="82" t="n"/>
-      <c r="F15" s="82" t="n"/>
-      <c r="G15" s="82" t="n"/>
-      <c r="H15" s="82" t="n"/>
-      <c r="I15" s="82" t="n"/>
-      <c r="J15" s="82" t="n"/>
-      <c r="K15" s="82" t="n"/>
-      <c r="L15" s="82" t="n"/>
-      <c r="M15" s="82" t="n"/>
-      <c r="N15" s="82" t="n"/>
-      <c r="O15" s="82" t="n"/>
-      <c r="P15" s="82" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="87" t="inlineStr">
@@ -1596,21 +1406,6 @@
           <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present را ست کن؛ قفل داخلی باتری کم فقط با ولتاژ زیر ۲۱۰۰۰ میلی‌ولت بسته می‌شود (مستقیم ست نمی‌شود)؛ fault_mask را از Fault اعمال کن.</t>
         </is>
       </c>
-      <c r="B16" s="82" t="n"/>
-      <c r="C16" s="82" t="n"/>
-      <c r="D16" s="82" t="n"/>
-      <c r="E16" s="82" t="n"/>
-      <c r="F16" s="82" t="n"/>
-      <c r="G16" s="82" t="n"/>
-      <c r="H16" s="82" t="n"/>
-      <c r="I16" s="82" t="n"/>
-      <c r="J16" s="82" t="n"/>
-      <c r="K16" s="82" t="n"/>
-      <c r="L16" s="82" t="n"/>
-      <c r="M16" s="82" t="n"/>
-      <c r="N16" s="82" t="n"/>
-      <c r="O16" s="82" t="n"/>
-      <c r="P16" s="82" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="87" t="inlineStr">
@@ -1618,21 +1413,6 @@
           <t>۴) برای تست 3000ms: شرط را حداقل 3500ms پایدار نگه دار و سپس PB11 و state را بخوان؛ برای تست &lt;3000ms: پس از 2500ms بخوان و مطمئن شو هنوز تغییر نکرده.</t>
         </is>
       </c>
-      <c r="B17" s="82" t="n"/>
-      <c r="C17" s="82" t="n"/>
-      <c r="D17" s="82" t="n"/>
-      <c r="E17" s="82" t="n"/>
-      <c r="F17" s="82" t="n"/>
-      <c r="G17" s="82" t="n"/>
-      <c r="H17" s="82" t="n"/>
-      <c r="I17" s="82" t="n"/>
-      <c r="J17" s="82" t="n"/>
-      <c r="K17" s="82" t="n"/>
-      <c r="L17" s="82" t="n"/>
-      <c r="M17" s="82" t="n"/>
-      <c r="N17" s="82" t="n"/>
-      <c r="O17" s="82" t="n"/>
-      <c r="P17" s="82" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="87" t="inlineStr">
@@ -1640,21 +1420,6 @@
           <t>۵) برای snapshot نامعتبر: valid=false یا NULL تزریق کن و ببین state و PB11 حفظ می‌ماند (باید «state فعلی حفظ شود» نه IDLE ثابت).</t>
         </is>
       </c>
-      <c r="B18" s="82" t="n"/>
-      <c r="C18" s="82" t="n"/>
-      <c r="D18" s="82" t="n"/>
-      <c r="E18" s="82" t="n"/>
-      <c r="F18" s="82" t="n"/>
-      <c r="G18" s="82" t="n"/>
-      <c r="H18" s="82" t="n"/>
-      <c r="I18" s="82" t="n"/>
-      <c r="J18" s="82" t="n"/>
-      <c r="K18" s="82" t="n"/>
-      <c r="L18" s="82" t="n"/>
-      <c r="M18" s="82" t="n"/>
-      <c r="N18" s="82" t="n"/>
-      <c r="O18" s="82" t="n"/>
-      <c r="P18" s="82" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="87" t="inlineStr">
@@ -1662,21 +1427,6 @@
           <t>۶) نتیجه واقعی را بنویس و در صورت رد، در «ثبت ایراد» ردیف بساز.</t>
         </is>
       </c>
-      <c r="B19" s="82" t="n"/>
-      <c r="C19" s="82" t="n"/>
-      <c r="D19" s="82" t="n"/>
-      <c r="E19" s="82" t="n"/>
-      <c r="F19" s="82" t="n"/>
-      <c r="G19" s="82" t="n"/>
-      <c r="H19" s="82" t="n"/>
-      <c r="I19" s="82" t="n"/>
-      <c r="J19" s="82" t="n"/>
-      <c r="K19" s="82" t="n"/>
-      <c r="L19" s="82" t="n"/>
-      <c r="M19" s="82" t="n"/>
-      <c r="N19" s="82" t="n"/>
-      <c r="O19" s="82" t="n"/>
-      <c r="P19" s="82" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="89" t="inlineStr">
@@ -1684,21 +1434,6 @@
           <t>تاریخچه نسخه</t>
         </is>
       </c>
-      <c r="B20" s="82" t="n"/>
-      <c r="C20" s="82" t="n"/>
-      <c r="D20" s="82" t="n"/>
-      <c r="E20" s="82" t="n"/>
-      <c r="F20" s="82" t="n"/>
-      <c r="G20" s="82" t="n"/>
-      <c r="H20" s="82" t="n"/>
-      <c r="I20" s="82" t="n"/>
-      <c r="J20" s="82" t="n"/>
-      <c r="K20" s="82" t="n"/>
-      <c r="L20" s="82" t="n"/>
-      <c r="M20" s="82" t="n"/>
-      <c r="N20" s="82" t="n"/>
-      <c r="O20" s="82" t="n"/>
-      <c r="P20" s="82" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="90" t="inlineStr">
@@ -1722,17 +1457,17 @@
         </is>
       </c>
       <c r="E21" s="91" t="n"/>
-      <c r="F21" s="85" t="n"/>
-      <c r="G21" s="85" t="n"/>
-      <c r="H21" s="85" t="n"/>
-      <c r="I21" s="85" t="n"/>
-      <c r="J21" s="85" t="n"/>
-      <c r="K21" s="85" t="n"/>
-      <c r="L21" s="85" t="n"/>
-      <c r="M21" s="85" t="n"/>
-      <c r="N21" s="85" t="n"/>
-      <c r="O21" s="85" t="n"/>
-      <c r="P21" s="86" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
+      <c r="P21" s="9" t="n"/>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="92" t="inlineStr">
@@ -1756,17 +1491,17 @@
         </is>
       </c>
       <c r="E22" s="93" t="n"/>
-      <c r="F22" s="85" t="n"/>
-      <c r="G22" s="85" t="n"/>
-      <c r="H22" s="85" t="n"/>
-      <c r="I22" s="85" t="n"/>
-      <c r="J22" s="85" t="n"/>
-      <c r="K22" s="85" t="n"/>
-      <c r="L22" s="85" t="n"/>
-      <c r="M22" s="85" t="n"/>
-      <c r="N22" s="85" t="n"/>
-      <c r="O22" s="85" t="n"/>
-      <c r="P22" s="86" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="9" t="n"/>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="92" t="inlineStr">
@@ -1790,17 +1525,17 @@
         </is>
       </c>
       <c r="E23" s="93" t="n"/>
-      <c r="F23" s="85" t="n"/>
-      <c r="G23" s="85" t="n"/>
-      <c r="H23" s="85" t="n"/>
-      <c r="I23" s="85" t="n"/>
-      <c r="J23" s="85" t="n"/>
-      <c r="K23" s="85" t="n"/>
-      <c r="L23" s="85" t="n"/>
-      <c r="M23" s="85" t="n"/>
-      <c r="N23" s="85" t="n"/>
-      <c r="O23" s="85" t="n"/>
-      <c r="P23" s="86" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="9" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="92" t="inlineStr">
@@ -1824,17 +1559,17 @@
         </is>
       </c>
       <c r="E24" s="93" t="n"/>
-      <c r="F24" s="85" t="n"/>
-      <c r="G24" s="85" t="n"/>
-      <c r="H24" s="85" t="n"/>
-      <c r="I24" s="85" t="n"/>
-      <c r="J24" s="85" t="n"/>
-      <c r="K24" s="85" t="n"/>
-      <c r="L24" s="85" t="n"/>
-      <c r="M24" s="85" t="n"/>
-      <c r="N24" s="85" t="n"/>
-      <c r="O24" s="85" t="n"/>
-      <c r="P24" s="86" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="94" t="inlineStr">
@@ -1869,6 +1604,14 @@
       <c r="N25" s="82" t="n"/>
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="130" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1938,21 +1681,6 @@
           <t>برنامه تست عملی — ماژول Changeover (قطع/وصل باتری با 3000ms)</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="82" t="n"/>
-      <c r="D1" s="82" t="n"/>
-      <c r="E1" s="82" t="n"/>
-      <c r="F1" s="82" t="n"/>
-      <c r="G1" s="82" t="n"/>
-      <c r="H1" s="82" t="n"/>
-      <c r="I1" s="82" t="n"/>
-      <c r="J1" s="82" t="n"/>
-      <c r="K1" s="82" t="n"/>
-      <c r="L1" s="82" t="n"/>
-      <c r="M1" s="82" t="n"/>
-      <c r="N1" s="82" t="n"/>
-      <c r="O1" s="82" t="n"/>
-      <c r="P1" s="82" t="n"/>
       <c r="Q1" s="82" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
@@ -1961,21 +1689,6 @@
           <t>ورودی‌ها بر حسب mV؛ زمان‌ها بر حسب ms. PB11 فقط از BSP_GPIO_PROTECT_BATTERY (فعال Low) — PB5/PB7 ممنوع. ورودی‌ها: valid، v_bat، input_present، flag، fault.</t>
         </is>
       </c>
-      <c r="B2" s="82" t="n"/>
-      <c r="C2" s="82" t="n"/>
-      <c r="D2" s="82" t="n"/>
-      <c r="E2" s="82" t="n"/>
-      <c r="F2" s="82" t="n"/>
-      <c r="G2" s="82" t="n"/>
-      <c r="H2" s="82" t="n"/>
-      <c r="I2" s="82" t="n"/>
-      <c r="J2" s="82" t="n"/>
-      <c r="K2" s="82" t="n"/>
-      <c r="L2" s="82" t="n"/>
-      <c r="M2" s="82" t="n"/>
-      <c r="N2" s="82" t="n"/>
-      <c r="O2" s="82" t="n"/>
-      <c r="P2" s="82" t="n"/>
       <c r="Q2" s="82" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -1984,21 +1697,6 @@
           <t>snapshot نامعتبر → «state فعلی حفظ شود» (نه IDLE ثابت). CO-010/012 باید INPUT باشد. معیار قبولی هر ردیف توضیح می‌دهد PASS چیست و FAIL چیست.</t>
         </is>
       </c>
-      <c r="B3" s="82" t="n"/>
-      <c r="C3" s="82" t="n"/>
-      <c r="D3" s="82" t="n"/>
-      <c r="E3" s="82" t="n"/>
-      <c r="F3" s="82" t="n"/>
-      <c r="G3" s="82" t="n"/>
-      <c r="H3" s="82" t="n"/>
-      <c r="I3" s="82" t="n"/>
-      <c r="J3" s="82" t="n"/>
-      <c r="K3" s="82" t="n"/>
-      <c r="L3" s="82" t="n"/>
-      <c r="M3" s="82" t="n"/>
-      <c r="N3" s="82" t="n"/>
-      <c r="O3" s="82" t="n"/>
-      <c r="P3" s="82" t="n"/>
       <c r="Q3" s="82" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -2044,7 +1742,7 @@
       </c>
       <c r="I4" s="84" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="J4" s="84" t="inlineStr">
@@ -2085,911 +1783,27 @@
       <c r="Q4" s="84" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="82" t="n"/>
-      <c r="B5" s="82" t="n"/>
-      <c r="C5" s="82" t="n"/>
-      <c r="D5" s="82" t="n"/>
-      <c r="E5" s="82" t="n"/>
-      <c r="F5" s="82" t="n"/>
-      <c r="G5" s="82" t="n"/>
-      <c r="H5" s="82" t="n"/>
-      <c r="I5" s="82" t="n"/>
-      <c r="J5" s="82" t="n"/>
-      <c r="K5" s="82" t="n"/>
-      <c r="L5" s="82" t="n"/>
-      <c r="M5" s="82" t="n"/>
-      <c r="N5" s="82" t="n"/>
-      <c r="O5" s="82" t="n"/>
-      <c r="P5" s="82" t="n"/>
-      <c r="Q5" s="98">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="67.5" customHeight="1">
-      <c r="A6" s="82" t="n"/>
-      <c r="B6" s="82" t="n"/>
-      <c r="C6" s="82" t="n"/>
-      <c r="D6" s="82" t="n"/>
-      <c r="E6" s="82" t="n"/>
-      <c r="F6" s="82" t="n"/>
-      <c r="G6" s="82" t="n"/>
-      <c r="H6" s="82" t="n"/>
-      <c r="I6" s="82" t="n"/>
-      <c r="J6" s="82" t="n"/>
-      <c r="K6" s="82" t="n"/>
-      <c r="L6" s="82" t="n"/>
-      <c r="M6" s="82" t="n"/>
-      <c r="N6" s="82" t="n"/>
-      <c r="O6" s="82" t="n"/>
-      <c r="P6" s="82" t="n"/>
-      <c r="Q6" s="98">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="82" t="n"/>
-      <c r="B7" s="82" t="n"/>
-      <c r="C7" s="82" t="n"/>
-      <c r="D7" s="82" t="n"/>
-      <c r="E7" s="82" t="n"/>
-      <c r="F7" s="82" t="n"/>
-      <c r="G7" s="82" t="n"/>
-      <c r="H7" s="82" t="n"/>
-      <c r="I7" s="82" t="n"/>
-      <c r="J7" s="82" t="n"/>
-      <c r="K7" s="82" t="n"/>
-      <c r="L7" s="82" t="n"/>
-      <c r="M7" s="82" t="n"/>
-      <c r="N7" s="82" t="n"/>
-      <c r="O7" s="82" t="n"/>
-      <c r="P7" s="82" t="n"/>
-      <c r="Q7" s="98">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="82" t="n"/>
-      <c r="B8" s="82" t="n"/>
-      <c r="C8" s="82" t="n"/>
-      <c r="D8" s="82" t="n"/>
-      <c r="E8" s="82" t="inlineStr">
-        <is>
-          <t>#'برنامه تست'!A12</t>
-        </is>
-      </c>
-      <c r="F8" s="82" t="n"/>
-      <c r="G8" s="82" t="n"/>
-      <c r="H8" s="82" t="n"/>
-      <c r="I8" s="82" t="n"/>
-      <c r="J8" s="82" t="n"/>
-      <c r="K8" s="82" t="n"/>
-      <c r="L8" s="82" t="n"/>
-      <c r="M8" s="82" t="n"/>
-      <c r="N8" s="82" t="n"/>
-      <c r="O8" s="82" t="n"/>
-      <c r="P8" s="82" t="n"/>
-      <c r="Q8" s="98">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="82" t="n"/>
-      <c r="B9" s="82" t="n"/>
-      <c r="C9" s="82" t="n"/>
-      <c r="D9" s="82" t="n"/>
-      <c r="E9" s="82" t="n"/>
-      <c r="F9" s="82" t="n"/>
-      <c r="G9" s="82" t="n"/>
-      <c r="H9" s="82" t="n"/>
-      <c r="I9" s="82" t="n"/>
-      <c r="J9" s="82" t="n"/>
-      <c r="K9" s="82" t="n"/>
-      <c r="L9" s="82" t="n"/>
-      <c r="M9" s="82" t="n"/>
-      <c r="N9" s="82" t="n"/>
-      <c r="O9" s="82" t="n"/>
-      <c r="P9" s="82" t="n"/>
-      <c r="Q9" s="98">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="82" t="n"/>
-      <c r="B10" s="82" t="n"/>
-      <c r="C10" s="82" t="n"/>
-      <c r="D10" s="82" t="n"/>
-      <c r="E10" s="82" t="n"/>
-      <c r="F10" s="82" t="n"/>
-      <c r="G10" s="82" t="n"/>
-      <c r="H10" s="82" t="n"/>
-      <c r="I10" s="82" t="n"/>
-      <c r="J10" s="82" t="n"/>
-      <c r="K10" s="82" t="n"/>
-      <c r="L10" s="82" t="n"/>
-      <c r="M10" s="82" t="n"/>
-      <c r="N10" s="82" t="n"/>
-      <c r="O10" s="82" t="n"/>
-      <c r="P10" s="82" t="n"/>
-      <c r="Q10" s="98">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="82" t="n"/>
-      <c r="B11" s="82" t="n"/>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="82" t="n"/>
-      <c r="F11" s="82" t="n"/>
-      <c r="G11" s="82" t="n"/>
-      <c r="H11" s="82" t="n"/>
-      <c r="I11" s="82" t="n"/>
-      <c r="J11" s="82" t="n"/>
-      <c r="K11" s="82" t="n"/>
-      <c r="L11" s="82" t="n"/>
-      <c r="M11" s="82" t="n"/>
-      <c r="N11" s="82" t="n"/>
-      <c r="O11" s="82" t="n"/>
-      <c r="P11" s="82" t="n"/>
-      <c r="Q11" s="98">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="82" t="n"/>
-      <c r="B12" s="82" t="n"/>
-      <c r="C12" s="82" t="n"/>
-      <c r="D12" s="82" t="n"/>
-      <c r="E12" s="82" t="n"/>
-      <c r="F12" s="82" t="n"/>
-      <c r="G12" s="82" t="n"/>
-      <c r="H12" s="82" t="n"/>
-      <c r="I12" s="82" t="n"/>
-      <c r="J12" s="82" t="n"/>
-      <c r="K12" s="82" t="n"/>
-      <c r="L12" s="82" t="n"/>
-      <c r="M12" s="82" t="n"/>
-      <c r="N12" s="82" t="n"/>
-      <c r="O12" s="82" t="n"/>
-      <c r="P12" s="82" t="n"/>
-      <c r="Q12" s="98">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="82" t="n"/>
-      <c r="B13" s="82" t="n"/>
-      <c r="C13" s="82" t="n"/>
-      <c r="D13" s="82" t="n"/>
-      <c r="E13" s="82" t="n"/>
-      <c r="F13" s="82" t="n"/>
-      <c r="G13" s="82" t="n"/>
-      <c r="H13" s="82" t="n"/>
-      <c r="I13" s="82" t="n"/>
-      <c r="J13" s="82" t="n"/>
-      <c r="K13" s="82" t="n"/>
-      <c r="L13" s="82" t="n"/>
-      <c r="M13" s="82" t="n"/>
-      <c r="N13" s="82" t="n"/>
-      <c r="O13" s="82" t="n"/>
-      <c r="P13" s="82" t="n"/>
-      <c r="Q13" s="98">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="82" t="n"/>
-      <c r="B14" s="82" t="n"/>
-      <c r="C14" s="82" t="n"/>
-      <c r="D14" s="82" t="n"/>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="n"/>
-      <c r="G14" s="82" t="n"/>
-      <c r="H14" s="82" t="n"/>
-      <c r="I14" s="82" t="n"/>
-      <c r="J14" s="82" t="n"/>
-      <c r="K14" s="82" t="n"/>
-      <c r="L14" s="82" t="n"/>
-      <c r="M14" s="82" t="n"/>
-      <c r="N14" s="82" t="n"/>
-      <c r="O14" s="82" t="n"/>
-      <c r="P14" s="82" t="n"/>
-      <c r="Q14" s="98">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="82" t="n"/>
-      <c r="B15" s="82" t="n"/>
-      <c r="C15" s="82" t="n"/>
-      <c r="D15" s="82" t="n"/>
-      <c r="E15" s="82" t="n"/>
-      <c r="F15" s="82" t="n"/>
-      <c r="G15" s="82" t="n"/>
-      <c r="H15" s="82" t="n"/>
-      <c r="I15" s="82" t="n"/>
-      <c r="J15" s="82" t="n"/>
-      <c r="K15" s="82" t="n"/>
-      <c r="L15" s="82" t="n"/>
-      <c r="M15" s="82" t="n"/>
-      <c r="N15" s="82" t="n"/>
-      <c r="O15" s="82" t="n"/>
-      <c r="P15" s="82" t="n"/>
-      <c r="Q15" s="98">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="82" t="n"/>
-      <c r="B16" s="82" t="n"/>
-      <c r="C16" s="82" t="n"/>
-      <c r="D16" s="82" t="n"/>
-      <c r="E16" s="82" t="n"/>
-      <c r="F16" s="82" t="n"/>
-      <c r="G16" s="82" t="n"/>
-      <c r="H16" s="82" t="n"/>
-      <c r="I16" s="82" t="n"/>
-      <c r="J16" s="82" t="n"/>
-      <c r="K16" s="82" t="n"/>
-      <c r="L16" s="82" t="n"/>
-      <c r="M16" s="82" t="n"/>
-      <c r="N16" s="82" t="n"/>
-      <c r="O16" s="82" t="n"/>
-      <c r="P16" s="82" t="n"/>
-      <c r="Q16" s="98">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="82" t="n"/>
-      <c r="B17" s="82" t="n"/>
-      <c r="C17" s="82" t="n"/>
-      <c r="D17" s="82" t="n"/>
-      <c r="E17" s="82" t="n"/>
-      <c r="F17" s="82" t="n"/>
-      <c r="G17" s="82" t="n"/>
-      <c r="H17" s="82" t="n"/>
-      <c r="I17" s="82" t="n"/>
-      <c r="J17" s="82" t="n"/>
-      <c r="K17" s="82" t="n"/>
-      <c r="L17" s="82" t="n"/>
-      <c r="M17" s="82" t="n"/>
-      <c r="N17" s="82" t="n"/>
-      <c r="O17" s="82" t="n"/>
-      <c r="P17" s="82" t="n"/>
-      <c r="Q17" s="98">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="82" t="n"/>
-      <c r="B18" s="82" t="n"/>
-      <c r="C18" s="82" t="n"/>
-      <c r="D18" s="82" t="n"/>
-      <c r="E18" s="82" t="n"/>
-      <c r="F18" s="82" t="n"/>
-      <c r="G18" s="82" t="n"/>
-      <c r="H18" s="82" t="n"/>
-      <c r="I18" s="82" t="n"/>
-      <c r="J18" s="82" t="n"/>
-      <c r="K18" s="82" t="n"/>
-      <c r="L18" s="82" t="n"/>
-      <c r="M18" s="82" t="n"/>
-      <c r="N18" s="82" t="n"/>
-      <c r="O18" s="82" t="n"/>
-      <c r="P18" s="82" t="n"/>
-      <c r="Q18" s="98">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="82" t="n"/>
-      <c r="B19" s="82" t="n"/>
-      <c r="C19" s="82" t="n"/>
-      <c r="D19" s="82" t="n"/>
-      <c r="E19" s="82" t="n"/>
-      <c r="F19" s="82" t="n"/>
-      <c r="G19" s="82" t="n"/>
-      <c r="H19" s="82" t="n"/>
-      <c r="I19" s="82" t="n"/>
-      <c r="J19" s="82" t="n"/>
-      <c r="K19" s="82" t="n"/>
-      <c r="L19" s="82" t="n"/>
-      <c r="M19" s="82" t="n"/>
-      <c r="N19" s="82" t="n"/>
-      <c r="O19" s="82" t="n"/>
-      <c r="P19" s="82" t="n"/>
-      <c r="Q19" s="98">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="40.5" customHeight="1">
-      <c r="A20" s="82" t="n"/>
-      <c r="B20" s="82" t="n"/>
-      <c r="C20" s="82" t="n"/>
-      <c r="D20" s="82" t="n"/>
-      <c r="E20" s="82" t="n"/>
-      <c r="F20" s="82" t="n"/>
-      <c r="G20" s="82" t="n"/>
-      <c r="H20" s="82" t="n"/>
-      <c r="I20" s="82" t="n"/>
-      <c r="J20" s="82" t="n"/>
-      <c r="K20" s="82" t="n"/>
-      <c r="L20" s="82" t="n"/>
-      <c r="M20" s="82" t="n"/>
-      <c r="N20" s="82" t="n"/>
-      <c r="O20" s="82" t="n"/>
-      <c r="P20" s="82" t="n"/>
-      <c r="Q20" s="98">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="40.5" customHeight="1">
-      <c r="A21" s="82" t="n"/>
-      <c r="B21" s="82" t="n"/>
-      <c r="C21" s="82" t="n"/>
-      <c r="D21" s="82" t="n"/>
-      <c r="E21" s="82" t="n"/>
-      <c r="F21" s="82" t="n"/>
-      <c r="G21" s="82" t="n"/>
-      <c r="H21" s="82" t="n"/>
-      <c r="I21" s="82" t="n"/>
-      <c r="J21" s="82" t="n"/>
-      <c r="K21" s="82" t="n"/>
-      <c r="L21" s="82" t="n"/>
-      <c r="M21" s="82" t="n"/>
-      <c r="N21" s="82" t="n"/>
-      <c r="O21" s="82" t="n"/>
-      <c r="P21" s="82" t="n"/>
-      <c r="Q21" s="98">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="82" t="n"/>
-      <c r="B22" s="82" t="n"/>
-      <c r="C22" s="82" t="n"/>
-      <c r="D22" s="82" t="n"/>
-      <c r="E22" s="82" t="n"/>
-      <c r="F22" s="82" t="n"/>
-      <c r="G22" s="82" t="n"/>
-      <c r="H22" s="82" t="n"/>
-      <c r="I22" s="82" t="n"/>
-      <c r="J22" s="82" t="n"/>
-      <c r="K22" s="82" t="n"/>
-      <c r="L22" s="82" t="n"/>
-      <c r="M22" s="82" t="n"/>
-      <c r="N22" s="82" t="n"/>
-      <c r="O22" s="82" t="n"/>
-      <c r="P22" s="82" t="n"/>
-      <c r="Q22" s="98">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="82" t="n"/>
-      <c r="B23" s="82" t="n"/>
-      <c r="C23" s="82" t="n"/>
-      <c r="D23" s="82" t="n"/>
-      <c r="E23" s="82" t="n"/>
-      <c r="F23" s="82" t="n"/>
-      <c r="G23" s="82" t="n"/>
-      <c r="H23" s="82" t="n"/>
-      <c r="I23" s="82" t="n"/>
-      <c r="J23" s="82" t="n"/>
-      <c r="K23" s="82" t="n"/>
-      <c r="L23" s="82" t="n"/>
-      <c r="M23" s="82" t="n"/>
-      <c r="N23" s="82" t="n"/>
-      <c r="O23" s="82" t="n"/>
-      <c r="P23" s="82" t="n"/>
-      <c r="Q23" s="98">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="82" t="n"/>
-      <c r="B24" s="82" t="n"/>
-      <c r="C24" s="82" t="n"/>
-      <c r="D24" s="82" t="n"/>
-      <c r="E24" s="82" t="n"/>
-      <c r="F24" s="82" t="n"/>
-      <c r="G24" s="82" t="n"/>
-      <c r="H24" s="82" t="n"/>
-      <c r="I24" s="82" t="n"/>
-      <c r="J24" s="82" t="n"/>
-      <c r="K24" s="82" t="n"/>
-      <c r="L24" s="82" t="n"/>
-      <c r="M24" s="82" t="n"/>
-      <c r="N24" s="82" t="n"/>
-      <c r="O24" s="82" t="n"/>
-      <c r="P24" s="82" t="n"/>
-      <c r="Q24" s="98">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="82" t="n"/>
-      <c r="B25" s="82" t="n"/>
-      <c r="C25" s="82" t="n"/>
-      <c r="D25" s="82" t="n"/>
-      <c r="E25" s="82" t="n"/>
-      <c r="F25" s="82" t="n"/>
-      <c r="G25" s="82" t="n"/>
-      <c r="H25" s="82" t="n"/>
-      <c r="I25" s="82" t="n"/>
-      <c r="J25" s="82" t="n"/>
-      <c r="K25" s="82" t="n"/>
-      <c r="L25" s="82" t="n"/>
-      <c r="M25" s="82" t="n"/>
-      <c r="N25" s="82" t="n"/>
-      <c r="O25" s="82" t="n"/>
-      <c r="P25" s="82" t="n"/>
-      <c r="Q25" s="98">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="82" t="n"/>
-      <c r="B26" s="82" t="n"/>
-      <c r="C26" s="82" t="n"/>
-      <c r="D26" s="82" t="n"/>
-      <c r="E26" s="82" t="n"/>
-      <c r="F26" s="82" t="n"/>
-      <c r="G26" s="82" t="n"/>
-      <c r="H26" s="82" t="n"/>
-      <c r="I26" s="82" t="n"/>
-      <c r="J26" s="82" t="n"/>
-      <c r="K26" s="82" t="n"/>
-      <c r="L26" s="82" t="n"/>
-      <c r="M26" s="82" t="n"/>
-      <c r="N26" s="82" t="n"/>
-      <c r="O26" s="82" t="n"/>
-      <c r="P26" s="82" t="n"/>
-      <c r="Q26" s="98">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="82" t="n"/>
-      <c r="B27" s="82" t="n"/>
-      <c r="C27" s="82" t="n"/>
-      <c r="D27" s="82" t="n"/>
-      <c r="E27" s="82" t="n"/>
-      <c r="F27" s="82" t="n"/>
-      <c r="G27" s="82" t="n"/>
-      <c r="H27" s="82" t="n"/>
-      <c r="I27" s="82" t="n"/>
-      <c r="J27" s="82" t="n"/>
-      <c r="K27" s="82" t="n"/>
-      <c r="L27" s="82" t="n"/>
-      <c r="M27" s="82" t="n"/>
-      <c r="N27" s="82" t="n"/>
-      <c r="O27" s="82" t="n"/>
-      <c r="P27" s="82" t="n"/>
-      <c r="Q27" s="98">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="82" t="n"/>
-      <c r="B28" s="82" t="n"/>
-      <c r="C28" s="82" t="n"/>
-      <c r="D28" s="82" t="n"/>
-      <c r="E28" s="82" t="n"/>
-      <c r="F28" s="82" t="n"/>
-      <c r="G28" s="82" t="n"/>
-      <c r="H28" s="82" t="n"/>
-      <c r="I28" s="82" t="n"/>
-      <c r="J28" s="82" t="n"/>
-      <c r="K28" s="82" t="n"/>
-      <c r="L28" s="82" t="n"/>
-      <c r="M28" s="82" t="n"/>
-      <c r="N28" s="82" t="n"/>
-      <c r="O28" s="82" t="n"/>
-      <c r="P28" s="82" t="n"/>
-      <c r="Q28" s="98">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="82" t="n"/>
-      <c r="B29" s="82" t="n"/>
-      <c r="C29" s="82" t="n"/>
-      <c r="D29" s="82" t="n"/>
-      <c r="E29" s="82" t="n"/>
-      <c r="F29" s="82" t="n"/>
-      <c r="G29" s="82" t="n"/>
-      <c r="H29" s="82" t="n"/>
-      <c r="I29" s="82" t="n"/>
-      <c r="J29" s="82" t="n"/>
-      <c r="K29" s="82" t="n"/>
-      <c r="L29" s="82" t="n"/>
-      <c r="M29" s="82" t="n"/>
-      <c r="N29" s="82" t="n"/>
-      <c r="O29" s="82" t="n"/>
-      <c r="P29" s="82" t="n"/>
-      <c r="Q29" s="98">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="82" t="n"/>
-      <c r="B30" s="82" t="n"/>
-      <c r="C30" s="82" t="n"/>
-      <c r="D30" s="82" t="n"/>
-      <c r="E30" s="82" t="n"/>
-      <c r="F30" s="82" t="n"/>
-      <c r="G30" s="82" t="n"/>
-      <c r="H30" s="82" t="n"/>
-      <c r="I30" s="82" t="n"/>
-      <c r="J30" s="82" t="n"/>
-      <c r="K30" s="82" t="n"/>
-      <c r="L30" s="82" t="n"/>
-      <c r="M30" s="82" t="n"/>
-      <c r="N30" s="82" t="n"/>
-      <c r="O30" s="82" t="n"/>
-      <c r="P30" s="82" t="n"/>
-      <c r="Q30" s="98">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="82" t="n"/>
-      <c r="B31" s="82" t="n"/>
-      <c r="C31" s="82" t="n"/>
-      <c r="D31" s="82" t="n"/>
-      <c r="E31" s="82" t="n"/>
-      <c r="F31" s="82" t="n"/>
-      <c r="G31" s="82" t="n"/>
-      <c r="H31" s="82" t="n"/>
-      <c r="I31" s="82" t="n"/>
-      <c r="J31" s="82" t="n"/>
-      <c r="K31" s="82" t="n"/>
-      <c r="L31" s="82" t="n"/>
-      <c r="M31" s="82" t="n"/>
-      <c r="N31" s="82" t="n"/>
-      <c r="O31" s="82" t="n"/>
-      <c r="P31" s="82" t="n"/>
-      <c r="Q31" s="98">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="82" t="n"/>
-      <c r="B32" s="82" t="n"/>
-      <c r="C32" s="82" t="n"/>
-      <c r="D32" s="82" t="n"/>
-      <c r="E32" s="82" t="n"/>
-      <c r="F32" s="82" t="n"/>
-      <c r="G32" s="82" t="n"/>
-      <c r="H32" s="82" t="n"/>
-      <c r="I32" s="82" t="n"/>
-      <c r="J32" s="82" t="n"/>
-      <c r="K32" s="82" t="n"/>
-      <c r="L32" s="82" t="n"/>
-      <c r="M32" s="82" t="n"/>
-      <c r="N32" s="82" t="n"/>
-      <c r="O32" s="82" t="n"/>
-      <c r="P32" s="82" t="n"/>
-      <c r="Q32" s="98">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="82" t="n"/>
-      <c r="B33" s="82" t="n"/>
-      <c r="C33" s="82" t="n"/>
-      <c r="D33" s="82" t="n"/>
-      <c r="E33" s="82" t="n"/>
-      <c r="F33" s="82" t="n"/>
-      <c r="G33" s="82" t="n"/>
-      <c r="H33" s="82" t="n"/>
-      <c r="I33" s="82" t="n"/>
-      <c r="J33" s="82" t="n"/>
-      <c r="K33" s="82" t="n"/>
-      <c r="L33" s="82" t="n"/>
-      <c r="M33" s="82" t="n"/>
-      <c r="N33" s="82" t="n"/>
-      <c r="O33" s="82" t="n"/>
-      <c r="P33" s="82" t="n"/>
-      <c r="Q33" s="98">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="82" t="n"/>
-      <c r="B34" s="82" t="n"/>
-      <c r="C34" s="82" t="n"/>
-      <c r="D34" s="82" t="n"/>
-      <c r="E34" s="82" t="n"/>
-      <c r="F34" s="82" t="n"/>
-      <c r="G34" s="82" t="n"/>
-      <c r="H34" s="82" t="n"/>
-      <c r="I34" s="82" t="n"/>
-      <c r="J34" s="82" t="n"/>
-      <c r="K34" s="82" t="n"/>
-      <c r="L34" s="82" t="n"/>
-      <c r="M34" s="82" t="n"/>
-      <c r="N34" s="82" t="n"/>
-      <c r="O34" s="82" t="n"/>
-      <c r="P34" s="82" t="n"/>
-      <c r="Q34" s="98">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="82" t="n"/>
-      <c r="B35" s="82" t="n"/>
-      <c r="C35" s="82" t="n"/>
-      <c r="D35" s="82" t="n"/>
-      <c r="E35" s="82" t="n"/>
-      <c r="F35" s="82" t="n"/>
-      <c r="G35" s="82" t="n"/>
-      <c r="H35" s="82" t="n"/>
-      <c r="I35" s="82" t="n"/>
-      <c r="J35" s="82" t="n"/>
-      <c r="K35" s="82" t="n"/>
-      <c r="L35" s="82" t="n"/>
-      <c r="M35" s="82" t="n"/>
-      <c r="N35" s="82" t="n"/>
-      <c r="O35" s="82" t="n"/>
-      <c r="P35" s="82" t="n"/>
-      <c r="Q35" s="98">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="82" t="n"/>
-      <c r="B36" s="82" t="n"/>
-      <c r="C36" s="82" t="n"/>
-      <c r="D36" s="82" t="n"/>
-      <c r="E36" s="82" t="n"/>
-      <c r="F36" s="82" t="n"/>
-      <c r="G36" s="82" t="n"/>
-      <c r="H36" s="82" t="n"/>
-      <c r="I36" s="82" t="n"/>
-      <c r="J36" s="82" t="n"/>
-      <c r="K36" s="82" t="n"/>
-      <c r="L36" s="82" t="n"/>
-      <c r="M36" s="82" t="n"/>
-      <c r="N36" s="82" t="n"/>
-      <c r="O36" s="82" t="n"/>
-      <c r="P36" s="82" t="n"/>
-      <c r="Q36" s="98">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="82" t="n"/>
-      <c r="B37" s="82" t="n"/>
-      <c r="C37" s="82" t="n"/>
-      <c r="D37" s="82" t="n"/>
-      <c r="E37" s="82" t="n"/>
-      <c r="F37" s="82" t="n"/>
-      <c r="G37" s="82" t="n"/>
-      <c r="H37" s="82" t="n"/>
-      <c r="I37" s="82" t="n"/>
-      <c r="J37" s="82" t="n"/>
-      <c r="K37" s="82" t="n"/>
-      <c r="L37" s="82" t="n"/>
-      <c r="M37" s="82" t="n"/>
-      <c r="N37" s="82" t="n"/>
-      <c r="O37" s="82" t="n"/>
-      <c r="P37" s="82" t="n"/>
-      <c r="Q37" s="98">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="82" t="n"/>
-      <c r="B38" s="82" t="n"/>
-      <c r="C38" s="82" t="n"/>
-      <c r="D38" s="82" t="n"/>
-      <c r="E38" s="82" t="n"/>
-      <c r="F38" s="82" t="n"/>
-      <c r="G38" s="82" t="n"/>
-      <c r="H38" s="82" t="n"/>
-      <c r="I38" s="82" t="n"/>
-      <c r="J38" s="82" t="n"/>
-      <c r="K38" s="82" t="n"/>
-      <c r="L38" s="82" t="n"/>
-      <c r="M38" s="82" t="n"/>
-      <c r="N38" s="82" t="n"/>
-      <c r="O38" s="82" t="n"/>
-      <c r="P38" s="82" t="n"/>
-      <c r="Q38" s="98">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="82" t="n"/>
-      <c r="B39" s="82" t="n"/>
-      <c r="C39" s="82" t="n"/>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
-      <c r="G39" s="82" t="n"/>
-      <c r="H39" s="82" t="n"/>
-      <c r="I39" s="82" t="n"/>
-      <c r="J39" s="82" t="n"/>
-      <c r="K39" s="82" t="n"/>
-      <c r="L39" s="82" t="n"/>
-      <c r="M39" s="82" t="n"/>
-      <c r="N39" s="82" t="n"/>
-      <c r="O39" s="82" t="n"/>
-      <c r="P39" s="82" t="n"/>
-      <c r="Q39" s="98">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="82" t="n"/>
-      <c r="B40" s="82" t="n"/>
-      <c r="C40" s="82" t="n"/>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
-      <c r="G40" s="82" t="n"/>
-      <c r="H40" s="82" t="n"/>
-      <c r="I40" s="82" t="n"/>
-      <c r="J40" s="82" t="n"/>
-      <c r="K40" s="82" t="n"/>
-      <c r="L40" s="82" t="n"/>
-      <c r="M40" s="82" t="n"/>
-      <c r="N40" s="82" t="n"/>
-      <c r="O40" s="82" t="n"/>
-      <c r="P40" s="82" t="n"/>
-      <c r="Q40" s="98">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="82" t="n"/>
-      <c r="B41" s="82" t="n"/>
-      <c r="C41" s="82" t="n"/>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="82" t="n"/>
-      <c r="G41" s="82" t="n"/>
-      <c r="H41" s="82" t="n"/>
-      <c r="I41" s="82" t="n"/>
-      <c r="J41" s="82" t="n"/>
-      <c r="K41" s="82" t="n"/>
-      <c r="L41" s="82" t="n"/>
-      <c r="M41" s="82" t="n"/>
-      <c r="N41" s="82" t="n"/>
-      <c r="O41" s="82" t="n"/>
-      <c r="P41" s="82" t="n"/>
-      <c r="Q41" s="98">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="82" t="n"/>
-      <c r="B42" s="82" t="n"/>
-      <c r="C42" s="82" t="n"/>
-      <c r="D42" s="82" t="n"/>
-      <c r="E42" s="82" t="n"/>
-      <c r="F42" s="82" t="n"/>
-      <c r="G42" s="82" t="n"/>
-      <c r="H42" s="82" t="n"/>
-      <c r="I42" s="82" t="n"/>
-      <c r="J42" s="82" t="n"/>
-      <c r="K42" s="82" t="n"/>
-      <c r="L42" s="82" t="n"/>
-      <c r="M42" s="82" t="n"/>
-      <c r="N42" s="82" t="n"/>
-      <c r="O42" s="82" t="n"/>
-      <c r="P42" s="82" t="n"/>
-      <c r="Q42" s="98">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="82" t="n"/>
-      <c r="B43" s="82" t="n"/>
-      <c r="C43" s="82" t="n"/>
-      <c r="D43" s="82" t="n"/>
-      <c r="E43" s="82" t="n"/>
-      <c r="F43" s="82" t="n"/>
-      <c r="G43" s="82" t="n"/>
-      <c r="H43" s="82" t="n"/>
-      <c r="I43" s="82" t="n"/>
-      <c r="J43" s="82" t="n"/>
-      <c r="K43" s="82" t="n"/>
-      <c r="L43" s="82" t="n"/>
-      <c r="M43" s="82" t="n"/>
-      <c r="N43" s="82" t="n"/>
-      <c r="O43" s="82" t="n"/>
-      <c r="P43" s="82" t="n"/>
-      <c r="Q43" s="98">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="82" t="n"/>
-      <c r="B44" s="82" t="n"/>
-      <c r="C44" s="82" t="n"/>
-      <c r="D44" s="82" t="n"/>
-      <c r="E44" s="82" t="n"/>
-      <c r="F44" s="82" t="n"/>
-      <c r="G44" s="82" t="n"/>
-      <c r="H44" s="82" t="n"/>
-      <c r="I44" s="82" t="n"/>
-      <c r="J44" s="82" t="n"/>
-      <c r="K44" s="82" t="n"/>
-      <c r="L44" s="82" t="n"/>
-      <c r="M44" s="82" t="n"/>
-      <c r="N44" s="82" t="n"/>
-      <c r="O44" s="82" t="n"/>
-      <c r="P44" s="82" t="n"/>
-      <c r="Q44" s="98">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="54" customHeight="1">
-      <c r="A45" s="99" t="inlineStr">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>CO-025</t>
         </is>
       </c>
-      <c r="B45" s="100" t="inlineStr">
+      <c r="B5" s="100" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C45" s="101" t="inlineStr">
+      <c r="C5" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D45" s="100" t="inlineStr">
+      <c r="D5" s="100" t="inlineStr">
         <is>
           <t>دستگاه روشن، باتری وصل و یک بار (مثلاً لامپ) روی خروجی</t>
         </is>
       </c>
-      <c r="E45" s="100" t="inlineStr">
+      <c r="E5" s="100" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را فقط با باتری روشن کن و مطمئن شو بار روشن است.
 گام ۲: ولتاژ باتری را با منبع آزمایشگاهی آرام پایین بیاور تا زیر 21 ولت برسد.
@@ -2997,68 +1811,71 @@
 گام ۴: بار باید خاموش شود (خروجی قطع شود)؛ تا وقتی باتری بالای 21 ولت است بار نباید قطع شود.</t>
         </is>
       </c>
-      <c r="F45" s="100" t="inlineStr">
+      <c r="F5" s="100" t="inlineStr">
         <is>
           <t>باتری از 24 ولت تا زیر 21 ولت</t>
         </is>
       </c>
-      <c r="G45" s="101" t="inlineStr">
+      <c r="G5" s="101" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H45" s="100" t="inlineStr">
+      <c r="H5" s="100" t="inlineStr">
         <is>
           <t>با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود</t>
         </is>
       </c>
-      <c r="I45" s="100" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="100" t="inlineStr">
+      <c r="I5" s="100" t="inlineStr">
+        <is>
+          <t>باید ببینید: با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود؛ تا وقتی باتری بالای حد است بار روشن می‌ماند. اگر زود قطع کرد یا اصلاً قطع نکرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J5" s="100" t="inlineStr">
         <is>
           <t>بار قطع شود؛ قطع زودهنگام وقتی باتری هنوز بالای حد است = رد</t>
         </is>
       </c>
-      <c r="K45" s="100" t="inlineStr"/>
-      <c r="L45" s="102" t="inlineStr">
+      <c r="K5" s="100" t="n"/>
+      <c r="L5" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M45" s="100" t="n"/>
-      <c r="N45" s="100" t="n"/>
-      <c r="O45" s="101" t="n"/>
-      <c r="P45" s="101" t="n"/>
-      <c r="Q45" s="103">
+      <c r="M5" s="100" t="n"/>
+      <c r="N5" s="100" t="n"/>
+      <c r="O5" s="101" t="n"/>
+      <c r="P5" s="101">
+        <f>IF(OR(K5="",K5="در انتظار"),"",IF(P5="",TODAY(),P5))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="103">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="54" customHeight="1">
-      <c r="A46" s="99" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="99" t="inlineStr">
         <is>
           <t>CO-026</t>
         </is>
       </c>
-      <c r="B46" s="104" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C46" s="105" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D46" s="106" t="inlineStr">
+      <c r="D6" s="106" t="inlineStr">
         <is>
           <t>پایان CO-025 (خروجی قطع است)</t>
         </is>
       </c>
-      <c r="E46" s="106" t="inlineStr">
+      <c r="E6" s="106" t="inlineStr">
         <is>
           <t>گام ۱: از پایان CO-025 شروع کن که خروجی قطع و بار خاموش است.
 گام ۲: برق شهر (ورودی) را وصل کن و ولتاژ باتری را به بالای 21.2 ولت برگردان (با شارژ یا منبع).
@@ -3066,68 +1883,71 @@
 گام ۴: بار باید دوباره روشن شود؛ اگر ولتاژ باتری هنوز پایین است نباید وصل شود.</t>
         </is>
       </c>
-      <c r="F46" s="104" t="inlineStr">
+      <c r="F6" s="104" t="inlineStr">
         <is>
           <t>ورودی حاضر + باتری بالای 21.2 ولت</t>
         </is>
       </c>
-      <c r="G46" s="105" t="inlineStr">
+      <c r="G6" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H46" s="104" t="inlineStr">
+      <c r="H6" s="104" t="inlineStr">
         <is>
           <t>خروجی وصل و بار روشن می‌شود</t>
         </is>
       </c>
-      <c r="I46" s="104" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="104" t="inlineStr">
+      <c r="I6" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید: با برگشت ورودی و باتریِ کافی، خروجی وصل و بار روشن می‌شود. اگر با باتری پایین وصل شد یا اصلاً وصل نشد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J6" s="104" t="inlineStr">
         <is>
           <t>بار دوباره روشن شود؛ وصل شدن با باتری پایین = رد</t>
         </is>
       </c>
-      <c r="K46" s="104" t="inlineStr"/>
-      <c r="L46" s="102" t="inlineStr">
+      <c r="K6" s="104" t="n"/>
+      <c r="L6" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M46" s="104" t="n"/>
-      <c r="N46" s="104" t="n"/>
-      <c r="O46" s="105" t="n"/>
-      <c r="P46" s="105" t="n"/>
-      <c r="Q46" s="107">
+      <c r="M6" s="104" t="n"/>
+      <c r="N6" s="104" t="n"/>
+      <c r="O6" s="105" t="n"/>
+      <c r="P6" s="105">
+        <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="107">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="54" customHeight="1">
-      <c r="A47" s="99" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="99" t="inlineStr">
         <is>
           <t>CO-027</t>
         </is>
       </c>
-      <c r="B47" s="100" t="inlineStr">
+      <c r="B7" s="100" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C47" s="101" t="inlineStr">
+      <c r="C7" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D47" s="100" t="inlineStr">
+      <c r="D7" s="100" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر و باتری وصل، بار روشن</t>
         </is>
       </c>
-      <c r="E47" s="100" t="inlineStr">
+      <c r="E7" s="100" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را با برق شهر و باتری روشن کن و بار را روشن ببین.
 گام ۲: برق شهر را بکش؛ دستگاه نباید خاموش شود و بار باید بی‌وقفه روشن بماند (کار روی باتری).
@@ -3135,68 +1955,71 @@
 گام ۴: در هیچ‌کدام از این دو جابه‌جایی نباید دستگاه در وضعیت خطا گیر کند.</t>
         </is>
       </c>
-      <c r="F47" s="100" t="inlineStr">
+      <c r="F7" s="100" t="inlineStr">
         <is>
           <t>قطع و وصل برق شهر</t>
         </is>
       </c>
-      <c r="G47" s="101" t="inlineStr">
+      <c r="G7" s="101" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H47" s="100" t="inlineStr">
+      <c r="H7" s="100" t="inlineStr">
         <is>
           <t>ادامهٔ بی‌وقفهٔ کار بار و برگشت عادی</t>
         </is>
       </c>
-      <c r="I47" s="100" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="100" t="inlineStr">
+      <c r="I7" s="100" t="inlineStr">
+        <is>
+          <t>باید ببینید: با قطع و وصل برق شهر، بار هرگز خاموش نمی‌شود و دستگاه بعد از برگشت شهر عادی کار می‌کند. اگر بار لحظه‌ای هم خاموش شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J7" s="100" t="inlineStr">
         <is>
           <t>بار هرگز خاموش نشود و دستگاه بعد از برگشت شهر عادی کار کند</t>
         </is>
       </c>
-      <c r="K47" s="100" t="inlineStr"/>
-      <c r="L47" s="102" t="inlineStr">
+      <c r="K7" s="100" t="n"/>
+      <c r="L7" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M47" s="100" t="n"/>
-      <c r="N47" s="100" t="n"/>
-      <c r="O47" s="101" t="n"/>
-      <c r="P47" s="101" t="n"/>
-      <c r="Q47" s="103">
+      <c r="M7" s="100" t="n"/>
+      <c r="N7" s="100" t="n"/>
+      <c r="O7" s="101" t="n"/>
+      <c r="P7" s="101">
+        <f>IF(OR(K7="",K7="در انتظار"),"",IF(P7="",TODAY(),P7))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="103">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="99" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="99" t="inlineStr">
         <is>
           <t>CO-028</t>
         </is>
       </c>
-      <c r="B48" s="104" t="inlineStr">
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C48" s="105" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D48" s="104" t="inlineStr">
+      <c r="D8" s="104" t="inlineStr">
         <is>
           <t>دستگاه در حال کار عادی با بار روشن</t>
         </is>
       </c>
-      <c r="E48" s="104" t="inlineStr">
+      <c r="E8" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه در حال کار عادی باشد و بار روشن.
 گام ۲: یک خطای شارژر بساز (حین شارژ سیم باتری را قطع کن تا آلارم قطع باتری بیاید).
@@ -3204,45 +2027,808 @@
 گام ۴: بار نباید قطع‌ووصل یا چشمک بزند؛ خروجی باید همان وضعیت قبل از خطا را نگه دارد.</t>
         </is>
       </c>
-      <c r="F48" s="104" t="inlineStr">
+      <c r="F8" s="104" t="inlineStr">
         <is>
           <t>خطای قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G48" s="105" t="inlineStr">
+      <c r="G8" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H48" s="104" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>آلارم خطا می‌آید ولی خروجی تکان نمی‌خورد</t>
         </is>
       </c>
-      <c r="I48" s="104" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="104" t="inlineStr">
+      <c r="I8" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید: آلارم خطا می‌آید ولی بار بدون هیچ تکانی روشن می‌ماند. اگر خروجی تکان خورد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J8" s="104" t="inlineStr">
         <is>
           <t>بار بدون هیچ تکانی روشن بماند</t>
         </is>
       </c>
-      <c r="K48" s="104" t="inlineStr"/>
-      <c r="L48" s="102" t="inlineStr">
+      <c r="K8" s="104" t="n"/>
+      <c r="L8" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M48" s="104" t="n"/>
-      <c r="N48" s="104" t="n"/>
-      <c r="O48" s="105" t="n"/>
-      <c r="P48" s="105" t="n"/>
-      <c r="Q48" s="107">
+      <c r="M8" s="104" t="n"/>
+      <c r="N8" s="104" t="n"/>
+      <c r="O8" s="105" t="n"/>
+      <c r="P8" s="105">
+        <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="107">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="131" t="n"/>
+      <c r="B9" s="131" t="n"/>
+      <c r="C9" s="131" t="n"/>
+      <c r="D9" s="131" t="n"/>
+      <c r="E9" s="131" t="n"/>
+      <c r="F9" s="131" t="n"/>
+      <c r="G9" s="131" t="n"/>
+      <c r="H9" s="131" t="n"/>
+      <c r="I9" s="131" t="n"/>
+      <c r="J9" s="131" t="n"/>
+      <c r="K9" s="131" t="n"/>
+      <c r="L9" s="131" t="n"/>
+      <c r="M9" s="131" t="n"/>
+      <c r="N9" s="131" t="n"/>
+      <c r="O9" s="131" t="n"/>
+      <c r="P9" s="131" t="n"/>
+      <c r="Q9" s="132" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="131" t="n"/>
+      <c r="B10" s="131" t="n"/>
+      <c r="C10" s="131" t="n"/>
+      <c r="D10" s="131" t="n"/>
+      <c r="E10" s="131" t="n"/>
+      <c r="F10" s="131" t="n"/>
+      <c r="G10" s="131" t="n"/>
+      <c r="H10" s="131" t="n"/>
+      <c r="I10" s="131" t="n"/>
+      <c r="J10" s="131" t="n"/>
+      <c r="K10" s="131" t="n"/>
+      <c r="L10" s="131" t="n"/>
+      <c r="M10" s="131" t="n"/>
+      <c r="N10" s="131" t="n"/>
+      <c r="O10" s="131" t="n"/>
+      <c r="P10" s="131" t="n"/>
+      <c r="Q10" s="132" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="131" t="n"/>
+      <c r="B11" s="131" t="n"/>
+      <c r="C11" s="131" t="n"/>
+      <c r="D11" s="131" t="n"/>
+      <c r="E11" s="131" t="n"/>
+      <c r="F11" s="131" t="n"/>
+      <c r="G11" s="131" t="n"/>
+      <c r="H11" s="131" t="n"/>
+      <c r="I11" s="131" t="n"/>
+      <c r="J11" s="131" t="n"/>
+      <c r="K11" s="131" t="n"/>
+      <c r="L11" s="131" t="n"/>
+      <c r="M11" s="131" t="n"/>
+      <c r="N11" s="131" t="n"/>
+      <c r="O11" s="131" t="n"/>
+      <c r="P11" s="131" t="n"/>
+      <c r="Q11" s="132" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="131" t="n"/>
+      <c r="B12" s="131" t="n"/>
+      <c r="C12" s="131" t="n"/>
+      <c r="D12" s="131" t="n"/>
+      <c r="E12" s="131" t="n"/>
+      <c r="F12" s="131" t="n"/>
+      <c r="G12" s="131" t="n"/>
+      <c r="H12" s="131" t="n"/>
+      <c r="I12" s="131" t="n"/>
+      <c r="J12" s="131" t="n"/>
+      <c r="K12" s="131" t="n"/>
+      <c r="L12" s="131" t="n"/>
+      <c r="M12" s="131" t="n"/>
+      <c r="N12" s="131" t="n"/>
+      <c r="O12" s="131" t="n"/>
+      <c r="P12" s="131" t="n"/>
+      <c r="Q12" s="132" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="131" t="n"/>
+      <c r="B13" s="131" t="n"/>
+      <c r="C13" s="131" t="n"/>
+      <c r="D13" s="131" t="n"/>
+      <c r="E13" s="131" t="n"/>
+      <c r="F13" s="131" t="n"/>
+      <c r="G13" s="131" t="n"/>
+      <c r="H13" s="131" t="n"/>
+      <c r="I13" s="131" t="n"/>
+      <c r="J13" s="131" t="n"/>
+      <c r="K13" s="131" t="n"/>
+      <c r="L13" s="131" t="n"/>
+      <c r="M13" s="131" t="n"/>
+      <c r="N13" s="131" t="n"/>
+      <c r="O13" s="131" t="n"/>
+      <c r="P13" s="131" t="n"/>
+      <c r="Q13" s="132" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="131" t="n"/>
+      <c r="B14" s="131" t="n"/>
+      <c r="C14" s="131" t="n"/>
+      <c r="D14" s="131" t="n"/>
+      <c r="E14" s="131" t="n"/>
+      <c r="F14" s="131" t="n"/>
+      <c r="G14" s="131" t="n"/>
+      <c r="H14" s="131" t="n"/>
+      <c r="I14" s="131" t="n"/>
+      <c r="J14" s="131" t="n"/>
+      <c r="K14" s="131" t="n"/>
+      <c r="L14" s="131" t="n"/>
+      <c r="M14" s="131" t="n"/>
+      <c r="N14" s="131" t="n"/>
+      <c r="O14" s="131" t="n"/>
+      <c r="P14" s="131" t="n"/>
+      <c r="Q14" s="132" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="131" t="n"/>
+      <c r="B15" s="131" t="n"/>
+      <c r="C15" s="131" t="n"/>
+      <c r="D15" s="131" t="n"/>
+      <c r="E15" s="131" t="n"/>
+      <c r="F15" s="131" t="n"/>
+      <c r="G15" s="131" t="n"/>
+      <c r="H15" s="131" t="n"/>
+      <c r="I15" s="131" t="n"/>
+      <c r="J15" s="131" t="n"/>
+      <c r="K15" s="131" t="n"/>
+      <c r="L15" s="131" t="n"/>
+      <c r="M15" s="131" t="n"/>
+      <c r="N15" s="131" t="n"/>
+      <c r="O15" s="131" t="n"/>
+      <c r="P15" s="131" t="n"/>
+      <c r="Q15" s="132" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="131" t="n"/>
+      <c r="B16" s="131" t="n"/>
+      <c r="C16" s="131" t="n"/>
+      <c r="D16" s="131" t="n"/>
+      <c r="E16" s="131" t="n"/>
+      <c r="F16" s="131" t="n"/>
+      <c r="G16" s="131" t="n"/>
+      <c r="H16" s="131" t="n"/>
+      <c r="I16" s="131" t="n"/>
+      <c r="J16" s="131" t="n"/>
+      <c r="K16" s="131" t="n"/>
+      <c r="L16" s="131" t="n"/>
+      <c r="M16" s="131" t="n"/>
+      <c r="N16" s="131" t="n"/>
+      <c r="O16" s="131" t="n"/>
+      <c r="P16" s="131" t="n"/>
+      <c r="Q16" s="132" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="131" t="n"/>
+      <c r="B17" s="131" t="n"/>
+      <c r="C17" s="131" t="n"/>
+      <c r="D17" s="131" t="n"/>
+      <c r="E17" s="131" t="n"/>
+      <c r="F17" s="131" t="n"/>
+      <c r="G17" s="131" t="n"/>
+      <c r="H17" s="131" t="n"/>
+      <c r="I17" s="131" t="n"/>
+      <c r="J17" s="131" t="n"/>
+      <c r="K17" s="131" t="n"/>
+      <c r="L17" s="131" t="n"/>
+      <c r="M17" s="131" t="n"/>
+      <c r="N17" s="131" t="n"/>
+      <c r="O17" s="131" t="n"/>
+      <c r="P17" s="131" t="n"/>
+      <c r="Q17" s="132" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="131" t="n"/>
+      <c r="B18" s="131" t="n"/>
+      <c r="C18" s="131" t="n"/>
+      <c r="D18" s="131" t="n"/>
+      <c r="E18" s="131" t="n"/>
+      <c r="F18" s="131" t="n"/>
+      <c r="G18" s="131" t="n"/>
+      <c r="H18" s="131" t="n"/>
+      <c r="I18" s="131" t="n"/>
+      <c r="J18" s="131" t="n"/>
+      <c r="K18" s="131" t="n"/>
+      <c r="L18" s="131" t="n"/>
+      <c r="M18" s="131" t="n"/>
+      <c r="N18" s="131" t="n"/>
+      <c r="O18" s="131" t="n"/>
+      <c r="P18" s="131" t="n"/>
+      <c r="Q18" s="132" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="131" t="n"/>
+      <c r="B19" s="131" t="n"/>
+      <c r="C19" s="131" t="n"/>
+      <c r="D19" s="131" t="n"/>
+      <c r="E19" s="131" t="n"/>
+      <c r="F19" s="131" t="n"/>
+      <c r="G19" s="131" t="n"/>
+      <c r="H19" s="131" t="n"/>
+      <c r="I19" s="131" t="n"/>
+      <c r="J19" s="131" t="n"/>
+      <c r="K19" s="131" t="n"/>
+      <c r="L19" s="131" t="n"/>
+      <c r="M19" s="131" t="n"/>
+      <c r="N19" s="131" t="n"/>
+      <c r="O19" s="131" t="n"/>
+      <c r="P19" s="131" t="n"/>
+      <c r="Q19" s="132" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="131" t="n"/>
+      <c r="B20" s="131" t="n"/>
+      <c r="C20" s="131" t="n"/>
+      <c r="D20" s="131" t="n"/>
+      <c r="E20" s="131" t="n"/>
+      <c r="F20" s="131" t="n"/>
+      <c r="G20" s="131" t="n"/>
+      <c r="H20" s="131" t="n"/>
+      <c r="I20" s="131" t="n"/>
+      <c r="J20" s="131" t="n"/>
+      <c r="K20" s="131" t="n"/>
+      <c r="L20" s="131" t="n"/>
+      <c r="M20" s="131" t="n"/>
+      <c r="N20" s="131" t="n"/>
+      <c r="O20" s="131" t="n"/>
+      <c r="P20" s="131" t="n"/>
+      <c r="Q20" s="132" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="131" t="n"/>
+      <c r="B21" s="131" t="n"/>
+      <c r="C21" s="131" t="n"/>
+      <c r="D21" s="131" t="n"/>
+      <c r="E21" s="131" t="n"/>
+      <c r="F21" s="131" t="n"/>
+      <c r="G21" s="131" t="n"/>
+      <c r="H21" s="131" t="n"/>
+      <c r="I21" s="131" t="n"/>
+      <c r="J21" s="131" t="n"/>
+      <c r="K21" s="131" t="n"/>
+      <c r="L21" s="131" t="n"/>
+      <c r="M21" s="131" t="n"/>
+      <c r="N21" s="131" t="n"/>
+      <c r="O21" s="131" t="n"/>
+      <c r="P21" s="131" t="n"/>
+      <c r="Q21" s="132" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="131" t="n"/>
+      <c r="B22" s="131" t="n"/>
+      <c r="C22" s="131" t="n"/>
+      <c r="D22" s="131" t="n"/>
+      <c r="E22" s="131" t="n"/>
+      <c r="F22" s="131" t="n"/>
+      <c r="G22" s="131" t="n"/>
+      <c r="H22" s="131" t="n"/>
+      <c r="I22" s="131" t="n"/>
+      <c r="J22" s="131" t="n"/>
+      <c r="K22" s="131" t="n"/>
+      <c r="L22" s="131" t="n"/>
+      <c r="M22" s="131" t="n"/>
+      <c r="N22" s="131" t="n"/>
+      <c r="O22" s="131" t="n"/>
+      <c r="P22" s="131" t="n"/>
+      <c r="Q22" s="132" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="131" t="n"/>
+      <c r="B23" s="131" t="n"/>
+      <c r="C23" s="131" t="n"/>
+      <c r="D23" s="131" t="n"/>
+      <c r="E23" s="131" t="n"/>
+      <c r="F23" s="131" t="n"/>
+      <c r="G23" s="131" t="n"/>
+      <c r="H23" s="131" t="n"/>
+      <c r="I23" s="131" t="n"/>
+      <c r="J23" s="131" t="n"/>
+      <c r="K23" s="131" t="n"/>
+      <c r="L23" s="131" t="n"/>
+      <c r="M23" s="131" t="n"/>
+      <c r="N23" s="131" t="n"/>
+      <c r="O23" s="131" t="n"/>
+      <c r="P23" s="131" t="n"/>
+      <c r="Q23" s="132" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="131" t="n"/>
+      <c r="B24" s="131" t="n"/>
+      <c r="C24" s="131" t="n"/>
+      <c r="D24" s="131" t="n"/>
+      <c r="E24" s="131" t="n"/>
+      <c r="F24" s="131" t="n"/>
+      <c r="G24" s="131" t="n"/>
+      <c r="H24" s="131" t="n"/>
+      <c r="I24" s="131" t="n"/>
+      <c r="J24" s="131" t="n"/>
+      <c r="K24" s="131" t="n"/>
+      <c r="L24" s="131" t="n"/>
+      <c r="M24" s="131" t="n"/>
+      <c r="N24" s="131" t="n"/>
+      <c r="O24" s="131" t="n"/>
+      <c r="P24" s="131" t="n"/>
+      <c r="Q24" s="132" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="131" t="n"/>
+      <c r="B25" s="131" t="n"/>
+      <c r="C25" s="131" t="n"/>
+      <c r="D25" s="131" t="n"/>
+      <c r="E25" s="131" t="n"/>
+      <c r="F25" s="131" t="n"/>
+      <c r="G25" s="131" t="n"/>
+      <c r="H25" s="131" t="n"/>
+      <c r="I25" s="131" t="n"/>
+      <c r="J25" s="131" t="n"/>
+      <c r="K25" s="131" t="n"/>
+      <c r="L25" s="131" t="n"/>
+      <c r="M25" s="131" t="n"/>
+      <c r="N25" s="131" t="n"/>
+      <c r="O25" s="131" t="n"/>
+      <c r="P25" s="131" t="n"/>
+      <c r="Q25" s="132" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="131" t="n"/>
+      <c r="B26" s="131" t="n"/>
+      <c r="C26" s="131" t="n"/>
+      <c r="D26" s="131" t="n"/>
+      <c r="E26" s="131" t="n"/>
+      <c r="F26" s="131" t="n"/>
+      <c r="G26" s="131" t="n"/>
+      <c r="H26" s="131" t="n"/>
+      <c r="I26" s="131" t="n"/>
+      <c r="J26" s="131" t="n"/>
+      <c r="K26" s="131" t="n"/>
+      <c r="L26" s="131" t="n"/>
+      <c r="M26" s="131" t="n"/>
+      <c r="N26" s="131" t="n"/>
+      <c r="O26" s="131" t="n"/>
+      <c r="P26" s="131" t="n"/>
+      <c r="Q26" s="132" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="131" t="n"/>
+      <c r="B27" s="131" t="n"/>
+      <c r="C27" s="131" t="n"/>
+      <c r="D27" s="131" t="n"/>
+      <c r="E27" s="131" t="n"/>
+      <c r="F27" s="131" t="n"/>
+      <c r="G27" s="131" t="n"/>
+      <c r="H27" s="131" t="n"/>
+      <c r="I27" s="131" t="n"/>
+      <c r="J27" s="131" t="n"/>
+      <c r="K27" s="131" t="n"/>
+      <c r="L27" s="131" t="n"/>
+      <c r="M27" s="131" t="n"/>
+      <c r="N27" s="131" t="n"/>
+      <c r="O27" s="131" t="n"/>
+      <c r="P27" s="131" t="n"/>
+      <c r="Q27" s="132" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="131" t="n"/>
+      <c r="B28" s="131" t="n"/>
+      <c r="C28" s="131" t="n"/>
+      <c r="D28" s="131" t="n"/>
+      <c r="E28" s="131" t="n"/>
+      <c r="F28" s="131" t="n"/>
+      <c r="G28" s="131" t="n"/>
+      <c r="H28" s="131" t="n"/>
+      <c r="I28" s="131" t="n"/>
+      <c r="J28" s="131" t="n"/>
+      <c r="K28" s="131" t="n"/>
+      <c r="L28" s="131" t="n"/>
+      <c r="M28" s="131" t="n"/>
+      <c r="N28" s="131" t="n"/>
+      <c r="O28" s="131" t="n"/>
+      <c r="P28" s="131" t="n"/>
+      <c r="Q28" s="132" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="131" t="n"/>
+      <c r="B29" s="131" t="n"/>
+      <c r="C29" s="131" t="n"/>
+      <c r="D29" s="131" t="n"/>
+      <c r="E29" s="131" t="n"/>
+      <c r="F29" s="131" t="n"/>
+      <c r="G29" s="131" t="n"/>
+      <c r="H29" s="131" t="n"/>
+      <c r="I29" s="131" t="n"/>
+      <c r="J29" s="131" t="n"/>
+      <c r="K29" s="131" t="n"/>
+      <c r="L29" s="131" t="n"/>
+      <c r="M29" s="131" t="n"/>
+      <c r="N29" s="131" t="n"/>
+      <c r="O29" s="131" t="n"/>
+      <c r="P29" s="131" t="n"/>
+      <c r="Q29" s="132" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="131" t="n"/>
+      <c r="B30" s="131" t="n"/>
+      <c r="C30" s="131" t="n"/>
+      <c r="D30" s="131" t="n"/>
+      <c r="E30" s="131" t="n"/>
+      <c r="F30" s="131" t="n"/>
+      <c r="G30" s="131" t="n"/>
+      <c r="H30" s="131" t="n"/>
+      <c r="I30" s="131" t="n"/>
+      <c r="J30" s="131" t="n"/>
+      <c r="K30" s="131" t="n"/>
+      <c r="L30" s="131" t="n"/>
+      <c r="M30" s="131" t="n"/>
+      <c r="N30" s="131" t="n"/>
+      <c r="O30" s="131" t="n"/>
+      <c r="P30" s="131" t="n"/>
+      <c r="Q30" s="132" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="131" t="n"/>
+      <c r="B31" s="131" t="n"/>
+      <c r="C31" s="131" t="n"/>
+      <c r="D31" s="131" t="n"/>
+      <c r="E31" s="131" t="n"/>
+      <c r="F31" s="131" t="n"/>
+      <c r="G31" s="131" t="n"/>
+      <c r="H31" s="131" t="n"/>
+      <c r="I31" s="131" t="n"/>
+      <c r="J31" s="131" t="n"/>
+      <c r="K31" s="131" t="n"/>
+      <c r="L31" s="131" t="n"/>
+      <c r="M31" s="131" t="n"/>
+      <c r="N31" s="131" t="n"/>
+      <c r="O31" s="131" t="n"/>
+      <c r="P31" s="131" t="n"/>
+      <c r="Q31" s="132" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="131" t="n"/>
+      <c r="B32" s="131" t="n"/>
+      <c r="C32" s="131" t="n"/>
+      <c r="D32" s="131" t="n"/>
+      <c r="E32" s="131" t="n"/>
+      <c r="F32" s="131" t="n"/>
+      <c r="G32" s="131" t="n"/>
+      <c r="H32" s="131" t="n"/>
+      <c r="I32" s="131" t="n"/>
+      <c r="J32" s="131" t="n"/>
+      <c r="K32" s="131" t="n"/>
+      <c r="L32" s="131" t="n"/>
+      <c r="M32" s="131" t="n"/>
+      <c r="N32" s="131" t="n"/>
+      <c r="O32" s="131" t="n"/>
+      <c r="P32" s="131" t="n"/>
+      <c r="Q32" s="132" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="131" t="n"/>
+      <c r="B33" s="131" t="n"/>
+      <c r="C33" s="131" t="n"/>
+      <c r="D33" s="131" t="n"/>
+      <c r="E33" s="131" t="n"/>
+      <c r="F33" s="131" t="n"/>
+      <c r="G33" s="131" t="n"/>
+      <c r="H33" s="131" t="n"/>
+      <c r="I33" s="131" t="n"/>
+      <c r="J33" s="131" t="n"/>
+      <c r="K33" s="131" t="n"/>
+      <c r="L33" s="131" t="n"/>
+      <c r="M33" s="131" t="n"/>
+      <c r="N33" s="131" t="n"/>
+      <c r="O33" s="131" t="n"/>
+      <c r="P33" s="131" t="n"/>
+      <c r="Q33" s="132" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="131" t="n"/>
+      <c r="B34" s="131" t="n"/>
+      <c r="C34" s="131" t="n"/>
+      <c r="D34" s="131" t="n"/>
+      <c r="E34" s="131" t="n"/>
+      <c r="F34" s="131" t="n"/>
+      <c r="G34" s="131" t="n"/>
+      <c r="H34" s="131" t="n"/>
+      <c r="I34" s="131" t="n"/>
+      <c r="J34" s="131" t="n"/>
+      <c r="K34" s="131" t="n"/>
+      <c r="L34" s="131" t="n"/>
+      <c r="M34" s="131" t="n"/>
+      <c r="N34" s="131" t="n"/>
+      <c r="O34" s="131" t="n"/>
+      <c r="P34" s="131" t="n"/>
+      <c r="Q34" s="132" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="131" t="n"/>
+      <c r="B35" s="131" t="n"/>
+      <c r="C35" s="131" t="n"/>
+      <c r="D35" s="131" t="n"/>
+      <c r="E35" s="131" t="n"/>
+      <c r="F35" s="131" t="n"/>
+      <c r="G35" s="131" t="n"/>
+      <c r="H35" s="131" t="n"/>
+      <c r="I35" s="131" t="n"/>
+      <c r="J35" s="131" t="n"/>
+      <c r="K35" s="131" t="n"/>
+      <c r="L35" s="131" t="n"/>
+      <c r="M35" s="131" t="n"/>
+      <c r="N35" s="131" t="n"/>
+      <c r="O35" s="131" t="n"/>
+      <c r="P35" s="131" t="n"/>
+      <c r="Q35" s="132" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="131" t="n"/>
+      <c r="B36" s="131" t="n"/>
+      <c r="C36" s="131" t="n"/>
+      <c r="D36" s="131" t="n"/>
+      <c r="E36" s="131" t="n"/>
+      <c r="F36" s="131" t="n"/>
+      <c r="G36" s="131" t="n"/>
+      <c r="H36" s="131" t="n"/>
+      <c r="I36" s="131" t="n"/>
+      <c r="J36" s="131" t="n"/>
+      <c r="K36" s="131" t="n"/>
+      <c r="L36" s="131" t="n"/>
+      <c r="M36" s="131" t="n"/>
+      <c r="N36" s="131" t="n"/>
+      <c r="O36" s="131" t="n"/>
+      <c r="P36" s="131" t="n"/>
+      <c r="Q36" s="132" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="131" t="n"/>
+      <c r="B37" s="131" t="n"/>
+      <c r="C37" s="131" t="n"/>
+      <c r="D37" s="131" t="n"/>
+      <c r="E37" s="131" t="n"/>
+      <c r="F37" s="131" t="n"/>
+      <c r="G37" s="131" t="n"/>
+      <c r="H37" s="131" t="n"/>
+      <c r="I37" s="131" t="n"/>
+      <c r="J37" s="131" t="n"/>
+      <c r="K37" s="131" t="n"/>
+      <c r="L37" s="131" t="n"/>
+      <c r="M37" s="131" t="n"/>
+      <c r="N37" s="131" t="n"/>
+      <c r="O37" s="131" t="n"/>
+      <c r="P37" s="131" t="n"/>
+      <c r="Q37" s="132" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="131" t="n"/>
+      <c r="B38" s="131" t="n"/>
+      <c r="C38" s="131" t="n"/>
+      <c r="D38" s="131" t="n"/>
+      <c r="E38" s="131" t="n"/>
+      <c r="F38" s="131" t="n"/>
+      <c r="G38" s="131" t="n"/>
+      <c r="H38" s="131" t="n"/>
+      <c r="I38" s="131" t="n"/>
+      <c r="J38" s="131" t="n"/>
+      <c r="K38" s="131" t="n"/>
+      <c r="L38" s="131" t="n"/>
+      <c r="M38" s="131" t="n"/>
+      <c r="N38" s="131" t="n"/>
+      <c r="O38" s="131" t="n"/>
+      <c r="P38" s="131" t="n"/>
+      <c r="Q38" s="132" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="131" t="n"/>
+      <c r="B39" s="131" t="n"/>
+      <c r="C39" s="131" t="n"/>
+      <c r="D39" s="131" t="n"/>
+      <c r="E39" s="131" t="n"/>
+      <c r="F39" s="131" t="n"/>
+      <c r="G39" s="131" t="n"/>
+      <c r="H39" s="131" t="n"/>
+      <c r="I39" s="131" t="n"/>
+      <c r="J39" s="131" t="n"/>
+      <c r="K39" s="131" t="n"/>
+      <c r="L39" s="131" t="n"/>
+      <c r="M39" s="131" t="n"/>
+      <c r="N39" s="131" t="n"/>
+      <c r="O39" s="131" t="n"/>
+      <c r="P39" s="131" t="n"/>
+      <c r="Q39" s="132" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="131" t="n"/>
+      <c r="B40" s="131" t="n"/>
+      <c r="C40" s="131" t="n"/>
+      <c r="D40" s="131" t="n"/>
+      <c r="E40" s="131" t="n"/>
+      <c r="F40" s="131" t="n"/>
+      <c r="G40" s="131" t="n"/>
+      <c r="H40" s="131" t="n"/>
+      <c r="I40" s="131" t="n"/>
+      <c r="J40" s="131" t="n"/>
+      <c r="K40" s="131" t="n"/>
+      <c r="L40" s="131" t="n"/>
+      <c r="M40" s="131" t="n"/>
+      <c r="N40" s="131" t="n"/>
+      <c r="O40" s="131" t="n"/>
+      <c r="P40" s="131" t="n"/>
+      <c r="Q40" s="132" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="131" t="n"/>
+      <c r="B41" s="131" t="n"/>
+      <c r="C41" s="131" t="n"/>
+      <c r="D41" s="131" t="n"/>
+      <c r="E41" s="131" t="n"/>
+      <c r="F41" s="131" t="n"/>
+      <c r="G41" s="131" t="n"/>
+      <c r="H41" s="131" t="n"/>
+      <c r="I41" s="131" t="n"/>
+      <c r="J41" s="131" t="n"/>
+      <c r="K41" s="131" t="n"/>
+      <c r="L41" s="131" t="n"/>
+      <c r="M41" s="131" t="n"/>
+      <c r="N41" s="131" t="n"/>
+      <c r="O41" s="131" t="n"/>
+      <c r="P41" s="131" t="n"/>
+      <c r="Q41" s="132" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="131" t="n"/>
+      <c r="B42" s="131" t="n"/>
+      <c r="C42" s="131" t="n"/>
+      <c r="D42" s="131" t="n"/>
+      <c r="E42" s="131" t="n"/>
+      <c r="F42" s="131" t="n"/>
+      <c r="G42" s="131" t="n"/>
+      <c r="H42" s="131" t="n"/>
+      <c r="I42" s="131" t="n"/>
+      <c r="J42" s="131" t="n"/>
+      <c r="K42" s="131" t="n"/>
+      <c r="L42" s="131" t="n"/>
+      <c r="M42" s="131" t="n"/>
+      <c r="N42" s="131" t="n"/>
+      <c r="O42" s="131" t="n"/>
+      <c r="P42" s="131" t="n"/>
+      <c r="Q42" s="132" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="131" t="n"/>
+      <c r="B43" s="131" t="n"/>
+      <c r="C43" s="131" t="n"/>
+      <c r="D43" s="131" t="n"/>
+      <c r="E43" s="131" t="n"/>
+      <c r="F43" s="131" t="n"/>
+      <c r="G43" s="131" t="n"/>
+      <c r="H43" s="131" t="n"/>
+      <c r="I43" s="131" t="n"/>
+      <c r="J43" s="131" t="n"/>
+      <c r="K43" s="131" t="n"/>
+      <c r="L43" s="131" t="n"/>
+      <c r="M43" s="131" t="n"/>
+      <c r="N43" s="131" t="n"/>
+      <c r="O43" s="131" t="n"/>
+      <c r="P43" s="131" t="n"/>
+      <c r="Q43" s="132" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="131" t="n"/>
+      <c r="B44" s="131" t="n"/>
+      <c r="C44" s="131" t="n"/>
+      <c r="D44" s="131" t="n"/>
+      <c r="E44" s="131" t="n"/>
+      <c r="F44" s="131" t="n"/>
+      <c r="G44" s="131" t="n"/>
+      <c r="H44" s="131" t="n"/>
+      <c r="I44" s="131" t="n"/>
+      <c r="J44" s="131" t="n"/>
+      <c r="K44" s="131" t="n"/>
+      <c r="L44" s="131" t="n"/>
+      <c r="M44" s="131" t="n"/>
+      <c r="N44" s="131" t="n"/>
+      <c r="O44" s="131" t="n"/>
+      <c r="P44" s="131" t="n"/>
+      <c r="Q44" s="132" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="133" t="n"/>
+      <c r="B45" s="134" t="n"/>
+      <c r="C45" s="135" t="n"/>
+      <c r="D45" s="134" t="n"/>
+      <c r="E45" s="134" t="n"/>
+      <c r="F45" s="134" t="n"/>
+      <c r="G45" s="135" t="n"/>
+      <c r="H45" s="134" t="n"/>
+      <c r="I45" s="134" t="n"/>
+      <c r="J45" s="134" t="n"/>
+      <c r="K45" s="134" t="n"/>
+      <c r="L45" s="135" t="n"/>
+      <c r="M45" s="134" t="n"/>
+      <c r="N45" s="134" t="n"/>
+      <c r="O45" s="135" t="n"/>
+      <c r="P45" s="135" t="n"/>
+      <c r="Q45" s="136" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="133" t="n"/>
+      <c r="B46" s="134" t="n"/>
+      <c r="C46" s="135" t="n"/>
+      <c r="D46" s="134" t="n"/>
+      <c r="E46" s="134" t="n"/>
+      <c r="F46" s="134" t="n"/>
+      <c r="G46" s="135" t="n"/>
+      <c r="H46" s="134" t="n"/>
+      <c r="I46" s="134" t="n"/>
+      <c r="J46" s="134" t="n"/>
+      <c r="K46" s="134" t="n"/>
+      <c r="L46" s="135" t="n"/>
+      <c r="M46" s="134" t="n"/>
+      <c r="N46" s="134" t="n"/>
+      <c r="O46" s="135" t="n"/>
+      <c r="P46" s="135" t="n"/>
+      <c r="Q46" s="136" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="133" t="n"/>
+      <c r="B47" s="134" t="n"/>
+      <c r="C47" s="135" t="n"/>
+      <c r="D47" s="134" t="n"/>
+      <c r="E47" s="134" t="n"/>
+      <c r="F47" s="134" t="n"/>
+      <c r="G47" s="135" t="n"/>
+      <c r="H47" s="134" t="n"/>
+      <c r="I47" s="134" t="n"/>
+      <c r="J47" s="134" t="n"/>
+      <c r="K47" s="134" t="n"/>
+      <c r="L47" s="135" t="n"/>
+      <c r="M47" s="134" t="n"/>
+      <c r="N47" s="134" t="n"/>
+      <c r="O47" s="135" t="n"/>
+      <c r="P47" s="135" t="n"/>
+      <c r="Q47" s="136" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="133" t="n"/>
+      <c r="B48" s="134" t="n"/>
+      <c r="C48" s="135" t="n"/>
+      <c r="D48" s="134" t="n"/>
+      <c r="E48" s="134" t="n"/>
+      <c r="F48" s="134" t="n"/>
+      <c r="G48" s="135" t="n"/>
+      <c r="H48" s="134" t="n"/>
+      <c r="I48" s="134" t="n"/>
+      <c r="J48" s="134" t="n"/>
+      <c r="K48" s="134" t="n"/>
+      <c r="L48" s="135" t="n"/>
+      <c r="M48" s="134" t="n"/>
+      <c r="N48" s="134" t="n"/>
+      <c r="O48" s="135" t="n"/>
+      <c r="P48" s="135" t="n"/>
+      <c r="Q48" s="136" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q48"/>
@@ -3251,17 +2837,14 @@
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L5:L108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="L45 L46 L47 L48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="K5:K8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D46" location="'برنامه تست'!A45"/>
-    <hyperlink ref="E46" location="'برنامه تست'!A45"/>
+    <hyperlink ref="D6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6217,11 +5800,11 @@
           <t>مرجع سریع سناریوهای Changeover</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
-      <c r="D1" s="85" t="n"/>
-      <c r="E1" s="85" t="n"/>
-      <c r="F1" s="86" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="9" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="118" t="inlineStr">
@@ -6229,11 +5812,6 @@
           <t>این صفحه مرجع انتظار است؛ نتیجه واقعی فقط در «برنامه تست» ثبت شود. مقادیر از کد واقعی استخراج شده؛ مقدار حدسی وجود ندارد.</t>
         </is>
       </c>
-      <c r="B2" s="82" t="n"/>
-      <c r="C2" s="82" t="n"/>
-      <c r="D2" s="82" t="n"/>
-      <c r="E2" s="82" t="n"/>
-      <c r="F2" s="82" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="90" t="inlineStr">
@@ -6712,18 +6290,6 @@
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="82" t="n"/>
-      <c r="D1" s="82" t="n"/>
-      <c r="E1" s="82" t="n"/>
-      <c r="F1" s="82" t="n"/>
-      <c r="G1" s="82" t="n"/>
-      <c r="H1" s="82" t="n"/>
-      <c r="I1" s="82" t="n"/>
-      <c r="J1" s="82" t="n"/>
-      <c r="K1" s="82" t="n"/>
-      <c r="L1" s="82" t="n"/>
-      <c r="M1" s="82" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="84" t="inlineStr">
@@ -6731,18 +6297,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
       </c>
-      <c r="B2" s="85" t="n"/>
-      <c r="C2" s="85" t="n"/>
-      <c r="D2" s="85" t="n"/>
-      <c r="E2" s="85" t="n"/>
-      <c r="F2" s="85" t="n"/>
-      <c r="G2" s="85" t="n"/>
-      <c r="H2" s="85" t="n"/>
-      <c r="I2" s="85" t="n"/>
-      <c r="J2" s="85" t="n"/>
-      <c r="K2" s="85" t="n"/>
-      <c r="L2" s="85" t="n"/>
-      <c r="M2" s="86" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="9" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="90" t="inlineStr">
@@ -6996,11 +6562,6 @@
           <t>تأیید نهایی اعتبارسنجی روی برد — Changeover — PB11</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="82" t="n"/>
-      <c r="D1" s="82" t="n"/>
-      <c r="E1" s="82" t="n"/>
-      <c r="F1" s="82" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="125" t="inlineStr">
@@ -7008,11 +6569,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بستن ایرادهای باز امضا شود. بدون تکمیل این صفحه، اعتبارسنجی ناقص است.</t>
         </is>
       </c>
-      <c r="B2" s="82" t="n"/>
-      <c r="C2" s="82" t="n"/>
-      <c r="D2" s="82" t="n"/>
-      <c r="E2" s="82" t="n"/>
-      <c r="F2" s="82" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="89" t="inlineStr">
@@ -7020,11 +6576,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="82" t="n"/>
-      <c r="C3" s="82" t="n"/>
-      <c r="D3" s="82" t="n"/>
-      <c r="E3" s="82" t="n"/>
-      <c r="F3" s="82" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="126" t="inlineStr">
@@ -7048,7 +6599,7 @@
         </is>
       </c>
       <c r="E4" s="93" t="n"/>
-      <c r="F4" s="86" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="126" t="inlineStr">
@@ -7072,7 +6623,7 @@
         </is>
       </c>
       <c r="E5" s="93" t="n"/>
-      <c r="F5" s="86" t="n"/>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="126" t="inlineStr">
@@ -7092,7 +6643,7 @@
       </c>
       <c r="D6" s="127" t="inlineStr"/>
       <c r="E6" s="93" t="n"/>
-      <c r="F6" s="86" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="126" t="inlineStr">
@@ -7108,7 +6659,7 @@
       </c>
       <c r="D7" s="127" t="inlineStr"/>
       <c r="E7" s="93" t="n"/>
-      <c r="F7" s="86" t="n"/>
+      <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="126" t="inlineStr">
@@ -7128,7 +6679,7 @@
         </is>
       </c>
       <c r="E8" s="93" t="n"/>
-      <c r="F8" s="86" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="126" t="inlineStr">
@@ -7144,7 +6695,7 @@
       <c r="C9" s="126" t="inlineStr"/>
       <c r="D9" s="127" t="inlineStr"/>
       <c r="E9" s="93" t="n"/>
-      <c r="F9" s="86" t="n"/>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="126" t="inlineStr">
@@ -7232,11 +6783,6 @@
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
-      <c r="B15" s="82" t="n"/>
-      <c r="C15" s="82" t="n"/>
-      <c r="D15" s="82" t="n"/>
-      <c r="E15" s="82" t="n"/>
-      <c r="F15" s="82" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="90" t="inlineStr">
@@ -7259,8 +6805,8 @@
           <t>فرمول پیشنهادی</t>
         </is>
       </c>
-      <c r="E16" s="85" t="n"/>
-      <c r="F16" s="86" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="92" t="inlineStr">
@@ -7278,8 +6824,8 @@
         </is>
       </c>
       <c r="D17" s="92" t="inlineStr"/>
-      <c r="E17" s="85" t="n"/>
-      <c r="F17" s="86" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="92" t="inlineStr">
@@ -7301,8 +6847,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E18" s="85" t="n"/>
-      <c r="F18" s="86" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="92" t="inlineStr">
@@ -7324,8 +6870,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E19" s="85" t="n"/>
-      <c r="F19" s="86" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="92" t="inlineStr">
@@ -7347,8 +6893,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E20" s="85" t="n"/>
-      <c r="F20" s="86" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="92" t="inlineStr">
@@ -7366,8 +6912,8 @@
         </is>
       </c>
       <c r="D21" s="92" t="inlineStr"/>
-      <c r="E21" s="85" t="n"/>
-      <c r="F21" s="86" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="92" t="inlineStr">
@@ -7385,8 +6931,8 @@
         </is>
       </c>
       <c r="D22" s="92" t="inlineStr"/>
-      <c r="E22" s="85" t="n"/>
-      <c r="F22" s="86" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="89" t="inlineStr">
@@ -7394,11 +6940,6 @@
           <t>امضاها</t>
         </is>
       </c>
-      <c r="B23" s="82" t="n"/>
-      <c r="C23" s="82" t="n"/>
-      <c r="D23" s="82" t="n"/>
-      <c r="E23" s="82" t="n"/>
-      <c r="F23" s="82" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="90" t="inlineStr">
@@ -7426,7 +6967,7 @@
           <t>توضیحات</t>
         </is>
       </c>
-      <c r="F24" s="86" t="n"/>
+      <c r="F24" s="9" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="92" t="inlineStr">
@@ -7438,7 +6979,7 @@
       <c r="C25" s="92" t="inlineStr"/>
       <c r="D25" s="92" t="inlineStr"/>
       <c r="E25" s="92" t="inlineStr"/>
-      <c r="F25" s="86" t="n"/>
+      <c r="F25" s="9" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="92" t="inlineStr">
@@ -7450,7 +6991,7 @@
       <c r="C26" s="92" t="inlineStr"/>
       <c r="D26" s="92" t="inlineStr"/>
       <c r="E26" s="92" t="inlineStr"/>
-      <c r="F26" s="86" t="n"/>
+      <c r="F26" s="9" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="92" t="inlineStr">
@@ -7462,7 +7003,7 @@
       <c r="C27" s="92" t="inlineStr"/>
       <c r="D27" s="92" t="inlineStr"/>
       <c r="E27" s="92" t="inlineStr"/>
-      <c r="F27" s="86" t="n"/>
+      <c r="F27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="125" t="inlineStr">
@@ -7470,11 +7011,6 @@
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
       </c>
-      <c r="B28" s="82" t="n"/>
-      <c r="C28" s="82" t="n"/>
-      <c r="D28" s="82" t="n"/>
-      <c r="E28" s="82" t="n"/>
-      <c r="F28" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -7748,8 +7284,6 @@
           <t>ماشین حالت ماژول تغییر مسیر (Changeover)</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="82" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="82" t="n"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1849,10 +1849,7 @@
         <f>IF(OR(K5="",K5="در انتظار"),"",IF(P5="",TODAY(),P5))</f>
         <v/>
       </c>
-      <c r="Q5" s="103">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="Q5" s="103" t="n"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="99" t="inlineStr">
@@ -1921,10 +1918,7 @@
         <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
         <v/>
       </c>
-      <c r="Q6" s="107">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="Q6" s="107" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="99" t="inlineStr">
@@ -1993,10 +1987,7 @@
         <f>IF(OR(K7="",K7="در انتظار"),"",IF(P7="",TODAY(),P7))</f>
         <v/>
       </c>
-      <c r="Q7" s="103">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="Q7" s="103" t="n"/>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="99" t="inlineStr">
@@ -2065,10 +2056,7 @@
         <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
         <v/>
       </c>
-      <c r="Q8" s="107">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="Q8" s="107" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="131" t="n"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1605,6 +1605,7 @@
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="130" t="inlineStr">
         <is>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1290,7 +1290,9 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="83" t="inlineStr">
         <is>
-          <t>ChangeOver | PB11 (BSP_GPIO_PROTECT_BATTERY) | آستانه‌ها: 21000/20800/21200 و فیلتر 3000ms | نسخه 2.1 — فقط PB11، زمان rtos_time</t>
+          <t>ChangeOver | این ماژول فقط پایهٔ PB11 را کنترل می‌کند (BSP_GPIO_PROTECT_BATTERY).
+حدها: 21000 و 20800 و 21200 میلی‌ولت. زمان صبر: 3000 میلی‌ثانیه. نسخه 2.1.
+پایهٔ دیگری اینجا دست نمی‌خورد؛ فقط PB11.</t>
         </is>
       </c>
     </row>
@@ -1319,63 +1321,78 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="87" t="inlineStr">
         <is>
-          <t>این فایل برای اعتبارسنجی منطق Changeover تهیه شده است: بررسی snapshot.valid، fault_mask، input_present، v_bat24_mv، قفل داخلی باتری کم و تایمر 3000ms.</t>
+          <t>این فایل برای چک‌کردن منطق Changeover است.
+این‌ها چک می‌شوند: معتبر بودن داده (snapshot.valid)، ماسک خطا (fault_mask)، حاضر بودن ورودی (input_present)، ولتاژ باتری (v_bat24_mv)، قفل داخلی باتری کم و تایمر 3000 میلی‌ثانیه.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="87" t="inlineStr">
         <is>
-          <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار mV و ms و state/PB11 قابل اندازه‌گیری تعریف شده است.</t>
+          <t>در هر ردیف، روش اجرا و نتیجهٔ مورد انتظار نوشته شده است.
+قبول یا رد هر تست با عدد مشخص است: ولتاژ (mV)، زمان (ms)، وضعیت و پایهٔ PB11.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="87" t="inlineStr">
         <is>
-          <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است. فقط یک Workbook برای Changeover باقی بماند.</t>
+          <t>قبل از تست روی برد، ستون «نتیجه واقعی» را خالی بگذار و وضعیت را «در انتظار» نگه دار.
+برای تستی که انجام نشده، «قبول» ننویس.
+برای Changeover فقط همین یک فایل داریم.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="88" t="inlineStr">
         <is>
-          <t>دامنه: فقط Changeover؛ Measurement برای snapshot، Fault برای fault_mask و UI برای فلگ</t>
+          <t>دامنه فقط Changeover است. دادهٔ اندازه‌گیری از Measurement می‌آید، ماسک خطا از Fault و فلگ از UI.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="87" t="inlineStr">
         <is>
-          <t>منطق (snapshot-first): اگر snapshot==NULL یا valid==false → هیچ تصمیمی، state حفظ، PB11 حفظ، تایمر reset، fault هم state را تغییر نمی‌دهد، زمان نامعتبر شمرده نشود.</t>
+          <t>اول دادهٔ اندازه‌گیری چک می‌شود.
+اگر داده حاضر نباشد (NULL) یا معتبر نباشد (valid=false)، هیچ تصمیمی گرفته نمی‌شود:
+وضعیت همان قبلی می‌ماند. پایهٔ PB11 هم تغییر نمی‌کند. تایمر از نو شروع می‌شود.
+در این حالت، خطا هم وضعیت را عوض نمی‌کند و آن زمان جزو زمان صبر حساب نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="87" t="inlineStr">
         <is>
-          <t>فقط وقتی snapshot معتبر و fault!=0 → state=FAULT بدون تغییر هیچ pin (PB11/PB5/PB7).</t>
+          <t>فقط وقتی داده معتبر است و خطایی هست (fault!=0)، وضعیت «خطا» (FAULT) می‌شود.
+در این حالت هیچ پایه‌ای تغییر نمی‌کند: نه PB11، نه PB5 و نه PB7.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="87" t="inlineStr">
         <is>
-          <t>قطع با گیت: v_bat&lt;21000 و flag true به‌مدت پیوسته 3000ms → قطع (PB11 Low) → SAFE. قطع مستقل: v_bat&lt;20800 مستقل از فلگ 3000ms → SAFE.</t>
+          <t>قطع خروجی دو راه دارد:
+راه اول: ولتاژ باتری زیر 21000 میلی‌ولت باشد و فلگ باتری کم هم فعال باشد. این وضع باید 3000 میلی‌ثانیه پشت سر هم بماند. بعد خروجی قطع می‌شود (PB11 پایین) و وضعیت «امن» (SAFE) می‌شود.
+راه دوم: ولتاژ باتری زیر 20800 میلی‌ولت باشد. در این راه فلگ لازم نیست؛ همان 3000 میلی‌ثانیه صبر کافی است و بعد وضعیت «امن» می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="87" t="inlineStr">
         <is>
-          <t>وصل مجدد: input_present==true و v_bat≥21200 به‌مدت پیوسته 3000ms → وصل (PB11 High) → INPUT (هرگز IDLE).</t>
+          <t>وصل دوباره هم شرط دارد:
+ورودی حاضر باشد و ولتاژ باتری دست‌کم 21200 میلی‌ولت باشد.
+این وضع باید 3000 میلی‌ثانیه پشت سر هم بماند.
+بعد خروجی وصل می‌شود (PB11 بالا) و وضعیت «ورودی» (INPUT) می‌شود. وضعیت هیچ‌وقت «بیکار» (IDLE) نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="87" t="inlineStr">
         <is>
-          <t>زمان فقط با func__Rtos_MillisecondsToTicks و osKernelGetTickCount؛ فرض tick=1ms ممنوع؛ durationTicks==0 → هیچ قطع/وصل فوری.</t>
+          <t>زمان فقط با تابع تبدیل میلی‌ثانیه به تیک حساب می‌شود (func__Rtos_MillisecondsToTicks) و ساعت سیستم خوانده می‌شود (osKernelGetTickCount).
+فرض نکن هر تیک 1 میلی‌ثانیه است.
+اگر مدت به تیک صفر شد (durationTicks=0)، هیچ قطع یا وصل فوری انجام نمی‌شود.</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1406,9 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="87" t="inlineStr">
         <is>
-          <t>۱) برد را با منبع آزمایشگاهی و رعایت ایمنی تغذیه کن؛ PB11 را با DMM/اسکوپ نسبت به GND اندازه بگیر (فعال Low). PB5/PB7 را هم هم‌زمان اسکوپ کن و مطمئن شو تغییری ندارند.</t>
+          <t>۱) برد را با منبع آزمایشگاهی و با رعایت ایمنی روشن کن.
+پایهٔ PB11 را با مولتی‌متر یا اسکوپ نسبت به زمین (GND) اندازه بگیر. این پایه فعال-پایین است: پایین یعنی قطع.
+پایه‌های PB5 و PB7 را هم هم‌زمان با اسکوپ ببین. نباید هیچ تغییری بکنند.</t>
         </is>
       </c>
     </row>
@@ -1403,21 +1422,26 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="87" t="inlineStr">
         <is>
-          <t>۳) snapshot را تزریق کن: valid، v_bat24_mv، input_present را ست کن؛ قفل داخلی باتری کم فقط با ولتاژ زیر ۲۱۰۰۰ میلی‌ولت بسته می‌شود (مستقیم ست نمی‌شود)؛ fault_mask را از Fault اعمال کن.</t>
+          <t>۳) دادهٔ اندازه‌گیری را تزریق کن: valid و v_bat24_mv و input_present را ست کن.
+قفل باتری کم را نمی‌شود مستقیم ست کرد؛ خودش وقتی بسته می‌شود که ولتاژ زیر ۲۱۰۰۰ میلی‌ولت برود.
+ماسک خطا (fault_mask) را از ماژول Fault بده.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="87" t="inlineStr">
         <is>
-          <t>۴) برای تست 3000ms: شرط را حداقل 3500ms پایدار نگه دار و سپس PB11 و state را بخوان؛ برای تست &lt;3000ms: پس از 2500ms بخوان و مطمئن شو هنوز تغییر نکرده.</t>
+          <t>۴) برای تست زمان 3000 میلی‌ثانیه: شرط را دست‌کم 3500 میلی‌ثانیه نگه دار. بعد PB11 و وضعیت را بخوان.
+برای تست کمتر از 3000 میلی‌ثانیه: بعد از 2500 میلی‌ثانیه بخوان. هنوز نباید چیزی تغییر کرده باشد.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="87" t="inlineStr">
         <is>
-          <t>۵) برای snapshot نامعتبر: valid=false یا NULL تزریق کن و ببین state و PB11 حفظ می‌ماند (باید «state فعلی حفظ شود» نه IDLE ثابت).</t>
+          <t>۵) برای دادهٔ نامعتبر: valid=false یا NULL بده.
+ببین وضعیت و PB11 همان قبلی می‌مانند.
+یعنی وضعیت فعلی حفظ می‌شود، نه اینکه وضعیت ثابت «بیکار» شود.</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1477,7 @@
       </c>
       <c r="D21" s="90" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="E21" s="91" t="n"/>
@@ -1482,7 +1506,7 @@
       </c>
       <c r="C22" s="92" t="inlineStr">
         <is>
-          <t>تکمیل ۲۲ تست مطابق لیست درخواستی، ستون‌های ۱۶گانه، PASS/FAIL per test، زمان rtos_time و duration0 guard</t>
+          <t>۲۲ تست کامل شد. هر تست ۱۶ ستون دارد. برای هر تست قبول یا رد جدا نوشته می‌شود. زمان‌ها با ساعت سیستم (rtos_time) حساب می‌شوند. اگر مدت صفر شد (0)، قطع و وصل فوری نداریم.</t>
         </is>
       </c>
       <c r="D22" s="92" t="inlineStr">
@@ -1516,7 +1540,7 @@
       </c>
       <c r="C23" s="92" t="inlineStr">
         <is>
-          <t>snapshot-first با MillisecondsToTicks، نگاشت BATTERY/INPUT/SAFE/FAULT بدون IDLE</t>
+          <t>تصمیم فقط وقتی گرفته می‌شود که داده معتبر باشد. زمان با تبدیل میلی‌ثانیه به تیک حساب می‌شود. وضعیت‌ها: باتری، ورودی، امن و خطا. وضعیت «بیکار» (IDLE) نداریم.</t>
         </is>
       </c>
       <c r="D23" s="92" t="inlineStr">
@@ -1550,7 +1574,7 @@
       </c>
       <c r="C24" s="92" t="inlineStr">
         <is>
-          <t>پیاده‌سازی با 21 سناریو</t>
+          <t>در نسخهٔ اول 21 سناریو پیاده شد.</t>
         </is>
       </c>
       <c r="D24" s="92" t="inlineStr">
@@ -1584,7 +1608,7 @@
       </c>
       <c r="C25" s="94" t="inlineStr">
         <is>
-          <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
+          <t>دیالوگ پنل تیره و هم‌رنگ شد. صف پیام (PMQ) اضافه شد. کلیدهای Enter و Esc درست کار می‌کنند. در تسک کنترل، عکس لحظه‌ای (snapshot) اول کامل صفر می‌شود. (62f3782)</t>
         </is>
       </c>
       <c r="D25" s="94" t="inlineStr">
@@ -1605,12 +1629,15 @@
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="130" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1795,7 @@
       </c>
       <c r="N4" s="84" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="O4" s="84" t="inlineStr">
@@ -1829,7 +1856,10 @@
       </c>
       <c r="I5" s="100" t="inlineStr">
         <is>
-          <t>باید ببینید: با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود؛ تا وقتی باتری بالای حد است بار روشن می‌ماند. اگر زود قطع کرد یا اصلاً قطع نکرد، قبول نیست.</t>
+          <t>باید ببینید:
+با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع می‌شود و بار خاموش می‌شود.
+تا وقتی باتری بالای حد است، بار روشن می‌ماند.
+اگر زود قطع کرد یا اصلاً قطع نکرد، قبول نیست.</t>
         </is>
       </c>
       <c r="J5" s="100" t="inlineStr">
@@ -3003,7 +3033,7 @@
       </c>
       <c r="N4" s="84" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="O4" s="84" t="inlineStr">
@@ -3041,10 +3071,11 @@
       </c>
       <c r="E5" s="100" t="inlineStr">
         <is>
-          <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد؛ PB11 باید High و امن باشد.
-گام ۲: یک snapshot نامعتبر اعمال کن: valid=false ولی v_bat=24000، input=false و fault=0.
-گام ۳: 500 میلی‌ثانیه صبر کن و وضعیت (state) و پایهٔ PB11 را بخوان.
-گام ۴: وضعیت قبلی (BOOT یا هر وضعیت قبلی) و PB11 باید بدون هیچ تغییری حفظ شده باشند؛ رفتن به FAULT یا IDLE یا تغییر PB11 یعنی رد تست.</t>
+          <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد. PB11 باید High و امن باشد.
+گام ۲: یک دادهٔ نامعتبر اعمال کن: valid=false ولی v_bat=24000 و input=false و fault=0.
+گام ۳: 500 میلی‌ثانیه صبر کن. بعد وضعیت (state) و پایهٔ PB11 را بخوان.
+گام ۴: وضعیت قبلی و PB11 باید بدون هیچ تغییری مانده باشند.
+گام ۵: اگر وضعیت به FAULT یا IDLE رفت یا PB11 تغییر کرد، تست رد است.</t>
         </is>
       </c>
       <c r="F5" s="101" t="inlineStr">
@@ -3111,10 +3142,11 @@
       <c r="E6" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
-گام ۲: دو ثانیه شرط قطع را اعمال کن: snapshot معتبر با v=20900 و flag=true.
-گام ۳: بعد یک ثانیه snapshot نامعتبر بده (valid=false).
+گام ۲: دو ثانیه شرط قطع را اعمال کن: دادهٔ معتبر با v=20900 و flag=true.
+گام ۳: یک دادهٔ نامعتبر بده (valid=false) و 1 ثانیه نگه دار.
 گام ۴: دوباره دو ثانیه شرط قطع را اعمال کن و PB11 را زیر نظر بگیر.
-گام ۵: PB11 نباید قطع شود؛ آن یک ثانیهٔ نامعتبر تایمر 3 ثانیه‌ای را از نو شروع می‌کند، پس در هیچ‌کدام از دو بازهٔ 2 ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
+گام ۵: PB11 نباید قطع شود. آن یک ثانیهٔ نامعتبر، تایمر ۳ ثانیه‌ای را از نو شروع می‌کند.
+گام ۶: پس در هیچ‌کدام از دو بازهٔ ۲ ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
         </is>
       </c>
       <c r="F6" s="105" t="inlineStr">
@@ -3129,7 +3161,10 @@
       </c>
       <c r="H6" s="104" t="inlineStr">
         <is>
-          <t>PB11 نباید پس از 2s اول قطع شود؛ پس از 1s invalid، تایمر reset و 2s بعدی هم هنوز قطع نشود (نیاز به 3s پیوسته). PASS: invalid تایمر را reset. FAIL: قطع زود در 2s.</t>
+          <t>PB11 بعد از ۲ ثانیهٔ اول نباید قطع شود.
+بعد از ۱ ثانیه دادهٔ نامعتبر، تایمر از نو شروع می‌شود. پس در ۲ ثانیهٔ بعدی هم نباید قطع شود؛ ۳ ثانیهٔ پیوسته لازم است.
+قبول: دادهٔ نامعتبر تایمر را از نو شروع کند.
+رد: قطع زود در ۲ ثانیه.</t>
         </is>
       </c>
       <c r="I6" s="104" t="inlineStr">
@@ -3526,9 +3561,11 @@
       <c r="E12" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
-گام ۲: snapshot معتبر با v=20900 (کمتر از 21000)، flag=true و input=false اعمال کن.
-گام ۳: این شرط را 3500 میلی‌ثانیه پیوسته نگه دار و ساعت بگیر.
-گام ۴: در 2500 میلی‌ثانیه اول باید هنوز BATTERY/INPUT و PB11 وصل باشد؛ فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت SAFE شود. قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
+گام ۲: دادهٔ معتبر بده: v=20900 (کمتر از 21000)، flag=true و input=false.
+گام ۳: این شرط را 3500 میلی‌ثانیه پشت سر هم نگه دار و ساعت بگیر.
+گام ۴: در 2500 میلی‌ثانیهٔ اول باید هنوز BATTERY/INPUT باشد و PB11 وصل بماند.
+گام ۵: فقط بعد از 3000 میلی‌ثانیهٔ پیوسته باید PB11 قطع (Low) شود و وضعیت امن (SAFE) شود.
+گام ۶: قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F12" s="105" t="inlineStr">
@@ -3595,9 +3632,10 @@
       <c r="E13" s="100" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY و flag=false باشد.
-گام ۲: snapshot معتبر با v=20700 (کمتر از 20800)، flag=false و input=false اعمال کن.
-گام ۳: 3500 میلی‌ثانیه پیوسته نگه دار.
-گام ۴: بعد از 3000 میلی‌ثانیه باید SAFE با PB11 قطع شود؛ این قطع به flag ربطی ندارد و با flag=false هم باید اتفاق بیفتد.</t>
+گام ۲: دادهٔ معتبر بده: v=20700 (کمتر از 20800)، flag=false و input=false.
+گام ۳: 3500 میلی‌ثانیه پشت سر هم نگه دار.
+گام ۴: بعد از 3000 میلی‌ثانیه باید وضعیت امن (SAFE) شود و PB11 قطع شود.
+گام ۵: این قطع به فلگ ربطی ندارد؛ با flag=false هم باید اتفاق بیفتد.</t>
         </is>
       </c>
       <c r="F13" s="101" t="inlineStr">
@@ -3664,9 +3702,10 @@
       <c r="E14" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
-گام ۲: snapshot معتبر با v دقیقاً 21000 (مرز)، flag=true و input=true (Vin=24 ولت) اعمال کن.
+گام ۲: دادهٔ معتبر بده: v دقیقاً 21000 (روی مرز)، flag=true و input=true (Vin=24 ولت).
 گام ۳: 3500 میلی‌ثانیه پایدار نگه دار.
-گام ۴: هیچ قطعی نباید رخ دهد (شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی»)؛ وضعیت باید INPUT شده باشد (چون ورودی حاضر است) و PB11 High و امن بماند.</t>
+گام ۴: هیچ قطعی نباید رخ دهد. شرط قطع «کمتر از 21000» است، نه «کمتر یا مساوی».
+گام ۵: وضعیت باید «ورودی» (INPUT) شده باشد، چون ورودی حاضر است. PB11 باید High و امن بماند.</t>
         </is>
       </c>
       <c r="F14" s="105" t="inlineStr">
@@ -3939,10 +3978,11 @@
       </c>
       <c r="E18" s="104" t="inlineStr">
         <is>
-          <t>گام ۱: برد در SAFE باشد.
-گام ۲: input=true و v دقیقاً 21200 اعمال کن (روی خودِ مرز).
+          <t>گام ۱: برد در وضعیت امن (SAFE) باشد.
+گام ۲: input=true و v دقیقاً 21200 بده (روی خود مرز).
 گام ۳: 3500 میلی‌ثانیه نگه دار.
-گام ۴: بعد از 3000 میلی‌ثانیه باید INPUT و PB11 وصل شده باشد؛ شرط وصل «دست‌کم 21200» است، پس روی مرز هم باید وصل شود.</t>
+گام ۴: بعد از 3000 میلی‌ثانیه باید وضعیت «ورودی» (INPUT) شود و PB11 وصل شده باشد.
+گام ۵: شرط وصل «دست‌کم 21200» است؛ پس روی مرز هم باید وصل شود.</t>
         </is>
       </c>
       <c r="F18" s="105" t="inlineStr">
@@ -4282,9 +4322,11 @@
       </c>
       <c r="E23" s="116" t="inlineStr">
         <is>
-          <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015 که انجام می‌دهی، علاوه بر PB11 دو پایهٔ PB5 (BAT_SWITCH) و PB7 (RELAY) را هم با اسیلوسکوپ یا لاگ BSP زیر نظر بگیر.
+          <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015، سه پایه را با اسکوپ یا لاگ BSP زیر نظر بگیر:
+پایهٔ PB11، پایهٔ PB5 (همان BAT_SWITCH) و پایهٔ PB7 (همان RELAY).
 گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
-گام ۳: PB5 باید همیشه High امن (active-low) و PB7 همیشه Low بماند؛ هر تغییر (toggle) روی این دو یعنی رد تست.</t>
+گام ۳: PB5 باید همیشه High و امن بماند (فعال-پایین است) و PB7 همیشه Low بماند.
+گام ۴: هر تغییری روی این دو پایه یعنی رد تست.</t>
         </is>
       </c>
       <c r="F23" s="101" t="inlineStr">
@@ -4350,10 +4392,11 @@
       </c>
       <c r="E24" s="106" t="inlineStr">
         <is>
-          <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و ولتاژ باتری 24 ولت باشد.
-گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پیوسته حاضر نگه دار.
-گام ۳: بعد از آن 3 ثانیه ولتاژ را روی 21200 نگه دار (در مجموع 33 ثانیه).
-گام ۴: در پایان، پس از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی، باید وصل مجدد کامل شده باشد و وضعیت INPUT شود؛ سطح PB11 در لحظهٔ وصل را با اسکوپ ثبت کن و با الگوی CO-013 مقایسه کن.</t>
+          <t>گام ۱: از تست CO-008 شروع کن تا برد در وضعیت امن و ولتاژ باتری 24 ولت باشد.
+گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پشت سر هم حاضر نگه دار.
+گام ۳: بعد از آن، 3 ثانیه ولتاژ را روی 21200 نگه دار. در مجموع 33 ثانیه می‌شود.
+گام ۴: آن 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ کافی که تمام شد، وصل دوباره باید کامل شده باشد. وضعیت باید «ورودی» (INPUT) شود.
+گام ۵: سطح PB11 را در لحظهٔ وصل با اسکوپ ثبت کن و با الگوی تست CO-013 مقایسه کن.</t>
         </is>
       </c>
       <c r="F24" s="105" t="inlineStr">
@@ -5017,7 +5060,7 @@
       </c>
       <c r="N4" s="84" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="O4" s="84" t="inlineStr">
@@ -5262,10 +5305,11 @@
       </c>
       <c r="E8" s="100" t="inlineStr">
         <is>
-          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن (یا ADC را نگه دار تا valid=false بماند).
+          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن. یا ADC را نگه دار تا valid=false بماند.
 گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
-گام ۳: هیچ فیلد snapshot نباید زبالهٔ پشته داشته باشد: task_control مثل task_comm و task_ui و task_protection هر 9 فیلد را از قبل صفر می‌کند.
-گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند؛ هیچ تصمیمی بر اساس زباله قبول نیست.</t>
+گام ۳: هیچ فیلدی از داده نباید زبالهٔ پشته داشته باشد. هر چهار تسک (کنترل، ارتباط، UI و حفاظت) هر 9 فیلد را از قبل صفر می‌کنند.
+گام ۴: Changeover باید فقط روی valid تصمیم بگیرد و PB11 امن بماند.
+گام ۵: هیچ تصمیمی بر اساس زباله قبول نیست.</t>
         </is>
       </c>
       <c r="F8" s="101" t="inlineStr">
@@ -5280,7 +5324,9 @@
       </c>
       <c r="H8" s="100" t="inlineStr">
         <is>
-          <t>هیچ فیلد snapshot حاوی زباله پشته نباشد؛ Changeover باید فقط روی valid گیت بزند و PB11 امن بماند؛ task_control مانند task_comm/task_ui/task_protection هر 9 فیلد را صفر کند</t>
+          <t>هیچ فیلدی از داده نباید زبالهٔ پشته داشته باشد.
+Changeover باید فقط روی valid گیت بزند و PB11 امن بماند.
+تسک کنترل، مثل تسک‌های ارتباط و UI و حفاظت، هر 9 فیلد را صفر می‌کند.</t>
         </is>
       </c>
       <c r="I8" s="100" t="inlineStr">
@@ -6347,7 +6393,7 @@
       </c>
       <c r="J3" s="90" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="90" t="inlineStr">
@@ -6617,12 +6663,12 @@
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="126" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B6" s="92" t="inlineStr">
         <is>
-          <t>TESTER: fill flashed firmware commit</t>
+          <t>نسخهٔ برنامهٔ فلش‌شده (تست‌کننده پر کند)</t>
         </is>
       </c>
       <c r="C6" s="126" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -365,7 +365,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -431,6 +431,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -519,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -891,6 +901,59 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="60" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1281,7 +1344,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Changeover — منطق قطع/وصل باتری</t>
         </is>
@@ -1297,7 +1360,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="138" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -1344,7 +1407,7 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="139" t="inlineStr">
         <is>
           <t>دامنه فقط Changeover است. دادهٔ اندازه‌گیری از Measurement می‌آید، ماسک خطا از Fault و فلگ از UI.</t>
         </is>
@@ -1397,7 +1460,7 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="139" t="inlineStr">
         <is>
           <t>روش اجرای تست</t>
         </is>
@@ -1453,34 +1516,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="89" t="inlineStr">
+      <c r="A20" s="140" t="inlineStr">
         <is>
           <t>تاریخچه نسخه</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="90" t="inlineStr">
+      <c r="A21" s="141" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B21" s="90" t="inlineStr">
+      <c r="B21" s="141" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C21" s="90" t="inlineStr">
+      <c r="C21" s="141" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D21" s="90" t="inlineStr">
+      <c r="D21" s="141" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="E21" s="91" t="n"/>
+      <c r="E21" s="142" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
@@ -1629,6 +1692,7 @@
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="130" t="inlineStr">
         <is>
@@ -1704,7 +1768,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="95" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Changeover (قطع/وصل باتری با 3000ms)</t>
         </is>
@@ -1728,87 +1792,87 @@
       <c r="Q3" s="82" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="138" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="138" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="138" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="84" t="inlineStr">
+      <c r="D4" s="138" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="84" t="inlineStr">
+      <c r="E4" s="138" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="84" t="inlineStr">
+      <c r="F4" s="138" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="84" t="inlineStr">
+      <c r="G4" s="138" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="84" t="inlineStr">
+      <c r="H4" s="138" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="84" t="inlineStr">
+      <c r="I4" s="138" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="J4" s="84" t="inlineStr">
+      <c r="J4" s="138" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="84" t="inlineStr">
+      <c r="K4" s="138" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="84" t="inlineStr">
+      <c r="L4" s="138" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="84" t="inlineStr">
+      <c r="M4" s="138" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="84" t="inlineStr">
+      <c r="N4" s="138" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="O4" s="84" t="inlineStr">
+      <c r="O4" s="138" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="84" t="inlineStr">
+      <c r="P4" s="138" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="84" t="n"/>
+      <c r="Q4" s="138" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="99" t="inlineStr">
@@ -1816,22 +1880,22 @@
           <t>CO-025</t>
         </is>
       </c>
-      <c r="B5" s="100" t="inlineStr">
+      <c r="B5" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C5" s="101" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="100" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>دستگاه روشن، باتری وصل و یک بار (مثلاً لامپ) روی خروجی</t>
         </is>
       </c>
-      <c r="E5" s="100" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را فقط با باتری روشن کن و مطمئن شو بار روشن است.
 گام ۲: ولتاژ باتری را با منبع آزمایشگاهی آرام پایین بیاور تا زیر 21 ولت برسد.
@@ -1839,22 +1903,22 @@
 گام ۴: بار باید خاموش شود (خروجی قطع شود)؛ تا وقتی باتری بالای 21 ولت است بار نباید قطع شود.</t>
         </is>
       </c>
-      <c r="F5" s="100" t="inlineStr">
+      <c r="F5" s="104" t="inlineStr">
         <is>
           <t>باتری از 24 ولت تا زیر 21 ولت</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H5" s="100" t="inlineStr">
+      <c r="H5" s="104" t="inlineStr">
         <is>
           <t>با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="100" t="inlineStr">
+      <c r="I5" s="104" t="inlineStr">
         <is>
           <t>باید ببینید:
 با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع می‌شود و بار خاموش می‌شود.
@@ -1862,7 +1926,7 @@
 اگر زود قطع کرد یا اصلاً قطع نکرد، قبول نیست.</t>
         </is>
       </c>
-      <c r="J5" s="100" t="inlineStr">
+      <c r="J5" s="104" t="inlineStr">
         <is>
           <t>بار قطع شود؛ قطع زودهنگام وقتی باتری هنوز بالای حد است = رد</t>
         </is>
@@ -1876,7 +1940,7 @@
       <c r="M5" s="100" t="n"/>
       <c r="N5" s="100" t="n"/>
       <c r="O5" s="101" t="n"/>
-      <c r="P5" s="101">
+      <c r="P5" s="105">
         <f>IF(OR(K5="",K5="در انتظار"),"",IF(P5="",TODAY(),P5))</f>
         <v/>
       </c>
@@ -1888,22 +1952,22 @@
           <t>CO-026</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="143" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="144" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="106" t="inlineStr">
+      <c r="D6" s="145" t="inlineStr">
         <is>
           <t>پایان CO-025 (خروجی قطع است)</t>
         </is>
       </c>
-      <c r="E6" s="106" t="inlineStr">
+      <c r="E6" s="145" t="inlineStr">
         <is>
           <t>گام ۱: از پایان CO-025 شروع کن که خروجی قطع و بار خاموش است.
 گام ۲: برق شهر (ورودی) را وصل کن و ولتاژ باتری را به بالای 21.2 ولت برگردان (با شارژ یا منبع).
@@ -1911,27 +1975,27 @@
 گام ۴: بار باید دوباره روشن شود؛ اگر ولتاژ باتری هنوز پایین است نباید وصل شود.</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
+      <c r="F6" s="143" t="inlineStr">
         <is>
           <t>ورودی حاضر + باتری بالای 21.2 ولت</t>
         </is>
       </c>
-      <c r="G6" s="105" t="inlineStr">
+      <c r="G6" s="144" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H6" s="104" t="inlineStr">
+      <c r="H6" s="143" t="inlineStr">
         <is>
           <t>خروجی وصل و بار روشن می‌شود</t>
         </is>
       </c>
-      <c r="I6" s="104" t="inlineStr">
+      <c r="I6" s="143" t="inlineStr">
         <is>
           <t>باید ببینید: با برگشت ورودی و باتریِ کافی، خروجی وصل و بار روشن می‌شود. اگر با باتری پایین وصل شد یا اصلاً وصل نشد، قبول نیست.</t>
         </is>
       </c>
-      <c r="J6" s="104" t="inlineStr">
+      <c r="J6" s="143" t="inlineStr">
         <is>
           <t>بار دوباره روشن شود؛ وصل شدن با باتری پایین = رد</t>
         </is>
@@ -1945,7 +2009,7 @@
       <c r="M6" s="104" t="n"/>
       <c r="N6" s="104" t="n"/>
       <c r="O6" s="105" t="n"/>
-      <c r="P6" s="105">
+      <c r="P6" s="144">
         <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
         <v/>
       </c>
@@ -1957,22 +2021,22 @@
           <t>CO-027</t>
         </is>
       </c>
-      <c r="B7" s="100" t="inlineStr">
+      <c r="B7" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C7" s="101" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="100" t="inlineStr">
+      <c r="D7" s="104" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر و باتری وصل، بار روشن</t>
         </is>
       </c>
-      <c r="E7" s="100" t="inlineStr">
+      <c r="E7" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را با برق شهر و باتری روشن کن و بار را روشن ببین.
 گام ۲: برق شهر را بکش؛ دستگاه نباید خاموش شود و بار باید بی‌وقفه روشن بماند (کار روی باتری).
@@ -1980,27 +2044,27 @@
 گام ۴: در هیچ‌کدام از این دو جابه‌جایی نباید دستگاه در وضعیت خطا گیر کند.</t>
         </is>
       </c>
-      <c r="F7" s="100" t="inlineStr">
+      <c r="F7" s="104" t="inlineStr">
         <is>
           <t>قطع و وصل برق شهر</t>
         </is>
       </c>
-      <c r="G7" s="101" t="inlineStr">
+      <c r="G7" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H7" s="100" t="inlineStr">
+      <c r="H7" s="104" t="inlineStr">
         <is>
           <t>ادامهٔ بی‌وقفهٔ کار بار و برگشت عادی</t>
         </is>
       </c>
-      <c r="I7" s="100" t="inlineStr">
+      <c r="I7" s="104" t="inlineStr">
         <is>
           <t>باید ببینید: با قطع و وصل برق شهر، بار هرگز خاموش نمی‌شود و دستگاه بعد از برگشت شهر عادی کار می‌کند. اگر بار لحظه‌ای هم خاموش شد، قبول نیست.</t>
         </is>
       </c>
-      <c r="J7" s="100" t="inlineStr">
+      <c r="J7" s="104" t="inlineStr">
         <is>
           <t>بار هرگز خاموش نشود و دستگاه بعد از برگشت شهر عادی کار کند</t>
         </is>
@@ -2014,7 +2078,7 @@
       <c r="M7" s="100" t="n"/>
       <c r="N7" s="100" t="n"/>
       <c r="O7" s="101" t="n"/>
-      <c r="P7" s="101">
+      <c r="P7" s="105">
         <f>IF(OR(K7="",K7="در انتظار"),"",IF(P7="",TODAY(),P7))</f>
         <v/>
       </c>
@@ -2026,22 +2090,22 @@
           <t>CO-028</t>
         </is>
       </c>
-      <c r="B8" s="104" t="inlineStr">
+      <c r="B8" s="143" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="144" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="104" t="inlineStr">
+      <c r="D8" s="143" t="inlineStr">
         <is>
           <t>دستگاه در حال کار عادی با بار روشن</t>
         </is>
       </c>
-      <c r="E8" s="104" t="inlineStr">
+      <c r="E8" s="143" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه در حال کار عادی باشد و بار روشن.
 گام ۲: یک خطای شارژر بساز (حین شارژ سیم باتری را قطع کن تا آلارم قطع باتری بیاید).
@@ -2049,27 +2113,27 @@
 گام ۴: بار نباید قطع‌ووصل یا چشمک بزند؛ خروجی باید همان وضعیت قبل از خطا را نگه دارد.</t>
         </is>
       </c>
-      <c r="F8" s="104" t="inlineStr">
+      <c r="F8" s="143" t="inlineStr">
         <is>
           <t>خطای قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G8" s="105" t="inlineStr">
+      <c r="G8" s="144" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H8" s="104" t="inlineStr">
+      <c r="H8" s="143" t="inlineStr">
         <is>
           <t>آلارم خطا می‌آید ولی خروجی تکان نمی‌خورد</t>
         </is>
       </c>
-      <c r="I8" s="104" t="inlineStr">
+      <c r="I8" s="143" t="inlineStr">
         <is>
           <t>باید ببینید: آلارم خطا می‌آید ولی بار بدون هیچ تکانی روشن می‌ماند. اگر خروجی تکان خورد، قبول نیست.</t>
         </is>
       </c>
-      <c r="J8" s="104" t="inlineStr">
+      <c r="J8" s="143" t="inlineStr">
         <is>
           <t>بار بدون هیچ تکانی روشن بماند</t>
         </is>
@@ -2083,7 +2147,7 @@
       <c r="M8" s="104" t="n"/>
       <c r="N8" s="104" t="n"/>
       <c r="O8" s="105" t="n"/>
-      <c r="P8" s="105">
+      <c r="P8" s="144">
         <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
         <v/>
       </c>
@@ -2901,7 +2965,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -2966,87 +3030,87 @@
       <c r="Q3" s="82" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="138" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="138" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="138" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="84" t="inlineStr">
+      <c r="D4" s="138" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="84" t="inlineStr">
+      <c r="E4" s="138" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="84" t="inlineStr">
+      <c r="F4" s="138" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="84" t="inlineStr">
+      <c r="G4" s="138" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="84" t="inlineStr">
+      <c r="H4" s="138" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="84" t="inlineStr">
+      <c r="I4" s="138" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="84" t="inlineStr">
+      <c r="J4" s="138" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="84" t="inlineStr">
+      <c r="K4" s="138" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="84" t="inlineStr">
+      <c r="L4" s="138" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="84" t="inlineStr">
+      <c r="M4" s="138" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="84" t="inlineStr">
+      <c r="N4" s="138" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="O4" s="84" t="inlineStr">
+      <c r="O4" s="138" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="84" t="inlineStr">
+      <c r="P4" s="138" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="84" t="n"/>
+      <c r="Q4" s="138" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="99" t="inlineStr">
@@ -3054,22 +3118,22 @@
           <t>CO-001</t>
         </is>
       </c>
-      <c r="B5" s="100" t="inlineStr">
+      <c r="B5" s="104" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر / حفظ</t>
         </is>
       </c>
-      <c r="C5" s="110" t="inlineStr">
+      <c r="C5" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="100" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>Init → BOOT, PB11 High-safe</t>
         </is>
       </c>
-      <c r="E5" s="100" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد را بوت کن و بگذار به وضعیت اولیه (BOOT) برسد. PB11 باید High و امن باشد.
 گام ۲: یک دادهٔ نامعتبر اعمال کن: valid=false ولی v_bat=24000 و input=false و fault=0.
@@ -3078,27 +3142,27 @@
 گام ۵: اگر وضعیت به FAULT یا IDLE رفت یا PB11 تغییر کرد، تست رد است.</t>
         </is>
       </c>
-      <c r="F5" s="101" t="inlineStr">
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>valid=false, v=24000, input=false, flag false, fault0</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H5" s="100" t="inlineStr">
+      <c r="H5" s="104" t="inlineStr">
         <is>
           <t>state حفظ شود: «state فعلی حفظ شود» (BOOT/BATTERY/INPUT/SAFE قبلی) و PB11 حفظ (High-safe). PASS: state و PB11 بدون تغییر. FAIL: هر تغییر به FAULT یا IDLE یا تغییر PB11.</t>
         </is>
       </c>
-      <c r="I5" s="100" t="inlineStr">
+      <c r="I5" s="104" t="inlineStr">
         <is>
           <t>PASS: state فعلی حفظ. FAIL: تغییر خودبه‌خود.</t>
         </is>
       </c>
-      <c r="J5" s="111" t="n"/>
+      <c r="J5" s="104" t="n"/>
       <c r="K5" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3106,14 +3170,14 @@
       </c>
       <c r="L5" s="113" t="n"/>
       <c r="M5" s="100" t="n"/>
-      <c r="N5" s="100" t="inlineStr">
+      <c r="N5" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O5" s="101" t="n"/>
       <c r="P5" s="101" t="n"/>
-      <c r="Q5" s="103">
+      <c r="Q5" s="107">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -3124,22 +3188,22 @@
           <t>CO-002</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="143" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر / تایمر reset</t>
         </is>
       </c>
-      <c r="C6" s="114" t="inlineStr">
+      <c r="C6" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="104" t="inlineStr">
+      <c r="D6" s="143" t="inlineStr">
         <is>
           <t>BATTERY با شرط قطع نیمه‌کاره</t>
         </is>
       </c>
-      <c r="E6" s="104" t="inlineStr">
+      <c r="E6" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
 گام ۲: دو ثانیه شرط قطع را اعمال کن: دادهٔ معتبر با v=20900 و flag=true.
@@ -3149,17 +3213,17 @@
 گام ۶: پس در هیچ‌کدام از دو بازهٔ ۲ ثانیه‌ای نباید قطع اتفاق بیفتد. قطع زود یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="105" t="inlineStr">
+      <c r="F6" s="144" t="inlineStr">
         <is>
           <t>valid true 2s → false 1s → true 2s, v20900 flag true</t>
         </is>
       </c>
-      <c r="G6" s="105" t="inlineStr">
+      <c r="G6" s="144" t="inlineStr">
         <is>
           <t>2+1+2s</t>
         </is>
       </c>
-      <c r="H6" s="104" t="inlineStr">
+      <c r="H6" s="143" t="inlineStr">
         <is>
           <t>PB11 بعد از ۲ ثانیهٔ اول نباید قطع شود.
 بعد از ۱ ثانیه دادهٔ نامعتبر، تایمر از نو شروع می‌شود. پس در ۲ ثانیهٔ بعدی هم نباید قطع شود؛ ۳ ثانیهٔ پیوسته لازم است.
@@ -3167,27 +3231,27 @@
 رد: قطع زود در ۲ ثانیه.</t>
         </is>
       </c>
-      <c r="I6" s="104" t="inlineStr">
+      <c r="I6" s="143" t="inlineStr">
         <is>
           <t>PASS: reset پس از invalid. FAIL: قطع زود.</t>
         </is>
       </c>
       <c r="J6" s="104" t="n"/>
-      <c r="K6" s="104" t="inlineStr">
+      <c r="K6" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L6" s="115" t="n"/>
       <c r="M6" s="104" t="n"/>
-      <c r="N6" s="104" t="inlineStr">
+      <c r="N6" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O6" s="105" t="n"/>
       <c r="P6" s="105" t="n"/>
-      <c r="Q6" s="107">
+      <c r="Q6" s="148">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -3198,22 +3262,22 @@
           <t>CO-003</t>
         </is>
       </c>
-      <c r="B7" s="100" t="inlineStr">
+      <c r="B7" s="104" t="inlineStr">
         <is>
           <t>Snapshot نامعتبر + Fault</t>
         </is>
       </c>
-      <c r="C7" s="110" t="inlineStr">
+      <c r="C7" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="100" t="inlineStr">
+      <c r="D7" s="104" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E7" s="100" t="inlineStr">
+      <c r="E7" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت BATTERY باشد.
 گام ۲: snapshot نامعتبر با fault=FAULT_ADC (مقدار 1) و v=25000 اعمال کن.
@@ -3221,27 +3285,27 @@
 گام ۴: وضعیت نباید FAULT شود و PB11 نباید تغییر کند؛ fault همراه snapshot نامعتبر شمرده نمی‌شود و تایمر قطع هم reset می‌شود.</t>
         </is>
       </c>
-      <c r="F7" s="101" t="inlineStr">
+      <c r="F7" s="105" t="inlineStr">
         <is>
           <t>valid=false, fault=1 (ADC), v25000</t>
         </is>
       </c>
-      <c r="G7" s="101" t="inlineStr">
+      <c r="G7" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H7" s="100" t="inlineStr">
+      <c r="H7" s="104" t="inlineStr">
         <is>
           <t>state حفظ شود (نه FAULT)، PB11 حفظ، تایمر reset. PASS: fault همراه invalid نباید FAULT شود. FAIL: FAULT شدن.</t>
         </is>
       </c>
-      <c r="I7" s="100" t="inlineStr">
+      <c r="I7" s="104" t="inlineStr">
         <is>
           <t>PASS: حفظ state قبلی. FAIL: FAULT.</t>
         </is>
       </c>
-      <c r="J7" s="111" t="n"/>
+      <c r="J7" s="104" t="n"/>
       <c r="K7" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3249,14 +3313,14 @@
       </c>
       <c r="L7" s="113" t="n"/>
       <c r="M7" s="100" t="n"/>
-      <c r="N7" s="100" t="inlineStr">
+      <c r="N7" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O7" s="101" t="n"/>
       <c r="P7" s="101" t="n"/>
-      <c r="Q7" s="103">
+      <c r="Q7" s="107">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -3267,22 +3331,22 @@
           <t>CO-004</t>
         </is>
       </c>
-      <c r="B8" s="104" t="inlineStr">
+      <c r="B8" s="143" t="inlineStr">
         <is>
           <t>Fault با snapshot معتبر</t>
         </is>
       </c>
-      <c r="C8" s="114" t="inlineStr">
+      <c r="C8" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="104" t="inlineStr">
+      <c r="D8" s="143" t="inlineStr">
         <is>
           <t>INPUT/BATTERY</t>
         </is>
       </c>
-      <c r="E8" s="104" t="inlineStr">
+      <c r="E8" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت INPUT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true و fault=FAULT_ADC (مقدار 1) اعمال کن.
@@ -3290,42 +3354,42 @@
 گام ۴: وضعیت باید FAULT شود ولی PB11 دقیقاً همان قبلی بماند (از High به Low نرود) و تایمر قطع reset شود.</t>
         </is>
       </c>
-      <c r="F8" s="105" t="inlineStr">
+      <c r="F8" s="144" t="inlineStr">
         <is>
           <t>valid=true, v24000, input true, fault 1</t>
         </is>
       </c>
-      <c r="G8" s="105" t="inlineStr">
+      <c r="G8" s="144" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H8" s="104" t="inlineStr">
+      <c r="H8" s="143" t="inlineStr">
         <is>
           <t>state=FAULT، PB11 حفظ (بدون تغییر High→Low)، تایمر reset. PASS: FAULT بدون تغییر PB11. FAIL: تغییر PB11 یا ماندن در INPUT.</t>
         </is>
       </c>
-      <c r="I8" s="104" t="inlineStr">
+      <c r="I8" s="143" t="inlineStr">
         <is>
           <t>PASS: FAULT و PB11 حفظ. FAIL: تغییر PB11.</t>
         </is>
       </c>
       <c r="J8" s="104" t="n"/>
-      <c r="K8" s="104" t="inlineStr">
+      <c r="K8" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L8" s="115" t="n"/>
       <c r="M8" s="104" t="n"/>
-      <c r="N8" s="104" t="inlineStr">
+      <c r="N8" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O8" s="105" t="n"/>
       <c r="P8" s="105" t="n"/>
-      <c r="Q8" s="107">
+      <c r="Q8" s="148">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -3336,22 +3400,22 @@
           <t>CO-005</t>
         </is>
       </c>
-      <c r="B9" s="100" t="inlineStr">
+      <c r="B9" s="104" t="inlineStr">
         <is>
           <t>Fault چند بیتی</t>
         </is>
       </c>
-      <c r="C9" s="101" t="inlineStr">
+      <c r="C9" s="105" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="100" t="inlineStr">
+      <c r="D9" s="104" t="inlineStr">
         <is>
           <t>FAULT قبلی</t>
         </is>
       </c>
-      <c r="E9" s="100" t="inlineStr">
+      <c r="E9" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد از قبل در وضعیت FAULT باشد.
 گام ۲: snapshot معتبر با fault برابر 63 (همهٔ بیت‌های خطا با هم) اعمال کن.
@@ -3359,27 +3423,27 @@
 گام ۴: وضعیت باید FAULT بماند و هیچ‌کدام از سه پایه نباید تغییر کرده باشند.</t>
         </is>
       </c>
-      <c r="F9" s="101" t="inlineStr">
+      <c r="F9" s="105" t="inlineStr">
         <is>
           <t>valid true, fault ALL</t>
         </is>
       </c>
-      <c r="G9" s="101" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H9" s="100" t="inlineStr">
+      <c r="H9" s="104" t="inlineStr">
         <is>
           <t>state=FAULT، هیچ pin (PB11/PB5/PB7) تغییر نکند. PASS: همه fault‌ها → FAULT بدون pin. FAIL: هر تغییر pin.</t>
         </is>
       </c>
-      <c r="I9" s="100" t="inlineStr">
+      <c r="I9" s="104" t="inlineStr">
         <is>
           <t>PASS: همه fault → FAULT no pin. FAIL: pin change.</t>
         </is>
       </c>
-      <c r="J9" s="111" t="n"/>
+      <c r="J9" s="104" t="n"/>
       <c r="K9" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3387,14 +3451,14 @@
       </c>
       <c r="L9" s="113" t="n"/>
       <c r="M9" s="100" t="n"/>
-      <c r="N9" s="100" t="inlineStr">
+      <c r="N9" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O9" s="101" t="n"/>
       <c r="P9" s="101" t="n"/>
-      <c r="Q9" s="103">
+      <c r="Q9" s="107">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -3405,22 +3469,22 @@
           <t>CO-006</t>
         </is>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B10" s="143" t="inlineStr">
         <is>
           <t>ورودی قطع → BATTERY</t>
         </is>
       </c>
-      <c r="C10" s="114" t="inlineStr">
+      <c r="C10" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="104" t="inlineStr">
+      <c r="D10" s="143" t="inlineStr">
         <is>
           <t>BOOT با snapshot معتبر</t>
         </is>
       </c>
-      <c r="E10" s="104" t="inlineStr">
+      <c r="E10" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در BOOT با snapshot معتبر باشد.
 گام ۲: snapshot معتبر با v=24000، input=false (یعنی Vin حداکثر 20 ولت) و fault=0 اعمال کن.
@@ -3428,42 +3492,42 @@
 گام ۴: وضعیت باید BATTERY شود و PB11 باید High و امن (متصل) باشد؛ رفتن به INPUT یا SAFE یا FAULT یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F10" s="105" t="inlineStr">
+      <c r="F10" s="144" t="inlineStr">
         <is>
           <t>valid true, v24000, input false</t>
         </is>
       </c>
-      <c r="G10" s="105" t="inlineStr">
+      <c r="G10" s="144" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H10" s="104" t="inlineStr">
+      <c r="H10" s="143" t="inlineStr">
         <is>
           <t>state=BATTERY, PB11 High-safe (متصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
         </is>
       </c>
-      <c r="I10" s="104" t="inlineStr">
+      <c r="I10" s="143" t="inlineStr">
         <is>
           <t>PASS: BATTERY. FAIL: otherwise.</t>
         </is>
       </c>
       <c r="J10" s="104" t="n"/>
-      <c r="K10" s="104" t="inlineStr">
+      <c r="K10" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L10" s="115" t="n"/>
       <c r="M10" s="104" t="n"/>
-      <c r="N10" s="104" t="inlineStr">
+      <c r="N10" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O10" s="105" t="n"/>
       <c r="P10" s="105" t="n"/>
-      <c r="Q10" s="107">
+      <c r="Q10" s="148">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -3474,22 +3538,22 @@
           <t>CO-007</t>
         </is>
       </c>
-      <c r="B11" s="100" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>ورودی حاضر → INPUT</t>
         </is>
       </c>
-      <c r="C11" s="110" t="inlineStr">
+      <c r="C11" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="100" t="inlineStr">
+      <c r="D11" s="104" t="inlineStr">
         <is>
           <t>BOOT/BATTERY</t>
         </is>
       </c>
-      <c r="E11" s="100" t="inlineStr">
+      <c r="E11" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BOOT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
@@ -3497,27 +3561,27 @@
 گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
         </is>
       </c>
-      <c r="F11" s="101" t="inlineStr">
+      <c r="F11" s="105" t="inlineStr">
         <is>
           <t>valid true, v24000, input true</t>
         </is>
       </c>
-      <c r="G11" s="101" t="inlineStr">
+      <c r="G11" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H11" s="100" t="inlineStr">
+      <c r="H11" s="104" t="inlineStr">
         <is>
           <t>state=INPUT, PB11 High-safe. PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
         </is>
       </c>
-      <c r="I11" s="100" t="inlineStr">
+      <c r="I11" s="104" t="inlineStr">
         <is>
           <t>PASS: INPUT. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J11" s="111" t="n"/>
+      <c r="J11" s="104" t="n"/>
       <c r="K11" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3525,14 +3589,14 @@
       </c>
       <c r="L11" s="113" t="n"/>
       <c r="M11" s="100" t="n"/>
-      <c r="N11" s="100" t="inlineStr">
+      <c r="N11" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O11" s="101" t="n"/>
       <c r="P11" s="101" t="n"/>
-      <c r="Q11" s="103">
+      <c r="Q11" s="107">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
@@ -3543,22 +3607,22 @@
           <t>CO-008</t>
         </is>
       </c>
-      <c r="B12" s="104" t="inlineStr">
+      <c r="B12" s="143" t="inlineStr">
         <is>
           <t>قطع با گیت / 21000 + flag</t>
         </is>
       </c>
-      <c r="C12" s="114" t="inlineStr">
+      <c r="C12" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="104" t="inlineStr">
+      <c r="D12" s="143" t="inlineStr">
         <is>
           <t>BATTERY/INPUT, PB11 High</t>
         </is>
       </c>
-      <c r="E12" s="104" t="inlineStr">
+      <c r="E12" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY یا INPUT و PB11 وصل (High) باشد.
 گام ۲: دادهٔ معتبر بده: v=20900 (کمتر از 21000)، flag=true و input=false.
@@ -3568,42 +3632,42 @@
 گام ۶: قطع زودتر یا قطع‌نشدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="105" t="inlineStr">
+      <c r="F12" s="144" t="inlineStr">
         <is>
           <t>v20900 (&lt;21000) flag true</t>
         </is>
       </c>
-      <c r="G12" s="105" t="inlineStr">
+      <c r="G12" s="144" t="inlineStr">
         <is>
           <t>3500ms (≥3000)</t>
         </is>
       </c>
-      <c r="H12" s="104" t="inlineStr">
+      <c r="H12" s="143" t="inlineStr">
         <is>
           <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 High؛ پس از 3000ms PB11 Low (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
         </is>
       </c>
-      <c r="I12" s="104" t="inlineStr">
+      <c r="I12" s="143" t="inlineStr">
         <is>
           <t>PASS: 2500 still no cut, 3000 SAFE. FAIL: early or no cut.</t>
         </is>
       </c>
       <c r="J12" s="104" t="n"/>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L12" s="115" t="n"/>
       <c r="M12" s="104" t="n"/>
-      <c r="N12" s="104" t="inlineStr">
+      <c r="N12" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O12" s="105" t="n"/>
       <c r="P12" s="105" t="n"/>
-      <c r="Q12" s="107">
+      <c r="Q12" s="148">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -3614,22 +3678,22 @@
           <t>CO-009</t>
         </is>
       </c>
-      <c r="B13" s="100" t="inlineStr">
+      <c r="B13" s="104" t="inlineStr">
         <is>
           <t>قطع مستقل / 20800</t>
         </is>
       </c>
-      <c r="C13" s="110" t="inlineStr">
+      <c r="C13" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="100" t="inlineStr">
+      <c r="D13" s="104" t="inlineStr">
         <is>
           <t>BATTERY, flag false</t>
         </is>
       </c>
-      <c r="E13" s="100" t="inlineStr">
+      <c r="E13" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY و flag=false باشد.
 گام ۲: دادهٔ معتبر بده: v=20700 (کمتر از 20800)، flag=false و input=false.
@@ -3638,27 +3702,27 @@
 گام ۵: این قطع به فلگ ربطی ندارد؛ با flag=false هم باید اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F13" s="101" t="inlineStr">
+      <c r="F13" s="105" t="inlineStr">
         <is>
           <t>v20700 (&lt;20800) flag false</t>
         </is>
       </c>
-      <c r="G13" s="101" t="inlineStr">
+      <c r="G13" s="105" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H13" s="100" t="inlineStr">
+      <c r="H13" s="104" t="inlineStr">
         <is>
           <t>پس از 3000ms SAFE با PB11 Low مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
         </is>
       </c>
-      <c r="I13" s="100" t="inlineStr">
+      <c r="I13" s="104" t="inlineStr">
         <is>
           <t>PASS: independent cut. FAIL: no cut due flag.</t>
         </is>
       </c>
-      <c r="J13" s="111" t="n"/>
+      <c r="J13" s="104" t="n"/>
       <c r="K13" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3666,14 +3730,14 @@
       </c>
       <c r="L13" s="113" t="n"/>
       <c r="M13" s="100" t="n"/>
-      <c r="N13" s="100" t="inlineStr">
+      <c r="N13" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O13" s="101" t="n"/>
       <c r="P13" s="101" t="n"/>
-      <c r="Q13" s="103">
+      <c r="Q13" s="107">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
@@ -3684,22 +3748,22 @@
           <t>CO-010</t>
         </is>
       </c>
-      <c r="B14" s="104" t="inlineStr">
+      <c r="B14" s="143" t="inlineStr">
         <is>
           <t>مرز دقیق 21000 نباید cut</t>
         </is>
       </c>
-      <c r="C14" s="114" t="inlineStr">
+      <c r="C14" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="104" t="inlineStr">
+      <c r="D14" s="143" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E14" s="104" t="inlineStr">
+      <c r="E14" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: دادهٔ معتبر بده: v دقیقاً 21000 (روی مرز)، flag=true و input=true (Vin=24 ولت).
@@ -3708,42 +3772,42 @@
 گام ۵: وضعیت باید «ورودی» (INPUT) شده باشد، چون ورودی حاضر است. PB11 باید High و امن بماند.</t>
         </is>
       </c>
-      <c r="F14" s="105" t="inlineStr">
+      <c r="F14" s="144" t="inlineStr">
         <is>
           <t>valid=true, v=21000 (دقیق) flag=true, input=true (Vin≥21V)</t>
         </is>
       </c>
-      <c r="G14" s="105" t="inlineStr">
+      <c r="G14" s="144" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H14" s="104" t="inlineStr">
+      <c r="H14" s="143" t="inlineStr">
         <is>
           <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 High-safe بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
         </is>
       </c>
-      <c r="I14" s="104" t="inlineStr">
+      <c r="I14" s="143" t="inlineStr">
         <is>
           <t>PASS: با v=21000 و input true، state=INPUT و PB11 High. FAIL: هر cut یا BATTERY.</t>
         </is>
       </c>
       <c r="J14" s="104" t="n"/>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L14" s="115" t="n"/>
       <c r="M14" s="104" t="n"/>
-      <c r="N14" s="104" t="inlineStr">
+      <c r="N14" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O14" s="105" t="n"/>
       <c r="P14" s="105" t="n"/>
-      <c r="Q14" s="107">
+      <c r="Q14" s="148">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
@@ -3754,22 +3818,22 @@
           <t>CO-011</t>
         </is>
       </c>
-      <c r="B15" s="100" t="inlineStr">
+      <c r="B15" s="104" t="inlineStr">
         <is>
           <t>مرز دقیق 20800 نباید cut</t>
         </is>
       </c>
-      <c r="C15" s="110" t="inlineStr">
+      <c r="C15" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="100" t="inlineStr">
+      <c r="D15" s="104" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E15" s="100" t="inlineStr">
+      <c r="E15" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v دقیقاً 20800 و flag=false اعمال کن.
@@ -3777,27 +3841,27 @@
 گام ۴: هیچ قطعی نباید رخ دهد؛ قطع فقط برای «کمتر از 20800» است و روی خودِ مرز 20800 نباید اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F15" s="101" t="inlineStr">
+      <c r="F15" s="105" t="inlineStr">
         <is>
           <t>v=20800 flag false</t>
         </is>
       </c>
-      <c r="G15" s="101" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H15" s="100" t="inlineStr">
+      <c r="H15" s="104" t="inlineStr">
         <is>
           <t>هیچ قطع نشود. PASS: need &lt;20800. FAIL: cut at exact.</t>
         </is>
       </c>
-      <c r="I15" s="100" t="inlineStr">
+      <c r="I15" s="104" t="inlineStr">
         <is>
           <t>PASS: 20800 no independent cut. FAIL: cut.</t>
         </is>
       </c>
-      <c r="J15" s="111" t="n"/>
+      <c r="J15" s="104" t="n"/>
       <c r="K15" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3805,14 +3869,14 @@
       </c>
       <c r="L15" s="113" t="n"/>
       <c r="M15" s="100" t="n"/>
-      <c r="N15" s="100" t="inlineStr">
+      <c r="N15" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O15" s="101" t="n"/>
       <c r="P15" s="101" t="n"/>
-      <c r="Q15" s="103">
+      <c r="Q15" s="107">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
@@ -3823,22 +3887,22 @@
           <t>CO-012</t>
         </is>
       </c>
-      <c r="B16" s="104" t="inlineStr">
+      <c r="B16" s="143" t="inlineStr">
         <is>
           <t>قطع &lt;3000ms نباید</t>
         </is>
       </c>
-      <c r="C16" s="114" t="inlineStr">
+      <c r="C16" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="104" t="inlineStr">
+      <c r="D16" s="143" t="inlineStr">
         <is>
           <t>BATTERY</t>
         </is>
       </c>
-      <c r="E16" s="104" t="inlineStr">
+      <c r="E16" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در BATTERY باشد.
 گام ۲: snapshot معتبر با v=20900، flag=true و input=true (Vin=24 ولت) بده.
@@ -3846,42 +3910,42 @@
 گام ۴: تا 2500 میلی‌ثانیه باید هنوز INPUT و PB11 وصل باشد؛ SAFE شدن زودتر از 3000 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="105" t="inlineStr">
+      <c r="F16" s="144" t="inlineStr">
         <is>
           <t>valid=true, v=20900 (&lt;21000) flag=true, input=true, فقط 2500ms (&lt;3000)</t>
         </is>
       </c>
-      <c r="G16" s="105" t="inlineStr">
+      <c r="G16" s="144" t="inlineStr">
         <is>
           <t>2500ms</t>
         </is>
       </c>
-      <c r="H16" s="104" t="inlineStr">
+      <c r="H16" s="143" t="inlineStr">
         <is>
           <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 High. PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
         </is>
       </c>
-      <c r="I16" s="104" t="inlineStr">
+      <c r="I16" s="143" t="inlineStr">
         <is>
           <t>PASS: 2500ms still INPUT (no cut). FAIL: early SAFE یا BATTERY.</t>
         </is>
       </c>
       <c r="J16" s="104" t="n"/>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L16" s="115" t="n"/>
       <c r="M16" s="104" t="n"/>
-      <c r="N16" s="104" t="inlineStr">
+      <c r="N16" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O16" s="105" t="n"/>
       <c r="P16" s="105" t="n"/>
-      <c r="Q16" s="107">
+      <c r="Q16" s="148">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
@@ -3892,22 +3956,22 @@
           <t>CO-013</t>
         </is>
       </c>
-      <c r="B17" s="100" t="inlineStr">
+      <c r="B17" s="104" t="inlineStr">
         <is>
           <t>وصل مجدد / 21200 + input</t>
         </is>
       </c>
-      <c r="C17" s="110" t="inlineStr">
+      <c r="C17" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="100" t="inlineStr">
+      <c r="D17" s="104" t="inlineStr">
         <is>
           <t>SAFE, PB11 Low</t>
         </is>
       </c>
-      <c r="E17" s="116" t="inlineStr">
+      <c r="E17" s="106" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
 گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
@@ -3915,27 +3979,27 @@
 گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="101" t="inlineStr">
+      <c r="F17" s="105" t="inlineStr">
         <is>
           <t>SAFE, input true, v21300</t>
         </is>
       </c>
-      <c r="G17" s="101" t="inlineStr">
+      <c r="G17" s="105" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H17" s="100" t="inlineStr">
+      <c r="H17" s="104" t="inlineStr">
         <is>
           <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
         </is>
       </c>
-      <c r="I17" s="100" t="inlineStr">
+      <c r="I17" s="104" t="inlineStr">
         <is>
           <t>PASS: قبل 3000 SAFE Low، بعد 3000 INPUT High. FAIL: early or no reconnect.</t>
         </is>
       </c>
-      <c r="J17" s="111" t="n"/>
+      <c r="J17" s="104" t="n"/>
       <c r="K17" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3943,14 +4007,14 @@
       </c>
       <c r="L17" s="113" t="n"/>
       <c r="M17" s="100" t="n"/>
-      <c r="N17" s="100" t="inlineStr">
+      <c r="N17" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O17" s="101" t="n"/>
       <c r="P17" s="101" t="n"/>
-      <c r="Q17" s="103">
+      <c r="Q17" s="107">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
@@ -3961,22 +4025,22 @@
           <t>CO-014</t>
         </is>
       </c>
-      <c r="B18" s="104" t="inlineStr">
+      <c r="B18" s="143" t="inlineStr">
         <is>
           <t>مرز دقیق 21200 باید reconnect</t>
         </is>
       </c>
-      <c r="C18" s="114" t="inlineStr">
+      <c r="C18" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="104" t="inlineStr">
+      <c r="D18" s="143" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="E18" s="104" t="inlineStr">
+      <c r="E18" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت امن (SAFE) باشد.
 گام ۲: input=true و v دقیقاً 21200 بده (روی خود مرز).
@@ -3985,42 +4049,42 @@
 گام ۵: شرط وصل «دست‌کم 21200» است؛ پس روی مرز هم باید وصل شود.</t>
         </is>
       </c>
-      <c r="F18" s="105" t="inlineStr">
+      <c r="F18" s="144" t="inlineStr">
         <is>
           <t>v=21200 input true</t>
         </is>
       </c>
-      <c r="G18" s="105" t="inlineStr">
+      <c r="G18" s="144" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H18" s="104" t="inlineStr">
+      <c r="H18" s="143" t="inlineStr">
         <is>
           <t>پس از 3000ms INPUT و PB11 High. PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
         </is>
       </c>
-      <c r="I18" s="104" t="inlineStr">
+      <c r="I18" s="143" t="inlineStr">
         <is>
           <t>PASS: 21200 reconnects (need ≥). FAIL: no.</t>
         </is>
       </c>
       <c r="J18" s="104" t="n"/>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L18" s="115" t="n"/>
       <c r="M18" s="104" t="n"/>
-      <c r="N18" s="104" t="inlineStr">
+      <c r="N18" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O18" s="105" t="n"/>
       <c r="P18" s="105" t="n"/>
-      <c r="Q18" s="107">
+      <c r="Q18" s="148">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
@@ -4031,22 +4095,22 @@
           <t>CO-015</t>
         </is>
       </c>
-      <c r="B19" s="100" t="inlineStr">
+      <c r="B19" s="104" t="inlineStr">
         <is>
           <t>reconnect &lt;3000 نباید</t>
         </is>
       </c>
-      <c r="C19" s="110" t="inlineStr">
+      <c r="C19" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="100" t="inlineStr">
+      <c r="D19" s="104" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="E19" s="100" t="inlineStr">
+      <c r="E19" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در SAFE باشد.
 گام ۲: input=true و v=21300 اعمال کن.
@@ -4054,27 +4118,27 @@
 گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F19" s="101" t="inlineStr">
+      <c r="F19" s="105" t="inlineStr">
         <is>
           <t>v21300 input true</t>
         </is>
       </c>
-      <c r="G19" s="101" t="inlineStr">
+      <c r="G19" s="105" t="inlineStr">
         <is>
           <t>2500ms</t>
         </is>
       </c>
-      <c r="H19" s="100" t="inlineStr">
+      <c r="H19" s="104" t="inlineStr">
         <is>
           <t>هنوز SAFE و PB11 Low. PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
         </is>
       </c>
-      <c r="I19" s="100" t="inlineStr">
+      <c r="I19" s="104" t="inlineStr">
         <is>
           <t>PASS: 2500 still SAFE. FAIL: INPUT early.</t>
         </is>
       </c>
-      <c r="J19" s="111" t="n"/>
+      <c r="J19" s="104" t="n"/>
       <c r="K19" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -4082,14 +4146,14 @@
       </c>
       <c r="L19" s="113" t="n"/>
       <c r="M19" s="100" t="n"/>
-      <c r="N19" s="100" t="inlineStr">
+      <c r="N19" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O19" s="101" t="n"/>
       <c r="P19" s="101" t="n"/>
-      <c r="Q19" s="103">
+      <c r="Q19" s="107">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
@@ -4100,64 +4164,64 @@
           <t>CO-016</t>
         </is>
       </c>
-      <c r="B20" s="104" t="inlineStr">
+      <c r="B20" s="143" t="inlineStr">
         <is>
           <t>پس از reconnect state INPUT</t>
         </is>
       </c>
-      <c r="C20" s="114" t="inlineStr">
+      <c r="C20" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="106" t="inlineStr">
+      <c r="D20" s="145" t="inlineStr">
         <is>
           <t>پس از CO-013</t>
         </is>
       </c>
-      <c r="E20" s="106" t="inlineStr">
+      <c r="E20" s="145" t="inlineStr">
         <is>
           <t>گام ۱: تست CO-013 را انجام بده تا وصل مجدد موفق اتفاق بیفتد.
 گام ۲: بلافاصله (در حد 100 میلی‌ثانیه بعد) وضعیت را بخوان.
 گام ۳: وضعیت باید INPUT باشد؛ IDLE برای snapshot معتبر هرگز نباید دیده شود.</t>
         </is>
       </c>
-      <c r="F20" s="105" t="inlineStr">
+      <c r="F20" s="144" t="inlineStr">
         <is>
           <t>post-reconnect</t>
         </is>
       </c>
-      <c r="G20" s="105" t="inlineStr">
+      <c r="G20" s="144" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H20" s="104" t="inlineStr">
+      <c r="H20" s="143" t="inlineStr">
         <is>
           <t>state=INPUT باشد، نه IDLE (IDLE برای معتبر ممنوع). PASS: INPUT. FAIL: IDLE.</t>
         </is>
       </c>
-      <c r="I20" s="104" t="inlineStr">
+      <c r="I20" s="143" t="inlineStr">
         <is>
           <t>PASS: INPUT not IDLE. FAIL: IDLE.</t>
         </is>
       </c>
       <c r="J20" s="104" t="n"/>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L20" s="115" t="n"/>
       <c r="M20" s="104" t="n"/>
-      <c r="N20" s="104" t="inlineStr">
+      <c r="N20" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O20" s="105" t="n"/>
       <c r="P20" s="105" t="n"/>
-      <c r="Q20" s="107">
+      <c r="Q20" s="148">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
@@ -4168,49 +4232,49 @@
           <t>CO-017</t>
         </is>
       </c>
-      <c r="B21" s="100" t="inlineStr">
+      <c r="B21" s="104" t="inlineStr">
         <is>
           <t>PB11 در invalid حفظ</t>
         </is>
       </c>
-      <c r="C21" s="110" t="inlineStr">
+      <c r="C21" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="100" t="inlineStr">
+      <c r="D21" s="104" t="inlineStr">
         <is>
           <t>INPUT با PB11 High</t>
         </is>
       </c>
-      <c r="E21" s="100" t="inlineStr">
+      <c r="E21" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد را با snapshot معتبر و input=true به INPUT ببر و PB11 را چک کن که وصل (High) است.
 گام ۲: حالا valid=false کن و 500 میلی‌ثانیه صبر کن.
 گام ۳: PB11 را دوباره بخوان: باید بدون تغییر همان High مانده باشد.</t>
         </is>
       </c>
-      <c r="F21" s="101" t="inlineStr">
+      <c r="F21" s="105" t="inlineStr">
         <is>
           <t>valid true→false</t>
         </is>
       </c>
-      <c r="G21" s="101" t="inlineStr">
+      <c r="G21" s="105" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H21" s="100" t="inlineStr">
+      <c r="H21" s="104" t="inlineStr">
         <is>
           <t>PB11 Low-High بدون تغییر بماند (High). PASS: حفظ. FAIL: تغییر.</t>
         </is>
       </c>
-      <c r="I21" s="100" t="inlineStr">
+      <c r="I21" s="104" t="inlineStr">
         <is>
           <t>PASS: PB11 preserved in invalid. FAIL: change.</t>
         </is>
       </c>
-      <c r="J21" s="111" t="n"/>
+      <c r="J21" s="104" t="n"/>
       <c r="K21" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -4218,14 +4282,14 @@
       </c>
       <c r="L21" s="113" t="n"/>
       <c r="M21" s="100" t="n"/>
-      <c r="N21" s="100" t="inlineStr">
+      <c r="N21" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O21" s="101" t="n"/>
       <c r="P21" s="101" t="n"/>
-      <c r="Q21" s="103">
+      <c r="Q21" s="107">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
@@ -4236,22 +4300,22 @@
           <t>CO-018</t>
         </is>
       </c>
-      <c r="B22" s="104" t="inlineStr">
+      <c r="B22" s="143" t="inlineStr">
         <is>
           <t>PB11 در fault حفظ</t>
         </is>
       </c>
-      <c r="C22" s="114" t="inlineStr">
+      <c r="C22" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="104" t="inlineStr">
+      <c r="D22" s="143" t="inlineStr">
         <is>
           <t>INPUT</t>
         </is>
       </c>
-      <c r="E22" s="104" t="inlineStr">
+      <c r="E22" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در INPUT باشد.
 گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
@@ -4259,42 +4323,42 @@
 گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F22" s="105" t="inlineStr">
+      <c r="F22" s="144" t="inlineStr">
         <is>
           <t>valid true fault1</t>
         </is>
       </c>
-      <c r="G22" s="105" t="inlineStr">
+      <c r="G22" s="144" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H22" s="104" t="inlineStr">
+      <c r="H22" s="143" t="inlineStr">
         <is>
           <t>PB11 حفظ (High). PASS. FAIL: Low شدن.</t>
         </is>
       </c>
-      <c r="I22" s="104" t="inlineStr">
+      <c r="I22" s="143" t="inlineStr">
         <is>
           <t>PASS: PB11 preserved in fault. FAIL: change.</t>
         </is>
       </c>
       <c r="J22" s="104" t="n"/>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L22" s="115" t="n"/>
       <c r="M22" s="104" t="n"/>
-      <c r="N22" s="104" t="inlineStr">
+      <c r="N22" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O22" s="105" t="n"/>
       <c r="P22" s="105" t="n"/>
-      <c r="Q22" s="107">
+      <c r="Q22" s="148">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
@@ -4305,22 +4369,22 @@
           <t>CO-019</t>
         </is>
       </c>
-      <c r="B23" s="100" t="inlineStr">
+      <c r="B23" s="104" t="inlineStr">
         <is>
           <t>PB5 و PB7 هیچ‌گاه تغییر نکنند</t>
         </is>
       </c>
-      <c r="C23" s="110" t="inlineStr">
+      <c r="C23" s="114" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="100" t="inlineStr">
+      <c r="D23" s="104" t="inlineStr">
         <is>
           <t>هر حالت</t>
         </is>
       </c>
-      <c r="E23" s="116" t="inlineStr">
+      <c r="E23" s="106" t="inlineStr">
         <is>
           <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015، سه پایه را با اسکوپ یا لاگ BSP زیر نظر بگیر:
 پایهٔ PB11، پایهٔ PB5 (همان BAT_SWITCH) و پایهٔ PB7 (همان RELAY).
@@ -4329,27 +4393,27 @@
 گام ۴: هر تغییری روی این دو پایه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="101" t="inlineStr">
+      <c r="F23" s="105" t="inlineStr">
         <is>
           <t>تمام حالات</t>
         </is>
       </c>
-      <c r="G23" s="101" t="inlineStr">
+      <c r="G23" s="105" t="inlineStr">
         <is>
           <t>هر تست</t>
         </is>
       </c>
-      <c r="H23" s="100" t="inlineStr">
+      <c r="H23" s="104" t="inlineStr">
         <is>
           <t>PB5 و PB7 ثابت بمانند (PB5 High-safe active-low، PB7 Low). PASS: بدون تغییر. FAIL: هر toggle.</t>
         </is>
       </c>
-      <c r="I23" s="100" t="inlineStr">
+      <c r="I23" s="104" t="inlineStr">
         <is>
           <t>PASS: PB5/PB7 never change. FAIL: any toggle.</t>
         </is>
       </c>
-      <c r="J23" s="111" t="n"/>
+      <c r="J23" s="104" t="n"/>
       <c r="K23" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -4357,14 +4421,14 @@
       </c>
       <c r="L23" s="113" t="n"/>
       <c r="M23" s="100" t="n"/>
-      <c r="N23" s="100" t="inlineStr">
+      <c r="N23" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O23" s="101" t="n"/>
       <c r="P23" s="101" t="n"/>
-      <c r="Q23" s="103">
+      <c r="Q23" s="107">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
@@ -4375,22 +4439,22 @@
           <t>CO-024</t>
         </is>
       </c>
-      <c r="B24" s="104" t="inlineStr">
+      <c r="B24" s="143" t="inlineStr">
         <is>
           <t>وصل مجدد 30s پایداری ورودی</t>
         </is>
       </c>
-      <c r="C24" s="114" t="inlineStr">
+      <c r="C24" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="104" t="inlineStr">
+      <c r="D24" s="143" t="inlineStr">
         <is>
           <t>برد در SAFE پس از قطع، v_bat=24V</t>
         </is>
       </c>
-      <c r="E24" s="106" t="inlineStr">
+      <c r="E24" s="145" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در وضعیت امن و ولتاژ باتری 24 ولت باشد.
 گام ۲: ورودی را وصل کن (input=true) و 30 ثانیه پشت سر هم حاضر نگه دار.
@@ -4399,42 +4463,42 @@
 گام ۵: سطح PB11 را در لحظهٔ وصل با اسکوپ ثبت کن و با الگوی تست CO-013 مقایسه کن.</t>
         </is>
       </c>
-      <c r="F24" s="105" t="inlineStr">
+      <c r="F24" s="144" t="inlineStr">
         <is>
           <t>input=true v=24000</t>
         </is>
       </c>
-      <c r="G24" s="105" t="inlineStr">
+      <c r="G24" s="144" t="inlineStr">
         <is>
           <t>33s</t>
         </is>
       </c>
-      <c r="H24" s="104" t="inlineStr">
+      <c r="H24" s="143" t="inlineStr">
         <is>
           <t>بعد از 30 ثانیه پایداری ورودی و 3 ثانیه ولتاژ 21200، PB11 از Low به High و وضعیت INPUT شود</t>
         </is>
       </c>
-      <c r="I24" s="104" t="inlineStr">
+      <c r="I24" s="143" t="inlineStr">
         <is>
           <t>PASS: PB11 بعد 33s وصل، قبلش SAFE. FAIL: وصل زودتر از 30s</t>
         </is>
       </c>
       <c r="J24" s="104" t="n"/>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="143" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
       <c r="L24" s="115" t="n"/>
       <c r="M24" s="104" t="n"/>
-      <c r="N24" s="104" t="inlineStr">
+      <c r="N24" s="143" t="inlineStr">
         <is>
           <t>thermal+30s</t>
         </is>
       </c>
       <c r="O24" s="105" t="n"/>
       <c r="P24" s="105" t="n"/>
-      <c r="Q24" s="107">
+      <c r="Q24" s="148">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
@@ -4901,7 +4965,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4928,7 +4992,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -4993,87 +5057,87 @@
       <c r="Q3" s="82" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="138" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="138" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="138" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="84" t="inlineStr">
+      <c r="D4" s="138" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="84" t="inlineStr">
+      <c r="E4" s="138" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="84" t="inlineStr">
+      <c r="F4" s="138" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="84" t="inlineStr">
+      <c r="G4" s="138" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="84" t="inlineStr">
+      <c r="H4" s="138" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="84" t="inlineStr">
+      <c r="I4" s="138" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="84" t="inlineStr">
+      <c r="J4" s="138" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="84" t="inlineStr">
+      <c r="K4" s="138" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="84" t="inlineStr">
+      <c r="L4" s="138" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="84" t="inlineStr">
+      <c r="M4" s="138" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="84" t="inlineStr">
+      <c r="N4" s="138" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="O4" s="84" t="inlineStr">
+      <c r="O4" s="138" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="84" t="inlineStr">
+      <c r="P4" s="138" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="84" t="n"/>
+      <c r="Q4" s="138" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="99" t="inlineStr">
@@ -5150,22 +5214,22 @@
           <t>CO-021</t>
         </is>
       </c>
-      <c r="B6" s="100" t="inlineStr">
+      <c r="B6" s="143" t="inlineStr">
         <is>
           <t>زمان از rtos_time</t>
         </is>
       </c>
-      <c r="C6" s="101" t="inlineStr">
+      <c r="C6" s="144" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="100" t="inlineStr">
+      <c r="D6" s="143" t="inlineStr">
         <is>
           <t>هر زمان</t>
         </is>
       </c>
-      <c r="E6" s="100" t="inlineStr">
+      <c r="E6" s="143" t="inlineStr">
         <is>
           <t>گام ۱: کد را بازبینی کن: همهٔ تبدیل‌های میلی‌ثانیه به تیک باید فقط از func__Rtos_MillisecondsToTicks و زمان فعلی از osKernelGetTickCount گرفته شود.
 گام ۲: دنبال هر جا که «تیک برابر 1 میلی‌ثانیه» فرض شده باشد بگرد؛ نباید هیچ جا باشد.
@@ -5173,27 +5237,27 @@
 گام ۴: رفتار باید با هر فرکانس تیک درست بماند؛ وابستگی به فرض 1 میلی‌ثانیه یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="101" t="inlineStr">
+      <c r="F6" s="144" t="inlineStr">
         <is>
           <t>کد review</t>
         </is>
       </c>
-      <c r="G6" s="101" t="inlineStr">
+      <c r="G6" s="144" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="100" t="inlineStr">
+      <c r="H6" s="143" t="inlineStr">
         <is>
           <t>زمان با rtos_time قابل‌حمل باشد، 3000ms با هر فرکانس تیک درست کار کند. PASS: portable. FAIL: فرض 1ms.</t>
         </is>
       </c>
-      <c r="I6" s="100" t="inlineStr">
+      <c r="I6" s="143" t="inlineStr">
         <is>
           <t>PASS: portable via rtos_time. FAIL: hardcoded 1ms.</t>
         </is>
       </c>
-      <c r="J6" s="111" t="n"/>
+      <c r="J6" s="104" t="n"/>
       <c r="K6" s="112" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -5201,14 +5265,14 @@
       </c>
       <c r="L6" s="113" t="n"/>
       <c r="M6" s="100" t="n"/>
-      <c r="N6" s="100" t="inlineStr">
+      <c r="N6" s="143" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O6" s="101" t="n"/>
       <c r="P6" s="101" t="n"/>
-      <c r="Q6" s="103">
+      <c r="Q6" s="148">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -5288,22 +5352,22 @@
           <t>CO-023</t>
         </is>
       </c>
-      <c r="B8" s="100" t="inlineStr">
+      <c r="B8" s="143" t="inlineStr">
         <is>
           <t>snapshot zeroing task_control</t>
         </is>
       </c>
-      <c r="C8" s="110" t="inlineStr">
+      <c r="C8" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="100" t="inlineStr">
+      <c r="D8" s="143" t="inlineStr">
         <is>
           <t>MODULE_MEASUREMENT=0 یا GetSnapshot=false</t>
         </is>
       </c>
-      <c r="E8" s="100" t="inlineStr">
+      <c r="E8" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بیلد کن. یا ADC را نگه دار تا valid=false بماند.
 گام ۲: 3 ثانیه وضعیت و PB11 را نگاه کن.
@@ -5312,29 +5376,29 @@
 گام ۵: هیچ تصمیمی بر اساس زباله قبول نیست.</t>
         </is>
       </c>
-      <c r="F8" s="101" t="inlineStr">
+      <c r="F8" s="144" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" s="101" t="inlineStr">
+      <c r="G8" s="144" t="inlineStr">
         <is>
           <t>3500ms</t>
         </is>
       </c>
-      <c r="H8" s="100" t="inlineStr">
+      <c r="H8" s="143" t="inlineStr">
         <is>
           <t>هیچ فیلدی از داده نباید زبالهٔ پشته داشته باشد.
 Changeover باید فقط روی valid گیت بزند و PB11 امن بماند.
 تسک کنترل، مثل تسک‌های ارتباط و UI و حفاظت، هر 9 فیلد را صفر می‌کند.</t>
         </is>
       </c>
-      <c r="I8" s="100" t="inlineStr">
+      <c r="I8" s="143" t="inlineStr">
         <is>
           <t>امن</t>
         </is>
       </c>
-      <c r="J8" s="100" t="inlineStr">
+      <c r="J8" s="143" t="inlineStr">
         <is>
           <t>بدون تصمیم بر اساس زباله؛ PB11 حفظ</t>
         </is>
@@ -5347,13 +5411,13 @@
       </c>
       <c r="M8" s="100" t="n"/>
       <c r="N8" s="100" t="n"/>
-      <c r="O8" s="101" t="inlineStr">
+      <c r="O8" s="144" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P8" s="101" t="n"/>
-      <c r="Q8" s="103" t="inlineStr">
+      <c r="Q8" s="148" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -5830,7 +5894,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="149" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوهای Changeover</t>
         </is>
@@ -5849,32 +5913,32 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="90" t="inlineStr">
+      <c r="A3" s="141" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="90" t="inlineStr">
+      <c r="B3" s="141" t="inlineStr">
         <is>
           <t>شرط / مقدار (از کد)</t>
         </is>
       </c>
-      <c r="C3" s="90" t="inlineStr">
+      <c r="C3" s="141" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="90" t="inlineStr">
+      <c r="D3" s="141" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="90" t="inlineStr">
+      <c r="E3" s="141" t="inlineStr">
         <is>
           <t>توضیح تکمیلی</t>
         </is>
       </c>
-      <c r="F3" s="90" t="inlineStr">
+      <c r="F3" s="141" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
@@ -6320,14 +6384,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="121" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
@@ -6346,86 +6410,86 @@
       <c r="M2" s="9" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="90" t="inlineStr">
+      <c r="A3" s="141" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="90" t="inlineStr">
+      <c r="B3" s="141" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="90" t="inlineStr">
+      <c r="C3" s="141" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="90" t="inlineStr">
+      <c r="D3" s="141" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="90" t="inlineStr">
+      <c r="E3" s="141" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="90" t="inlineStr">
+      <c r="F3" s="141" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="90" t="inlineStr">
+      <c r="G3" s="141" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="90" t="inlineStr">
+      <c r="H3" s="141" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="90" t="inlineStr">
+      <c r="I3" s="141" t="inlineStr">
         <is>
           <t>مدرک / مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="90" t="inlineStr">
+      <c r="J3" s="141" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="K3" s="90" t="inlineStr">
+      <c r="K3" s="141" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="90" t="inlineStr">
+      <c r="L3" s="141" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="90" t="inlineStr">
+      <c r="M3" s="141" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="122" t="inlineStr"/>
-      <c r="B4" s="122" t="inlineStr"/>
-      <c r="C4" s="122" t="inlineStr"/>
-      <c r="D4" s="122" t="inlineStr"/>
-      <c r="E4" s="122" t="inlineStr"/>
-      <c r="F4" s="122" t="inlineStr"/>
-      <c r="G4" s="122" t="inlineStr"/>
-      <c r="H4" s="122" t="inlineStr"/>
-      <c r="I4" s="122" t="inlineStr"/>
-      <c r="J4" s="122" t="inlineStr"/>
-      <c r="K4" s="122" t="inlineStr"/>
-      <c r="L4" s="122" t="inlineStr"/>
-      <c r="M4" s="122" t="inlineStr"/>
+      <c r="A4" s="150" t="inlineStr"/>
+      <c r="B4" s="150" t="inlineStr"/>
+      <c r="C4" s="150" t="inlineStr"/>
+      <c r="D4" s="150" t="inlineStr"/>
+      <c r="E4" s="150" t="inlineStr"/>
+      <c r="F4" s="150" t="inlineStr"/>
+      <c r="G4" s="150" t="inlineStr"/>
+      <c r="H4" s="150" t="inlineStr"/>
+      <c r="I4" s="150" t="inlineStr"/>
+      <c r="J4" s="150" t="inlineStr"/>
+      <c r="K4" s="150" t="inlineStr"/>
+      <c r="L4" s="150" t="inlineStr"/>
+      <c r="M4" s="150" t="inlineStr"/>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="123" t="inlineStr"/>
@@ -6443,19 +6507,19 @@
       <c r="M5" s="123" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="122" t="inlineStr"/>
-      <c r="B6" s="122" t="inlineStr"/>
-      <c r="C6" s="122" t="inlineStr"/>
-      <c r="D6" s="122" t="inlineStr"/>
-      <c r="E6" s="122" t="inlineStr"/>
-      <c r="F6" s="122" t="inlineStr"/>
-      <c r="G6" s="122" t="inlineStr"/>
-      <c r="H6" s="122" t="inlineStr"/>
-      <c r="I6" s="122" t="inlineStr"/>
-      <c r="J6" s="122" t="inlineStr"/>
-      <c r="K6" s="122" t="inlineStr"/>
-      <c r="L6" s="122" t="inlineStr"/>
-      <c r="M6" s="122" t="inlineStr"/>
+      <c r="A6" s="150" t="inlineStr"/>
+      <c r="B6" s="150" t="inlineStr"/>
+      <c r="C6" s="150" t="inlineStr"/>
+      <c r="D6" s="150" t="inlineStr"/>
+      <c r="E6" s="150" t="inlineStr"/>
+      <c r="F6" s="150" t="inlineStr"/>
+      <c r="G6" s="150" t="inlineStr"/>
+      <c r="H6" s="150" t="inlineStr"/>
+      <c r="I6" s="150" t="inlineStr"/>
+      <c r="J6" s="150" t="inlineStr"/>
+      <c r="K6" s="150" t="inlineStr"/>
+      <c r="L6" s="150" t="inlineStr"/>
+      <c r="M6" s="150" t="inlineStr"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="123" t="inlineStr"/>
@@ -6473,19 +6537,19 @@
       <c r="M7" s="123" t="inlineStr"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="122" t="inlineStr"/>
-      <c r="B8" s="122" t="inlineStr"/>
-      <c r="C8" s="122" t="inlineStr"/>
-      <c r="D8" s="122" t="inlineStr"/>
-      <c r="E8" s="122" t="inlineStr"/>
-      <c r="F8" s="122" t="inlineStr"/>
-      <c r="G8" s="122" t="inlineStr"/>
-      <c r="H8" s="122" t="inlineStr"/>
-      <c r="I8" s="122" t="inlineStr"/>
-      <c r="J8" s="122" t="inlineStr"/>
-      <c r="K8" s="122" t="inlineStr"/>
-      <c r="L8" s="122" t="inlineStr"/>
-      <c r="M8" s="122" t="inlineStr"/>
+      <c r="A8" s="150" t="inlineStr"/>
+      <c r="B8" s="150" t="inlineStr"/>
+      <c r="C8" s="150" t="inlineStr"/>
+      <c r="D8" s="150" t="inlineStr"/>
+      <c r="E8" s="150" t="inlineStr"/>
+      <c r="F8" s="150" t="inlineStr"/>
+      <c r="G8" s="150" t="inlineStr"/>
+      <c r="H8" s="150" t="inlineStr"/>
+      <c r="I8" s="150" t="inlineStr"/>
+      <c r="J8" s="150" t="inlineStr"/>
+      <c r="K8" s="150" t="inlineStr"/>
+      <c r="L8" s="150" t="inlineStr"/>
+      <c r="M8" s="150" t="inlineStr"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="123" t="inlineStr"/>
@@ -6503,19 +6567,19 @@
       <c r="M9" s="123" t="inlineStr"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="122" t="inlineStr"/>
-      <c r="B10" s="122" t="inlineStr"/>
-      <c r="C10" s="122" t="inlineStr"/>
-      <c r="D10" s="122" t="inlineStr"/>
-      <c r="E10" s="122" t="inlineStr"/>
-      <c r="F10" s="122" t="inlineStr"/>
-      <c r="G10" s="122" t="inlineStr"/>
-      <c r="H10" s="122" t="inlineStr"/>
-      <c r="I10" s="122" t="inlineStr"/>
-      <c r="J10" s="122" t="inlineStr"/>
-      <c r="K10" s="122" t="inlineStr"/>
-      <c r="L10" s="122" t="inlineStr"/>
-      <c r="M10" s="122" t="inlineStr"/>
+      <c r="A10" s="150" t="inlineStr"/>
+      <c r="B10" s="150" t="inlineStr"/>
+      <c r="C10" s="150" t="inlineStr"/>
+      <c r="D10" s="150" t="inlineStr"/>
+      <c r="E10" s="150" t="inlineStr"/>
+      <c r="F10" s="150" t="inlineStr"/>
+      <c r="G10" s="150" t="inlineStr"/>
+      <c r="H10" s="150" t="inlineStr"/>
+      <c r="I10" s="150" t="inlineStr"/>
+      <c r="J10" s="150" t="inlineStr"/>
+      <c r="K10" s="150" t="inlineStr"/>
+      <c r="L10" s="150" t="inlineStr"/>
+      <c r="M10" s="150" t="inlineStr"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="123" t="inlineStr"/>
@@ -6533,19 +6597,19 @@
       <c r="M11" s="123" t="inlineStr"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="122" t="inlineStr"/>
-      <c r="B12" s="122" t="inlineStr"/>
-      <c r="C12" s="122" t="inlineStr"/>
-      <c r="D12" s="122" t="inlineStr"/>
-      <c r="E12" s="122" t="inlineStr"/>
-      <c r="F12" s="122" t="inlineStr"/>
-      <c r="G12" s="122" t="inlineStr"/>
-      <c r="H12" s="122" t="inlineStr"/>
-      <c r="I12" s="122" t="inlineStr"/>
-      <c r="J12" s="122" t="inlineStr"/>
-      <c r="K12" s="122" t="inlineStr"/>
-      <c r="L12" s="122" t="inlineStr"/>
-      <c r="M12" s="122" t="inlineStr"/>
+      <c r="A12" s="150" t="inlineStr"/>
+      <c r="B12" s="150" t="inlineStr"/>
+      <c r="C12" s="150" t="inlineStr"/>
+      <c r="D12" s="150" t="inlineStr"/>
+      <c r="E12" s="150" t="inlineStr"/>
+      <c r="F12" s="150" t="inlineStr"/>
+      <c r="G12" s="150" t="inlineStr"/>
+      <c r="H12" s="150" t="inlineStr"/>
+      <c r="I12" s="150" t="inlineStr"/>
+      <c r="J12" s="150" t="inlineStr"/>
+      <c r="K12" s="150" t="inlineStr"/>
+      <c r="L12" s="150" t="inlineStr"/>
+      <c r="M12" s="150" t="inlineStr"/>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="123" t="inlineStr"/>
@@ -6592,7 +6656,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="124" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — Changeover — PB11</t>
         </is>
@@ -6606,14 +6670,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="89" t="inlineStr">
+      <c r="A3" s="140" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="126" t="inlineStr">
+      <c r="A4" s="155" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
@@ -6623,7 +6687,7 @@
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="C4" s="126" t="inlineStr">
+      <c r="C4" s="155" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
@@ -6637,7 +6701,7 @@
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="126" t="inlineStr">
+      <c r="A5" s="155" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
@@ -6647,7 +6711,7 @@
           <t>2026-09-16 (2.1 — فیلتر 3000ms)</t>
         </is>
       </c>
-      <c r="C5" s="126" t="inlineStr">
+      <c r="C5" s="155" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
@@ -6661,7 +6725,7 @@
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="126" t="inlineStr">
+      <c r="A6" s="155" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
@@ -6671,7 +6735,7 @@
           <t>نسخهٔ برنامهٔ فلش‌شده (تست‌کننده پر کند)</t>
         </is>
       </c>
-      <c r="C6" s="126" t="inlineStr">
+      <c r="C6" s="155" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
@@ -6681,13 +6745,13 @@
       <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="126" t="inlineStr">
+      <c r="A7" s="155" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
       <c r="B7" s="127" t="inlineStr"/>
-      <c r="C7" s="126" t="inlineStr">
+      <c r="C7" s="155" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
@@ -6697,18 +6761,18 @@
       <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="126" t="inlineStr">
+      <c r="A8" s="155" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
       <c r="B8" s="127" t="inlineStr"/>
-      <c r="C8" s="126" t="inlineStr">
+      <c r="C8" s="155" t="inlineStr">
         <is>
           <t>ابزار اندازه‌گیری</t>
         </is>
       </c>
-      <c r="D8" s="92" t="inlineStr">
+      <c r="D8" s="151" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسیلوسکوپ + تایمر RTOS</t>
         </is>
@@ -6717,125 +6781,125 @@
       <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="126" t="inlineStr">
+      <c r="A9" s="155" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="152" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
       </c>
-      <c r="C9" s="126" t="inlineStr"/>
+      <c r="C9" s="155" t="inlineStr"/>
       <c r="D9" s="127" t="inlineStr"/>
       <c r="E9" s="93" t="n"/>
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="126" t="inlineStr">
+      <c r="A10" s="155" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B10" s="92" t="inlineStr">
+      <c r="B10" s="151" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
       </c>
-      <c r="C10" s="126" t="inlineStr"/>
+      <c r="C10" s="155" t="inlineStr"/>
       <c r="D10" s="127" t="inlineStr"/>
       <c r="E10" s="93" t="n"/>
       <c r="F10" s="93" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="126" t="inlineStr">
+      <c r="A11" s="155" t="inlineStr">
         <is>
           <t>آستانه‌ها</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="152" t="inlineStr">
         <is>
           <t>21000/20800/21200</t>
         </is>
       </c>
-      <c r="C11" s="126" t="inlineStr"/>
+      <c r="C11" s="155" t="inlineStr"/>
       <c r="D11" s="127" t="inlineStr"/>
       <c r="E11" s="93" t="n"/>
       <c r="F11" s="93" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="126" t="inlineStr">
+      <c r="A12" s="155" t="inlineStr">
         <is>
           <t>فیلتر</t>
         </is>
       </c>
-      <c r="B12" s="92" t="inlineStr">
+      <c r="B12" s="151" t="inlineStr">
         <is>
           <t>3000ms</t>
         </is>
       </c>
-      <c r="C12" s="126" t="inlineStr"/>
+      <c r="C12" s="155" t="inlineStr"/>
       <c r="D12" s="127" t="inlineStr"/>
       <c r="E12" s="93" t="n"/>
       <c r="F12" s="93" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="126" t="inlineStr">
+      <c r="A13" s="155" t="inlineStr">
         <is>
           <t>مجاز pin</t>
         </is>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="152" t="inlineStr">
         <is>
           <t>فقط BSP_GPIO_PROTECT_BATTERY</t>
         </is>
       </c>
-      <c r="C13" s="126" t="inlineStr"/>
+      <c r="C13" s="155" t="inlineStr"/>
       <c r="D13" s="127" t="inlineStr"/>
       <c r="E13" s="93" t="n"/>
       <c r="F13" s="93" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="126" t="inlineStr">
+      <c r="A14" s="155" t="inlineStr">
         <is>
           <t>ممنوع</t>
         </is>
       </c>
-      <c r="B14" s="92" t="inlineStr">
+      <c r="B14" s="151" t="inlineStr">
         <is>
           <t>PB5/PB7/HAL/board_pins</t>
         </is>
       </c>
-      <c r="C14" s="126" t="inlineStr"/>
+      <c r="C14" s="155" t="inlineStr"/>
       <c r="D14" s="127" t="inlineStr"/>
       <c r="E14" s="93" t="n"/>
       <c r="F14" s="93" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="89" t="inlineStr">
+      <c r="A15" s="140" t="inlineStr">
         <is>
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="90" t="inlineStr">
+      <c r="A16" s="141" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B16" s="90" t="inlineStr">
+      <c r="B16" s="141" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C16" s="90" t="inlineStr">
+      <c r="C16" s="141" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="D16" s="90" t="inlineStr">
+      <c r="D16" s="141" t="inlineStr">
         <is>
           <t>فرمول پیشنهادی</t>
         </is>
@@ -6844,7 +6908,7 @@
       <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="92" t="inlineStr">
+      <c r="A17" s="153" t="inlineStr">
         <is>
           <t>تعداد کل تست‌ها</t>
         </is>
@@ -6853,7 +6917,7 @@
         <f>COUNTA('برنامه تست'!A5:A200)</f>
         <v/>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="152" t="inlineStr">
         <is>
           <t>کل ردیف‌های برنامه تست</t>
         </is>
@@ -6863,7 +6927,7 @@
       <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="92" t="inlineStr">
+      <c r="A18" s="153" t="inlineStr">
         <is>
           <t>تعداد قبول (PASS)</t>
         </is>
@@ -6872,12 +6936,12 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"قبول")</f>
         <v/>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="151" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = قبول</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="D18" s="151" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
@@ -6886,7 +6950,7 @@
       <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="92" t="inlineStr">
+      <c r="A19" s="153" t="inlineStr">
         <is>
           <t>تعداد رد (FAIL)</t>
         </is>
@@ -6895,12 +6959,12 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"رد")</f>
         <v/>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="152" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = رد</t>
         </is>
       </c>
-      <c r="D19" s="92" t="inlineStr">
+      <c r="D19" s="152" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
@@ -6909,7 +6973,7 @@
       <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="92" t="inlineStr">
+      <c r="A20" s="153" t="inlineStr">
         <is>
           <t>تعداد در انتظار</t>
         </is>
@@ -6918,12 +6982,12 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C20" s="92" t="inlineStr">
+      <c r="C20" s="151" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = در انتظار</t>
         </is>
       </c>
-      <c r="D20" s="92" t="inlineStr">
+      <c r="D20" s="151" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
@@ -6932,7 +6996,7 @@
       <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="A21" s="153" t="inlineStr">
         <is>
           <t>تعداد مسدود</t>
         </is>
@@ -6941,7 +7005,7 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"مسدود")</f>
         <v/>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="152" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = مسدود</t>
         </is>
@@ -6951,7 +7015,7 @@
       <c r="F21" s="9" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="92" t="inlineStr">
+      <c r="A22" s="153" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
@@ -6960,7 +7024,7 @@
         <f>IF(B17=0,"",TEXT(B18/B17,"0%"))</f>
         <v/>
       </c>
-      <c r="C22" s="92" t="inlineStr">
+      <c r="C22" s="151" t="inlineStr">
         <is>
           <t>PASS / TOTAL</t>
         </is>
@@ -6970,34 +7034,34 @@
       <c r="F22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="89" t="inlineStr">
+      <c r="A23" s="140" t="inlineStr">
         <is>
           <t>امضاها</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="90" t="inlineStr">
+      <c r="A24" s="141" t="inlineStr">
         <is>
           <t>نقش</t>
         </is>
       </c>
-      <c r="B24" s="90" t="inlineStr">
+      <c r="B24" s="141" t="inlineStr">
         <is>
           <t>نام و نام خانوادگی</t>
         </is>
       </c>
-      <c r="C24" s="90" t="inlineStr">
+      <c r="C24" s="141" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="D24" s="90" t="inlineStr">
+      <c r="D24" s="141" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
-      <c r="E24" s="90" t="inlineStr">
+      <c r="E24" s="141" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
@@ -7005,7 +7069,7 @@
       <c r="F24" s="9" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="92" t="inlineStr">
+      <c r="A25" s="153" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
@@ -7017,7 +7081,7 @@
       <c r="F25" s="9" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="92" t="inlineStr">
+      <c r="A26" s="153" t="inlineStr">
         <is>
           <t>بازبین فنی</t>
         </is>
@@ -7029,7 +7093,7 @@
       <c r="F26" s="9" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="92" t="inlineStr">
+      <c r="A27" s="153" t="inlineStr">
         <is>
           <t>تأیید نهایی</t>
         </is>
@@ -7041,7 +7105,7 @@
       <c r="F27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="125" t="inlineStr">
+      <c r="A28" s="154" t="inlineStr">
         <is>
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
@@ -7082,7 +7146,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7093,7 +7157,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="89" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -7142,7 +7206,7 @@
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="89" t="inlineStr">
+      <c r="A8" s="140" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -7180,7 +7244,7 @@
       <c r="A13" s="82" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="89" t="inlineStr">
+      <c r="A14" s="140" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
@@ -7260,7 +7324,7 @@
       <c r="A25" s="82" t="n"/>
     </row>
     <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="89" t="inlineStr">
+      <c r="A26" s="140" t="inlineStr">
         <is>
           <t>نتیجه ایراد</t>
         </is>
@@ -7320,11 +7384,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="82" t="n"/>
-      <c r="B2" s="82" t="n"/>
-      <c r="C2" s="82" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -7336,7 +7396,6 @@
           <t>Changeover_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="82" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="32" t="inlineStr">
@@ -7349,7 +7408,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="82" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="32" t="inlineStr">
@@ -7362,7 +7420,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="82" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="32" t="inlineStr">
@@ -7370,12 +7427,11 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7384,7 +7440,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="63">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -364,8 +364,19 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -441,6 +452,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -529,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -955,6 +971,24 @@
     </xf>
     <xf numFmtId="0" fontId="59" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1322,7 +1356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1692,7 +1726,6 @@
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="130" t="inlineStr">
         <is>
@@ -1702,6 +1735,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="156" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B29" s="157" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1765,15 +1810,23 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="137" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Changeover (قطع/وصل باتری با 3000ms)</t>
         </is>
       </c>
       <c r="Q1" s="82" t="n"/>
+      <c r="T1" s="158" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="96" t="inlineStr">
@@ -1782,6 +1835,14 @@
         </is>
       </c>
       <c r="Q2" s="82" t="n"/>
+      <c r="T2" s="159" t="inlineStr">
+        <is>
+          <t>ولتاژ باتری (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U2" s="160" t="n">
+        <v>24000</v>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="97" t="inlineStr">
@@ -1790,6 +1851,14 @@
         </is>
       </c>
       <c r="Q3" s="82" t="n"/>
+      <c r="T3" s="159" t="inlineStr">
+        <is>
+          <t>ورودی حاضر است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U3" s="160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="138" t="inlineStr">
@@ -1873,6 +1942,19 @@
         </is>
       </c>
       <c r="Q4" s="138" t="n"/>
+      <c r="R4" s="138" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="159" t="inlineStr">
+        <is>
+          <t>خطا هست؟ fault (1/0)</t>
+        </is>
+      </c>
+      <c r="U4" s="160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="99" t="inlineStr">
@@ -1945,6 +2027,18 @@
         <v/>
       </c>
       <c r="Q5" s="103" t="n"/>
+      <c r="R5" s="157">
+        <f>IF($U$6=0,"داده نامعتبر: وضعیت و خروجی همان قبلی می‌ماند",IF($U$4=1,"وضعیت خطا (FAULT) و خروجی تغییر نمی‌کند",IF(AND($U$2&lt;20800,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$2&lt;21000,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$3=1,$U$2&gt;=21200,$U$5&gt;=3),"خروجی وصل روی ورودی (INPUT)",IF($U$3=1,"ورودی حاضر است؛ وصل و قطع فقط بعد از ۳ ثانیهٔ کاملِ شرط انجام می‌شود","روی باتری (BATTERY)؛ با باتری کافی خروجی وصل است"))))))</f>
+        <v/>
+      </c>
+      <c r="T5" s="159" t="inlineStr">
+        <is>
+          <t>مدت ماندن شرط (ثانیه)</t>
+        </is>
+      </c>
+      <c r="U5" s="160" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="99" t="inlineStr">
@@ -2014,6 +2108,18 @@
         <v/>
       </c>
       <c r="Q6" s="107" t="n"/>
+      <c r="R6" s="157">
+        <f>IF($U$6=0,"داده نامعتبر: وضعیت و خروجی همان قبلی می‌ماند",IF($U$4=1,"وضعیت خطا (FAULT) و خروجی تغییر نمی‌کند",IF(AND($U$2&lt;20800,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$2&lt;21000,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$3=1,$U$2&gt;=21200,$U$5&gt;=3),"خروجی وصل روی ورودی (INPUT)",IF($U$3=1,"ورودی حاضر است؛ وصل و قطع فقط بعد از ۳ ثانیهٔ کاملِ شرط انجام می‌شود","روی باتری (BATTERY)؛ با باتری کافی خروجی وصل است"))))))</f>
+        <v/>
+      </c>
+      <c r="T6" s="159" t="inlineStr">
+        <is>
+          <t>داده معتبر است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U6" s="160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="99" t="inlineStr">
@@ -2083,6 +2189,15 @@
         <v/>
       </c>
       <c r="Q7" s="103" t="n"/>
+      <c r="R7" s="157">
+        <f>IF($U$6=0,"داده نامعتبر: وضعیت و خروجی همان قبلی می‌ماند",IF($U$4=1,"وضعیت خطا (FAULT) و خروجی تغییر نمی‌کند",IF(AND($U$2&lt;20800,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$2&lt;21000,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$3=1,$U$2&gt;=21200,$U$5&gt;=3),"خروجی وصل روی ورودی (INPUT)",IF($U$3=1,"ورودی حاضر است؛ وصل و قطع فقط بعد از ۳ ثانیهٔ کاملِ شرط انجام می‌شود","روی باتری (BATTERY)؛ با باتری کافی خروجی وصل است"))))))</f>
+        <v/>
+      </c>
+      <c r="T7" s="161" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="99" t="inlineStr">
@@ -2152,6 +2267,10 @@
         <v/>
       </c>
       <c r="Q8" s="107" t="n"/>
+      <c r="R8" s="157">
+        <f>IF($U$6=0,"داده نامعتبر: وضعیت و خروجی همان قبلی می‌ماند",IF($U$4=1,"وضعیت خطا (FAULT) و خروجی تغییر نمی‌کند",IF(AND($U$2&lt;20800,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$2&lt;21000,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$3=1,$U$2&gt;=21200,$U$5&gt;=3),"خروجی وصل روی ورودی (INPUT)",IF($U$3=1,"ورودی حاضر است؛ وصل و قطع فقط بعد از ۳ ثانیهٔ کاملِ شرط انجام می‌شود","روی باتری (BATTERY)؛ با باتری کافی خروجی وصل است"))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="131" t="n"/>
@@ -2915,8 +3034,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q48"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:P1"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -7384,7 +7505,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -545,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -989,6 +989,9 @@
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6597,20 +6600,72 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="150" t="inlineStr"/>
-      <c r="B4" s="150" t="inlineStr"/>
-      <c r="C4" s="150" t="inlineStr"/>
-      <c r="D4" s="150" t="inlineStr"/>
-      <c r="E4" s="150" t="inlineStr"/>
-      <c r="F4" s="150" t="inlineStr"/>
-      <c r="G4" s="150" t="inlineStr"/>
-      <c r="H4" s="150" t="inlineStr"/>
-      <c r="I4" s="150" t="inlineStr"/>
-      <c r="J4" s="150" t="inlineStr"/>
-      <c r="K4" s="150" t="inlineStr"/>
-      <c r="L4" s="150" t="inlineStr"/>
-      <c r="M4" s="150" t="inlineStr"/>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="162" t="inlineStr">
+        <is>
+          <t>IR-001</t>
+        </is>
+      </c>
+      <c r="B4" s="162" t="inlineStr">
+        <is>
+          <t>CO-027</t>
+        </is>
+      </c>
+      <c r="C4" s="162" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D4" s="162" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="E4" s="162" t="inlineStr">
+        <is>
+          <t>قطبیت PB11 برعکس بود: با قطع ورودی، باتری به خروجی نمی‌رسید</t>
+        </is>
+      </c>
+      <c r="F4" s="162" t="inlineStr">
+        <is>
+          <t>گام ۱: ورودی ۲۴ ولت را جدا کن. گام ۲: باتری سالم (بالای ۲۴ ولت) وصل باشد. گام ۳: خروجی و پایهٔ ۲۲ میکرو را اندازه بگیر.</t>
+        </is>
+      </c>
+      <c r="G4" s="162" t="inlineStr">
+        <is>
+          <t>باتری روی خروجی بیاید و خروجی ۲۴ ولت شود</t>
+        </is>
+      </c>
+      <c r="H4" s="162" t="inlineStr">
+        <is>
+          <t>خروجی مرده ماند و پایهٔ ۲۲ حدود ۳٫۳ ولت (سطح بالا) بود</t>
+        </is>
+      </c>
+      <c r="I4" s="162" t="inlineStr">
+        <is>
+          <t>شماتیک Circuit/ChangeOver(24V_DC).pdf صفحهٔ ChangeOver: PB11 → R45 → بیس Q17</t>
+        </is>
+      </c>
+      <c r="J4" s="162" t="inlineStr">
+        <is>
+          <t>v2 (بیلد جاری)</t>
+        </is>
+      </c>
+      <c r="K4" s="162" t="inlineStr">
+        <is>
+          <t>Firmware/Config/Inc/board_pins.h</t>
+        </is>
+      </c>
+      <c r="L4" s="162" t="inlineStr">
+        <is>
+          <t>رفع شد</t>
+        </is>
+      </c>
+      <c r="M4" s="162" t="inlineStr">
+        <is>
+          <t>قطبیت PROTECT_BATT به active-high اصلاح شد؛ Init یک‌بار مسیر باتری را وصل می‌کند؛ تست هاست BSP همین قطبیت را می‌سنجد</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="123" t="inlineStr"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -2276,23 +2276,79 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="n"/>
-      <c r="B9" s="131" t="n"/>
-      <c r="C9" s="131" t="n"/>
-      <c r="D9" s="131" t="n"/>
-      <c r="E9" s="131" t="n"/>
-      <c r="F9" s="131" t="n"/>
-      <c r="G9" s="131" t="n"/>
-      <c r="H9" s="131" t="n"/>
-      <c r="I9" s="131" t="n"/>
-      <c r="J9" s="131" t="n"/>
-      <c r="K9" s="131" t="n"/>
-      <c r="L9" s="131" t="n"/>
-      <c r="M9" s="131" t="n"/>
-      <c r="N9" s="131" t="n"/>
-      <c r="O9" s="131" t="n"/>
-      <c r="P9" s="131" t="n"/>
-      <c r="Q9" s="132" t="n"/>
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>CO-029</t>
+        </is>
+      </c>
+      <c r="B9" s="143" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C9" s="144" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="143" t="inlineStr">
+        <is>
+          <t>پایان CO-025 (خروجی قطع است و برق شهر هم قطع است)</t>
+        </is>
+      </c>
+      <c r="E9" s="143" t="inlineStr">
+        <is>
+          <t>گام ۱: از پایان CO-025 شروع کن: برق شهر قطع، خروجی قطع و بار خاموش.
+گام ۲: یک سیم باتری را حدود ۴ ثانیه جدا کن (برق شهر باید همچنان قطع باشد) و بعد وصل کن.
+گام ۳: باتری را در محدودهٔ سالم (بالای ۲۱٫۲ ولت) نگه دار و حدود ۱۰ ثانیه صبر کن.
+گام ۴: خروجی و بار را نگاه کن؛ برق شهر را وصل نکن.</t>
+        </is>
+      </c>
+      <c r="F9" s="143" t="inlineStr">
+        <is>
+          <t>نبودِ پیوستهٔ باتری حدود ۴ ثانیه، بدون ورودی</t>
+        </is>
+      </c>
+      <c r="G9" s="144" t="inlineStr">
+        <is>
+          <t>حدود ۱۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H9" s="143" t="inlineStr">
+        <is>
+          <t>خروجی حدود ۳ ثانیه بعد از وصل شدن سیم باتری برمی‌گردد و بار روشن می‌ماند</t>
+        </is>
+      </c>
+      <c r="I9" s="143" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از جدا و وصل کردن سیم باتری (حدود ۴ ثانیه جدا بودن) و با باتری بالای ۲۱٫۲ ولت، خروجی بدون نیاز به برق شهر و بعد از حدود ۳ ثانیه وصل می‌شود و بار روشن می‌ماند.
+اگر خروجی وصل نشد = رد؛ این همان ایراد گزارش‌شدهٔ ۲۰۲۶-۱۰-۲۳ است.</t>
+        </is>
+      </c>
+      <c r="J9" s="143" t="inlineStr">
+        <is>
+          <t>وصل شدن خروجی روی باتری بدون برق شهر؛ وصل نشدن = رد</t>
+        </is>
+      </c>
+      <c r="K9" s="104" t="n"/>
+      <c r="L9" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="104" t="n"/>
+      <c r="N9" s="104" t="n"/>
+      <c r="O9" s="105" t="n"/>
+      <c r="P9" s="144">
+        <f>IF(OR(K9="",K9="در انتظار"),"",IF(P9="",TODAY(),P9))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="107" t="n"/>
+      <c r="R9" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول (مدل زنده ورودی «تعویض باتری» ندارد): با ۳ ثانیه نبودِ پیوستهٔ باتری و ولتاژ ≥ ۲۱۲۰۰ به‌مدت ۳ ثانیه، خروجی بدون ورودی وصل و وضعیت BATTERY می‌شود.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="131" t="n"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -2299,35 +2299,35 @@
       <c r="E9" s="143" t="inlineStr">
         <is>
           <t>گام ۱: از پایان CO-025 شروع کن: برق شهر قطع، خروجی قطع و بار خاموش.
-گام ۲: یک سیم باتری را حدود ۴ ثانیه جدا کن (برق شهر باید همچنان قطع باشد) و بعد وصل کن.
-گام ۳: باتری را در محدودهٔ سالم (بالای ۲۱٫۲ ولت) نگه دار و حدود ۱۰ ثانیه صبر کن.
+گام ۲: ولتاژ باتری را به محدودهٔ سالم (بالای ۲۱٫۲ ولت) برگردان و حدود ۲۰ ثانیه صبر کن.
+گام ۳: در این مدت یک بار ولتاژ را یک لحظه زیر ۲۱٫۲ ببر و برگردان (شمارش باید از صفر شروع شود).
 گام ۴: خروجی و بار را نگاه کن؛ برق شهر را وصل نکن.</t>
         </is>
       </c>
       <c r="F9" s="143" t="inlineStr">
         <is>
-          <t>نبودِ پیوستهٔ باتری حدود ۴ ثانیه، بدون ورودی</t>
+          <t>ولتاژ سالم پیوسته، بدون برق شهر</t>
         </is>
       </c>
       <c r="G9" s="144" t="inlineStr">
         <is>
-          <t>حدود ۱۰ ثانیه</t>
+          <t>حدود ۲۰ ثانیه</t>
         </is>
       </c>
       <c r="H9" s="143" t="inlineStr">
         <is>
-          <t>خروجی حدود ۳ ثانیه بعد از وصل شدن سیم باتری برمی‌گردد و بار روشن می‌ماند</t>
+          <t>خروجی حدود ۱۳ ثانیه بعد از پایدار شدن ولتاژ برمی‌گردد و بار روشن می‌ماند</t>
         </is>
       </c>
       <c r="I9" s="143" t="inlineStr">
         <is>
-          <t>باید ببینید: بعد از جدا و وصل کردن سیم باتری (حدود ۴ ثانیه جدا بودن) و با باتری بالای ۲۱٫۲ ولت، خروجی بدون نیاز به برق شهر و بعد از حدود ۳ ثانیه وصل می‌شود و بار روشن می‌ماند.
+          <t>باید ببینید: با باتری سالم و بدون برق شهر، خروجی حدود ۱۳ ثانیه بعد (۱۰ ثانیه پنجرهٔ سالم + ۳ ثانیه فیلتر) وصل می‌شود و بار روشن می‌ماند. اگر وسط این ۱۰ ثانیه ولتاژ یک لحظه افت کند، باید از صفر شمرده شود.
 اگر خروجی وصل نشد = رد؛ این همان ایراد گزارش‌شدهٔ ۲۰۲۶-۱۰-۲۳ است.</t>
         </is>
       </c>
       <c r="J9" s="143" t="inlineStr">
         <is>
-          <t>وصل شدن خروجی روی باتری بدون برق شهر؛ وصل نشدن = رد</t>
+          <t>وصل شدن خروجی روی باتری بدون برق شهر؛ وصل نشدن یا وصلِ زودتر از ۱۰ ثانیه = رد</t>
         </is>
       </c>
       <c r="K9" s="104" t="n"/>
@@ -2346,7 +2346,7 @@
       <c r="Q9" s="107" t="n"/>
       <c r="R9" s="157" t="inlineStr">
         <is>
-          <t>بدون فرمول (مدل زنده ورودی «تعویض باتری» ندارد): با ۳ ثانیه نبودِ پیوستهٔ باتری و ولتاژ ≥ ۲۱۲۰۰ به‌مدت ۳ ثانیه، خروجی بدون ورودی وصل و وضعیت BATTERY می‌شود.</t>
+          <t>بدون فرمول: با ۱۰ ثانیه ولتاژ سالمِ پیوسته و ۳ ثانیه فیلتر، خروجی بدون ورودی وصل و وضعیت BATTERY می‌شود؛ اگر بعد از این وصل ظرف ۶۰ ثانیه دوباره قطع شود، دیگر بدون برق شهر وصل نمی‌شود (محافظ چرخه).</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -4683,21 +4683,69 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="82" t="n"/>
-      <c r="B25" s="82" t="n"/>
-      <c r="C25" s="82" t="n"/>
-      <c r="D25" s="82" t="n"/>
-      <c r="E25" s="82" t="n"/>
-      <c r="F25" s="82" t="n"/>
-      <c r="G25" s="82" t="n"/>
-      <c r="H25" s="82" t="n"/>
-      <c r="I25" s="82" t="n"/>
-      <c r="J25" s="82" t="n"/>
-      <c r="K25" s="82" t="n"/>
-      <c r="L25" s="82" t="n"/>
-      <c r="M25" s="82" t="n"/>
-      <c r="N25" s="82" t="n"/>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="99" t="inlineStr">
+        <is>
+          <t>CO-025</t>
+        </is>
+      </c>
+      <c r="B25" s="143" t="inlineStr">
+        <is>
+          <t>وصل بدون برق شهر / ۱۰ ثانیه سالم</t>
+        </is>
+      </c>
+      <c r="C25" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D25" s="143" t="inlineStr">
+        <is>
+          <t>برد در SAFE، برق شهر قطع، باتری &gt;= 21200 mV</t>
+        </is>
+      </c>
+      <c r="E25" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: از تست CO-008 شروع کن تا باتری قطع شود و برد در SAFE باشد؛ برق شهر قطع بماند.
+گام ۲: ولتاژ باتری را با یک منبع روی 21500 mV نگه دار.
+گام ۳: در ثانیهٔ ۹ وضعیت را بخوان: باید هنوز SAFE و PB11 قطع باشد.
+گام ۴: در ثانیهٔ ۱۰ با ۳ ثانیه فیلتر، بعد از حدود ۱۳ ثانیه باید PB11 وصل و وضعیت BATTERY شود.
+گام ۵: وصل زودتر از ۱۰ ثانیهٔ پیوسته یعنی رد.</t>
+        </is>
+      </c>
+      <c r="F25" s="144" t="inlineStr">
+        <is>
+          <t>input=false, v=21500 برای ۱۳ ثانیه</t>
+        </is>
+      </c>
+      <c r="G25" s="144" t="inlineStr">
+        <is>
+          <t>۱۳s</t>
+        </is>
+      </c>
+      <c r="H25" s="143" t="inlineStr">
+        <is>
+          <t>قبل از ۱۰ ثانیه SAFE می‌ماند؛ پس از ۱۰ ثانیه سالمِ پیوسته + ۳ ثانیه فیلتر، PB11 وصل و state=BATTERY. PASS: وصل فقط پس از ۱۰ ثانیه پیوسته. FAIL: وصل زودتر.</t>
+        </is>
+      </c>
+      <c r="I25" s="143" t="inlineStr">
+        <is>
+          <t>PASS: 9s SAFE، 13s BATTERY. FAIL: وصل زودتر.</t>
+        </is>
+      </c>
+      <c r="J25" s="104" t="n"/>
+      <c r="K25" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L25" s="115" t="n"/>
+      <c r="M25" s="104" t="n"/>
+      <c r="N25" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
       <c r="Q25" s="98">
@@ -4705,21 +4753,69 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="82" t="n"/>
-      <c r="B26" s="82" t="n"/>
-      <c r="C26" s="82" t="n"/>
-      <c r="D26" s="82" t="n"/>
-      <c r="E26" s="82" t="n"/>
-      <c r="F26" s="82" t="n"/>
-      <c r="G26" s="82" t="n"/>
-      <c r="H26" s="82" t="n"/>
-      <c r="I26" s="82" t="n"/>
-      <c r="J26" s="82" t="n"/>
-      <c r="K26" s="82" t="n"/>
-      <c r="L26" s="82" t="n"/>
-      <c r="M26" s="82" t="n"/>
-      <c r="N26" s="82" t="n"/>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="99" t="inlineStr">
+        <is>
+          <t>CO-026</t>
+        </is>
+      </c>
+      <c r="B26" s="143" t="inlineStr">
+        <is>
+          <t>محافظ چرخه / قطع دوبارهٔ سریع</t>
+        </is>
+      </c>
+      <c r="C26" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D26" s="143" t="inlineStr">
+        <is>
+          <t>پس از CO-025 وصل بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="E26" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: بعد از وصلِ CO-025، داخل ۶۰ ثانیه ولتاژ باتری را زیر 21000 mV بیاور تا قطع رخ دهد.
+گام ۲: ولتاژ را دوباره به 21500 mV برگردان و ۳۰ ثانیه صبر کن.
+گام ۳: برد نباید بدون برق شهر وصل شود؛ باید در SAFE بماند.
+گام ۴: حالا برق شهر را وصل کن و ۳۰ ثانیه پایدار نگه دار.
+گام ۵: فقط پس از برگشت برق شهر باید وصل شود؛ وصل خودکار بدون برق شهر یعنی رد.</t>
+        </is>
+      </c>
+      <c r="F26" s="144" t="inlineStr">
+        <is>
+          <t>قطع داخل ۶۰ ثانیه بعد از CO-025، سپس v=21500</t>
+        </is>
+      </c>
+      <c r="G26" s="144" t="inlineStr">
+        <is>
+          <t>۳۰s + ۳۳s</t>
+        </is>
+      </c>
+      <c r="H26" s="143" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف قفل می‌شود، مسیر باتری بسته می‌ماند و وصل خودکار بدون برق شهر انجام نمی‌شود؛ با برگشت برق شهر وصل مجاز است. PASS: قفل محافظ چرخه. FAIL: وصل خودکار بدون برق شهر.</t>
+        </is>
+      </c>
+      <c r="I26" s="143" t="inlineStr">
+        <is>
+          <t>PASS: بدون وصل تا برگشت برق شهر. FAIL: وصل خودکار.</t>
+        </is>
+      </c>
+      <c r="J26" s="104" t="n"/>
+      <c r="K26" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L26" s="115" t="n"/>
+      <c r="M26" s="104" t="n"/>
+      <c r="N26" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O26" s="82" t="n"/>
       <c r="P26" s="82" t="n"/>
       <c r="Q26" s="98">
@@ -4727,21 +4823,69 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="82" t="n"/>
-      <c r="B27" s="82" t="n"/>
-      <c r="C27" s="82" t="n"/>
-      <c r="D27" s="82" t="n"/>
-      <c r="E27" s="82" t="n"/>
-      <c r="F27" s="82" t="n"/>
-      <c r="G27" s="82" t="n"/>
-      <c r="H27" s="82" t="n"/>
-      <c r="I27" s="82" t="n"/>
-      <c r="J27" s="82" t="n"/>
-      <c r="K27" s="82" t="n"/>
-      <c r="L27" s="82" t="n"/>
-      <c r="M27" s="82" t="n"/>
-      <c r="N27" s="82" t="n"/>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="99" t="inlineStr">
+        <is>
+          <t>CO-027</t>
+        </is>
+      </c>
+      <c r="B27" s="143" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف / چهرهٔ قرمز و بوق</t>
+        </is>
+      </c>
+      <c r="C27" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D27" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل (پس از CO-026)</t>
+        </is>
+      </c>
+      <c r="E27" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: پس از CO-026 برد در وضعیت حکم باتری ضعیف باشد و برق شهر قطع بماند.
+گام ۲: چراغ قرمز را ۵ ثانیه نگاه کن: باید با دورهٔ ۵۰۰ میلی‌ثانیه و سهم ۵۰٪ چشمک بزند؛ سبز و زرد باید خاموش باشند.
+گام ۳: گوش کن: هر ۳۰۰۰ میلی‌ثانیه سه بوق ۲۰۰ میلی‌ثانیه‌ای با گپ ۱۰۰ میلی‌ثانیه باید شنیده شود.
+گام ۴: از پنل دورهٔ قرمز را ۱۰۰۰ و دورهٔ بوق را صفر کن؛ قرمز باید کندتر چشمک بزند و بوق قطع شود.
+گام ۵: قرمز ثابت یا بوق با الگوی سناریوی ۵/۶/۷ یعنی رد.</t>
+        </is>
+      </c>
+      <c r="F27" s="144" t="inlineStr">
+        <is>
+          <t>پارامترهای ۱۵۱..۱۵۶ با پیش‌فرض کارخانه</t>
+        </is>
+      </c>
+      <c r="G27" s="144" t="inlineStr">
+        <is>
+          <t>۵s + ۱۰s</t>
+        </is>
+      </c>
+      <c r="H27" s="143" t="inlineStr">
+        <is>
+          <t>قرمز چشمک‌زن با دوره/سهم مستقل و بوق سه‌تایی مستقل؛ سبز و زرد خاموش. PASS: همان چهرهٔ تعریف‌شده. FAIL: قرمز ثابت یا الگوی قرض‌گرفته.</t>
+        </is>
+      </c>
+      <c r="I27" s="143" t="inlineStr">
+        <is>
+          <t>PASS: چشمک ۵۰۰ms + سه بوق. FAIL: چهرهٔ دیگر.</t>
+        </is>
+      </c>
+      <c r="J27" s="104" t="n"/>
+      <c r="K27" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L27" s="115" t="n"/>
+      <c r="M27" s="104" t="n"/>
+      <c r="N27" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O27" s="82" t="n"/>
       <c r="P27" s="82" t="n"/>
       <c r="Q27" s="98">
@@ -4749,21 +4893,69 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="82" t="n"/>
-      <c r="B28" s="82" t="n"/>
-      <c r="C28" s="82" t="n"/>
-      <c r="D28" s="82" t="n"/>
-      <c r="E28" s="82" t="n"/>
-      <c r="F28" s="82" t="n"/>
-      <c r="G28" s="82" t="n"/>
-      <c r="H28" s="82" t="n"/>
-      <c r="I28" s="82" t="n"/>
-      <c r="J28" s="82" t="n"/>
-      <c r="K28" s="82" t="n"/>
-      <c r="L28" s="82" t="n"/>
-      <c r="M28" s="82" t="n"/>
-      <c r="N28" s="82" t="n"/>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="99" t="inlineStr">
+        <is>
+          <t>CO-028</t>
+        </is>
+      </c>
+      <c r="B28" s="143" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف / بسته‌ماندن خروجی</t>
+        </is>
+      </c>
+      <c r="C28" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D28" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل، شناسهٔ ۱۵۷ = ۱</t>
+        </is>
+      </c>
+      <c r="E28" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل و برق شهر قطع، خروجی را با بار ۱ آمپر بسنج.
+گام ۲: ولتاژ خروجی باید صفر بماند و PB11 باید High (قطع) باشد.
+گام ۳: حالا از پنل شناسهٔ ۱۵۷ را صفر کن؛ با حفظ حکم، باتری باید روی خروجی بیاید.
+گام ۴: دوباره ۱۵۷ را یک کن؛ مسیر باید بسته شود.
+گام ۵: اگر با ۱۵۷ = ۱ بار روی باتری دیده شود، رد است.</t>
+        </is>
+      </c>
+      <c r="F28" s="144" t="inlineStr">
+        <is>
+          <t>id157 = 1 سپس 0 سپس 1</t>
+        </is>
+      </c>
+      <c r="G28" s="144" t="inlineStr">
+        <is>
+          <t>۳۰s</t>
+        </is>
+      </c>
+      <c r="H28" s="143" t="inlineStr">
+        <is>
+          <t>با ۱۵۷ = ۱ مسیر باتری بسته می‌ماند؛ با ۱۵۷ = ۰ فقط هشدار می‌ماند و خروجی برمی‌گردد؛ شارژ قطع نمی‌شود. PASS: تبعیت دقیق از ۱۵۷. FAIL: بار روی باتری با ۱۵۷ = ۱.</t>
+        </is>
+      </c>
+      <c r="I28" s="143" t="inlineStr">
+        <is>
+          <t>PASS: خروجی صفر با ۱۵۷=۱. FAIL: بار روی باتری.</t>
+        </is>
+      </c>
+      <c r="J28" s="104" t="n"/>
+      <c r="K28" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L28" s="115" t="n"/>
+      <c r="M28" s="104" t="n"/>
+      <c r="N28" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O28" s="82" t="n"/>
       <c r="P28" s="82" t="n"/>
       <c r="Q28" s="98">
@@ -4771,21 +4963,69 @@
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="82" t="n"/>
-      <c r="B29" s="82" t="n"/>
-      <c r="C29" s="82" t="n"/>
-      <c r="D29" s="82" t="n"/>
-      <c r="E29" s="82" t="n"/>
-      <c r="F29" s="82" t="n"/>
-      <c r="G29" s="82" t="n"/>
-      <c r="H29" s="82" t="n"/>
-      <c r="I29" s="82" t="n"/>
-      <c r="J29" s="82" t="n"/>
-      <c r="K29" s="82" t="n"/>
-      <c r="L29" s="82" t="n"/>
-      <c r="M29" s="82" t="n"/>
-      <c r="N29" s="82" t="n"/>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="99" t="inlineStr">
+        <is>
+          <t>CO-029</t>
+        </is>
+      </c>
+      <c r="B29" s="143" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف / پاک‌شدن پس از استراحت</t>
+        </is>
+      </c>
+      <c r="C29" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D29" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل، شناسهٔ ۱۴۸ = ۶۰۰۰۰۰</t>
+        </is>
+      </c>
+      <c r="E29" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل، ولتاژ باتری را روی 21500 mV و پیوسته نگه دار.
+گام ۲: در دقیقهٔ ۹ وضعیت را بخوان: حکم باید هنوز قفل و قرمز چشمک‌زن باشد.
+گام ۳: پس از ۱۰ دقیقهٔ پیوسته، حکم باید خودش پاک شود و یک بار تلاش مجدد انجام شود.
+گام ۴: اگر داخل این ۱۰ دقیقه ولتاژ یک لحظه افت کند، شمارش باید از صفر شروع شود.
+گام ۵: پاک‌شدن زودتر از ۱۰ دقیقه یا پاک‌نشدن یعنی رد.</t>
+        </is>
+      </c>
+      <c r="F29" s="144" t="inlineStr">
+        <is>
+          <t>v=21500 پیوسته برای ۱۰ دقیقه</t>
+        </is>
+      </c>
+      <c r="G29" s="144" t="inlineStr">
+        <is>
+          <t>۱۰min</t>
+        </is>
+      </c>
+      <c r="H29" s="143" t="inlineStr">
+        <is>
+          <t>حکم فقط پس از ۱۰ دقیقهٔ سالمِ پیوسته پاک می‌شود و تنها یک تلاش مجدد انجام می‌شود. PASS: پاک‌شدن در دقیقهٔ ۱۰. FAIL: زودتر یا هرگز.</t>
+        </is>
+      </c>
+      <c r="I29" s="143" t="inlineStr">
+        <is>
+          <t>PASS: پاک‌شدن در ۱۰ دقیقه. FAIL: زودتر/هرگز.</t>
+        </is>
+      </c>
+      <c r="J29" s="104" t="n"/>
+      <c r="K29" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L29" s="115" t="n"/>
+      <c r="M29" s="104" t="n"/>
+      <c r="N29" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O29" s="82" t="n"/>
       <c r="P29" s="82" t="n"/>
       <c r="Q29" s="98">
@@ -4793,21 +5033,68 @@
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="82" t="n"/>
-      <c r="B30" s="82" t="n"/>
-      <c r="C30" s="82" t="n"/>
-      <c r="D30" s="82" t="n"/>
-      <c r="E30" s="82" t="n"/>
-      <c r="F30" s="82" t="n"/>
-      <c r="G30" s="82" t="n"/>
-      <c r="H30" s="82" t="n"/>
-      <c r="I30" s="82" t="n"/>
-      <c r="J30" s="82" t="n"/>
-      <c r="K30" s="82" t="n"/>
-      <c r="L30" s="82" t="n"/>
-      <c r="M30" s="82" t="n"/>
-      <c r="N30" s="82" t="n"/>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="99" t="inlineStr">
+        <is>
+          <t>CO-030</t>
+        </is>
+      </c>
+      <c r="B30" s="143" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف / برگشت برق شهر حکم را پاک نمی‌کند</t>
+        </is>
+      </c>
+      <c r="C30" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D30" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل</t>
+        </is>
+      </c>
+      <c r="E30" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل، برق شهر را وصل کن و ۳۰ ثانیه پایدار نگه دار.
+گام ۲: مسیر باتری باید وصل شود (چون برق شهر هست) ولی حکم نباید پاک شود.
+گام ۳: برق شهر را دوباره قطع کن؛ چراغ قرمز باید همچنان چشمک بزند و مسیر باتری بسته بماند.
+گام ۴: پاک‌شدن حکم فقط با شناسهٔ ۱۴۷ = ۰ یا ۱۰ دقیقهٔ سالمِ پیوسته مجاز است.</t>
+        </is>
+      </c>
+      <c r="F30" s="144" t="inlineStr">
+        <is>
+          <t>input=true برای ۳۰ ثانیه، سپس قطع</t>
+        </is>
+      </c>
+      <c r="G30" s="144" t="inlineStr">
+        <is>
+          <t>۳۰s + ۱۰s</t>
+        </is>
+      </c>
+      <c r="H30" s="143" t="inlineStr">
+        <is>
+          <t>برگشت برق شهر حکم را پاک نمی‌کند؛ با قطع دوباره همان چهره و همان بسته‌بودن برمی‌گردد. PASS: حکم پایدار. FAIL: پاک‌شدن با برق شهر.</t>
+        </is>
+      </c>
+      <c r="I30" s="143" t="inlineStr">
+        <is>
+          <t>PASS: حکم پس از برق شهر می‌ماند. FAIL: پاک شد.</t>
+        </is>
+      </c>
+      <c r="J30" s="104" t="n"/>
+      <c r="K30" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L30" s="115" t="n"/>
+      <c r="M30" s="104" t="n"/>
+      <c r="N30" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O30" s="82" t="n"/>
       <c r="P30" s="82" t="n"/>
       <c r="Q30" s="98">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -5890,21 +5890,69 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="82" t="n"/>
-      <c r="B9" s="82" t="n"/>
-      <c r="C9" s="82" t="n"/>
-      <c r="D9" s="82" t="n"/>
-      <c r="E9" s="82" t="n"/>
-      <c r="F9" s="82" t="n"/>
-      <c r="G9" s="82" t="n"/>
-      <c r="H9" s="82" t="n"/>
-      <c r="I9" s="82" t="n"/>
-      <c r="J9" s="82" t="n"/>
-      <c r="K9" s="82" t="n"/>
-      <c r="L9" s="82" t="n"/>
-      <c r="M9" s="82" t="n"/>
-      <c r="N9" s="82" t="n"/>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>CO-031</t>
+        </is>
+      </c>
+      <c r="B9" s="143" t="inlineStr">
+        <is>
+          <t>نمایش حکم باتری ضعیف در پنل کالیبراسیون و پنل کاربری</t>
+        </is>
+      </c>
+      <c r="C9" s="147" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل روی برد</t>
+        </is>
+      </c>
+      <c r="E9" s="143" t="inlineStr">
+        <is>
+          <t>گام ۱: روی برد حکم باتری ضعیف را قفل کن (یا در تست هاست بیت `0x10` را در بایت وضعیت بگذار).
+گام ۲: پنل کالیبراسیون را باز کن: چراغ «باتری ضعیف» در نوار خطاهای قفل‌شده باید قرمز شود و کارت ۸ باید بگوید حکم قفل است و مسیر باتری بسته مانده.
+گام ۳: روی همان چراغ کلیک کن؛ باید کارت ۸ باز شود.
+گام ۴: حکم را پاک کن؛ چراغ باید سبز و خط وضعیت باید بگوید حکم قفل نیست.
+گام ۵: در پنل کاربری ESP، پیام بالای صفحه باید «باتری ضعیف» را با همان توضیح نشان دهد.</t>
+        </is>
+      </c>
+      <c r="F9" s="144" t="inlineStr">
+        <is>
+          <t>bit 0x10 = 1 سپس 0</t>
+        </is>
+      </c>
+      <c r="G9" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="143" t="inlineStr">
+        <is>
+          <t>هر دو پنل حکم را از همان بیت فریم زنده بخوانند؛ چراغ همیشه سوار باشد (سبز/قرمز) و کلیکش کارت ۸ را باز کند. PASS: نمایش درست در هر دو پنل. FAIL: چراغ نبودن یا متن نادرست.</t>
+        </is>
+      </c>
+      <c r="I9" s="143" t="inlineStr">
+        <is>
+          <t>PASS: weak lamp + status line in both panels. FAIL: no lamp.</t>
+        </is>
+      </c>
+      <c r="J9" s="143" t="n"/>
+      <c r="K9" s="100" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L9" s="117" t="n"/>
+      <c r="M9" s="100" t="n"/>
+      <c r="N9" s="100" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O9" s="82" t="n"/>
       <c r="P9" s="82" t="n"/>
       <c r="Q9" s="98">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -5102,21 +5102,69 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="82" t="n"/>
-      <c r="B31" s="82" t="n"/>
-      <c r="C31" s="82" t="n"/>
-      <c r="D31" s="82" t="n"/>
-      <c r="E31" s="82" t="n"/>
-      <c r="F31" s="82" t="n"/>
-      <c r="G31" s="82" t="n"/>
-      <c r="H31" s="82" t="n"/>
-      <c r="I31" s="82" t="n"/>
-      <c r="J31" s="82" t="n"/>
-      <c r="K31" s="82" t="n"/>
-      <c r="L31" s="82" t="n"/>
-      <c r="M31" s="82" t="n"/>
-      <c r="N31" s="82" t="n"/>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="99" t="inlineStr">
+        <is>
+          <t>CO-032</t>
+        </is>
+      </c>
+      <c r="B31" s="143" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف / پاک‌کردن دستی از پنل</t>
+        </is>
+      </c>
+      <c r="C31" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D31" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل + پنل کالیبراسیون باز</t>
+        </is>
+      </c>
+      <c r="E31" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: روی برد حکم را قفل کن: بدون برق شهر وصل شود و داخل پنجرهٔ محافظ دوباره قطع شود.
+گام ۲: در کارت ۸ دکمهٔ «پاک‌کردن حکم» را بزن و تأیید کن.
+گام ۳: خط وضعیت باید «در حال ارسال…» و بعد «پاک شد» نشان دهد.
+گام ۴: چراغ قرمز و بوق باید خاموش شوند.
+گام ۵: دوباره همان دکمه را بزن؛ باید بگوید حکمی نیست و خطا ندهد.</t>
+        </is>
+      </c>
+      <c r="F31" s="144" t="inlineStr">
+        <is>
+          <t>حکم=۱ → دکمهٔ پاک‌کردن حکم</t>
+        </is>
+      </c>
+      <c r="G31" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="143" t="inlineStr">
+        <is>
+          <t>حکم همان لحظه پاک می‌شود؛ چهره خاموش و یک بار وصل دوباره آزاد می‌شود. زدن دوبارهٔ دکمه خطا نمی‌دهد. PASS: حکم پاک شد. FAIL: حکم ماند یا دکمه خطا داد.</t>
+        </is>
+      </c>
+      <c r="I31" s="143" t="inlineStr">
+        <is>
+          <t>PASS: حکم پاک. FAIL: حکم ماند.</t>
+        </is>
+      </c>
+      <c r="J31" s="104" t="n"/>
+      <c r="K31" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L31" s="115" t="n"/>
+      <c r="M31" s="104" t="n"/>
+      <c r="N31" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O31" s="82" t="n"/>
       <c r="P31" s="82" t="n"/>
       <c r="Q31" s="98">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$48</definedName>
@@ -1391,7 +1391,7 @@
       <c r="A2" s="83" t="inlineStr">
         <is>
           <t>ChangeOver | این ماژول فقط پایهٔ PB11 را کنترل می‌کند (BSP_GPIO_PROTECT_BATTERY).
-حدها: 21000 و 20800 و 21200 میلی‌ولت. زمان صبر: 3000 میلی‌ثانیه. نسخه 2.1.
+حدها: 21000 و 20800 و 21200 میلی‌ولت. زمان صبر: 3000 میلی‌ثانیه. آستانهٔ استراحت باتری: 25000 میلی‌ولت. نسخه 2.2.
 پایهٔ دیگری اینجا دست نمی‌خورد؛ فقط PB11.</t>
         </is>
       </c>
@@ -1728,6 +1728,28 @@
       <c r="N25" s="82" t="n"/>
       <c r="O25" s="82" t="n"/>
       <c r="P25" s="82" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>آستانهٔ استراحت باتری (شناسهٔ ۱۶۵، پیش‌فرض ۲۵٬۰۰۰ mV): زیر آن بدون برق شهر هیچ وصل و هیچ حکمی نیست. سقف تلاش بدون برق شهر یک است. حکم باتری فرسوده فقط بدون برق شهر نمایش داده می‌شود. در حالت قطع بدون برق شهر، هر سه چراغ و بوق خاموش‌اند. قطع سیم باتری بدون برق شهر بی‌صدا است. شناسه‌های تست با شیت «تست‌های آزمایشگاهی» یکسان شد و CO-031/CO-033/CO-034 اضافه شدند.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>a07719c</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="130" t="inlineStr">
@@ -1962,7 +1984,7 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="99" t="inlineStr">
         <is>
-          <t>CO-025</t>
+          <t>CO-008</t>
         </is>
       </c>
       <c r="B5" s="104" t="inlineStr">
@@ -1977,20 +1999,19 @@
       </c>
       <c r="D5" s="104" t="inlineStr">
         <is>
-          <t>دستگاه روشن، باتری وصل و یک بار (مثلاً لامپ) روی خروجی</t>
+          <t>دستگاه روشن با باتری و یک بار روی خروجی</t>
         </is>
       </c>
       <c r="E5" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را فقط با باتری روشن کن و مطمئن شو بار روشن است.
-گام ۲: ولتاژ باتری را با منبع آزمایشگاهی آرام پایین بیاور تا زیر 21 ولت برسد.
-گام ۳: چند ثانیه صبر کن و بار را نگاه کن.
-گام ۴: بار باید خاموش شود (خروجی قطع شود)؛ تا وقتی باتری بالای 21 ولت است بار نباید قطع شود.</t>
+گام ۲: ولتاژ باتری را آرام پایین بیاور تا زیر ۲۱ ولت برسد.
+گام ۳: چند ثانیه صبر کن و بار و چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
       <c r="F5" s="104" t="inlineStr">
         <is>
-          <t>باتری از 24 ولت تا زیر 21 ولت</t>
+          <t>باتری از ۲۴ ولت تا زیر ۲۱ ولت</t>
         </is>
       </c>
       <c r="G5" s="105" t="inlineStr">
@@ -2000,20 +2021,20 @@
       </c>
       <c r="H5" s="104" t="inlineStr">
         <is>
-          <t>با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع و بار خاموش می‌شود</t>
+          <t>خروجی بعد از ۳ ثانیه قطع می‌شود و بار خاموش می‌ماند</t>
         </is>
       </c>
       <c r="I5" s="104" t="inlineStr">
         <is>
           <t>باید ببینید:
-با افت باتری زیر حد، خروجی بعد از چند ثانیه قطع می‌شود و بار خاموش می‌شود.
+با افت باتری زیر حد، خروجی بعد از ۳ ثانیهٔ پیوسته قطع می‌شود و بار خاموش می‌ماند.
 تا وقتی باتری بالای حد است، بار روشن می‌ماند.
 اگر زود قطع کرد یا اصلاً قطع نکرد، قبول نیست.</t>
         </is>
       </c>
       <c r="J5" s="104" t="inlineStr">
         <is>
-          <t>بار قطع شود؛ قطع زودهنگام وقتی باتری هنوز بالای حد است = رد</t>
+          <t>بار قطع شود؛ قطع زودهنگام وقتی باتری بالای حد است = رد</t>
         </is>
       </c>
       <c r="K5" s="100" t="n"/>
@@ -2046,71 +2067,72 @@
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="99" t="inlineStr">
         <is>
-          <t>CO-026</t>
-        </is>
-      </c>
-      <c r="B6" s="143" t="inlineStr">
+          <t>CO-013</t>
+        </is>
+      </c>
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C6" s="144" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="145" t="inlineStr">
-        <is>
-          <t>پایان CO-025 (خروجی قطع است)</t>
-        </is>
-      </c>
-      <c r="E6" s="145" t="inlineStr">
-        <is>
-          <t>گام ۱: از پایان CO-025 شروع کن که خروجی قطع و بار خاموش است.
-گام ۲: برق شهر (ورودی) را وصل کن و ولتاژ باتری را به بالای 21.2 ولت برگردان (با شارژ یا منبع).
-گام ۳: چند ثانیه صبر کن.
-گام ۴: بار باید دوباره روشن شود؛ اگر ولتاژ باتری هنوز پایین است نباید وصل شود.</t>
-        </is>
-      </c>
-      <c r="F6" s="143" t="inlineStr">
-        <is>
-          <t>ورودی حاضر + باتری بالای 21.2 ولت</t>
-        </is>
-      </c>
-      <c r="G6" s="144" t="inlineStr">
-        <is>
-          <t>چند ثانیه</t>
-        </is>
-      </c>
-      <c r="H6" s="143" t="inlineStr">
-        <is>
-          <t>خروجی وصل و بار روشن می‌شود</t>
-        </is>
-      </c>
-      <c r="I6" s="143" t="inlineStr">
-        <is>
-          <t>باید ببینید: با برگشت ورودی و باتریِ کافی، خروجی وصل و بار روشن می‌شود. اگر با باتری پایین وصل شد یا اصلاً وصل نشد، قبول نیست.</t>
-        </is>
-      </c>
-      <c r="J6" s="143" t="inlineStr">
-        <is>
-          <t>بار دوباره روشن شود؛ وصل شدن با باتری پایین = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="104" t="n"/>
+      <c r="D6" s="104" t="inlineStr">
+        <is>
+          <t>پایان CO-008 (خروجی قطع است)</t>
+        </is>
+      </c>
+      <c r="E6" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: از پایان CO-008 شروع کن.
+گام ۲: برق شهر را وصل کن و ولتاژ باتری را بالای ۲۱٫۲ ولت نگه دار.
+گام ۳: ۳۵ ثانیه صبر کن و بار را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F6" s="104" t="inlineStr">
+        <is>
+          <t>برگشت برق شهر + باتری بالای ۲۱٫۲ ولت</t>
+        </is>
+      </c>
+      <c r="G6" s="105" t="inlineStr">
+        <is>
+          <t>حدود ۳۵ ثانیه</t>
+        </is>
+      </c>
+      <c r="H6" s="104" t="inlineStr">
+        <is>
+          <t>بعد از ۳۰ ثانیه ورودیِ ثابت و ۳ ثانیه فیلتر، خروجی وصل و بار روشن می‌شود</t>
+        </is>
+      </c>
+      <c r="I6" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+خروجی فقط بعد از ۳۰ ثانیه ورودیِ ثابت + ۳ ثانیه فیلتر وصل می‌شود.
+اگر زودتر وصل شد یا اصلاً وصل نشد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J6" s="104" t="inlineStr">
+        <is>
+          <t>وصل بعد از ۳۳ ثانیه؛ وصل زودتر = رد</t>
+        </is>
+      </c>
+      <c r="K6" s="100" t="n"/>
       <c r="L6" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="104" t="n"/>
-      <c r="N6" s="104" t="n"/>
-      <c r="O6" s="105" t="n"/>
-      <c r="P6" s="144">
+      <c r="M6" s="100" t="n"/>
+      <c r="N6" s="100" t="n"/>
+      <c r="O6" s="101" t="n"/>
+      <c r="P6" s="105">
         <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
         <v/>
       </c>
-      <c r="Q6" s="107" t="n"/>
+      <c r="Q6" s="103" t="n"/>
       <c r="R6" s="157">
         <f>IF($U$6=0,"داده نامعتبر: وضعیت و خروجی همان قبلی می‌ماند",IF($U$4=1,"وضعیت خطا (FAULT) و خروجی تغییر نمی‌کند",IF(AND($U$2&lt;20800,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$2&lt;21000,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$3=1,$U$2&gt;=21200,$U$5&gt;=3),"خروجی وصل روی ورودی (INPUT)",IF($U$3=1,"ورودی حاضر است؛ وصل و قطع فقط بعد از ۳ ثانیهٔ کاملِ شرط انجام می‌شود","روی باتری (BATTERY)؛ با باتری کافی خروجی وصل است"))))))</f>
         <v/>
@@ -2127,7 +2149,7 @@
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="99" t="inlineStr">
         <is>
-          <t>CO-027</t>
+          <t>CO-006</t>
         </is>
       </c>
       <c r="B7" s="104" t="inlineStr">
@@ -2137,7 +2159,7 @@
       </c>
       <c r="C7" s="105" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D7" s="104" t="inlineStr">
@@ -2147,10 +2169,9 @@
       </c>
       <c r="E7" s="104" t="inlineStr">
         <is>
-          <t>گام ۱: دستگاه را با برق شهر و باتری روشن کن و بار را روشن ببین.
-گام ۲: برق شهر را بکش؛ دستگاه نباید خاموش شود و بار باید بی‌وقفه روشن بماند (کار روی باتری).
-گام ۳: برق شهر را برگردان؛ دستگاه باید به حالت عادی برگردد و شارژ از سر گرفته شود.
-گام ۴: در هیچ‌کدام از این دو جابه‌جایی نباید دستگاه در وضعیت خطا گیر کند.</t>
+          <t>گام ۱: دستگاه را با برق شهر روشن کن و بار را روشن ببین.
+گام ۲: برق شهر را قطع کن؛ بار باید بی‌وقفه روی باتری بماند.
+گام ۳: برق شهر را برگردان و دوباره نگاه کن.</t>
         </is>
       </c>
       <c r="F7" s="104" t="inlineStr">
@@ -2165,17 +2186,19 @@
       </c>
       <c r="H7" s="104" t="inlineStr">
         <is>
-          <t>ادامهٔ بی‌وقفهٔ کار بار و برگشت عادی</t>
+          <t>بار در هر دو جابه‌جایی روشن می‌ماند و دستگاه در خطا گیر نمی‌کند</t>
         </is>
       </c>
       <c r="I7" s="104" t="inlineStr">
         <is>
-          <t>باید ببینید: با قطع و وصل برق شهر، بار هرگز خاموش نمی‌شود و دستگاه بعد از برگشت شهر عادی کار می‌کند. اگر بار لحظه‌ای هم خاموش شد، قبول نیست.</t>
+          <t>باید ببینید:
+با قطع و وصل برق شهر، بار هرگز خاموش نمی‌شود.
+اگر بار لحظه‌ای هم خاموش شد، قبول نیست.</t>
         </is>
       </c>
       <c r="J7" s="104" t="inlineStr">
         <is>
-          <t>بار هرگز خاموش نشود و دستگاه بعد از برگشت شهر عادی کار کند</t>
+          <t>بار بی‌وقفه روشن بماند</t>
         </is>
       </c>
       <c r="K7" s="100" t="n"/>
@@ -2205,321 +2228,833 @@
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="99" t="inlineStr">
         <is>
-          <t>CO-028</t>
-        </is>
-      </c>
-      <c r="B8" s="143" t="inlineStr">
+          <t>CO-018</t>
+        </is>
+      </c>
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C8" s="144" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="143" t="inlineStr">
+      <c r="D8" s="104" t="inlineStr">
         <is>
           <t>دستگاه در حال کار عادی با بار روشن</t>
         </is>
       </c>
-      <c r="E8" s="143" t="inlineStr">
+      <c r="E8" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه در حال کار عادی باشد و بار روشن.
-گام ۲: یک خطای شارژر بساز (حین شارژ سیم باتری را قطع کن تا آلارم قطع باتری بیاید).
-گام ۳: چراغ و بوق خطا را ببین و هم‌زمان بار را نگاه کن.
-گام ۴: بار نباید قطع‌ووصل یا چشمک بزند؛ خروجی باید همان وضعیت قبل از خطا را نگه دارد.</t>
-        </is>
-      </c>
-      <c r="F8" s="143" t="inlineStr">
+گام ۲: حین شارژ سیم باتری را قطع کن تا آلارم قطع باتری بیاید.
+گام ۳: چراغ و بوق خطا و هم‌زمان بار را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F8" s="104" t="inlineStr">
         <is>
           <t>خطای قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G8" s="144" t="inlineStr">
+      <c r="G8" s="105" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H8" s="143" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>آلارم خطا می‌آید ولی خروجی تکان نمی‌خورد</t>
         </is>
       </c>
-      <c r="I8" s="143" t="inlineStr">
-        <is>
-          <t>باید ببینید: آلارم خطا می‌آید ولی بار بدون هیچ تکانی روشن می‌ماند. اگر خروجی تکان خورد، قبول نیست.</t>
-        </is>
-      </c>
-      <c r="J8" s="143" t="inlineStr">
-        <is>
-          <t>بار بدون هیچ تکانی روشن بماند</t>
-        </is>
-      </c>
-      <c r="K8" s="104" t="n"/>
+      <c r="I8" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+آلارم خطا می‌آید ولی بار بدون هیچ تکانی روشن می‌ماند.
+اگر خروجی تکان خورد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J8" s="104" t="inlineStr">
+        <is>
+          <t>بار بدون تکان روشن بماند</t>
+        </is>
+      </c>
+      <c r="K8" s="100" t="n"/>
       <c r="L8" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="104" t="n"/>
-      <c r="N8" s="104" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="144">
+      <c r="M8" s="100" t="n"/>
+      <c r="N8" s="100" t="n"/>
+      <c r="O8" s="101" t="n"/>
+      <c r="P8" s="105">
         <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
         <v/>
       </c>
-      <c r="Q8" s="107" t="n"/>
+      <c r="Q8" s="103" t="n"/>
       <c r="R8" s="157">
         <f>IF($U$6=0,"داده نامعتبر: وضعیت و خروجی همان قبلی می‌ماند",IF($U$4=1,"وضعیت خطا (FAULT) و خروجی تغییر نمی‌کند",IF(AND($U$2&lt;20800,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$2&lt;21000,$U$5&gt;=3),"خروجی قطع و وضعیت امن (SAFE)",IF(AND($U$3=1,$U$2&gt;=21200,$U$5&gt;=3),"خروجی وصل روی ورودی (INPUT)",IF($U$3=1,"ورودی حاضر است؛ وصل و قطع فقط بعد از ۳ ثانیهٔ کاملِ شرط انجام می‌شود","روی باتری (BATTERY)؛ با باتری کافی خروجی وصل است"))))))</f>
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="99" t="inlineStr">
         <is>
-          <t>CO-029</t>
-        </is>
-      </c>
-      <c r="B9" s="143" t="inlineStr">
+          <t>CO-025</t>
+        </is>
+      </c>
+      <c r="B9" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی خروجی</t>
         </is>
       </c>
-      <c r="C9" s="144" t="inlineStr">
+      <c r="C9" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="143" t="inlineStr">
-        <is>
-          <t>پایان CO-025 (خروجی قطع است و برق شهر هم قطع است)</t>
-        </is>
-      </c>
-      <c r="E9" s="143" t="inlineStr">
-        <is>
-          <t>گام ۱: از پایان CO-025 شروع کن: برق شهر قطع، خروجی قطع و بار خاموش.
-گام ۲: ولتاژ باتری را به محدودهٔ سالم (بالای ۲۱٫۲ ولت) برگردان و حدود ۲۰ ثانیه صبر کن.
-گام ۳: در این مدت یک بار ولتاژ را یک لحظه زیر ۲۱٫۲ ببر و برگردان (شمارش باید از صفر شروع شود).
-گام ۴: خروجی و بار را نگاه کن؛ برق شهر را وصل نکن.</t>
-        </is>
-      </c>
-      <c r="F9" s="143" t="inlineStr">
-        <is>
-          <t>ولتاژ سالم پیوسته، بدون برق شهر</t>
-        </is>
-      </c>
-      <c r="G9" s="144" t="inlineStr">
-        <is>
-          <t>حدود ۲۰ ثانیه</t>
-        </is>
-      </c>
-      <c r="H9" s="143" t="inlineStr">
-        <is>
-          <t>خروجی حدود ۱۳ ثانیه بعد از پایدار شدن ولتاژ برمی‌گردد و بار روشن می‌ماند</t>
-        </is>
-      </c>
-      <c r="I9" s="143" t="inlineStr">
-        <is>
-          <t>باید ببینید: با باتری سالم و بدون برق شهر، خروجی حدود ۱۳ ثانیه بعد (۱۰ ثانیه پنجرهٔ سالم + ۳ ثانیه فیلتر) وصل می‌شود و بار روشن می‌ماند. اگر وسط این ۱۰ ثانیه ولتاژ یک لحظه افت کند، باید از صفر شمرده شود.
-اگر خروجی وصل نشد = رد؛ این همان ایراد گزارش‌شدهٔ ۲۰۲۶-۱۰-۲۳ است.</t>
-        </is>
-      </c>
-      <c r="J9" s="143" t="inlineStr">
-        <is>
-          <t>وصل شدن خروجی روی باتری بدون برق شهر؛ وصل نشدن یا وصلِ زودتر از ۱۰ ثانیه = رد</t>
-        </is>
-      </c>
-      <c r="K9" s="104" t="n"/>
+      <c r="D9" s="104" t="inlineStr">
+        <is>
+          <t>پایان CO-008 (خروجی قطع و برق شهر قطع است)</t>
+        </is>
+      </c>
+      <c r="E9" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: از پایان CO-008 شروع کن: برق شهر قطع، خروجی قطع، بار خاموش.
+گام ۲: ولتاژ باتری را به ۲۵٫۵ ولت برسان و حدود ۲۰ ثانیه صبر کن.
+گام ۳: در ثانیهٔ نهم وضعیت را بخوان و در ثانیهٔ چهاردهم دوباره بخوان.
+گام ۴: همین را با ۲۳٫۰ ولت تکرار کن.</t>
+        </is>
+      </c>
+      <c r="F9" s="104" t="inlineStr">
+        <is>
+          <t>بدون برق شهر: ۲۵٫۵ ولت برای ۲۰ ثانیه، سپس ۲۳٫۰ ولت</t>
+        </is>
+      </c>
+      <c r="G9" s="105" t="inlineStr">
+        <is>
+          <t>حدود ۲۰ ثانیه + ۳۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H9" s="104" t="inlineStr">
+        <is>
+          <t>با ۲۵٫۵ ولت حدود ۱۳ ثانیه بعد وصل می‌شود؛ با ۲۳ ولت هیچ وصل نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I9" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+در گام ۲ خروجی حدود ۱۳ ثانیه بعد (۱۰ ثانیهٔ سالم + ۳ ثانیه فیلتر) وصل می‌شود و بار روشن می‌ماند.
+در گام ۴ با استراحت ۲۳ ولت هیچ وصل و هیچ حکمی نمی‌شود (باتری دشارژ حساب می‌شود).
+اگر وسط ۱۰ ثانیه ولتاژ یک لحظه افت کند، شمارش از صفر شروع می‌شود.</t>
+        </is>
+      </c>
+      <c r="J9" s="104" t="inlineStr">
+        <is>
+          <t>وصل با ۲۵٫۵ ولت و عدم وصل با ۲۳ ولت؛ وصل با ۲۳ ولت = رد</t>
+        </is>
+      </c>
+      <c r="K9" s="100" t="n"/>
       <c r="L9" s="102" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="104" t="n"/>
-      <c r="N9" s="104" t="n"/>
-      <c r="O9" s="105" t="n"/>
-      <c r="P9" s="144">
+      <c r="M9" s="100" t="n"/>
+      <c r="N9" s="100" t="n"/>
+      <c r="O9" s="101" t="n"/>
+      <c r="P9" s="105">
         <f>IF(OR(K9="",K9="در انتظار"),"",IF(P9="",TODAY(),P9))</f>
         <v/>
       </c>
-      <c r="Q9" s="107" t="n"/>
+      <c r="Q9" s="103" t="n"/>
       <c r="R9" s="157" t="inlineStr">
         <is>
-          <t>بدون فرمول: با ۱۰ ثانیه ولتاژ سالمِ پیوسته و ۳ ثانیه فیلتر، خروجی بدون ورودی وصل و وضعیت BATTERY می‌شود؛ اگر بعد از این وصل ظرف ۶۰ ثانیه دوباره قطع شود، دیگر بدون برق شهر وصل نمی‌شود (محافظ چرخه).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="131" t="n"/>
-      <c r="B10" s="131" t="n"/>
-      <c r="C10" s="131" t="n"/>
-      <c r="D10" s="131" t="n"/>
-      <c r="E10" s="131" t="n"/>
-      <c r="F10" s="131" t="n"/>
-      <c r="G10" s="131" t="n"/>
-      <c r="H10" s="131" t="n"/>
-      <c r="I10" s="131" t="n"/>
-      <c r="J10" s="131" t="n"/>
-      <c r="K10" s="131" t="n"/>
-      <c r="L10" s="131" t="n"/>
-      <c r="M10" s="131" t="n"/>
-      <c r="N10" s="131" t="n"/>
-      <c r="O10" s="131" t="n"/>
-      <c r="P10" s="131" t="n"/>
-      <c r="Q10" s="132" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="131" t="n"/>
-      <c r="B11" s="131" t="n"/>
-      <c r="C11" s="131" t="n"/>
-      <c r="D11" s="131" t="n"/>
-      <c r="E11" s="131" t="n"/>
-      <c r="F11" s="131" t="n"/>
-      <c r="G11" s="131" t="n"/>
-      <c r="H11" s="131" t="n"/>
-      <c r="I11" s="131" t="n"/>
-      <c r="J11" s="131" t="n"/>
-      <c r="K11" s="131" t="n"/>
-      <c r="L11" s="131" t="n"/>
-      <c r="M11" s="131" t="n"/>
-      <c r="N11" s="131" t="n"/>
-      <c r="O11" s="131" t="n"/>
-      <c r="P11" s="131" t="n"/>
-      <c r="Q11" s="132" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="131" t="n"/>
-      <c r="B12" s="131" t="n"/>
-      <c r="C12" s="131" t="n"/>
-      <c r="D12" s="131" t="n"/>
-      <c r="E12" s="131" t="n"/>
-      <c r="F12" s="131" t="n"/>
-      <c r="G12" s="131" t="n"/>
-      <c r="H12" s="131" t="n"/>
-      <c r="I12" s="131" t="n"/>
-      <c r="J12" s="131" t="n"/>
-      <c r="K12" s="131" t="n"/>
-      <c r="L12" s="131" t="n"/>
-      <c r="M12" s="131" t="n"/>
-      <c r="N12" s="131" t="n"/>
-      <c r="O12" s="131" t="n"/>
-      <c r="P12" s="131" t="n"/>
-      <c r="Q12" s="132" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="131" t="n"/>
-      <c r="B13" s="131" t="n"/>
-      <c r="C13" s="131" t="n"/>
-      <c r="D13" s="131" t="n"/>
-      <c r="E13" s="131" t="n"/>
-      <c r="F13" s="131" t="n"/>
-      <c r="G13" s="131" t="n"/>
-      <c r="H13" s="131" t="n"/>
-      <c r="I13" s="131" t="n"/>
-      <c r="J13" s="131" t="n"/>
-      <c r="K13" s="131" t="n"/>
-      <c r="L13" s="131" t="n"/>
-      <c r="M13" s="131" t="n"/>
-      <c r="N13" s="131" t="n"/>
-      <c r="O13" s="131" t="n"/>
-      <c r="P13" s="131" t="n"/>
-      <c r="Q13" s="132" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="131" t="n"/>
-      <c r="B14" s="131" t="n"/>
-      <c r="C14" s="131" t="n"/>
-      <c r="D14" s="131" t="n"/>
-      <c r="E14" s="131" t="n"/>
-      <c r="F14" s="131" t="n"/>
-      <c r="G14" s="131" t="n"/>
-      <c r="H14" s="131" t="n"/>
-      <c r="I14" s="131" t="n"/>
-      <c r="J14" s="131" t="n"/>
-      <c r="K14" s="131" t="n"/>
-      <c r="L14" s="131" t="n"/>
-      <c r="M14" s="131" t="n"/>
-      <c r="N14" s="131" t="n"/>
-      <c r="O14" s="131" t="n"/>
-      <c r="P14" s="131" t="n"/>
-      <c r="Q14" s="132" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="131" t="n"/>
-      <c r="B15" s="131" t="n"/>
-      <c r="C15" s="131" t="n"/>
-      <c r="D15" s="131" t="n"/>
-      <c r="E15" s="131" t="n"/>
-      <c r="F15" s="131" t="n"/>
-      <c r="G15" s="131" t="n"/>
-      <c r="H15" s="131" t="n"/>
-      <c r="I15" s="131" t="n"/>
-      <c r="J15" s="131" t="n"/>
-      <c r="K15" s="131" t="n"/>
-      <c r="L15" s="131" t="n"/>
-      <c r="M15" s="131" t="n"/>
-      <c r="N15" s="131" t="n"/>
-      <c r="O15" s="131" t="n"/>
-      <c r="P15" s="131" t="n"/>
-      <c r="Q15" s="132" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="131" t="n"/>
-      <c r="B16" s="131" t="n"/>
-      <c r="C16" s="131" t="n"/>
-      <c r="D16" s="131" t="n"/>
-      <c r="E16" s="131" t="n"/>
-      <c r="F16" s="131" t="n"/>
-      <c r="G16" s="131" t="n"/>
-      <c r="H16" s="131" t="n"/>
-      <c r="I16" s="131" t="n"/>
-      <c r="J16" s="131" t="n"/>
-      <c r="K16" s="131" t="n"/>
-      <c r="L16" s="131" t="n"/>
-      <c r="M16" s="131" t="n"/>
-      <c r="N16" s="131" t="n"/>
-      <c r="O16" s="131" t="n"/>
-      <c r="P16" s="131" t="n"/>
-      <c r="Q16" s="132" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="131" t="n"/>
-      <c r="B17" s="131" t="n"/>
-      <c r="C17" s="131" t="n"/>
-      <c r="D17" s="131" t="n"/>
-      <c r="E17" s="131" t="n"/>
-      <c r="F17" s="131" t="n"/>
-      <c r="G17" s="131" t="n"/>
-      <c r="H17" s="131" t="n"/>
-      <c r="I17" s="131" t="n"/>
-      <c r="J17" s="131" t="n"/>
-      <c r="K17" s="131" t="n"/>
-      <c r="L17" s="131" t="n"/>
-      <c r="M17" s="131" t="n"/>
-      <c r="N17" s="131" t="n"/>
-      <c r="O17" s="131" t="n"/>
-      <c r="P17" s="131" t="n"/>
-      <c r="Q17" s="132" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="131" t="n"/>
-      <c r="B18" s="131" t="n"/>
-      <c r="C18" s="131" t="n"/>
-      <c r="D18" s="131" t="n"/>
-      <c r="E18" s="131" t="n"/>
-      <c r="F18" s="131" t="n"/>
-      <c r="G18" s="131" t="n"/>
-      <c r="H18" s="131" t="n"/>
-      <c r="I18" s="131" t="n"/>
-      <c r="J18" s="131" t="n"/>
-      <c r="K18" s="131" t="n"/>
-      <c r="L18" s="131" t="n"/>
-      <c r="M18" s="131" t="n"/>
-      <c r="N18" s="131" t="n"/>
-      <c r="O18" s="131" t="n"/>
-      <c r="P18" s="131" t="n"/>
-      <c r="Q18" s="132" t="n"/>
+          <t>بدون فرمول: آستانهٔ استراحت شناسهٔ ۱۶۵ (۲۵٬۰۰۰ mV) اجازهٔ وصل بدون برق شهر را می‌دهد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>CO-026</t>
+        </is>
+      </c>
+      <c r="B10" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C10" s="105" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D10" s="104" t="inlineStr">
+        <is>
+          <t>پس از وصل CO-025</t>
+        </is>
+      </c>
+      <c r="E10" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: بعد از وصل CO-025، داخل ۶۰ ثانیه ولتاژ را زیر ۲۱ ولت بیاور تا قطع شود.
+گام ۲: ولتاژ را به ۲۵٫۵ ولت برگردان و ۶۰ ثانیه صبر کن.
+گام ۳: مسیر باتری، چراغ‌ها و بوق را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F10" s="104" t="inlineStr">
+        <is>
+          <t>قطع داخل ۶۰ ثانیه بعد از CO-025، سپس ۲۵٫۵ ولت</t>
+        </is>
+      </c>
+      <c r="G10" s="105" t="inlineStr">
+        <is>
+          <t>۳۰ ثانیه + ۶۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H10" s="104" t="inlineStr">
+        <is>
+          <t>حکم باتری فرسوده قفل می‌شود و مسیر باتری تا برگشت برق شهر بسته می‌ماند</t>
+        </is>
+      </c>
+      <c r="I10" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+بعد از قطع دوباره، حکم قفل است و بدون برق شهر هیچ وصل خودکار دیگری انجام نمی‌شود (سقف یک تلاش).
+با برگشت برق شهر، مسیر از راه ورودی باز می‌شود.</t>
+        </is>
+      </c>
+      <c r="J10" s="104" t="inlineStr">
+        <is>
+          <t>قفل حکم؛ وصل خودکار دوباره بدون برق شهر = رد</t>
+        </is>
+      </c>
+      <c r="K10" s="100" t="n"/>
+      <c r="L10" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M10" s="100" t="n"/>
+      <c r="N10" s="100" t="n"/>
+      <c r="O10" s="101" t="n"/>
+      <c r="P10" s="105">
+        <f>IF(OR(K10="",K10="در انتظار"),"",IF(P10="",TODAY(),P10))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="103" t="n"/>
+      <c r="R10" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: سقف تلاش بدون برق شهر یک است؛ حکم با ۱۰ دقیقه سالم یا دکمهٔ کارت ۸ پاک می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>CO-027</t>
+        </is>
+      </c>
+      <c r="B11" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C11" s="105" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D11" s="104" t="inlineStr">
+        <is>
+          <t>حکم قفل (پس از CO-026)</t>
+        </is>
+      </c>
+      <c r="E11" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل و برق شهر قطع، قرمز را ۵ ثانیه نگاه کن.
+گام ۲: گوش کن و الگوی بوق را بشمار.
+گام ۳: برق شهر را وصل کن و همان دو چراغ و بوق را دوباره نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F11" s="104" t="inlineStr">
+        <is>
+          <t>پارامترهای ۱۵۱ تا ۱۵۶ با پیش‌فرض کارخانه</t>
+        </is>
+      </c>
+      <c r="G11" s="105" t="inlineStr">
+        <is>
+          <t>۵ ثانیه + ۱۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H11" s="104" t="inlineStr">
+        <is>
+          <t>بدون برق شهر: قرمز چشمک‌زن + بوق، سبز و زرد خاموش؛ با برق شهر: چهرهٔ شارژ عادی</t>
+        </is>
+      </c>
+      <c r="I11" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+بدون برق شهر قرمز با دوره و سهم خودش چشمک می‌زند و بوق الگوی خودش را دارد؛ سبز و زرد خاموش‌اند.
+با برگشت برق شهر چهرهٔ شارژ (زرد چشمک‌زن یا سبز ثابت) می‌آید و بوق قطع می‌شود.</t>
+        </is>
+      </c>
+      <c r="J11" s="104" t="inlineStr">
+        <is>
+          <t>همان چهرهٔ تعریف‌شده بدون برق شهر و چهرهٔ شارژ با برق شهر</t>
+        </is>
+      </c>
+      <c r="K11" s="100" t="n"/>
+      <c r="L11" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M11" s="100" t="n"/>
+      <c r="N11" s="100" t="n"/>
+      <c r="O11" s="101" t="n"/>
+      <c r="P11" s="105">
+        <f>IF(OR(K11="",K11="در انتظار"),"",IF(P11="",TODAY(),P11))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="103" t="n"/>
+      <c r="R11" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: نمایش حکم فقط بدون برق ورودی است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>CO-028</t>
+        </is>
+      </c>
+      <c r="B12" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C12" s="105" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D12" s="104" t="inlineStr">
+        <is>
+          <t>حکم قفل، شناسهٔ ۱۵۷ = ۱</t>
+        </is>
+      </c>
+      <c r="E12" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل و برق شهر قطع، خروجی را با بار ۱ آمپر بسنج.
+گام ۲: حالا شناسهٔ ۱۵۷ را صفر کن و خروجی را دوباره بسنج.
+گام ۳: شناسه را به ۱ برگردان.</t>
+        </is>
+      </c>
+      <c r="F12" s="104" t="inlineStr">
+        <is>
+          <t>۱۵۷ = ۱ سپس ۰ سپس ۱</t>
+        </is>
+      </c>
+      <c r="G12" s="105" t="inlineStr">
+        <is>
+          <t>۳۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H12" s="104" t="inlineStr">
+        <is>
+          <t>با ۱۵۷ = ۱ مسیر بسته می‌ماند؛ با ۱۵۷ = ۰ فقط هشدار می‌ماند و مسیر باز می‌شود</t>
+        </is>
+      </c>
+      <c r="I12" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+با ۱۵۷ = ۱ خروجی صفر می‌ماند و بار روشن نمی‌شود.
+با ۱۵۷ = ۰ چراغ هشدار می‌ماند ولی مسیر باتری باز می‌شود.</t>
+        </is>
+      </c>
+      <c r="J12" s="104" t="inlineStr">
+        <is>
+          <t>تبعیت دقیق از ۱۵۷؛ بار روی باتری با ۱۵۷ = ۱ = رد</t>
+        </is>
+      </c>
+      <c r="K12" s="100" t="n"/>
+      <c r="L12" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M12" s="100" t="n"/>
+      <c r="N12" s="100" t="n"/>
+      <c r="O12" s="101" t="n"/>
+      <c r="P12" s="105">
+        <f>IF(OR(K12="",K12="در انتظار"),"",IF(P12="",TODAY(),P12))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="103" t="n"/>
+      <c r="R12" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: شناسهٔ ۱۵۷ تعیین می‌کند حکم مسیر را ببندد یا فقط هشدار بدهد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>CO-029</t>
+        </is>
+      </c>
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C13" s="105" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D13" s="104" t="inlineStr">
+        <is>
+          <t>حکم قفل، شناسهٔ ۱۴۸ = ۶۰۰۰۰۰</t>
+        </is>
+      </c>
+      <c r="E13" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل، ولتاژ باتری را روی ۲۵٫۵ ولت پیوسته نگه دار.
+گام ۲: در دقیقهٔ ۹ وضعیت را بخوان.
+گام ۳: در دقیقهٔ ۱۱ دوباره بخوان و چراغ‌ها را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F13" s="104" t="inlineStr">
+        <is>
+          <t>۲۵٫۵ ولت پیوسته برای ۱۰ دقیقه</t>
+        </is>
+      </c>
+      <c r="G13" s="105" t="inlineStr">
+        <is>
+          <t>۱۰ دقیقه</t>
+        </is>
+      </c>
+      <c r="H13" s="104" t="inlineStr">
+        <is>
+          <t>حکم فقط بعد از ۱۰ دقیقهٔ سالمِ پیوسته پاک می‌شود و همان یک تلاش آزاد می‌شود</t>
+        </is>
+      </c>
+      <c r="I13" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+تا دقیقهٔ ۹ حکم قفل است و قرمز چشمک می‌زند.
+بعد از ۱۰ دقیقهٔ سالمِ پیوسته حکم پاک می‌شود و یک بار دیگر می‌تواند بدون برق شهر وصل شود.</t>
+        </is>
+      </c>
+      <c r="J13" s="104" t="inlineStr">
+        <is>
+          <t>پاک‌شدن در دقیقهٔ ۱۰؛ زودتر یا هرگز = رد</t>
+        </is>
+      </c>
+      <c r="K13" s="100" t="n"/>
+      <c r="L13" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M13" s="100" t="n"/>
+      <c r="N13" s="100" t="n"/>
+      <c r="O13" s="101" t="n"/>
+      <c r="P13" s="105">
+        <f>IF(OR(K13="",K13="در انتظار"),"",IF(P13="",TODAY(),P13))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="103" t="n"/>
+      <c r="R13" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: مدت استراحت سالم شناسهٔ ۱۴۸ (پیش‌فرض ۶۰۰٬۰۰۰ ms) است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="99" t="inlineStr">
+        <is>
+          <t>CO-030</t>
+        </is>
+      </c>
+      <c r="B14" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C14" s="105" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D14" s="104" t="inlineStr">
+        <is>
+          <t>حکم قفل</t>
+        </is>
+      </c>
+      <c r="E14" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: با حکم قفل، برق شهر را وصل کن و ۳۰ ثانیه پایدار نگه دار.
+گام ۲: مسیر باتری و چراغ‌ها را نگاه کن.
+گام ۳: برق شهر را دوباره قطع کن.</t>
+        </is>
+      </c>
+      <c r="F14" s="104" t="inlineStr">
+        <is>
+          <t>برگشت برق شهر برای ۳۰ ثانیه، سپس قطع</t>
+        </is>
+      </c>
+      <c r="G14" s="105" t="inlineStr">
+        <is>
+          <t>۳۵ ثانیه + ۱۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H14" s="104" t="inlineStr">
+        <is>
+          <t>برگشت برق شهر حکم را پاک نمی‌کند؛ با قطع دوباره همان چهره برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I14" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+با برق شهر، چهرهٔ شارژ می‌آید و خروجی بعد از ۳۰ + ۳ ثانیه وصل می‌شود.
+با قطع دوبارهٔ برق شهر، قرمز چشمک‌زن و بوق برمی‌گردند و مسیر باتری بسته می‌ماند.
+حکم فقط با ۱۰ دقیقهٔ سالم یا دکمهٔ کارت ۸ پاک می‌شود.</t>
+        </is>
+      </c>
+      <c r="J14" s="104" t="inlineStr">
+        <is>
+          <t>حکم پس از برق شهر می‌ماند؛ پاک شدن با برق شهر = رد</t>
+        </is>
+      </c>
+      <c r="K14" s="100" t="n"/>
+      <c r="L14" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M14" s="100" t="n"/>
+      <c r="N14" s="100" t="n"/>
+      <c r="O14" s="101" t="n"/>
+      <c r="P14" s="105">
+        <f>IF(OR(K14="",K14="در انتظار"),"",IF(P14="",TODAY(),P14))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="103" t="n"/>
+      <c r="R14" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: نمایش حکم فقط بدون برق ورودی است؛ خود حکم تا پایان استراحت می‌ماند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="99" t="inlineStr">
+        <is>
+          <t>CO-031</t>
+        </is>
+      </c>
+      <c r="B15" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C15" s="105" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D15" s="104" t="inlineStr">
+        <is>
+          <t>دستگاه بدون برق شهر و مسیر باتری بسته</t>
+        </is>
+      </c>
+      <c r="E15" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: بگذار باتری زیر ۲۱ ولت برود تا مسیر بسته شود.
+گام ۲: ولتاژ را روی ۲۳٫۰ ولت نگه دار و ۶۰ ثانیه نگاه کن.
+گام ۳: ولتاژ را به ۲۵٫۵ ولت برسان و ۲۰ ثانیه نگاه کن.
+گام ۴: داخل ۶۰ ثانیه بعد از وصل، دوباره زیر ۲۱ ولت بیاور.</t>
+        </is>
+      </c>
+      <c r="F15" s="104" t="inlineStr">
+        <is>
+          <t>استراحت ۲۳ ولت، سپس ۲۵٫۵ ولت، بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="G15" s="105" t="inlineStr">
+        <is>
+          <t>حدود دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H15" s="104" t="inlineStr">
+        <is>
+          <t>با ۲۳ ولت هیچ وصل و هیچ حکمی نمی‌شود؛ با ۲۵٫۵ ولت یک بار وصل و با قطع دوباره حکم قفل می‌شود</t>
+        </is>
+      </c>
+      <c r="I15" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+در گام ۲ هیچ وصل خودکاری انجام نمی‌شود و حکمی هم زده نمی‌شود (محافظت باتری، مستقل از تیک سناریو).
+در گام ۳ فقط یک بار وصل می‌شود.
+در گام ۴ دوباره وصل نمی‌شود و حکم باتری فرسوده قفل می‌شود.</t>
+        </is>
+      </c>
+      <c r="J15" s="104" t="inlineStr">
+        <is>
+          <t>عدم وصل با ۲۳ ولت + یک تلاش با ۲۵٫۵ ولت؛ وصل با ۲۳ ولت = رد</t>
+        </is>
+      </c>
+      <c r="K15" s="100" t="n"/>
+      <c r="L15" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M15" s="100" t="n"/>
+      <c r="N15" s="100" t="n"/>
+      <c r="O15" s="101" t="n"/>
+      <c r="P15" s="105">
+        <f>IF(OR(K15="",K15="در انتظار"),"",IF(P15="",TODAY(),P15))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="103" t="n"/>
+      <c r="R15" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: آستانهٔ استراحت شناسهٔ ۱۶۵ هم برای اجازهٔ وصل و هم برای حکم استفاده می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="99" t="inlineStr">
+        <is>
+          <t>CO-032</t>
+        </is>
+      </c>
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C16" s="105" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D16" s="104" t="inlineStr">
+        <is>
+          <t>حکم قفل + پنل کالیبراسیون باز</t>
+        </is>
+      </c>
+      <c r="E16" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: روی برد حکم را قفل کن.
+گام ۲: در کارت ۸ دکمهٔ پاک‌کردن حکم را بزن.
+گام ۳: خط وضعیت، چراغ قرمز و بوق را نگاه کن.
+گام ۴: همان دکمه را دوباره بزن.</t>
+        </is>
+      </c>
+      <c r="F16" s="104" t="inlineStr">
+        <is>
+          <t>حکم = ۱ → دکمهٔ پاک‌کردن حکم (شناسهٔ ۲۰۴)</t>
+        </is>
+      </c>
+      <c r="G16" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="104" t="inlineStr">
+        <is>
+          <t>حکم همان لحظه پاک می‌شود، چراغ و بوق خاموش می‌شوند و یک تلاش آزاد می‌شود</t>
+        </is>
+      </c>
+      <c r="I16" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+خط وضعیت «در حال ارسال…» و بعد «پاک شد» نشان می‌دهد.
+قرمز و بوق خاموش می‌شوند و با استراحت بالای ۲۵ ولت یک بار دیگر وصل می‌شود.
+زدن دوبارهٔ دکمه خطا نمی‌دهد؛ خود ریست پین را دست نمی‌زند.</t>
+        </is>
+      </c>
+      <c r="J16" s="104" t="inlineStr">
+        <is>
+          <t>حکم پاک شود و دکمهٔ دوم خطا ندهد</t>
+        </is>
+      </c>
+      <c r="K16" s="100" t="n"/>
+      <c r="L16" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M16" s="100" t="n"/>
+      <c r="N16" s="100" t="n"/>
+      <c r="O16" s="101" t="n"/>
+      <c r="P16" s="105">
+        <f>IF(OR(K16="",K16="در انتظار"),"",IF(P16="",TODAY(),P16))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="103" t="n"/>
+      <c r="R16" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: شناسهٔ ۲۰۴ دستور است، نه پارامتر؛ ذخیره نمی‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="99" t="inlineStr">
+        <is>
+          <t>CO-033</t>
+        </is>
+      </c>
+      <c r="B17" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C17" s="105" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D17" s="104" t="inlineStr">
+        <is>
+          <t>دستگاه بدون برق شهر و مسیر باتری بسته</t>
+        </is>
+      </c>
+      <c r="E17" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: بگذار باتری زیر ۲۱ ولت برود تا مسیر بسته شود.
+گام ۲: هر سه چراغ و بوق را ۱۰ ثانیه نگاه کن.
+گام ۳: برق شهر را برگردان و دوباره نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F17" s="104" t="inlineStr">
+        <is>
+          <t>قطع ولتاژ پایین، بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="G17" s="105" t="inlineStr">
+        <is>
+          <t>۱۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H17" s="104" t="inlineStr">
+        <is>
+          <t>در حالت قطع، هر سه چراغ و بوق کاملاً خاموش‌اند؛ با برگشت برق، چهرهٔ شارژ برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I17" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+بعد از قطع، هیچ چراغی چشمک نمی‌زند و بوق صدا نمی‌دهد.
+با برگشت برق شهر، چهرهٔ شارژ عادی برمی‌گردد.</t>
+        </is>
+      </c>
+      <c r="J17" s="104" t="inlineStr">
+        <is>
+          <t>خاموشی کامل چراغ‌ها و بوق؛ روشن‌ماندن هر چراغ = رد</t>
+        </is>
+      </c>
+      <c r="K17" s="100" t="n"/>
+      <c r="L17" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="100" t="n"/>
+      <c r="N17" s="100" t="n"/>
+      <c r="O17" s="101" t="n"/>
+      <c r="P17" s="105">
+        <f>IF(OR(K17="",K17="در انتظار"),"",IF(P17="",TODAY(),P17))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="103" t="n"/>
+      <c r="R17" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: خاموشی فقط وقتی است که مسیر بسته است و برق ورودی نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="99" t="inlineStr">
+        <is>
+          <t>CO-034</t>
+        </is>
+      </c>
+      <c r="B18" s="104" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی خروجی</t>
+        </is>
+      </c>
+      <c r="C18" s="105" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D18" s="104" t="inlineStr">
+        <is>
+          <t>دستگاه بدون برق شهر و مسیر باتری وصل</t>
+        </is>
+      </c>
+      <c r="E18" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: برق شهر را قطع کن و مطمئن شو بار از باتری کار می‌کند.
+گام ۲: سیم باتری را جدا کن.
+گام ۳: چند ثانیه چراغ‌ها و بوق را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F18" s="104" t="inlineStr">
+        <is>
+          <t>قطع سیم باتری، بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="G18" s="105" t="inlineStr">
+        <is>
+          <t>چند ثانیه</t>
+        </is>
+      </c>
+      <c r="H18" s="104" t="inlineStr">
+        <is>
+          <t>مسیر بعد از ۳ ثانیه بسته می‌شود، همه‌چیز خاموش می‌ماند و هیچ آلارمی نمی‌آید</t>
+        </is>
+      </c>
+      <c r="I18" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید:
+قطع سیم بدون برق شهر هیچ آلارمی نمی‌دهد و همه‌چیز خاموش است تا برگشت برق ورودی.
+این تصمیم ثبت‌شدهٔ ۲۰۲۶-۱۰-۲۳ است.</t>
+        </is>
+      </c>
+      <c r="J18" s="104" t="inlineStr">
+        <is>
+          <t>سکوت کامل و عدم آلارم؛ روشن‌شدن چراغ یا بوق = رد</t>
+        </is>
+      </c>
+      <c r="K18" s="100" t="n"/>
+      <c r="L18" s="102" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="100" t="n"/>
+      <c r="N18" s="100" t="n"/>
+      <c r="O18" s="101" t="n"/>
+      <c r="P18" s="105">
+        <f>IF(OR(K18="",K18="در انتظار"),"",IF(P18="",TODAY(),P18))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="103" t="n"/>
+      <c r="R18" s="157" t="inlineStr">
+        <is>
+          <t>بدون فرمول: آلارم قطع باتری عمداً فقط با برق ورودی کار می‌کند.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="131" t="n"/>
@@ -4707,15 +5242,15 @@
       <c r="E25" s="145" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا باتری قطع شود و برد در SAFE باشد؛ برق شهر قطع بماند.
-گام ۲: ولتاژ باتری را با یک منبع روی 21500 mV نگه دار.
+گام ۲: ولتاژ باتری را با یک منبع روی 25500 mV نگه دار (بالای آستانهٔ استراحت ۲۵٬۰۰۰).
 گام ۳: در ثانیهٔ ۹ وضعیت را بخوان: باید هنوز SAFE و PB11 قطع باشد.
-گام ۴: در ثانیهٔ ۱۰ با ۳ ثانیه فیلتر، بعد از حدود ۱۳ ثانیه باید PB11 وصل و وضعیت BATTERY شود.
+گام ۴: در ثانیهٔ ۱۴ دوباره بخوان: باید PB11 وصل و وضعیت BATTERY باشد.
 گام ۵: وصل زودتر از ۱۰ ثانیهٔ پیوسته یعنی رد.</t>
         </is>
       </c>
       <c r="F25" s="144" t="inlineStr">
         <is>
-          <t>input=false, v=21500 برای ۱۳ ثانیه</t>
+          <t>input=false, v=25500 برای ۱۳ ثانیه</t>
         </is>
       </c>
       <c r="G25" s="144" t="inlineStr">
@@ -4725,7 +5260,7 @@
       </c>
       <c r="H25" s="143" t="inlineStr">
         <is>
-          <t>قبل از ۱۰ ثانیه SAFE می‌ماند؛ پس از ۱۰ ثانیه سالمِ پیوسته + ۳ ثانیه فیلتر، PB11 وصل و state=BATTERY. PASS: وصل فقط پس از ۱۰ ثانیه پیوسته. FAIL: وصل زودتر.</t>
+          <t>قبل از ۱۰ ثانیه SAFE می‌ماند؛ پس از ۱۰ ثانیه سالمِ پیوسته + ۳ ثانیه فیلتر، PB11 وصل و state=BATTERY. استراحت زیر ۲۵٬۰۰۰ mV اجازهٔ وصل نمی‌دهد (تست CO-031). PASS: وصل فقط پس از ۱۰ ثانیه پیوسته. FAIL: وصل زودتر.</t>
         </is>
       </c>
       <c r="I25" s="143" t="inlineStr">
@@ -4777,15 +5312,14 @@
       <c r="E26" s="145" t="inlineStr">
         <is>
           <t>گام ۱: بعد از وصلِ CO-025، داخل ۶۰ ثانیه ولتاژ باتری را زیر 21000 mV بیاور تا قطع رخ دهد.
-گام ۲: ولتاژ را دوباره به 21500 mV برگردان و ۳۰ ثانیه صبر کن.
-گام ۳: برد نباید بدون برق شهر وصل شود؛ باید در SAFE بماند.
-گام ۴: حالا برق شهر را وصل کن و ۳۰ ثانیه پایدار نگه دار.
-گام ۵: فقط پس از برگشت برق شهر باید وصل شود؛ وصل خودکار بدون برق شهر یعنی رد.</t>
+گام ۲: ولتاژ را دوباره به 25500 mV برگردان و ۶۰ ثانیه صبر کن.
+گام ۳: برد نباید بدون برق شهر وصل شود؛ باید در SAFE بماند و حکم باتری فرسوده قفل شود.
+گام ۴: سقف تلاش بدون برق شهر یک است؛ تلاش دوم نباید انجام شود.</t>
         </is>
       </c>
       <c r="F26" s="144" t="inlineStr">
         <is>
-          <t>قطع داخل ۶۰ ثانیه بعد از CO-025، سپس v=21500</t>
+          <t>قطع داخل ۶۰ ثانیه بعد از CO-025، سپس v=25500</t>
         </is>
       </c>
       <c r="G26" s="144" t="inlineStr">
@@ -4795,7 +5329,7 @@
       </c>
       <c r="H26" s="143" t="inlineStr">
         <is>
-          <t>حکم باتری ضعیف قفل می‌شود، مسیر باتری بسته می‌ماند و وصل خودکار بدون برق شهر انجام نمی‌شود؛ با برگشت برق شهر وصل مجاز است. PASS: قفل محافظ چرخه. FAIL: وصل خودکار بدون برق شهر.</t>
+          <t>حکم باتری فرسوده قفل می‌شود، مسیر باتری بسته می‌ماند و وصل خودکار بدون برق شهر انجام نمی‌شود (سقف یک تلاش)؛ با برگشت برق شهر وصل مجاز است. PASS: قفل محافظ چرخه. FAIL: وصل خودکار بدون برق شهر.</t>
         </is>
       </c>
       <c r="I26" s="143" t="inlineStr">
@@ -4986,16 +5520,14 @@
       </c>
       <c r="E29" s="145" t="inlineStr">
         <is>
-          <t>گام ۱: با حکم قفل، ولتاژ باتری را روی 21500 mV و پیوسته نگه دار.
+          <t>گام ۱: با حکم قفل، ولتاژ باتری را روی 25500 mV و پیوسته نگه دار.
 گام ۲: در دقیقهٔ ۹ وضعیت را بخوان: حکم باید هنوز قفل و قرمز چشمک‌زن باشد.
-گام ۳: پس از ۱۰ دقیقهٔ پیوسته، حکم باید خودش پاک شود و یک بار تلاش مجدد انجام شود.
-گام ۴: اگر داخل این ۱۰ دقیقه ولتاژ یک لحظه افت کند، شمارش باید از صفر شروع شود.
-گام ۵: پاک‌شدن زودتر از ۱۰ دقیقه یا پاک‌نشدن یعنی رد.</t>
+گام ۳: پس از ۱۰ دقیقهٔ پیوسته، حکم باید خودش پاک شود و یک بار دیگر تلاش مجاز باشد.</t>
         </is>
       </c>
       <c r="F29" s="144" t="inlineStr">
         <is>
-          <t>v=21500 پیوسته برای ۱۰ دقیقه</t>
+          <t>v=25500 پیوسته برای ۱۰ دقیقه</t>
         </is>
       </c>
       <c r="G29" s="144" t="inlineStr">
@@ -5105,25 +5637,95 @@
     <row r="31" ht="54" customHeight="1">
       <c r="A31" s="99" t="inlineStr">
         <is>
+          <t>CO-031</t>
+        </is>
+      </c>
+      <c r="B31" s="143" t="inlineStr">
+        <is>
+          <t>آستانهٔ استراحت ۲۵٬۰۰۰ mV / بستهٔ دشارژ وصل نمی‌شود</t>
+        </is>
+      </c>
+      <c r="C31" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D31" s="143" t="inlineStr">
+        <is>
+          <t>برد در SAFE، برق شهر قطع، خروجی قطع</t>
+        </is>
+      </c>
+      <c r="E31" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: از تست CO-008 شروع کن تا خروجی قطع شود.
+گام ۲: ولتاژ را روی 23000 mV نگه دار و ۶۰ ثانیه بمان.
+گام ۳: PB11 و چهرهٔ LED را بخوان: باید بسته و خاموش بماند و حکمی زده نشود.
+گام ۴: ولتاژ را به 25500 mV برسان؛ بعد از حدود ۱۳ ثانیه باید یک بار وصل شود.
+گام ۵: داخل ۶۰ ثانیه دوباره زیر 21000 mV بیاور؛ باید حکم قفل شود.</t>
+        </is>
+      </c>
+      <c r="F31" s="144" t="inlineStr">
+        <is>
+          <t>input=false، v=23000 سپس 25500 سپس قطع دوباره</t>
+        </is>
+      </c>
+      <c r="G31" s="144" t="inlineStr">
+        <is>
+          <t>۶۰s + ۲۰s + ۶۰s</t>
+        </is>
+      </c>
+      <c r="H31" s="143" t="inlineStr">
+        <is>
+          <t>با استراحت ۲۳ ولت هیچ وصل و هیچ حکمی نمی‌شود؛ با ۲۵٫۵ ولت فقط یک بار وصل می‌شود و قطع دوباره حکم را قفل می‌کند. PASS: عدم وصل با ۲۳ ولت + یک تلاش با ۲۵٫۵ ولت. FAIL: وصل با ۲۳ ولت یا تلاش دوم.</t>
+        </is>
+      </c>
+      <c r="I31" s="143" t="inlineStr">
+        <is>
+          <t>PASS: ۲۳ ولت بدون وصل، ۲۵٫۵ ولت یک تلاش. FAIL: وصل با ۲۳ ولت.</t>
+        </is>
+      </c>
+      <c r="J31" s="104" t="n"/>
+      <c r="K31" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L31" s="115" t="n"/>
+      <c r="M31" s="104" t="n"/>
+      <c r="N31" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="O31" s="82" t="n"/>
+      <c r="P31" s="82" t="n"/>
+      <c r="Q31" s="98">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="99" t="inlineStr">
+        <is>
           <t>CO-032</t>
         </is>
       </c>
-      <c r="B31" s="143" t="inlineStr">
+      <c r="B32" s="143" t="inlineStr">
         <is>
           <t>حکم باتری ضعیف / پاک‌کردن دستی از پنل</t>
         </is>
       </c>
-      <c r="C31" s="147" t="inlineStr">
+      <c r="C32" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D31" s="143" t="inlineStr">
+      <c r="D32" s="143" t="inlineStr">
         <is>
           <t>حکم قفل + پنل کالیبراسیون باز</t>
         </is>
       </c>
-      <c r="E31" s="145" t="inlineStr">
+      <c r="E32" s="145" t="inlineStr">
         <is>
           <t>گام ۱: روی برد حکم را قفل کن: بدون برق شهر وصل شود و داخل پنجرهٔ محافظ دوباره قطع شود.
 گام ۲: در کارت ۸ دکمهٔ «پاک‌کردن حکم» را بزن و تأیید کن.
@@ -5132,61 +5734,39 @@
 گام ۵: دوباره همان دکمه را بزن؛ باید بگوید حکمی نیست و خطا ندهد.</t>
         </is>
       </c>
-      <c r="F31" s="144" t="inlineStr">
+      <c r="F32" s="144" t="inlineStr">
         <is>
           <t>حکم=۱ → دکمهٔ پاک‌کردن حکم</t>
         </is>
       </c>
-      <c r="G31" s="144" t="inlineStr">
+      <c r="G32" s="144" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="143" t="inlineStr">
+      <c r="H32" s="143" t="inlineStr">
         <is>
           <t>حکم همان لحظه پاک می‌شود؛ چهره خاموش و یک بار وصل دوباره آزاد می‌شود. زدن دوبارهٔ دکمه خطا نمی‌دهد. PASS: حکم پاک شد. FAIL: حکم ماند یا دکمه خطا داد.</t>
         </is>
       </c>
-      <c r="I31" s="143" t="inlineStr">
+      <c r="I32" s="143" t="inlineStr">
         <is>
           <t>PASS: حکم پاک. FAIL: حکم ماند.</t>
         </is>
       </c>
-      <c r="J31" s="104" t="n"/>
-      <c r="K31" s="143" t="inlineStr">
+      <c r="J32" s="104" t="n"/>
+      <c r="K32" s="143" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L31" s="115" t="n"/>
-      <c r="M31" s="104" t="n"/>
-      <c r="N31" s="143" t="inlineStr">
+      <c r="L32" s="115" t="n"/>
+      <c r="M32" s="104" t="n"/>
+      <c r="N32" s="143" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="O31" s="82" t="n"/>
-      <c r="P31" s="82" t="n"/>
-      <c r="Q31" s="98">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="82" t="n"/>
-      <c r="B32" s="82" t="n"/>
-      <c r="C32" s="82" t="n"/>
-      <c r="D32" s="82" t="n"/>
-      <c r="E32" s="82" t="n"/>
-      <c r="F32" s="82" t="n"/>
-      <c r="G32" s="82" t="n"/>
-      <c r="H32" s="82" t="n"/>
-      <c r="I32" s="82" t="n"/>
-      <c r="J32" s="82" t="n"/>
-      <c r="K32" s="82" t="n"/>
-      <c r="L32" s="82" t="n"/>
-      <c r="M32" s="82" t="n"/>
-      <c r="N32" s="82" t="n"/>
       <c r="O32" s="82" t="n"/>
       <c r="P32" s="82" t="n"/>
       <c r="Q32" s="98">
@@ -5194,21 +5774,67 @@
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="82" t="n"/>
-      <c r="B33" s="82" t="n"/>
-      <c r="C33" s="82" t="n"/>
-      <c r="D33" s="82" t="n"/>
-      <c r="E33" s="82" t="n"/>
-      <c r="F33" s="82" t="n"/>
-      <c r="G33" s="82" t="n"/>
-      <c r="H33" s="82" t="n"/>
-      <c r="I33" s="82" t="n"/>
-      <c r="J33" s="82" t="n"/>
-      <c r="K33" s="82" t="n"/>
-      <c r="L33" s="82" t="n"/>
-      <c r="M33" s="82" t="n"/>
-      <c r="N33" s="82" t="n"/>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="99" t="inlineStr">
+        <is>
+          <t>CO-033</t>
+        </is>
+      </c>
+      <c r="B33" s="143" t="inlineStr">
+        <is>
+          <t>حالت قطع بدون برق شهر / همهٔ چراغ‌ها و بوق خاموش</t>
+        </is>
+      </c>
+      <c r="C33" s="147" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D33" s="143" t="inlineStr">
+        <is>
+          <t>برد در SAFE، برق شهر قطع، مسیر باتری بسته</t>
+        </is>
+      </c>
+      <c r="E33" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: بگذار باتری زیر ۲۱۰۰۰ mV برود تا مسیر بسته شود.
+گام ۲: هر سه چراغ و بوق را ۱۰ ثانیه با چشم و گوش ببین.
+گام ۳: برق شهر را وصل کن و چراغ‌ها را دوباره بخوان.</t>
+        </is>
+      </c>
+      <c r="F33" s="144" t="inlineStr">
+        <is>
+          <t>input=false، مسیر بسته</t>
+        </is>
+      </c>
+      <c r="G33" s="144" t="inlineStr">
+        <is>
+          <t>۱۰s</t>
+        </is>
+      </c>
+      <c r="H33" s="143" t="inlineStr">
+        <is>
+          <t>در حالت قطع و بدون برق شهر، هر سه چراغ و بوق کاملاً خاموش‌اند؛ با برگشت برق شهر چهرهٔ شارژ برمی‌گردد. PASS: خاموشی کامل. FAIL: هر چراغ یا بوق روشن.</t>
+        </is>
+      </c>
+      <c r="I33" s="143" t="inlineStr">
+        <is>
+          <t>PASS: همه خاموش. FAIL: چراغ/بوق روشن.</t>
+        </is>
+      </c>
+      <c r="J33" s="104" t="n"/>
+      <c r="K33" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L33" s="115" t="n"/>
+      <c r="M33" s="104" t="n"/>
+      <c r="N33" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O33" s="82" t="n"/>
       <c r="P33" s="82" t="n"/>
       <c r="Q33" s="98">
@@ -5216,21 +5842,68 @@
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="82" t="n"/>
-      <c r="B34" s="82" t="n"/>
-      <c r="C34" s="82" t="n"/>
-      <c r="D34" s="82" t="n"/>
-      <c r="E34" s="82" t="n"/>
-      <c r="F34" s="82" t="n"/>
-      <c r="G34" s="82" t="n"/>
-      <c r="H34" s="82" t="n"/>
-      <c r="I34" s="82" t="n"/>
-      <c r="J34" s="82" t="n"/>
-      <c r="K34" s="82" t="n"/>
-      <c r="L34" s="82" t="n"/>
-      <c r="M34" s="82" t="n"/>
-      <c r="N34" s="82" t="n"/>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="99" t="inlineStr">
+        <is>
+          <t>CO-034</t>
+        </is>
+      </c>
+      <c r="B34" s="143" t="inlineStr">
+        <is>
+          <t>قطع سیم باتری بدون برق شهر / سکوت</t>
+        </is>
+      </c>
+      <c r="C34" s="147" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D34" s="143" t="inlineStr">
+        <is>
+          <t>برد در BATTERY، برق شهر قطع، بار روشن</t>
+        </is>
+      </c>
+      <c r="E34" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: برق شهر را قطع کن و مطمئن شو بار از باتری کار می‌کند.
+گام ۲: سیم باتری را جدا کن تا ولتاژ خوانده‌شده صفر شود.
+گام ۳: بعد از ۳ ثانیه PB11 و چهرهٔ LED و بوق را بخوان.
+گام ۴: برق شهر را برگردان و ببین چهرهٔ شارژ برمی‌گردد.</t>
+        </is>
+      </c>
+      <c r="F34" s="144" t="inlineStr">
+        <is>
+          <t>input=false، v≈0</t>
+        </is>
+      </c>
+      <c r="G34" s="144" t="inlineStr">
+        <is>
+          <t>۵s</t>
+        </is>
+      </c>
+      <c r="H34" s="143" t="inlineStr">
+        <is>
+          <t>مسیر بسته می‌شود، همه‌چیز خاموش می‌ماند و هیچ آلارمی نمی‌آید (تصمیم ۲۰۲۶-۱۰-۲۳). PASS: سکوت کامل. FAIL: هر آلارم یا چراغ.</t>
+        </is>
+      </c>
+      <c r="I34" s="143" t="inlineStr">
+        <is>
+          <t>PASS: سکوت کامل. FAIL: آلارم.</t>
+        </is>
+      </c>
+      <c r="J34" s="104" t="n"/>
+      <c r="K34" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L34" s="115" t="n"/>
+      <c r="M34" s="104" t="n"/>
+      <c r="N34" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O34" s="82" t="n"/>
       <c r="P34" s="82" t="n"/>
       <c r="Q34" s="98">
@@ -7323,17 +7996,17 @@
       </c>
       <c r="B5" s="92" t="inlineStr">
         <is>
-          <t>2026-09-16 (2.1 — فیلتر 3000ms)</t>
+          <t>2026-10-23 (2.2 — آستانهٔ استراحت ۲۵٬۰۰۰ mV)</t>
         </is>
       </c>
       <c r="C5" s="155" t="inlineStr">
         <is>
-          <t>نسخه فرم</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D5" s="92" t="inlineStr">
         <is>
-          <t>2.1 — فیلتر 3000ms</t>
+          <t>2.2 — آستانهٔ استراحت ۲۵٬۰۰۰ mV</t>
         </is>
       </c>
       <c r="E5" s="93" t="n"/>
@@ -7435,7 +8108,7 @@
       </c>
       <c r="B11" s="152" t="inlineStr">
         <is>
-          <t>21000/20800/21200</t>
+          <t>21000/20800/21200 + استراحت 25000</t>
         </is>
       </c>
       <c r="C11" s="155" t="inlineStr"/>

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>آستانهٔ استراحت باتری (شناسهٔ ۱۶۵، پیش‌فرض ۲۵٬۰۰۰ mV): زیر آن بدون برق شهر هیچ وصل و هیچ حکمی نیست. سقف تلاش بدون برق شهر یک است. حکم باتری فرسوده فقط بدون برق شهر نمایش داده می‌شود. در حالت قطع بدون برق شهر، هر سه چراغ و بوق خاموش‌اند. قطع سیم باتری بدون برق شهر بی‌صدا است. شناسه‌های تست با شیت «تست‌های آزمایشگاهی» یکسان شد و CO-031/CO-033/CO-034 اضافه شدند.</t>
+          <t>آستانهٔ استراحت باتری (شناسهٔ ۱۶۵، پیش‌فرض ۲۵٬۰۰۰ mV): زیر آن بدون برق شهر هیچ وصل و هیچ حکمی نیست. سقف تلاش بدون برق شهر یک است. حکم باتری فرسوده فقط بدون برق شهر نمایش داده می‌شود. در حالت قطع بدون برق شهر، هر سه چراغ و بوق خاموش‌اند. قطع سیم باتری بدون برق شهر بی‌صدا است. شناسه‌های تست یکسان شد: هر شناسه در «برنامه تست» نسخهٔ عملی و در «تست‌های آزمایشگاهی» نسخهٔ دقیق همان تست است، و CO-020..CO-023 فقط در «تست‌های برنامه‌نویسی» می‌آیند. CO-032/CO-033/CO-034/CO-035 اضافه شدند.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2755,7 +2755,7 @@
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="99" t="inlineStr">
         <is>
-          <t>CO-031</t>
+          <t>CO-032</t>
         </is>
       </c>
       <c r="B15" s="104" t="inlineStr">
@@ -2765,48 +2765,48 @@
       </c>
       <c r="C15" s="105" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D15" s="104" t="inlineStr">
         <is>
-          <t>دستگاه بدون برق شهر و مسیر باتری بسته</t>
+          <t>حکم قفل + پنل کالیبراسیون باز</t>
         </is>
       </c>
       <c r="E15" s="104" t="inlineStr">
         <is>
-          <t>گام ۱: بگذار باتری زیر ۲۱ ولت برود تا مسیر بسته شود.
-گام ۲: ولتاژ را روی ۲۳٫۰ ولت نگه دار و ۶۰ ثانیه نگاه کن.
-گام ۳: ولتاژ را به ۲۵٫۵ ولت برسان و ۲۰ ثانیه نگاه کن.
-گام ۴: داخل ۶۰ ثانیه بعد از وصل، دوباره زیر ۲۱ ولت بیاور.</t>
+          <t>گام ۱: روی برد حکم را قفل کن.
+گام ۲: در کارت ۸ دکمهٔ پاک‌کردن حکم را بزن.
+گام ۳: خط وضعیت، چراغ قرمز و بوق را نگاه کن.
+گام ۴: همان دکمه را دوباره بزن.</t>
         </is>
       </c>
       <c r="F15" s="104" t="inlineStr">
         <is>
-          <t>استراحت ۲۳ ولت، سپس ۲۵٫۵ ولت، بدون برق شهر</t>
+          <t>حکم = ۱ → دکمهٔ پاک‌کردن حکم (شناسهٔ ۲۰۴)</t>
         </is>
       </c>
       <c r="G15" s="105" t="inlineStr">
         <is>
-          <t>حدود دو دقیقه</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="104" t="inlineStr">
         <is>
-          <t>با ۲۳ ولت هیچ وصل و هیچ حکمی نمی‌شود؛ با ۲۵٫۵ ولت یک بار وصل و با قطع دوباره حکم قفل می‌شود</t>
+          <t>حکم همان لحظه پاک می‌شود، چراغ و بوق خاموش می‌شوند و یک تلاش آزاد می‌شود</t>
         </is>
       </c>
       <c r="I15" s="104" t="inlineStr">
         <is>
           <t>باید ببینید:
-در گام ۲ هیچ وصل خودکاری انجام نمی‌شود و حکمی هم زده نمی‌شود (محافظت باتری، مستقل از تیک سناریو).
-در گام ۳ فقط یک بار وصل می‌شود.
-در گام ۴ دوباره وصل نمی‌شود و حکم باتری فرسوده قفل می‌شود.</t>
+خط وضعیت «در حال ارسال…» و بعد «پاک شد» نشان می‌دهد.
+قرمز و بوق خاموش می‌شوند و با استراحت بالای ۲۵ ولت یک بار دیگر وصل می‌شود.
+زدن دوبارهٔ دکمه خطا نمی‌دهد؛ خود ریست پین را دست نمی‌زند.</t>
         </is>
       </c>
       <c r="J15" s="104" t="inlineStr">
         <is>
-          <t>عدم وصل با ۲۳ ولت + یک تلاش با ۲۵٫۵ ولت؛ وصل با ۲۳ ولت = رد</t>
+          <t>حکم پاک شود و دکمهٔ دوم خطا ندهد</t>
         </is>
       </c>
       <c r="K15" s="100" t="n"/>
@@ -2825,14 +2825,14 @@
       <c r="Q15" s="103" t="n"/>
       <c r="R15" s="157" t="inlineStr">
         <is>
-          <t>بدون فرمول: آستانهٔ استراحت شناسهٔ ۱۶۵ هم برای اجازهٔ وصل و هم برای حکم استفاده می‌شود.</t>
+          <t>بدون فرمول: شناسهٔ ۲۰۴ دستور است، نه پارامتر؛ ذخیره نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="99" t="inlineStr">
         <is>
-          <t>CO-032</t>
+          <t>CO-033</t>
         </is>
       </c>
       <c r="B16" s="104" t="inlineStr">
@@ -2842,48 +2842,48 @@
       </c>
       <c r="C16" s="105" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>بالا</t>
         </is>
       </c>
       <c r="D16" s="104" t="inlineStr">
         <is>
-          <t>حکم قفل + پنل کالیبراسیون باز</t>
+          <t>دستگاه بدون برق شهر و مسیر باتری بسته</t>
         </is>
       </c>
       <c r="E16" s="104" t="inlineStr">
         <is>
-          <t>گام ۱: روی برد حکم را قفل کن.
-گام ۲: در کارت ۸ دکمهٔ پاک‌کردن حکم را بزن.
-گام ۳: خط وضعیت، چراغ قرمز و بوق را نگاه کن.
-گام ۴: همان دکمه را دوباره بزن.</t>
+          <t>گام ۱: بگذار باتری زیر ۲۱ ولت برود تا مسیر بسته شود.
+گام ۲: ولتاژ را روی ۲۳٫۰ ولت نگه دار و ۶۰ ثانیه نگاه کن.
+گام ۳: ولتاژ را به ۲۵٫۵ ولت برسان و ۲۰ ثانیه نگاه کن.
+گام ۴: داخل ۶۰ ثانیه بعد از وصل، دوباره زیر ۲۱ ولت بیاور.</t>
         </is>
       </c>
       <c r="F16" s="104" t="inlineStr">
         <is>
-          <t>حکم = ۱ → دکمهٔ پاک‌کردن حکم (شناسهٔ ۲۰۴)</t>
+          <t>استراحت ۲۳ ولت، سپس ۲۵٫۵ ولت، بدون برق شهر</t>
         </is>
       </c>
       <c r="G16" s="105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>حدود دو دقیقه</t>
         </is>
       </c>
       <c r="H16" s="104" t="inlineStr">
         <is>
-          <t>حکم همان لحظه پاک می‌شود، چراغ و بوق خاموش می‌شوند و یک تلاش آزاد می‌شود</t>
+          <t>با ۲۳ ولت هیچ وصل و هیچ حکمی نمی‌شود؛ با ۲۵٫۵ ولت یک بار وصل و با قطع دوباره حکم قفل می‌شود</t>
         </is>
       </c>
       <c r="I16" s="104" t="inlineStr">
         <is>
           <t>باید ببینید:
-خط وضعیت «در حال ارسال…» و بعد «پاک شد» نشان می‌دهد.
-قرمز و بوق خاموش می‌شوند و با استراحت بالای ۲۵ ولت یک بار دیگر وصل می‌شود.
-زدن دوبارهٔ دکمه خطا نمی‌دهد؛ خود ریست پین را دست نمی‌زند.</t>
+در گام ۲ هیچ وصل خودکاری انجام نمی‌شود و حکمی هم زده نمی‌شود (محافظت باتری، مستقل از تیک سناریو).
+در گام ۳ فقط یک بار وصل می‌شود.
+در گام ۴ دوباره وصل نمی‌شود و حکم باتری فرسوده قفل می‌شود.</t>
         </is>
       </c>
       <c r="J16" s="104" t="inlineStr">
         <is>
-          <t>حکم پاک شود و دکمهٔ دوم خطا ندهد</t>
+          <t>عدم وصل با ۲۳ ولت + یک تلاش با ۲۵٫۵ ولت؛ وصل با ۲۳ ولت = رد</t>
         </is>
       </c>
       <c r="K16" s="100" t="n"/>
@@ -2902,14 +2902,14 @@
       <c r="Q16" s="103" t="n"/>
       <c r="R16" s="157" t="inlineStr">
         <is>
-          <t>بدون فرمول: شناسهٔ ۲۰۴ دستور است، نه پارامتر؛ ذخیره نمی‌شود.</t>
+          <t>بدون فرمول: آستانهٔ استراحت شناسهٔ ۱۶۵ هم برای اجازهٔ وصل و هم برای حکم استفاده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="99" t="inlineStr">
         <is>
-          <t>CO-033</t>
+          <t>CO-034</t>
         </is>
       </c>
       <c r="B17" s="104" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="99" t="inlineStr">
         <is>
-          <t>CO-034</t>
+          <t>CO-035</t>
         </is>
       </c>
       <c r="B18" s="104" t="inlineStr">
@@ -5637,25 +5637,95 @@
     <row r="31" ht="54" customHeight="1">
       <c r="A31" s="99" t="inlineStr">
         <is>
-          <t>CO-031</t>
+          <t>CO-032</t>
         </is>
       </c>
       <c r="B31" s="143" t="inlineStr">
         <is>
+          <t>حکم باتری ضعیف / پاک‌کردن دستی از پنل</t>
+        </is>
+      </c>
+      <c r="C31" s="147" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D31" s="143" t="inlineStr">
+        <is>
+          <t>حکم قفل + پنل کالیبراسیون باز</t>
+        </is>
+      </c>
+      <c r="E31" s="145" t="inlineStr">
+        <is>
+          <t>گام ۱: روی برد حکم را قفل کن: بدون برق شهر وصل شود و داخل پنجرهٔ محافظ دوباره قطع شود.
+گام ۲: در کارت ۸ دکمهٔ «پاک‌کردن حکم» را بزن و تأیید کن.
+گام ۳: خط وضعیت باید «در حال ارسال…» و بعد «پاک شد» نشان دهد.
+گام ۴: چراغ قرمز و بوق باید خاموش شوند.
+گام ۵: دوباره همان دکمه را بزن؛ باید بگوید حکمی نیست و خطا ندهد.</t>
+        </is>
+      </c>
+      <c r="F31" s="144" t="inlineStr">
+        <is>
+          <t>حکم=۱ → دکمهٔ پاک‌کردن حکم</t>
+        </is>
+      </c>
+      <c r="G31" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="143" t="inlineStr">
+        <is>
+          <t>حکم همان لحظه پاک می‌شود؛ چهره خاموش و یک بار وصل دوباره آزاد می‌شود. زدن دوبارهٔ دکمه خطا نمی‌دهد. PASS: حکم پاک شد. FAIL: حکم ماند یا دکمه خطا داد.</t>
+        </is>
+      </c>
+      <c r="I31" s="143" t="inlineStr">
+        <is>
+          <t>PASS: حکم پاک. FAIL: حکم ماند.</t>
+        </is>
+      </c>
+      <c r="J31" s="104" t="n"/>
+      <c r="K31" s="143" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L31" s="115" t="n"/>
+      <c r="M31" s="104" t="n"/>
+      <c r="N31" s="143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="O31" s="82" t="n"/>
+      <c r="P31" s="82" t="n"/>
+      <c r="Q31" s="98">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="99" t="inlineStr">
+        <is>
+          <t>CO-033</t>
+        </is>
+      </c>
+      <c r="B32" s="143" t="inlineStr">
+        <is>
           <t>آستانهٔ استراحت ۲۵٬۰۰۰ mV / بستهٔ دشارژ وصل نمی‌شود</t>
         </is>
       </c>
-      <c r="C31" s="147" t="inlineStr">
+      <c r="C32" s="147" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D31" s="143" t="inlineStr">
+      <c r="D32" s="143" t="inlineStr">
         <is>
           <t>برد در SAFE، برق شهر قطع، خروجی قطع</t>
         </is>
       </c>
-      <c r="E31" s="145" t="inlineStr">
+      <c r="E32" s="145" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا خروجی قطع شود.
 گام ۲: ولتاژ را روی 23000 mV نگه دار و ۶۰ ثانیه بمان.
@@ -5664,94 +5734,24 @@
 گام ۵: داخل ۶۰ ثانیه دوباره زیر 21000 mV بیاور؛ باید حکم قفل شود.</t>
         </is>
       </c>
-      <c r="F31" s="144" t="inlineStr">
+      <c r="F32" s="144" t="inlineStr">
         <is>
           <t>input=false، v=23000 سپس 25500 سپس قطع دوباره</t>
         </is>
       </c>
-      <c r="G31" s="144" t="inlineStr">
+      <c r="G32" s="144" t="inlineStr">
         <is>
           <t>۶۰s + ۲۰s + ۶۰s</t>
         </is>
       </c>
-      <c r="H31" s="143" t="inlineStr">
+      <c r="H32" s="143" t="inlineStr">
         <is>
           <t>با استراحت ۲۳ ولت هیچ وصل و هیچ حکمی نمی‌شود؛ با ۲۵٫۵ ولت فقط یک بار وصل می‌شود و قطع دوباره حکم را قفل می‌کند. PASS: عدم وصل با ۲۳ ولت + یک تلاش با ۲۵٫۵ ولت. FAIL: وصل با ۲۳ ولت یا تلاش دوم.</t>
         </is>
       </c>
-      <c r="I31" s="143" t="inlineStr">
+      <c r="I32" s="143" t="inlineStr">
         <is>
           <t>PASS: ۲۳ ولت بدون وصل، ۲۵٫۵ ولت یک تلاش. FAIL: وصل با ۲۳ ولت.</t>
-        </is>
-      </c>
-      <c r="J31" s="104" t="n"/>
-      <c r="K31" s="143" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L31" s="115" t="n"/>
-      <c r="M31" s="104" t="n"/>
-      <c r="N31" s="143" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="O31" s="82" t="n"/>
-      <c r="P31" s="82" t="n"/>
-      <c r="Q31" s="98">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="99" t="inlineStr">
-        <is>
-          <t>CO-032</t>
-        </is>
-      </c>
-      <c r="B32" s="143" t="inlineStr">
-        <is>
-          <t>حکم باتری ضعیف / پاک‌کردن دستی از پنل</t>
-        </is>
-      </c>
-      <c r="C32" s="147" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D32" s="143" t="inlineStr">
-        <is>
-          <t>حکم قفل + پنل کالیبراسیون باز</t>
-        </is>
-      </c>
-      <c r="E32" s="145" t="inlineStr">
-        <is>
-          <t>گام ۱: روی برد حکم را قفل کن: بدون برق شهر وصل شود و داخل پنجرهٔ محافظ دوباره قطع شود.
-گام ۲: در کارت ۸ دکمهٔ «پاک‌کردن حکم» را بزن و تأیید کن.
-گام ۳: خط وضعیت باید «در حال ارسال…» و بعد «پاک شد» نشان دهد.
-گام ۴: چراغ قرمز و بوق باید خاموش شوند.
-گام ۵: دوباره همان دکمه را بزن؛ باید بگوید حکمی نیست و خطا ندهد.</t>
-        </is>
-      </c>
-      <c r="F32" s="144" t="inlineStr">
-        <is>
-          <t>حکم=۱ → دکمهٔ پاک‌کردن حکم</t>
-        </is>
-      </c>
-      <c r="G32" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="143" t="inlineStr">
-        <is>
-          <t>حکم همان لحظه پاک می‌شود؛ چهره خاموش و یک بار وصل دوباره آزاد می‌شود. زدن دوبارهٔ دکمه خطا نمی‌دهد. PASS: حکم پاک شد. FAIL: حکم ماند یا دکمه خطا داد.</t>
-        </is>
-      </c>
-      <c r="I32" s="143" t="inlineStr">
-        <is>
-          <t>PASS: حکم پاک. FAIL: حکم ماند.</t>
         </is>
       </c>
       <c r="J32" s="104" t="n"/>
@@ -5777,7 +5777,7 @@
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="99" t="inlineStr">
         <is>
-          <t>CO-033</t>
+          <t>CO-034</t>
         </is>
       </c>
       <c r="B33" s="143" t="inlineStr">
@@ -5845,7 +5845,7 @@
     <row r="34" ht="54" customHeight="1">
       <c r="A34" s="99" t="inlineStr">
         <is>
-          <t>CO-034</t>
+          <t>CO-035</t>
         </is>
       </c>
       <c r="B34" s="143" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_Board_Validation.xlsx
@@ -1856,7 +1856,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="96" t="inlineStr">
         <is>
-          <t>ورودی‌ها بر حسب mV؛ زمان‌ها بر حسب ms. PB11 فقط از BSP_GPIO_PROTECT_BATTERY (فعال Low) — PB5/PB7 ممنوع. ورودی‌ها: valid، v_bat، input_present، flag، fault.</t>
+          <t>ورودی‌ها بر حسب mV؛ زمان‌ها بر حسب ms. PB11 فقط از BSP_GPIO_PROTECT_BATTERY (فعال High؛ High=قطع، Low=وصل). Changeover فقط PB11 می‌نویسد؛ PB5/PB7 مال ماژول‌های دیگرند. ورودی‌ها: valid، v_bat، input_present، flag، fault.</t>
         </is>
       </c>
       <c r="Q2" s="82" t="n"/>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="H9" s="104" t="inlineStr">
         <is>
-          <t>state=FAULT، هیچ pin (PB11/PB5/PB7) تغییر نکند. PASS: همه fault‌ها → FAULT بدون pin. FAIL: هر تغییر pin.</t>
+          <t>state=FAULT و PB11 حفظ شود. Changeover روی PB5/PB7 نمی‌نویسد؛ اگر مالک خودشان آن‌ها را تغییر دهد، ایراد Changeover نیست.</t>
         </is>
       </c>
       <c r="I9" s="104" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="H10" s="143" t="inlineStr">
         <is>
-          <t>state=BATTERY, PB11 High-safe (متصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
+          <t>state=BATTERY, PB11 Low (وصل). PASS: BATTERY. FAIL: INPUT یا SAFE یا FAULT.</t>
         </is>
       </c>
       <c r="I10" s="143" t="inlineStr">
@@ -4273,7 +4273,7 @@
           <t>گام ۱: برد در BOOT یا BATTERY باشد.
 گام ۲: snapshot معتبر با v=24000، input=true (یعنی Vin دست‌کم 21 ولت) و fault=0 اعمال کن.
 گام ۳: 500 میلی‌ثانیه صبر کن.
-گام ۴: وضعیت باید INPUT شود و PB11 High و امن بماند.</t>
+گام ۴: وضعیت باید INPUT شود و PB11 Low (وصل) بماند.</t>
         </is>
       </c>
       <c r="F11" s="105" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="H11" s="104" t="inlineStr">
         <is>
-          <t>state=INPUT, PB11 High-safe. PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
+          <t>state=INPUT, PB11 Low (وصل). PASS: INPUT. FAIL: BATTERY یا SAFE.</t>
         </is>
       </c>
       <c r="I11" s="104" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D12" s="143" t="inlineStr">
         <is>
-          <t>BATTERY/INPUT, PB11 High</t>
+          <t>BATTERY/INPUT, PB11 Low (وصل)</t>
         </is>
       </c>
       <c r="E12" s="143" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H12" s="143" t="inlineStr">
         <is>
-          <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 High؛ پس از 3000ms PB11 Low (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
+          <t>پس از 2500ms هنوز BATTERY/INPUT و PB11 Low (وصل)؛ پس از 3000ms PB11 High (قطع) و state=SAFE. PASS: قطع فقط پس از 3000ms پیوسته. FAIL: قطع زود یا عدم قطع.</t>
         </is>
       </c>
       <c r="I12" s="143" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="H13" s="104" t="inlineStr">
         <is>
-          <t>پس از 3000ms SAFE با PB11 Low مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
+          <t>پس از 3000ms SAFE با PB11 High (قطع) مستقل از flag. PASS: مستقل cuts. FAIL: عدم قطع به علت flag false.</t>
         </is>
       </c>
       <c r="I13" s="104" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="H14" s="143" t="inlineStr">
         <is>
-          <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 High-safe بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
+          <t>هیچ قطع رخ ندهد، state=INPUT (چون input_present=true و بدون cut) و PB11 Low (وصل) بماند. PASS: با input حاضر، بدون قطع باید INPUT باشد، نه BATTERY یا SAFE. FAIL: BATTERY/SAFE یا تغییر PB11.</t>
         </is>
       </c>
       <c r="I14" s="143" t="inlineStr">
         <is>
-          <t>PASS: با v=21000 و input true، state=INPUT و PB11 High. FAIL: هر cut یا BATTERY.</t>
+          <t>PASS: با v=21000 و input true، state=INPUT و PB11 Low (وصل). FAIL: هر cut یا BATTERY.</t>
         </is>
       </c>
       <c r="J14" s="104" t="n"/>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="H16" s="143" t="inlineStr">
         <is>
-          <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 High. PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
+          <t>پس از 2500ms هنوز state=INPUT (چون input true و هنوز SAFE نشده) و PB11 Low (وصل). PASS: &lt;3000ms هنوز INPUT، نه SAFE. FAIL: SAFE زود یا BATTERY.</t>
         </is>
       </c>
       <c r="I16" s="143" t="inlineStr">
@@ -4683,13 +4683,13 @@
       </c>
       <c r="D17" s="104" t="inlineStr">
         <is>
-          <t>SAFE, PB11 Low</t>
+          <t>SAFE, PB11 High (قطع)</t>
         </is>
       </c>
       <c r="E17" s="106" t="inlineStr">
         <is>
           <t>گام ۱: از تست CO-008 شروع کن تا برد در SAFE و PB11 قطع (Low) باشد.
-گام ۲: input=true و v=21300 (دست‌کم 21200) اعمال کن.
+گام ۲: پس از ۳۰ ثانیه پایداری ورودی (CO-024)، input=true و v=21300 (دست‌کم 21200) اعمال کن.
 گام ۳: 3500 میلی‌ثانیه نگه دار و PB11 را زیر نظر بگیر.
 گام ۴: قبل از 3000 میلی‌ثانیه باید SAFE و PB11 قطع بماند؛ بعد از 3000 میلی‌ثانیه باید وضعیت INPUT و PB11 وصل (High) شود. وصل شدن زودتر یا وصل‌نشدن یعنی رد تست.</t>
         </is>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H17" s="104" t="inlineStr">
         <is>
-          <t>قبل از 3000ms: SAFE و PB11 Low؛ بعد از 3000ms: INPUT و PB11 High. PASS: reconnect پس از 3000ms با PB11 High. FAIL: reconnect زود یا PB11 Low ماندن.</t>
+          <t>قبل از ۳۰۰۰ms: SAFE و PB11 High (قطع)؛ بعد از ۳۰۰۰ms: INPUT و PB11 Low (وصل). PASS: reconnect پس از ۳۰۰۰ms با PB11 Low (وصل). FAIL: reconnect زود یا PB11 High (قطع) ماندن.</t>
         </is>
       </c>
       <c r="I17" s="104" t="inlineStr">
@@ -4758,7 +4758,7 @@
       <c r="E18" s="143" t="inlineStr">
         <is>
           <t>گام ۱: برد در وضعیت امن (SAFE) باشد.
-گام ۲: input=true و v دقیقاً 21200 بده (روی خود مرز).
+گام ۲: پس از ۳۰ ثانیه پایداری ورودی (CO-024)، input=true و v دقیقاً 21200 بده (روی خود مرز).
 گام ۳: 3500 میلی‌ثانیه نگه دار.
 گام ۴: بعد از 3000 میلی‌ثانیه باید وضعیت «ورودی» (INPUT) شود و PB11 وصل شده باشد.
 گام ۵: شرط وصل «دست‌کم 21200» است؛ پس روی مرز هم باید وصل شود.</t>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H18" s="143" t="inlineStr">
         <is>
-          <t>پس از 3000ms INPUT و PB11 High. PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
+          <t>پس از 3000ms INPUT و PB11 Low (وصل). PASS: ≥21200 reconnect. FAIL: no reconnect at 21200.</t>
         </is>
       </c>
       <c r="I18" s="143" t="inlineStr">
@@ -4828,7 +4828,7 @@
       <c r="E19" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برد در SAFE باشد.
-گام ۲: input=true و v=21300 اعمال کن.
+گام ۲: پس از ۳۰ ثانیه پایداری ورودی (CO-024)، input=true و v=21300 اعمال کن.
 گام ۳: فقط 2500 میلی‌ثانیه نگه دار (کمتر از 3000).
 گام ۴: هنوز باید SAFE و PB11 قطع مانده باشد؛ وصل شدن در کمتر از 3 ثانیه یعنی رد تست.</t>
         </is>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="H19" s="104" t="inlineStr">
         <is>
-          <t>هنوز SAFE و PB11 Low. PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
+          <t>هنوز SAFE و PB11 High (قطع). PASS: &lt;3s no reconnect. FAIL: زود وصل.</t>
         </is>
       </c>
       <c r="I19" s="104" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D21" s="104" t="inlineStr">
         <is>
-          <t>INPUT با PB11 High</t>
+          <t>INPUT با PB11 Low (وصل)</t>
         </is>
       </c>
       <c r="E21" s="104" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="H21" s="104" t="inlineStr">
         <is>
-          <t>PB11 Low-High بدون تغییر بماند (High). PASS: حفظ. FAIL: تغییر.</t>
+          <t>PB11 بدون تغییر بماند (Low/وصل). PASS: حفظ. FAIL: تغییر.</t>
         </is>
       </c>
       <c r="I21" s="104" t="inlineStr">
@@ -5035,7 +5035,7 @@
           <t>گام ۱: برد در INPUT باشد.
 گام ۲: snapshot معتبر با fault مخالف صفر بده (fault=1) تا وضعیت FAULT شود.
 گام ۳: 500 میلی‌ثانیه صبر کن و PB11 را بخوان.
-گام ۴: PB11 باید حفظ شده باشد (High بماند)؛ Low شدنش یعنی رد تست.</t>
+گام ۴: PB11 باید حفظ شده باشد (Low (وصل) بماند)؛ High (قطع) شدنش یعنی رد تست.</t>
         </is>
       </c>
       <c r="F22" s="144" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="H22" s="143" t="inlineStr">
         <is>
-          <t>PB11 حفظ (High). PASS. FAIL: Low شدن.</t>
+          <t>PB11 حفظ (Low/وصل). PASS. FAIL: High (قطع) شدن.</t>
         </is>
       </c>
       <c r="I22" s="143" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B23" s="104" t="inlineStr">
         <is>
-          <t>PB5 و PB7 هیچ‌گاه تغییر نکنند</t>
+          <t>مالکیت پایه‌ها: Changeover فقط PB11</t>
         </is>
       </c>
       <c r="C23" s="114" t="inlineStr">
@@ -5101,11 +5101,10 @@
       </c>
       <c r="E23" s="106" t="inlineStr">
         <is>
-          <t>گام ۱: در همهٔ تست‌های CO-001 تا CO-015، سه پایه را با اسکوپ یا لاگ BSP زیر نظر بگیر:
-پایهٔ PB11، پایهٔ PB5 (همان BAT_SWITCH) و پایهٔ PB7 (همان RELAY).
-گام ۲: این تست ردیف جدا ندارد؛ در تک‌تک تست‌های بالا انجامش بده.
-گام ۳: PB5 باید همیشه High و امن بماند (فعال-پایین است) و PB7 همیشه Low بماند.
-گام ۴: هر تغییری روی این دو پایه یعنی رد تست.</t>
+          <t>گام ۱: در تست‌های Changeover، پایهٔ PB11 و نوشتن‌های BSP را زیر نظر بگیر.
+گام ۲: Changeover فقط باید BSP_GPIO_PROTECT_BATTERY (PB11) را بنویسد.
+گام ۳: PB5 مال McuPowerPath و PB7 مال رلهٔ شارژر است؛ تغییر آن‌ها توسط مالک خودشان مجاز است.
+گام ۴: هر نوشتن PB5/PB7 از مسیر Changeover یعنی رد تست.</t>
         </is>
       </c>
       <c r="F23" s="105" t="inlineStr">
@@ -5120,12 +5119,12 @@
       </c>
       <c r="H23" s="104" t="inlineStr">
         <is>
-          <t>PB5 و PB7 ثابت بمانند (PB5 High-safe active-low، PB7 Low). PASS: بدون تغییر. FAIL: هر toggle.</t>
+          <t>Changeover فقط PB11 را بنویسد. PASS: مالکیت رعایت شود. FAIL: نوشتن PB5/PB7 توسط Changeover.</t>
         </is>
       </c>
       <c r="I23" s="104" t="inlineStr">
         <is>
-          <t>PASS: PB5/PB7 never change. FAIL: any toggle.</t>
+          <t>PASS: Changeover writes PB11 only. FAIL: Changeover writes PB5/PB7.</t>
         </is>
       </c>
       <c r="J23" s="104" t="n"/>
@@ -6368,7 +6367,7 @@
       </c>
       <c r="H5" s="104" t="inlineStr">
         <is>
-          <t>هیچ کد board_pins/HAL/PB5/PB7 نباشد، فقط PB11 تغییر کند. PASS: فقط PB11. FAIL: PB5/7.</t>
+          <t>Changeover فقط BSP_GPIO_PROTECT_BATTERY (PB11) را بنویسد؛ هیچ نوشتن مستقیم HAL/PB5/PB7 نباشد. PASS: فقط PB11. FAIL: نوشتن PB5/PB7.</t>
         </is>
       </c>
       <c r="I5" s="104" t="inlineStr">
@@ -7257,7 +7256,7 @@
       </c>
       <c r="C6" s="119" t="inlineStr">
         <is>
-          <t>پس از 3000ms PB11 Low (قطع) → SAFE</t>
+          <t>پس از 3000ms PB11 High (قطع) (قطع) → SAFE</t>
         </is>
       </c>
       <c r="D6" s="119" t="inlineStr">
@@ -7289,7 +7288,7 @@
       </c>
       <c r="C7" s="119" t="inlineStr">
         <is>
-          <t>پس از 3000ms PB11 Low</t>
+          <t>پس از 3000ms PB11 High (قطع)</t>
         </is>
       </c>
       <c r="D7" s="119" t="inlineStr">
@@ -7353,7 +7352,7 @@
       </c>
       <c r="C9" s="119" t="inlineStr">
         <is>
-          <t>پس از 3000ms PB11 High → INPUT</t>
+          <t>پس از 3000ms PB11 Low (وصل) → INPUT</t>
         </is>
       </c>
       <c r="D9" s="119" t="inlineStr">
@@ -7439,17 +7438,17 @@
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="119" t="inlineStr">
         <is>
-          <t>PB5/PB7</t>
+          <t>مالکیت PB5/PB7</t>
         </is>
       </c>
       <c r="B12" s="119" t="inlineStr">
         <is>
-          <t>هیچ‌گاه</t>
+          <t>Changeover نمی‌نویسد</t>
         </is>
       </c>
       <c r="C12" s="119" t="inlineStr">
         <is>
-          <t>بدون تغییر</t>
+          <t>PB5 مال McuPowerPath؛ PB7 مال رلهٔ شارژر</t>
         </is>
       </c>
       <c r="D12" s="120" t="inlineStr">
@@ -7459,7 +7458,7 @@
       </c>
       <c r="E12" s="119" t="inlineStr">
         <is>
-          <t>فقط PROTECT_BATTERY</t>
+          <t>فقط PROTECT_BATTERY توسط Changeover</t>
         </is>
       </c>
       <c r="F12" s="120" t="inlineStr">
